--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Alibaba Direktimport" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Top 5 Empfehlungen" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Hinweise" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Casa dos Sonhos Detail" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -94,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -111,6 +112,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1600,7 +1604,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos Yurts (Alentejo)</t>
+          <t>Casa dos Sonhos Yurts (Alto Alentejo, Besteiros de Cima/Portalegre)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1610,7 +1614,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/yurtscasadossonhos/</t>
+          <t>https://www.casadossonhos.co.uk/copy-of-environmental-policy</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1625,27 +1629,27 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Solar-gefertigt, lokale Materialien</t>
+          <t>Portugiesisches Holz (Tueren, Khana-Gitter, Sparren, Fenster), portugiesische Korkboeden + Korkdaemmung, moderne Isolierung, Aussenhuelle mit 10-J. UV-Garantie</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>EXZELLENT - 10 Jahre UV/Faeulnis-Garantie auf Aussenhuelle!</t>
+          <t>EXZELLENT - 10 Jahre UV-Garantie auf Aussenhuelle, Plane rottet/schimmelt nicht, braucht keine Nachbehandlung; speziell fuer portugiesisches Wetter gefertigt</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Innerhalb PT inkl. Lieferung &amp; Aufbau</t>
+          <t>Innerhalb Festland-PT inkl. Lieferung &amp; Aufbau (im Preis enthalten)</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>BEST KLIMA-EIGNUNG: 10-Jahres-Garantie gegen UV-Schaeden ist einzigartig</t>
+          <t>STANDARD inkl.: 1x1 m doppelverglastes Alu-Fenster (9,1m: 120x120cm), Holztuer mit Fenster+Laden, Daemmung, oeffenbares Kuppel-Oberlicht. Selbsttragend ohne Mittelsaeule, Wand &gt;2 m, Mittelring min. 3,5 m. Solarwerkstatt. OPTIONEN: groessere Fenster, Sturm-Kit, Extra-Daemmlagen, franz. Doppeltueren 3/4-Glas+Lade, Kaminzug, Mueckennetze</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>8.000-15.000 (geschaetzt nach Groesse)</t>
+          <t>8.000-15.000 (geschaetzt nach Groesse) - Lieferung+Aufbau PT inklusive</t>
         </is>
       </c>
     </row>
@@ -3201,27 +3205,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos Yurts</t>
+          <t>Casa dos Sonhos Yurts (Alto Alentejo)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Hersteller PT (Alentejo)</t>
+          <t>Hersteller PT - lokale Spitzenoption</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ca. 8.000-15.000 nach Groesse</t>
+          <t>ca. 8.000-15.000 nach Groesse (Lieferung+Aufbau PT inkl.)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>BESTE KLIMA-EIGNUNG: 10 Jahre UV/Faeulnis-Garantie auf Aussenhuelle (einzigartig im Markt). Lokal in Alentejo gebaut, kein Import-Zoll/IVA, Lieferung und Aufbau in PT inklusive. Solarstrom-Werkstatt, lokale Materialien. Ideal fuer Algarve-Klima. Direkt vom Hersteller mit Garantie.</t>
+          <t>BESTE KLIMA-EIGNUNG IM MARKT: 10 Jahre UV-Garantie auf Aussenhuelle, Plane rottet/schimmelt nicht, keine Nachbehandlung noetig. Standorte: 5m/6,1m/7,3m/9,1m (20/30/42/64 m2). SELBSTTRAGEND ohne Mittelsaeule, Waende &gt;2 m, Mittelring 3,5 m -&gt; super geraeumig. STANDARD inkl.: doppelverglastes Alu-Fenster, Holztuer m. Fenster+Laden, Daemmung, oeffenbares Kuppel-Oberlicht. Portugiesisches Holz + portug. Korkboeden + Korkdaemmung. Solarwerkstatt in Alto Alentejo (Portalegre). Lieferung und Aufbau in Festland-PT IM PREIS. Kein Import-Zoll/IVA. Optionen: Sturm-Kit (Algarve-Winterstuerme!), Extra-Daemmung, franz. Doppeltueren, Kaminzug, Mueckennetze.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.casadossonhos.co.uk/ / https://www.facebook.com/yurtscasadossonhos/</t>
+          <t>https://www.casadossonhos.co.uk/copy-of-environmental-policy  |  https://www.facebook.com/yurtscasadossonhos/</t>
         </is>
       </c>
     </row>
@@ -3985,4 +3989,826 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B80"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="95" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Casa dos Sonhos Yurts - Detail-Analyse (Quelle: casadossonhos.co.uk/copy-of-environmental-policy + Facebook/Instagram)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Allgemein</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="21" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Firmenname</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Casa dos Sonhos Yurts ("House of Dreams")</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Standort</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Besteiros de Cima nahe Portalegre, Alto Alentejo, Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Werkstatt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Solar-betriebene (off-grid) Werkstatt im Alto Alentejo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Hauptseite</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.casadossonhos.co.uk/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="25" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Environmental Policy (Quelle dieses Detail-Sheets)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.casadossonhos.co.uk/copy-of-environmental-policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/yurtscasadossonhos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/casadossonhosyurts/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCfenMyhVzEkX7P-lz2hjS6A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Schwester-Projekt</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>https://casadossonhos.org/ (Wollverarbeitung in Planung)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="8" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Verfuegbare Groessen</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>5 m Durchmesser</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>20 m2 Innenflaeche</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>6,1 m (20 foot) Durchmesser</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>30 m2 Innenflaeche</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>7,3 m (24 foot) Durchmesser</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>42 m2 Innenflaeche</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>9,1 m (30 foot) Durchmesser</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>64 m2 Innenflaeche</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="8" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Bauart &amp; Konstruktion</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Selbsttragend</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ALLE Modelle ohne Mittelsaeule / -stuetze - max. offener Innenraum</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Wandhoehe</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>ueber 2 m (mehr als Standard-Mongolisch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Hoehe Mittelring (Toono)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>min. 3,5 m - sehr geraeumig, geeignet fuer Hochbett/Galerie</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Fertigung</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Handgefertigt vom Hersteller-Paar in Alentejo</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="8" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Standardausstattung (im Basispreis enthalten)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Fenster</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>1x1 m doppelverglastes Aluminium-Fenster (beim 9,1m-Modell: 120x120 cm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Tuer</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Holztuer mit kleinem Fenster und Holzladen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Daemmung</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Moderne Daemmung inklusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="27" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Dachoeffnung</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Oeffnungs-faehiges, klares Kuppel-Oberlicht ("opening clear domed skylight")</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="27" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Aussenhuelle</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Speziell fuer portugiesisches Wetter konzipierte Plane mit 10-J. UV-Garantie</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Lieferung &amp; Aufbau</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>IM PREIS ENTHALTEN innerhalb Festland-Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Materialien (Portuguese sourced)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="27" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Holz</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Portugiesisches Holz fuer Tueren, Khana-Lattengitter, Sparren, Fensterrahmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Bodenbelag</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Portugiesische Korkboeden (regional, oeko)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Daemmung</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Portugiesische Korkdaemmung</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Wolle</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Aktuell zugekauft; eigenes Wollverarbeitungs-Projekt geplant (Alentejo-Schafwolle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="28" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Aussenhuelle-Qualitaet</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Premium: 10-J. UV-Garantie, nie Faeulnis, nie Schimmel, KEINE Nachbehandlung noetig</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="8" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Optionale Zusatzausstattung</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Groessere Fenster</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Anstelle 1x1m Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>High Wind Kit / Sturm-Kit</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Verstaerkte Verankerung fuer stuermische Regionen (EMPFEHLUNG fuer Algarve-Kueste!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Zusaetzliche Daemmlagen</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Fuer kuehlere Lagen / Winterwohnen</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Zusaetzliche Tueren/Fenster</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Beliebig</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Franz. Doppeltueren</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>3/4-Verglasung mit Holzladen ("French double doors with 3/4 glass and shutters")</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="21" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Kaminzug (Flue Kit)</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Vorbereitung fuer Holzofen / Wood Burner</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Mueckennetze (Mosquito Screens)</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>WICHTIG fuer Algarve-Sommer</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1"/>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Garantie &amp; Klima-Eignung</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="23" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>UV-Garantie Aussenhuelle</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>10 JAHRE - hoechste am Markt nachgewiesene Garantie</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Schutzklassen</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Plane rottet nicht, schimmelt nicht, braucht keine UV-Nachbehandlungen</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="28" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Geeignet fuer</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Vollstaendig auf das portugiesische Klima (heisse Sommer, feuchte Winter) ausgelegt</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Empfehlung Algarve</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Mit Sturm-Kit + Mueckennetz + ggf. Extra-Daemmung -&gt; ideal fuer Algarve</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Preis &amp; Kommerzielles</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="25" customHeight="1">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Preisliste</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>Nicht oeffentlich. Anfrage per E-Mail / Facebook erforderlich.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="29" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Schaetzung 5m (20 m2)</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>ca. 8.000-10.500 EUR inkl. Aufbau (vergleichbar mit Yourtepoque-Niveau + Local-Bonus)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Schaetzung 6,1m (30 m2)</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>ca. 9.500-12.500 EUR inkl. Aufbau</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="23" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Schaetzung 7,3m (42 m2)</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>ca. 11.500-14.500 EUR inkl. Aufbau (an Budget-Grenze)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Schaetzung 9,1m (64 m2)</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>ca. 15.000-20.000+ EUR (ueber Budget)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>Lieferung &amp; Aufbau</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Inklusive in Festland-PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>Import-Zoll/IVA</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>ENTFAELLT (lokale PT-Produktion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>Zahlung</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Direkt mit Hersteller, vermutlich Anzahlung + Restzahlung bei Abnahme</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="8" customHeight="1"/>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Nachhaltigkeit / ESG</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Energie Produktion</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>100% Solar in der Werkstatt</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Materialien-Herkunft</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Portugiesisch (Holz, Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Soziales Engagement</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Plant Wollverarbeitung um lokale Schafwolle aufzuwerten (Alentejo) - aktuell unterbewertet</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Kreislaufwirtschaft</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Natuerliche Materialien, kein PVC im Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Risiken &amp; Hinweise</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>Lieferzeit</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Handarbeit -&gt; mehrere Monate Vorlauf einplanen</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>Skalierung</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Kleines Familienunternehmen - Reaktionszeit kann variieren</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>Preis intransparent</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>Keine oeffentliche Preisliste - immer schriftliches Angebot einholen + Optionen klar definieren</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="23" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>Sturmkomponente</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Algarve-Kueste: Sturm-Kit OBLIGATORISCH bestellen</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="29" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>Hitze Innenraum</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Trotz 10-J. Plane: zusaetzliches Schattennetz/Pergola fuer 40C+ Sommertage empfehlenswert</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="8" customHeight="1"/>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Fazit fuer Algarve</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="38" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>TOP-EMPFEHLUNG #1 - einzigartige 10-J. UV-Garantie, lokale Produktion, Lieferung+Aufbau inkl., portugiesische Materialien, kein Import-Risiko.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="36" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>Naechster Schritt</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Per Facebook Messenger / E-Mail Angebot fuer 5m oder 6,1m anfragen, mit Sturm-Kit, Mueckennetz, Kaminzug, ggf. franz. Doppeltueren.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A55:B55"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Top 5 Empfehlungen" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Hinweise" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Casa dos Sonhos Detail" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="OLX 6m+ Funde" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +48,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
     </font>
   </fonts>
   <fills count="4">
@@ -95,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -113,6 +118,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1812,102 +1820,154 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Yurt Workshop UK</t>
+          <t>Yurt Made in Portugal (Loures, ueber OLX)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Portugal (Loures, Lisboa)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>https://www.yurtworkshop.com/</t>
+          <t>https://www.olx.pt/d/anuncio/yurt-made-in-portugal-IDIyzPL.html</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>5-7m</t>
+          <t>5m=20m2 / 6m=28m2 / 7-8m auf Anfrage</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>Anfrage GBP/EUR</t>
+          <t>5m 6.900 / 6m 8.400 / 7-8m Anfrage</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Eichen-/Kastanien-Holz + Canvas + Wollfilz</t>
+          <t>Holz + Filz + Plane (modern), portugiesisch handgefertigt</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Mittel - Brexit-Zoll Aufschlag</t>
+          <t>Sehr gut - lokaler PT-Hersteller seit 2020, kein Import-Zoll/IVA</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>UK-&gt;PT 1.500-2.500 EUR + EU-Zoll/IVA bei Brexit-Import</t>
+          <t>Innerhalb PT - Lieferung+Aufbau EXTRA (standortabhaengig)</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Etabliert; Brexit verteuert Lieferung in EU erheblich</t>
+          <t>Neuer kleiner PT-Hersteller bei Lissabon, 'modern take on ancient living'. OLX-Praesenz seit 2020.</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>9.000-13.000</t>
+          <t>8.400-10.500 inkl. Aufbau (6m)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>Yurt Workshop UK</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurtworkshop.com/</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>5-7m</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage GBP/EUR</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Eichen-/Kastanien-Holz + Canvas + Wollfilz</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Mittel - Brexit-Zoll Aufschlag</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>UK-&gt;PT 1.500-2.500 EUR + EU-Zoll/IVA bei Brexit-Import</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Etabliert; Brexit verteuert Lieferung in EU erheblich</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>9.000-13.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>FamWest</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>https://www.famwest.de/en/mongolian-yurts/</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>5-9m Durchmesser</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Anfrage</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="3" t="inlineStr">
         <is>
           <t>Filz + Canvas</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Mittel</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>DE-&gt;PT 1.500-2.000 EUR</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="I29" s="3" t="inlineStr">
         <is>
           <t>5/6/7/8/9 m Optionen, inkl 19% MwSt</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="J29" s="3" t="inlineStr">
         <is>
           <t>ca. 6.000-15.000</t>
         </is>
@@ -1924,7 +1984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2123,64 +2183,62 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Kleinanzeigen - Jurte Suche</t>
+          <t>OLX PT: Yurts mongois (Igreja Nova/Cheleiros, Mafra)</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>kleinanzeigen.de</t>
+          <t>olx.pt</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Deutschland weit</t>
+          <t>PT - Mafra (bei Lissabon)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>diverse</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1.000-15.000</t>
-        </is>
+          <t>28 m2 (6 m Durchmesser)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>5000</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Neu bis stark gebraucht</t>
+          <t>Gebraucht / Restposten</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>https://www.kleinanzeigen.de/s-jurte/k0</t>
+          <t>https://www.olx.pt/d/anuncio/yurts-mongis-mongolian-yurts-IDHQ8sJ.html</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Ja - Spedition 500-1.500 EUR</t>
+          <t>Ja - inland PT, Transport+Aufbau gegen Aufpreis</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Marktplatz, wechselnde Angebote, regelmaessig pruefen</t>
+          <t>BESTPREIS 6m+ auf OLX! Filzdecke (warm/kuehl), mobile Aufbau auf jeder ebenen Flaeche. Optional Pelletofen gegen Aufpreis. Direkt vom Verkaeufer.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>eBay.de Jurten Kategorie</t>
+          <t>Kleinanzeigen - Jurte Suche</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>eBay.de</t>
+          <t>kleinanzeigen.de</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Deutschland weit</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2190,44 +2248,44 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>200-10.000+</t>
+          <t>1.000-15.000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Neu bis stark gebraucht</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.de/b/Jurte-Zelt/bn_7005694261</t>
+          <t>https://www.kleinanzeigen.de/s-jurte/k0</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Versand variiert</t>
+          <t>Ja - Spedition 500-1.500 EUR</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Auch Pfadfinder-Jurten (gross, billig, aber Plane nicht UV-fest)</t>
+          <t>Marktplatz, wechselnde Angebote, regelmaessig pruefen</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>eBay.co.uk Yurt</t>
+          <t>eBay.de Jurten Kategorie</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>eBay UK</t>
+          <t>eBay.de</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -2237,54 +2295,54 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1.500-12.000</t>
+          <t>200-10.000+</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Gebraucht</t>
+          <t>Neu/gebraucht</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebay.co.uk/sch/i.html?_nkw=yurt</t>
+          <t>https://www.ebay.de/b/Jurte-Zelt/bn_7005694261</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Ja - Brexit-Zoll bei Import nach PT (~7% Zoll + 23% IVA)</t>
+          <t>Versand variiert</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Brexit verteuert UK-Importe stark</t>
+          <t>Auch Pfadfinder-Jurten (gross, billig, aber Plane nicht UV-fest)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LeBonCoin Yourte</t>
+          <t>eBay.co.uk Yurt</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>leboncoin.fr</t>
+          <t>eBay UK</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Frankreich (variable)</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10-50 m2</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1.500-20.000</t>
+          <t>1.500-12.000</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2294,44 +2352,44 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.leboncoin.fr/ck/ventes_immobilieres/yourte</t>
+          <t>https://www.ebay.co.uk/sch/i.html?_nkw=yurt</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Ja - Spedition FR-&gt;PT 800-1.500 EUR</t>
+          <t>Ja - Brexit-Zoll bei Import nach PT (~7% Zoll + 23% IVA)</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Beispiel: 6m yourte mit Wollisolierung gelistet</t>
+          <t>Brexit verteuert UK-Importe stark</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Wallapop Yurtas</t>
+          <t>LeBonCoin Yourte</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>wallapop.com</t>
+          <t>leboncoin.fr</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Frankreich (variable)</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>10-50 m2</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>5.000-25.000</t>
+          <t>1.500-20.000</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -2341,29 +2399,29 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>https://es.wallapop.com/muebles-deco-y-jardin/yurtas</t>
+          <t>https://www.leboncoin.fr/ck/ventes_immobilieres/yourte</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Ja - ES-&gt;PT guenstig 500-1.000 EUR</t>
+          <t>Ja - Spedition FR-&gt;PT 800-1.500 EUR</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>9 Eintraege typischerweise gelistet</t>
+          <t>Beispiel: 6m yourte mit Wollisolierung gelistet</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Milanuncios Yurta</t>
+          <t>Wallapop Yurtas</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>milanuncios.com</t>
+          <t>wallapop.com</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2373,59 +2431,59 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>diverse 40-80 m2</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22.500-42.000</t>
+          <t>5.000-25.000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Gebraucht</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.milanuncios.com/anuncios/yurt-yurta.htm</t>
+          <t>https://es.wallapop.com/muebles-deco-y-jardin/yurtas</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Ja - ES-&gt;PT guenstig 500-1.000 EUR</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Komplett ausgestattet 27.500 EUR, ohne Moebel 22.500 EUR (Beispiel)</t>
+          <t>9 Eintraege typischerweise gelistet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>OLX Portugal yurts</t>
+          <t>Milanuncios Yurta</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>olx.pt</t>
+          <t>milanuncios.com</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>diverse 40-80 m2</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>variabel</t>
+          <t>22.500-42.000</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -2435,86 +2493,86 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/moveis-casa-e-jardim/q-yurts/</t>
+          <t>https://www.milanuncios.com/anuncios/yurt-yurta.htm</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Ja - innerhalb PT</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>INLAND PT - keine Zoll, kein Auslandsversand</t>
+          <t>Komplett ausgestattet 27.500 EUR, ohne Moebel 22.500 EUR (Beispiel)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Yurt Workshop Secondhand</t>
+          <t>OLX Portugal yurts (Kategorie-Uebersicht)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>yurtworkshop.com (Spanien)</t>
+          <t>olx.pt</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Spanien Granada</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5-7m</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3.000-10.000</t>
+          <t>variabel</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Gebraucht (vom Hersteller)</t>
+          <t>Neu/gebraucht</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.yurtworkshop.com/Buy_Your_Yurt/Second-Hand-Yurts-For-Sale.html</t>
+          <t>https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Ja - ES-&gt;PT 600-1.200 EUR</t>
+          <t>Ja - innerhalb PT</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Vom Hersteller selbst - Qualitaet gepruef</t>
+          <t>INLAND PT - keine Zoll, kein Auslandsversand</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Casa Dos Sonhos Secondhand</t>
+          <t>OLX PT: Tenda Yurt Original Quirguistao (Palmela)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Facebook Casa Dos Sonhos</t>
+          <t>olx.pt</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Portugal (Alentejo)</t>
+          <t>PT - Palmela (Setubal)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>28 m2 (ca. 6 m Durchmesser, 30 Personen)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -2524,133 +2582,133 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Gebraucht direkt vom Eigentuemer</t>
+          <t>Neu/handgefertigt (Originalimport Issyk-Kul Quirguistao)</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/yurtscasadossonhos/posts/3660919220624833/</t>
+          <t>https://www.olx.pt/d/anuncio/tenda-yurt-original-do-quirguisto-yurt-tent-original-from-kyrgystan-IDHEwz9.html</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Ja - inland PT</t>
+          <t>Ja - PT-inland, Versand EXTRA (Region Lissabon)</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Hersteller direkt, ggf. Garantie</t>
+          <t>Marke 'Yourta', Modell 'Serenity'. Komplette Originalausstattung: Schilf-Geflecht, Wolle/Filz, Shyrdak-Teppich, Baskur-Band, Korpe-Kissen, geschnitzte Holztuer. Hand-Applikation. Keine Baugenehmigung noetig.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Yurt Market (worldwide)</t>
+          <t>Yurt Workshop Secondhand</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>yurtmarket.com</t>
+          <t>yurtworkshop.com (Spanien)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Spanien Granada</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>5-7m</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>variabel</t>
+          <t>3.000-10.000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Gebraucht (vom Hersteller)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.yurtmarket.com/</t>
+          <t>https://www.yurtworkshop.com/Buy_Your_Yurt/Second-Hand-Yurts-For-Sale.html</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Versand variiert je Anbieter</t>
+          <t>Ja - ES-&gt;PT 600-1.200 EUR</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Welt-Marktplatz</t>
+          <t>Vom Hersteller selbst - Qualitaet gepruef</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Yurt Forum Classifieds</t>
+          <t>Casa Dos Sonhos Secondhand</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>yurtforum.com</t>
+          <t>Facebook Casa Dos Sonhos</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Portugal (Alentejo)</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>variabel</t>
+          <t>Anfrage</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Gebraucht</t>
+          <t>Gebraucht direkt vom Eigentuemer</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>https://www.yurtforum.com/classifieds/</t>
+          <t>https://www.facebook.com/yurtscasadossonhos/posts/3660919220624833/</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Versand variiert</t>
+          <t>Ja - inland PT</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Community-Marktplatz, oft USA-fokussiert</t>
+          <t>Hersteller direkt, ggf. Garantie</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Groovy Yurts Clearance</t>
+          <t>Yurt Market (worldwide)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>groovyyurts.com</t>
+          <t>yurtmarket.com</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Kanada/USA</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2660,72 +2718,166 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>USD 2.790-18.950</t>
+          <t>variabel</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Restposten/leicht gebraucht</t>
+          <t>Neu/gebraucht</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.groovyyurts.com/catalogue-clearance-and-sale</t>
+          <t>https://www.yurtmarket.com/</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Nein - hauptsaechlich Nordamerika; Versand teuer</t>
+          <t>Versand variiert je Anbieter</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Eher fuer US/CA - hohe Versandkosten nach EU/PT</t>
+          <t>Welt-Marktplatz</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Yurt Forum Classifieds</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>yurtforum.com</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>variabel</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Gebraucht</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yurtforum.com/classifieds/</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Versand variiert</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Community-Marktplatz, oft USA-fokussiert</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Groovy Yurts Clearance</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>groovyyurts.com</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Kanada/USA</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>USD 2.790-18.950</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Restposten/leicht gebraucht</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.groovyyurts.com/catalogue-clearance-and-sale</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Nein - hauptsaechlich Nordamerika; Versand teuer</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Eher fuer US/CA - hohe Versandkosten nach EU/PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>Facebook Marketplace EU</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>facebook.com/marketplace</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Diverse EU</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>diverse</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>variabel</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>Gebraucht</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/marketplace/category/search/?query=yurt</t>
         </is>
       </c>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Regional pruefen</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>Lokale Suche pro Land empfohlen</t>
         </is>
@@ -4811,4 +4963,252 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Titel/Listing</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Standort PT</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Durchmesser</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Innenflaeche m2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Preis EUR</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Zustand</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Material/Bauart</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Versand/Aufbau</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Direktlink</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Anmerkungen / Bewertung Algarve</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="110" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Yurts mongois / Mongolian Yurts</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Igreja Nova e Cheleiros (Mafra, naehe Lissabon)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>6 m</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>28 m2</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Gebraucht/Restposten - direkt vom Verkaeufer</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Klassische mongolische Bauweise: Filzdecke (warm im Winter, kuehl im Sommer), Holzgitter, mobil auf jeder ebenen Flaeche aufbaubar</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>PT-inland, Transport+Aufbau gegen Aufpreis. Optional Pelletofen gegen Aufpreis.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.olx.pt/d/anuncio/yurts-mongis-mongolian-yurts-IDHQ8sJ.html</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>TOP-FUND: Gueneststes 6m-Angebot auf OLX. ABER: traditioneller Filz/Canvas ohne UV-Schutz - mit Schattennetz nachruesten (siehe Hinweise-Sheet) sonst Plane nur 2-3 Jahre Lebensdauer in Algarve. Mit Pelletofen+Aufbau realistisch 6.000-7.500 EUR Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="110" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Yurt Made in Portugal (Hersteller-Insertion auf OLX)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Loures (naehe Lissabon)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>6 m verfuegbar (auch 5m, 7m, 8m)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>ca. 28 m2 (6m)</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>NEU - Hersteller seit 2020</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Modern interpretierte traditionelle Bauweise; portugiesischer Hersteller</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Lieferung+Aufbau NICHT inklusive - extra je nach Standort und Groesse</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.olx.pt/d/anuncio/yurt-made-in-portugal-IDIyzPL.html</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Lokaler PT-Hersteller (kein Importzoll), seit 2020 aktiv. Direktkontakt ueber OLX. 5m=6.900 EUR / 6m=8.400 EUR / 7-8m auf Anfrage. Hinweis: Klimaschutz/UV-Garantie nicht spezifiziert -&gt; dringend nachfragen, ob Plane fuer Algarve geeignet ist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="110" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TENDA YURT Original do Quirguistao (Marke Yourta - Modell 'Serenity')</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Palmela (Setubal, naehe Lissabon)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ca. 6 m (geschaetzt aus 28 m2)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28 m2 (Kapazitaet 30 Personen)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage (Region Lissabon)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Neu / handgefertigt, original aus Quirguistao (Issyk-Kul See)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Original kirgisisch: Schilf-Geflecht (Junco), Wolle und Filz. Komplette Originaldeko: Shyrdak-Teppich, Baskur-Band, Korpe-Linen-Kissen, geschnitzte Holztuer, Filz-Tuerverkleidung, dekorative Kuppelbaender</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Versand EXTRA (Region Lissabon - genauen Preis erfragen)</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.olx.pt/d/anuncio/tenda-yurt-original-do-quirguisto-yurt-tent-original-from-kyrgystan-IDHEwz9.html</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>HOHE AUTHENTIZITAET: Originalimport aus Quirguistao, traditionelle Stickerei und Applikationen. PROBLEM ALGARVE: traditioneller Filz/Wolle nicht fuer 40C+ ausgelegt; Plane unter UV-Belastung anfaellig. Sehr dekorativ - eher fuer kuehlere Bergstandorte als heisse Algarve geeignet. Inserent in PT, kein Importzoll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Ausgeschlossen (unter 6 m Mindestgroesse): 'Yurt mongol autentico Mafra' (5,5 m, 8.000 EUR) - https://www.olx.pt/d/anuncio/yurt-mongol-autntico-IDIR7sZ.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>WICHTIG: OLX-Angebote aendern sich taeglich. Vor Anfrage Live-Suche unter https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/ pruefen. Recherche-Stand: 2026-05-11.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:J8"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1560,7 +1560,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Bet Yurts (Algarve)</t>
+          <t>Bet Yurts (Algarve - Nadav &amp; Noga)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1575,37 +1575,37 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5-9 m Durchmesser</t>
+          <t>5/6/7/8/9 m Durchmesser</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Anfrage (vergleichbar 10-20k)</t>
+          <t>Basispreise auf https://www.betyurts.com/pricing (als Bild) - Aufpreis 800 EUR pro zusaetzlicher Oeffnung bestaetigt</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Holz + Aussenhuelle, glasierte Tueren</t>
+          <t>Gitterwand Nordische Kiefer (Wandhoehe 2,20 m), Innenwand 100% Baumwolle, Daemmung 8 cm recyceltes PET-Vlies, Aussenplane Acryl MARINE-GRADE UV-/schimmelfest mit PVC-Schuerze, Plexikuppel oeffenbar, Silikon-Kaminmanschette Standard, Glastuer Zedernholz-Rahmen doppelverglast</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Sehr gut - lokal in Algarve gebaut, klima-optimiert, Schreiner+Designerin</t>
+          <t>SEHR GUT FUER ALGARVE-KUESTE: Marine-grade UV-Plane (explizit kuestentauglich), PET-Daemmung (schimmel-/feuchteresistenter als Schafwolle in Salzluft), Kronenring 1,20 m / Hoehe 2,90-3,70 m</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Inland - Transport innerhalb PT inklusive (entfernungsabh.)</t>
+          <t>Inland Algarve - Transport+Aufbau gegen Aufpreis (Distanzabhaengig). Vorgefertigte gedaemmte Plattform mit Erdschrauben + Kiefer-Sperrholzboden im Angebot.</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>BESTE LOKALE OPTION. Carpenter+Designer Duo, lokale Materialien. +800 EUR pro extra Tuer/Fenster</t>
+          <t>Schreiner Nadav + Produktdesignerin Noga - lebt selbst was sie baut. Standard inkl.: doppelverglaste Glastuer, Plexikuppel, Kaminmanschette. Optionen: 800 EUR/Oeffnung. Kontakt: noga@betyurts.com / +351 961 592 792</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>10.000-15.000 (geschaetzt)</t>
+          <t>Basispreis aus Web nicht extrahierbar (Bild); Anfrage gestellt, Erwartung 12.000-18.000 EUR fuer 7-9m mit Plattform+Aufbau</t>
         </is>
       </c>
     </row>
@@ -1872,102 +1872,206 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Yurt Workshop UK</t>
+          <t>Atilla es a Fehernep (jurtak.hu)</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Ungarn</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>https://www.yurtworkshop.com/</t>
+          <t>https://jurtak.hu/  |  https://fehernep.hu/</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>5-7m</t>
+          <t>4 / 6 / 8 / 10 m</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Anfrage GBP/EUR</t>
+          <t>8m Rahmen 6.600 + 4 Fenster + Kuppel = 9.410 netto / +Plane (Sauleda+Airtex) 2.200 / +Versand PT 3.500</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Eichen-/Kastanien-Holz + Canvas + Wollfilz</t>
+          <t>Rahmen Buche (Standard) oder Eiche/Laerche (Upgrade), Rest Sibirische Kiefer lackiert (Sebastian wuenscht Oel-Finish), Plane Sauleda PVC Dach + Airtex Acryl Wand, Standard-Daemmung Spiegelfolie+Vatelin (fuer Algarve NICHT empfohlen - Sebastian sourct Wollfilz+Tyvek selbst)</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Mittel - Brexit-Zoll Aufschlag</t>
+          <t>Mittel: Erfahrung ES/BE/DE/PL aber NICHT explizit Atlantik-Kueste. Buche-Standard fuer humide Algarve ungeeignet -&gt; Holz-Upgrade obligatorisch.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>UK-&gt;PT 1.500-2.500 EUR + EU-Zoll/IVA bei Brexit-Import</t>
+          <t>Versand HU-&gt;Algarve 3.500 EUR (hoch). EU-USt-IdNr noetig fuer steuerfreie IC-Lieferung (sonst 27% MwSt HU). Lieferzeit 1-2 Monate. Foundation-Plaene inkl.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Etabliert; Brexit verteuert Lieferung in EU erheblich</t>
+          <t>Atilla Berki, Jurtenbauer seit 1996, erster kommerzieller HU-Hersteller. Sozial: Rahmen aus Therapieprogramm fuer Drogenabhaengige/Jugendstraftaeter. Ehrlich (sagt selbst Airtex nicht atmungsaktiv). Kontakt: jurtak@gmail.com / +36 30 657 0740</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>9.000-13.000</t>
+          <t>8m mit Eichen-Upgrade+Premium-Daemmung+Versand: 17.700-20.500 netto (UEBER 15k Budget)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>Les Tentes d'Avalon (vivrelayourte.fr) - NICHT Yourtepoque verwechseln!</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Frankreich (Val-du-Faby, Aude, Sued-FR)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>https://vivrelayourte.fr/</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Modelle Marco Polo (1 Tuer) / Da Vinci (2 Tueren) in 7m / 8m</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>7m Marco Polo 19.370 / 7m Da Vinci 20.840 / 8m Marco Polo 22.100 / 8m Da Vinci 23.590 EUR (jeweils ohne Plattform/Versand)</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Laerchen-Rahmen, Schafwoll-Filz, gedaemmt, Innenliner inklusive, oeffenbare Plexikuppel separat 1.900</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Mittel - franz. Hersteller, keine UV-Garantie ausgewiesen, KEINE decennale-Bauhaftung</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Versand Val-du-Faby-&gt;Algarve ca. 1.500 km, 1,40 EUR/km hin+rueck = ca. 4.200 EUR. Aide-au-montage 450-550 EUR (nur 2 Experten, 6-8 Personen Selbsthilfe noetig).</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>PREMIUM-Segment: Plancher Isole (Holz+55mm Kork) 6.250 (7m) / 9.000 (8m). 2/3-Anzahlung bei Bestellung (sehr hoch, branchenunueblich). Lieferzeit 2-4 Monate. Garantie nur 1 J. versteckte Maengel.</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>7m Gesamt mit Plattform+Versand+Montage: ~33.000-34.500 EUR / 8m: ~38.600-40.000 EUR (DEUTLICH UEBER BUDGET)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Yurt Workshop UK</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurtworkshop.com/</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>5-7m</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage GBP/EUR</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Eichen-/Kastanien-Holz + Canvas + Wollfilz</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Mittel - Brexit-Zoll Aufschlag</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>UK-&gt;PT 1.500-2.500 EUR + EU-Zoll/IVA bei Brexit-Import</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Etabliert; Brexit verteuert Lieferung in EU erheblich</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>9.000-13.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
           <t>FamWest</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B31" s="3" t="inlineStr">
         <is>
           <t>Deutschland</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>https://www.famwest.de/en/mongolian-yurts/</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>5-9m Durchmesser</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t>Anfrage</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="F31" s="3" t="inlineStr">
         <is>
           <t>Filz + Canvas</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G31" s="3" t="inlineStr">
         <is>
           <t>Mittel</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H31" s="3" t="inlineStr">
         <is>
           <t>DE-&gt;PT 1.500-2.000 EUR</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
+      <c r="I31" s="3" t="inlineStr">
         <is>
           <t>5/6/7/8/9 m Optionen, inkl 19% MwSt</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="J31" s="3" t="inlineStr">
         <is>
           <t>ca. 6.000-15.000</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -1632,7 +1632,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Anfrage</t>
+          <t>5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 (delivered+erected PT)</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1642,22 +1642,22 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>EXZELLENT - 10 Jahre UV-Garantie auf Aussenhuelle, Plane rottet/schimmelt nicht, braucht keine Nachbehandlung; speziell fuer portugiesisches Wetter gefertigt</t>
+          <t>EXZELLENT - 10 Jahre UV-Garantie auf Aussenhuelle SCHRIFTLICH, Plane rottet/schimmelt nicht, braucht keine Nachbehandlung; speziell fuer portugiesisches Wetter gefertigt</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Innerhalb Festland-PT inkl. Lieferung &amp; Aufbau (im Preis enthalten)</t>
+          <t>Innerhalb Festland-PT INKL. Lieferung+Aufbau im Preis</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>STANDARD inkl.: 1x1 m doppelverglastes Alu-Fenster (9,1m: 120x120cm), Holztuer mit Fenster+Laden, Daemmung, oeffenbares Kuppel-Oberlicht. Selbsttragend ohne Mittelsaeule, Wand &gt;2 m, Mittelring min. 3,5 m. Solarwerkstatt. OPTIONEN: groessere Fenster, Sturm-Kit, Extra-Daemmlagen, franz. Doppeltueren 3/4-Glas+Lade, Kaminzug, Mueckennetze</t>
+          <t>STANDARD inkl.: 1x1 m doppelverglastes Alu-Fenster (9,1m: 120x120cm) ODER Vollglas-UPVC-Tuer, Standardtuer mit Fenster+Holzladen, moderne Daemmung, Innenliner, oeffenbares Kuppel-Oberlicht. Selbsttragend ohne Mittelsaeule, Wand &gt;2 m, Mittelring min. 3,5 m. Solarwerkstatt. OPTIONEN (Preis offen): groessere/Vollhoehe-Fenster, STURM-KIT (storm-prone areas), Extra-Daemmlagen, franz. Doppeltueren 3/4-Glas+Lade, Vollhoehe-UPVC-Doppeltueren, Kaminzug, MEZZANINE-Ebenen</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>8.000-15.000 (geschaetzt nach Groesse) - Lieferung+Aufbau PT inklusive</t>
+          <t>5m: 7.900 / 6,1m: 9.700 / 7,3m: 15.750 / 9,1m: 18.000 EUR alles inkl. PT-Lieferung+Aufbau</t>
         </is>
       </c>
     </row>
@@ -3466,17 +3466,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Hersteller PT - lokale Spitzenoption</t>
+          <t>Hersteller PT - lokale Spitzenoption (BESTAETIGTE PREISE)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ca. 8.000-15.000 nach Groesse (Lieferung+Aufbau PT inkl.)</t>
+          <t>5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 EUR delivered+erected</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>BESTE KLIMA-EIGNUNG IM MARKT: 10 Jahre UV-Garantie auf Aussenhuelle, Plane rottet/schimmelt nicht, keine Nachbehandlung noetig. Standorte: 5m/6,1m/7,3m/9,1m (20/30/42/64 m2). SELBSTTRAGEND ohne Mittelsaeule, Waende &gt;2 m, Mittelring 3,5 m -&gt; super geraeumig. STANDARD inkl.: doppelverglastes Alu-Fenster, Holztuer m. Fenster+Laden, Daemmung, oeffenbares Kuppel-Oberlicht. Portugiesisches Holz + portug. Korkboeden + Korkdaemmung. Solarwerkstatt in Alto Alentejo (Portalegre). Lieferung und Aufbau in Festland-PT IM PREIS. Kein Import-Zoll/IVA. Optionen: Sturm-Kit (Algarve-Winterstuerme!), Extra-Daemmung, franz. Doppeltueren, Kaminzug, Mueckennetze.</t>
+          <t>BESTPREIS FUER KLEINE+MITTLERE GROESSEN MIT KLIMA-GARANTIE: 6,1m bei 9.700 EUR all-in (Lieferung+Aufbau PT inkl.) ist im Algarve-Markt kaum zu unterbieten. 10 Jahre UV-Garantie SCHRIFTLICH auf Aussenhuelle, kein Verrotten/Schimmel, keine Nachbehandlung noetig. SELBSTTRAGEND ohne Mittelsaeule, Waende &gt;2 m, Mittelring 3,5 m -&gt; super geraeumig. STANDARD inkl.: doppelverglastes Alu-Fenster oder Vollglas-UPVC-Tuer, Standardtuer mit Fenster+Laden, moderne Daemmung, Innenliner, oeffenbares Kuppel-Oberlicht, klima-angepasste Aussenhuelle. Portugiesisches Holz, Solarwerkstatt in Alto Alentejo (Portalegre). KEIN Import-Zoll/IVA, kein Versandstress. Optionen verfuegbar: Sturm-Kit (Algarve!), Vollhoehe-Fenster, Extra-Daemmung, franz. Doppeltueren, Kaminzug, MEZZANINE-Ebenen. HINWEIS 7,3m und 9,1m: Preis-Sprung ueberproportional - 6,1m bietet bestes EUR/m2.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4794,11 +4794,11 @@
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Preis &amp; Kommerzielles</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="25" customHeight="1">
+          <t>Preis &amp; Kommerzielles (BESTAETIGT per Mail an Sebastian Mai 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="27" customHeight="1">
       <c r="A56" s="8" t="inlineStr">
         <is>
           <t>Preisliste</t>
@@ -4806,263 +4806,311 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Nicht oeffentlich. Anfrage per E-Mail / Facebook erforderlich.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="29" customHeight="1">
+          <t>Direktangebot per Facebook-Messenger erhalten - oeffentlich nicht gelistet</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="21" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>Schaetzung 5m (20 m2)</t>
+          <t>5m (20 m2)</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>ca. 8.000-10.500 EUR inkl. Aufbau (vergleichbar mit Yourtepoque-Niveau + Local-Bonus)</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
+          <t>7.900 EUR delivered + erected mainland PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>Schaetzung 6,1m (30 m2)</t>
+          <t>6,1m / 20-foot (30 m2)</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>ca. 9.500-12.500 EUR inkl. Aufbau</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="23" customHeight="1">
+          <t>9.700 EUR delivered + erected mainland PT - BESTES EUR/m2-VERHAELTNIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>Schaetzung 7,3m (42 m2)</t>
+          <t>7,3m / 24-foot (42 m2)</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>ca. 11.500-14.500 EUR inkl. Aufbau (an Budget-Grenze)</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="21" customHeight="1">
+          <t>15.750 EUR delivered + erected mainland PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>Schaetzung 9,1m (64 m2)</t>
+          <t>9,1m / 30-foot (64 m2)</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>ca. 15.000-20.000+ EUR (ueber Budget)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="20" customHeight="1">
+          <t>18.000 EUR delivered + erected (inkl. 120x120cm Alu-Fenster fuer Proportionalitaet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="27" customHeight="1">
       <c r="A61" s="8" t="inlineStr">
         <is>
+          <t>EUR pro m2 Vergleich</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>5m: 395 / 6,1m: 323 / 7,3m: 375 / 9,1m: 281 - 6,1m und 9,1m am effizientesten</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
           <t>Lieferung &amp; Aufbau</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Inklusive in Festland-PT</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="8" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>IM PREIS ENTHALTEN (Festland-PT) - keine versteckten Versandkosten</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="8" t="inlineStr">
         <is>
           <t>Import-Zoll/IVA</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>ENTFAELLT (lokale PT-Produktion)</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="26" customHeight="1">
-      <c r="A63" s="8" t="inlineStr">
+    <row r="64" ht="33" customHeight="1">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>Optionen Preise</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Noch nicht bestaetigt - aktiv nachfragen: Sturm-Kit, franz. Doppeltueren, Extra-Daemmung, Kaminzug, Mezzanine</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Slot-Verfuegbarkeit (Mai 2026)</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Atilla Berki-Style Slot-System: aktuell Dezember 2026 oder 2027 angeboten -&gt; hohe Auslastung</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="29" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
         <is>
           <t>Zahlung</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Direkt mit Hersteller, vermutlich Anzahlung + Restzahlung bei Abnahme</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="8" customHeight="1"/>
-    <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="5" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Direkt mit Hersteller, Konditionen offen (Etappenzahlung gegen Baufortschritt anfragen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="8" customHeight="1"/>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>Nachhaltigkeit / ESG</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="8" t="inlineStr">
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
         <is>
           <t>Energie Produktion</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>100% Solar in der Werkstatt</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="8" t="inlineStr">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="8" t="inlineStr">
         <is>
           <t>Materialien-Herkunft</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>Portugiesisch (Holz, Kork)</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="8" t="inlineStr">
+    <row r="71" ht="30" customHeight="1">
+      <c r="A71" s="8" t="inlineStr">
         <is>
           <t>Soziales Engagement</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Plant Wollverarbeitung um lokale Schafwolle aufzuwerten (Alentejo) - aktuell unterbewertet</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
-        <is>
-          <t>Kreislaufwirtschaft</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Natuerliche Materialien, kein PVC im Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="8" customHeight="1"/>
-    <row r="71" ht="22" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
-        <is>
-          <t>Risiken &amp; Hinweise</t>
         </is>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="8" t="inlineStr">
         <is>
+          <t>Kreislaufwirtschaft</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Natuerliche Materialien, kein PVC im Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="8" customHeight="1"/>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Risiken &amp; Hinweise</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
           <t>Lieferzeit</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>Handarbeit -&gt; mehrere Monate Vorlauf einplanen</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="24" customHeight="1">
-      <c r="A73" s="8" t="inlineStr">
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="8" t="inlineStr">
         <is>
           <t>Skalierung</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>Kleines Familienunternehmen - Reaktionszeit kann variieren</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="8" t="inlineStr">
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="8" t="inlineStr">
         <is>
           <t>Preis intransparent</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>Keine oeffentliche Preisliste - immer schriftliches Angebot einholen + Optionen klar definieren</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="23" customHeight="1">
-      <c r="A75" s="8" t="inlineStr">
+    <row r="78" ht="23" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
         <is>
           <t>Sturmkomponente</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>Algarve-Kueste: Sturm-Kit OBLIGATORISCH bestellen</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="29" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
+    <row r="79" ht="29" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>Hitze Innenraum</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>Trotz 10-J. Plane: zusaetzliches Schattennetz/Pergola fuer 40C+ Sommertage empfehlenswert</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="8" customHeight="1"/>
-    <row r="78" ht="22" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
+    <row r="80" ht="8" customHeight="1"/>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="5" t="inlineStr">
         <is>
           <t>Fazit fuer Algarve</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="38" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="82" ht="54" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>Bewertung</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>TOP-EMPFEHLUNG #1 - einzigartige 10-J. UV-Garantie, lokale Produktion, Lieferung+Aufbau inkl., portugiesische Materialien, kein Import-Risiko.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="36" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>TOP-EMPFEHLUNG #1 BESTAETIGT - bei 6,1m fuer 9.700 EUR all-in nicht zu schlagen, einzigartige 10-J. UV-Garantie schriftlich, lokale Produktion, Lieferung+Aufbau inkl., portugiesische Materialien, kein Import-Risiko, kein Versandstress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="34" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>Sweet Spot</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>6,1m / 30 m2 zu 9.700 EUR - DEUTLICH UNTER 15k Budget, laesst Raum fuer Sturm-Kit + Kaminzug + Plattform-Vorbereitung</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="57" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>Naechster Schritt</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Per Facebook Messenger / E-Mail Angebot fuer 5m oder 6,1m anfragen, mit Sturm-Kit, Mueckennetz, Kaminzug, ggf. franz. Doppeltueren.</t>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Konkretes schriftliches Angebot fuer 6,1m oder 7,3m inkl. Sturm-Kit + Kaminzug + Mezzanine-Option (falls fuer 7,3m relevant) anfragen. Zahlungskonditionen klaeren (Etappenzahlung). Show-Yurt-Besuch Portalegre verhandeln. Slot 2026 bestaetigen (nicht 2027).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A78:B78"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A65:B65"/>
+    <mergeCell ref="A81:B81"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A68:B68"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A74:B74"/>
     <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -4253,7 +4253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -4906,7 +4906,7 @@
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
+    <row r="65" ht="25" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
           <t>Slot-Verfuegbarkeit (Mai 2026)</t>
@@ -4914,185 +4914,233 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Atilla Berki-Style Slot-System: aktuell Dezember 2026 oder 2027 angeboten -&gt; hohe Auslastung</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="29" customHeight="1">
+          <t>Aktuell Dezember 2026 oder 2027 angeboten -&gt; hohe Auslastung</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="50" customHeight="1">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>Zahlung</t>
+          <t>Zahlungsbedingungen BESTAETIGT</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>Direkt mit Hersteller, Konditionen offen (Etappenzahlung gegen Baufortschritt anfragen)</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="8" customHeight="1"/>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="5" t="inlineStr">
+          <t>1) Anzahlung sichert den Termin (Teil der Gesamtsumme). 2) VOLLZAHLUNG 2 Monate vor Lieferung (5m/6,1m/7,3m) bzw. 3 Monate vor Lieferung (9,1m). 3) Lieferung selbst KEIN Zahlungstrigger - alles vorher beglichen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="52" customHeight="1">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>RISIKO-Bewertung Zahlung</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>ROTE FLAGGE: 100% im Voraus, Monate vor Lieferung. Branchenstandard ist 30-50% Anzahlung + Restzahlung bei Abnahme. Bei CdS keinerlei Hebel mehr nach Vollzahlung. Insolvenz-/Qualitaetsrisiko liegt vollstaendig beim Kaeufer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Mitigation-Optionen</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>1) Per Kreditkarte zahlen (Chargeback-Schutz) - mit Bank vorab klaeren ob Limit reicht. 2) Treuhand-Konto (Escrow) in PT, kostet ~0,5-1% Volumen. 3) Etappenzahlung verhandeln: 30% Anzahlung / 40% bei Baustart mit Foto-/Video-Nachweis / 30% bei Abnahme vor Ort. 4) Persoenlicher Besuch+Werkstatt-Besichtigung VOR Vollzahlung erzwingen. 5) Referenzen (PT/Algarve) kontaktieren und Punkt: Termintreue+Qualitaet abfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="57" customHeight="1">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>Social-Media-Kanaele zur Verifikation</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Facebook https://www.facebook.com/yurtscasadossonhos/ - 3.617 Follower, regelmaessige Posts seit Jahren / YouTube https://www.youtube.com/channel/UCfenMyhVzEkX7P-lz2hjS6A - dokumentierte Aufbau-Videos / TikTok https://www.tiktok.com/@casadossonhosyurts</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="8" customHeight="1"/>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Nachhaltigkeit / ESG</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="8" t="inlineStr">
         <is>
           <t>Energie Produktion</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>100% Solar in der Werkstatt</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="8" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="8" t="inlineStr">
         <is>
           <t>Materialien-Herkunft</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>Portugiesisch (Holz, Kork)</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="8" t="inlineStr">
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>Soziales Engagement</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>Plant Wollverarbeitung um lokale Schafwolle aufzuwerten (Alentejo) - aktuell unterbewertet</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="22" customHeight="1">
-      <c r="A72" s="8" t="inlineStr">
-        <is>
-          <t>Kreislaufwirtschaft</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Natuerliche Materialien, kein PVC im Standard</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="8" customHeight="1"/>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>Risiken &amp; Hinweise</t>
         </is>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="8" t="inlineStr">
         <is>
+          <t>Kreislaufwirtschaft</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Natuerliche Materialien, kein PVC im Standard</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="8" customHeight="1"/>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Risiken &amp; Hinweise</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
           <t>Lieferzeit</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>Handarbeit -&gt; mehrere Monate Vorlauf einplanen</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="24" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>Handarbeit -&gt; aktuell Dezember 2026 oder 2027. Slot frueh sichern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="8" t="inlineStr">
         <is>
           <t>Skalierung</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>Kleines Familienunternehmen - Reaktionszeit kann variieren</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
-        <is>
-          <t>Preis intransparent</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Keine oeffentliche Preisliste - immer schriftliches Angebot einholen + Optionen klar definieren</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="23" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
+    <row r="80" ht="38" customHeight="1">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>HAUPTRISIKO Zahlung</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>100% Vorauszahlung 2-3 Monate vor Lieferung - vollstaendiges Kaeufer-Risiko ohne Sicherheit. Mitigation siehe Sektion 'Preis &amp; Kommerzielles'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="25" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>Sturmkomponente</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Algarve-Kueste: Sturm-Kit OBLIGATORISCH bestellen</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="29" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Algarve-Kueste: Sturm-Kit OBLIGATORISCH bestellen (Preis offen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="29" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>Hitze Innenraum</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>Trotz 10-J. Plane: zusaetzliches Schattennetz/Pergola fuer 40C+ Sommertage empfehlenswert</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="8" customHeight="1"/>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
+    <row r="83" ht="53" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>Verifikations-Schritte VOR Auftrag</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>1) Show-Yurt-Besuch Portalegre + Werkstatt-Tour. 2) 2 Algarve/Monchique-Referenzen telefonisch sprechen. 3) Rechtsform der Firma (Lda/Unipessoal/Einzelperson) checken. 4) Zahlungsmodalitaeten verhandeln (Etappen oder Kreditkarte).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="8" customHeight="1"/>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="5" t="inlineStr">
         <is>
           <t>Fazit fuer Algarve</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="54" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
+    <row r="86" ht="54" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>Bewertung</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>TOP-EMPFEHLUNG #1 BESTAETIGT - bei 6,1m fuer 9.700 EUR all-in nicht zu schlagen, einzigartige 10-J. UV-Garantie schriftlich, lokale Produktion, Lieferung+Aufbau inkl., portugiesische Materialien, kein Import-Risiko, kein Versandstress.</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="34" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
+    <row r="87" ht="34" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>Sweet Spot</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
         <is>
           <t>6,1m / 30 m2 zu 9.700 EUR - DEUTLICH UNTER 15k Budget, laesst Raum fuer Sturm-Kit + Kaminzug + Plattform-Vorbereitung</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="57" customHeight="1">
-      <c r="A84" s="8" t="inlineStr">
+    <row r="88" ht="57" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>Naechster Schritt</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>Konkretes schriftliches Angebot fuer 6,1m oder 7,3m inkl. Sturm-Kit + Kaminzug + Mezzanine-Option (falls fuer 7,3m relevant) anfragen. Zahlungskonditionen klaeren (Etappenzahlung). Show-Yurt-Besuch Portalegre verhandeln. Slot 2026 bestaetigen (nicht 2027).</t>
         </is>
@@ -5102,15 +5150,15 @@
   <mergeCells count="12">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A81:B81"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A68:B68"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A85:B85"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A77:B77"/>
     <mergeCell ref="A55:B55"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -14,6 +14,12 @@
     <sheet name="Hinweise" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Casa dos Sonhos Detail" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="OLX 6m+ Funde" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DIY 8 Bauplan Uebersicht" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="DIY 9 Materialliste" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="DIY 10 Quellen" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="DIY 11 Arbeitsschritte" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="DIY 12 Werkzeuge" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="DIY 13 Kostenrechnung" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +28,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0 &quot;EUR&quot;"/>
+  </numFmts>
   <fonts count="6">
     <font>
       <name val="Calibri"/>
@@ -100,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -122,6 +130,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2082,6 +2102,4039 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorie</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Anbieter</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Land</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Spezialisierung</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Website / Kontakt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Liefert nach PT?</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Anmerkung Algarve-Tauglichkeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Holz</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Mil Martins &amp; Irmao</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>PT (Norden)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Edelkastanie, Eiche, Pinie</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.milmartinsirmao.pt/</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Innerhalb PT</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Etablierte Saegerei, Castanho Premium getrocknet. Anfrage per Mail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Holz</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Industria de Madeiras</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Castanho-Handel, Industrie</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.industriademadeiras.com/</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Innerhalb PT</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Castanho-Bohlen, Latten zuschneiden lassen moeglich.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Holz</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Albano Leite da Silva</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Allgemeine Saegerei</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.albanoleitesilva.pt/</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Innerhalb PT</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Castanho + Pinie + Eukalyptus, KDI Behandlung verfuegbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Holz</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Maderterraneo</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Castanho Boden, Laerche, EU-Premium</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://maderterraneo.com/</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Ja, Versand ES-&gt;PT</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Boden-Komponente Laerche/Castanho premium. Online-Bestellung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Holz</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Siero Lam</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ES (Asturien)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Castanho-Bohlen Massivholz</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.sierolam.com/pt-pt/madeira-tabua/</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ja, EU-Spedition</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Spanischer Marktfuehrer Edelkastanie. Versand PT moeglich.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Holz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Holz Schiller AT</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sibir. Laerche, Robinie</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.holz-schiller.at/</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Ja, EU-Spedition 200-400 EUR</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Premium-Importeur, online bestellbar, USt-IdNr noetig fuer IC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Holz</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Holz Henkel AT</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Robinie, Eiche, Esche</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.holz-henkel.com/</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Ja, EU-Spedition</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Robinie fuer Tuer-Konstruktion, sehr salzwasserresistent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Holz</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Holz Possling DE</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sibir. Laerche, Uni-Material</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.holzpossling.de/</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Ja, ueber Spedition</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Online-Shop mit DE-Preisen. Versand nach PT moeglich.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Daemmung-Kork</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Amorim Cork</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>PT (national)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Welt-Markt-fuehrer Kork</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amorim.com/</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Innerhalb PT, Hauptsitz</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>PT-Heimspiel. Korkboden 30mm direkt vom Hersteller anfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Daemmung-Kork</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Sofalca</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Expandierter Naturkork</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sofalca.pt/</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Innerhalb PT</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ICB-Korkplatten, fuer Plattform-Daemmung optimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Daemmung-Wolle</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>ISOLENA AT</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>AT (Burgenland)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Schafwoll-Daemmung Premium</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.isolena.com/</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ja, EU-Spedition + USt-IdNr</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100% Wolle Ionic Protect 16mm. Direkt-Bestellung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Daemmung-Wolle</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>DAEMWOOL AT</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Schafwoll-Jurtenfilz</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.daemwool.at/</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Ja, EU-Spedition</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Spezialisiert auf Jurten-Anwendung. 8 oder 16mm verfuegbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Daemmung-Wolle</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Tobias Tumfart Schafwolldaemmung</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Jurtefilz 8/16 mm</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.schafwolldaemmung.at/</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Ja, EU-Spedition</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Preis 8mm = 8,16 EUR/m2 (excl VAT). Massmade verfuegbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Daemmung-Wolle</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Wollwerkstatt AT</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Nadelfilz nach Mass</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wollwerkstatt.at/</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Online-Konfigurator, Auf-Bestellung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Plane</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sauleda S.A.</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ES (Barcelona)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Solar Pro / Nautic Acryl 125+ Jahre</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://sauleda.com/</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Ja, B2B-Anfrage</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Hersteller selbst, Distributoren-Liste in PT anfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Plane</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Coartal (Sauleda PT-Distri)</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>PT (zu pruefen)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sauleda-Stoffe Vertrieb</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.coartal.com/files/Catlogo-Acrlico-Sauleda.pdf</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Lokaler Vertrieb der Sauleda-Produkte, direkt anfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Plane</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Toldum.es</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>ES (Murcia)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Sauleda + Markenstoffe online</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.toldum.com/nuestros-productos/lonas-y-tejidos/sauleda/</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Online-Vertrieb auch Stoff-Rollen, EU-Versand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Plane</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Parà Tempotest</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Tempotest Marine Acryl 6J-Garantie</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.para.it/en/</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Ja, Distributor-Liste</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Alternative zu Sauleda, oft etwas teurer aber Teflon-Finish.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Plane-Fachbetrieb</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Yurt Workshop Spain (Cadiar)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>ES (Granada)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Jurten-Plane Massanfertigung</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>http://yurtworkshop.es/</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Ja, ES-&gt;PT 600-1.200 EUR</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Rob Matthews kann Plane separat fertigen. Erfahrung mit Sebastian's Klima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Plane-Fachbetrieb</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Atilla Jurtak (HU)</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sauleda PVC + Airtex Acryl Set</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>https://jurtak.hu/</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Ja, HU-&gt;PT 3.500 EUR Spedition</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Komplettes Cover 8m = 2.200 EUR netto, sehr guter Preis. Versand teurer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Plane-Fachbetrieb</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Lokaler Persenningmacher PT</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Auftragsnaeherei</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Suche: 'oficina de toldos Algarve', 'velejaria PT'</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Innerhalb PT</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Du lieferst Stoff, sie naehen. Risiko: noch nie Jurte genaht. Skizzen mitbringen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Tono</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Camping Yurts</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Tono fertig gebohrt</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.campingyurts.com/yurt-parts/</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Ja, UK-&gt;PT post-Brexit Zoll</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Pre-drilled, sealed, varnished. Direkt online bestellbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Tono</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Groovy Yurts (CA, exportiert global)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sibir.-Kiefer Tono Mongolian-style</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.groovyyurts.com/accessories-and-add-ons/toono-dome</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Versand teuer</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Authentisch mongolisch, eher teuer fuer EU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Tono</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>FAMTENTS</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>CZ</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Tschechische Laerche Tono</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.famtents.com/yurts</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Ja, EU-Spedition</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Premium-Hersteller EU, Tono separat anfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Tono</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Atilla Jurtak (HU)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Tono separat moeglich (Anfrage)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://jurtak.hu/</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Ja, HU-Versand</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Custom in Hartholz. Anfragen ob er nur Tono+Uni verkauft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Tono</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Adorjan Jurta (HU)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>HU</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Tradi. mongolisch Tono</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>https://adorjan-jurta.hu/</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Ja, HU-Versand</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Hartholz, traditionell, lange Lieferzeit (bookings 1J voraus).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Schraubpfaehle</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Krinner GmbH</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Schraubpfaehle Marktfuehrer</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.krinner.de/</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Ja, EU-Spedition</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>KSF-M Profil 800-1000 mm, alle EU-baurelevanten Zulassungen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Schraubpfaehle</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Stop Schraubfundamente</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Alternative zu Krinner</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stop-schraubfundamente.de/</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Ja, EU-Spedition</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Etwas guenstiger als Krinner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Schraubpfaehle</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Bauhaus / Leroy Merlin PT</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Krinner-Lager+Vertrieb</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bauhaus.pt/  |  https://www.leroymerlin.pt/</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Innerhalb PT</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Lokales Lager, schneller als DE-Direkt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Beschlaege</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Wuerth Portugal</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Industrie-Schrauben/Beschlaege</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.wurth.pt/</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Innerhalb PT, oft Same-Day</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Edelstahl A4 fuer Algarve obligatorisch. Schraubenmusterbox empfehlenswert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Beschlaege</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Bauhaus PT</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>DIY-Sortiment</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bauhaus.pt/</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Innerhalb PT</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Gut fuer Standard-Sortiment. A4-Schrauben anfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Beschlaege</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Brico Marche</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>DIY landesweit</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bricomarche.pt/</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Innerhalb PT</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus-Alternative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Beschlaege</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Acastillaje (Bootsbedarf)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Marine-Edelstahl Spannschloss</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Suche 'acastillaje algarve'</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Lokal</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Spezialisiert auf Salzluft. Spannschlossglieder, Edelstahl-Karabiner.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Werkzeug-Verleih</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus PT Mietservice</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Tischkreissaege, Bohrer-Profi</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.bauhaus.pt/leihservice</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Lokal</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Tages-/Wochenmiete. Tischkreissaege 25-40 EUR/Tag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Werkzeug-Verleih</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Lokale Aluguer-Equipamentos Algarve</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Bau-Maschinen-Verleih</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Suche 'aluguer equipamentos Algarve'</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Lokal</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Oft Wochenpakete guenstiger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Paul King - The Complete Yurt Handbook</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Standard-Werk Bauanleitung</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Amazon / Yurtinfo.org</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>PDF/Print</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>ca. 25 EUR. Pflichtlektuere fuer DIY. Kein 8m-Plan, aber Skalierungs-Anleitung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Paul King - Build Your Own Yurt (kostenloses PDF)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Frueheres Werk, online</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://azinelibrary.org/approved/build-your-own-yurt-1.pdf</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>PDF kostenlos</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Aelter aber kostenlos. 3m Yurte als Skalierungs-Basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>SimplyDifferently Yurt Calculator</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Onlinerechner Bemassung</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>https://simplydifferently.org/Yurt_Notes</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>kostenlos</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>GOLD-STANDARD: Exakte Bohrwinkel, Latten-Anzahlen, Uni-Laengen fuer beliebige Durchmesser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Yurt Forum Community</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>DIY-Erfahrungsaustausch</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurtforum.com/</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>kostenlos</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Stelle Fragen, Bilder, Detail-Probleme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Doit Yurtself</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>DIY-Schritte, Tipps</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>https://doityurtself.com/</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>kostenlos</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>Schreibblog mit Foto-Doku eines Komplett-Baus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Yurt Plans Library DryUrts</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Plaene zum Kauf</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dryurts.com/yurt-plans.html</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>ca. 20-50 USD</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Mehrere Yurten-Plaene downloadbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Schattennetz</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Cooperativa Agricola Algarve</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>PT (lokal)</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Agrar-Schattennetz 90%</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Lokal vor Ort suchen z.B. Sao Bras de Alportel, Lagos</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Innerhalb PT</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Wichtigster Algarve-Tipp! 6m Breite Standard, 4-8 EUR/m2.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Phase</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Woche</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Aufgabe</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Dauer</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Werkzeug</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Output</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Vorbereitung</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Woche 0</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Pläne und Buch besorgen, SimplyDifferently durchrechnen</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>2-3 Tage</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>PC + Drucker</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Paul King Buch, Bemassungs-Ausdrucke</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Detail-Plan auf Papier mit allen Massen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Vorbereitung</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Woche 0</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Werkstattflaeche organisieren</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Massband</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>10x10 m flacher trockener Untergrund</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Khaana kann komplett ausgebreitet werden</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Vorbereitung</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Woche 0</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Material bestellen (lange Lieferzeit zuerst)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tono fertig (4-6 Wochen Lieferzeit), Wollfilz, Schraubpfaehle, Sauleda Plane Massanfertigung</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Bestellungen raus, Lieferzeit-Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Vorbereitung</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Woche 0</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Werkzeug mieten/kaufen</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Tischkreissaege, Stichsaege, Akkuschrauber 18V, Bohrmaschine, Hobel, Bohraufsatz, Schraubzwingen</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Werkstatt aufgeruestet</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Standort</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Woche 1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Standort markieren, Schraubpfaehle setzen</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Erdraketenwerkzeug oder hydraulische Eindrehhilfe</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>8 Krinner-Pfaehle, Wasserwaage</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Plattform-Fundament ueber Boden, perfekt nivelliert</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Standort</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Woche 1</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Plattform-Tragwerk bauen</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2 Tage</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Tischkreissaege, Akkuschrauber</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Kiefer KDI 50x200 Tragbalken, Edelstahl-Schrauben A4</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Tragwerk fertig, Doppel-T-Rahmen + Radial-Balken</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Standort</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Woche 1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Plattform-Daemmung + Decke</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Cuttermesser, Akkuschrauber</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Geo-Vlies, PE-Folie, Kork 30 mm, Laerchen-Deck T+G 27 mm</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Plattform begehbar, isoliert</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Khaana-Bau</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Woche 2</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Edelkastanie-Latten zuschneiden und hobeln</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2 Tage</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Tischkreissaege, Hobel, Schleifer</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>280 Latten 30x10x2100 mm</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Alle Latten fertig, gleichmaessig</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Khaana-Bau</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Woche 2-3</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Bohrloch-Lehre bauen + alle Latten bohren</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2 Tage</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Stationaer-Bohrer, selbstgebaute Bohrlehre</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>M5-Bohrer 5,2 mm, Schraubzwingen</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Alle Latten gebohrt, max. 1 mm Toleranz</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Khaana-Bau</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Woche 3</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Khaana-Sektionen zusammensetzen (Bolzen+Mutter)</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>3-4 Tage</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Akkuschrauber + 8mm-Steckschluessel</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>M5x30 Edelstahl Bolzen + Hutmuttern</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>8 Khaana-Sektionen klappbar, Vorabtest stehen lassen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Khaana-Bau</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Woche 3</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Khaana-Test: alle Sektionen verbinden + auf Plattform stellen</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2 Personen</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Hanf-Schnur fuer temporaere Verbindung</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Khaana steht im Kreis, Tono-Hoehe stimmt</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Tono+Uni</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Woche 4</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Tono-Lieferung pruefen + nachbohren falls noetig</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Akkuschrauber, Schleifer</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Sicherheitslack</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Tono fertig fuer Uni-Aufnahme</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Tono+Uni</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Woche 4</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Uni-Stangen zuschneiden, anschraegen</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2 Tage</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Tischkreissaege, Anschlagwinkel, Hobel</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>65 Laerche 30x30x4000 mm</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Alle 60 Uni-Stangen einsatzbereit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Tono+Uni</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Woche 4</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Uni-Schlaufen am Khaana-Wandkronenrand</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Sattler-Werkzeug, Schraubendreher</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Lederband oder Hanfschlaufen</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Sattel-Punkte fuer 60 Uni alle 60 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Tono+Uni</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Woche 4</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Test-Aufbau Tono+Uni (4-8 Helfer noetig!)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Leitern, 4-8 Helfer</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Erste komplette Skelett-Stehprobe</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Spannband+Tuer</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Woche 5</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Kuriye-Spannband installieren</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Spannschlossglieder, Edelstahl-Karabiner</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>PP-Gurt 50mm 30m, 4 Spannschloesser</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Wand-Spannband fixiert, Vorspannung gleichmaessig</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Spannband+Tuer</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Woche 5</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Tuerrahmen einsetzen+ausrichten</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Wasserwaage, Akkuschrauber</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Robinie-Rahmen 100x100 mm, A4-Schrauben</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Tuer steht 90 Grad, schwingt frei</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Spannband+Tuer</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Woche 5</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Tuerblatt einhaengen+justieren</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Bandscharnier-Schrauber</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Tuerblatt 2x 90x200 cm + Beschlaege</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Tuer schliesst sauber, kein Spalt</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Daemmung+Plane</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Woche 6</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Innenliner befestigen</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Tacker, Naehnadel</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Baumwoll-Sergeant 65 m2</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Wand- und Dachsegmente innen mit Liner bezogen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Daemmung+Plane</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Woche 6</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Wollfilz auflegen (Wand+Dach)</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Cuttermesser</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Wollfilz 16 mm, 105 m2</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Innenseite komplett gedaemmt</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Daemmung+Plane</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Woche 6</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Solitex-Membran ueber Daemmung</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Cuttermesser, Tacker</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Solitex 115 m2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Dampfsperre installiert, ueberlappend +10 cm</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Daemmung+Plane</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Woche 6</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Aussenplane aufziehen (Sauleda)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>1-2 Tage</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Saugen+Leitern, 4 Helfer</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Komplett-Plane 110 m2 inkl. Tunnel+Saeume</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Yurte wetterfest!</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Sturm-Kit</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Woche 7</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Erdanker Sturm-Kit einschrauben</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Erdraketenwerkzeug</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>8 M16 Anker 1.000 mm, Stahlseil 6 mm</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Sturm-Verankerung aktiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sturm-Kit</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Woche 7</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Ratschen-Riemen ueber Dach spannen</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>0,5 Tag</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>8 PP-Ratschen 5 Tonnen</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Plane gegen Aufwehung gesichert</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Sturm-Kit</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Woche 7</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Kaminzug-Durchfuehrung einbauen falls geplant</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1 Tag</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Akkuschrauber, Silikon-Spachtel</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Kaminzug-Manschette 600 Grad</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Holzofen einsetzbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Finale</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Woche 8</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Innen-Ausbau: Bett, Kueche, Boden-Teppich</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Variabel</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Wohnfertig</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Finale</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Woche 8</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Schattennetz ueber Dach spannen</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,5 Tag</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Leitern</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Agrar-Schattennetz 90% 60 m2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Algarve-Hitze entschaerft, Plane-Lebensdauer +X Jahre</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Finale</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Woche 8</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Foto-Doku + Wartungs-Checkliste</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>0,5 Tag</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Kamera</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Versicherung+Erinnerung+Dokumentation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Werkzeug</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Pflicht/Optional</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kauf/Miete</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Preis EUR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Bezugsquelle</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tischkreissaege</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Miete empfohlen</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Bauhaus PT Mietservice</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Hochpraezise Latten-Schnitte. 25-40 EUR/Tag x 7 Tage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Stichsaege</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus / Leroy Merlin</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Fuer Tono-Korrekturen, Tuer-Ausschnitte. Festool/Bosch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Akkuschrauber 18V</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Bauhaus</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2 Akkus empfohlen. Bosch GSR oder Makita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Bohrmaschine stationaer</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Miete oder Kauf</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus Miete o. Globus Baumarkt Kauf</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Fuer 280 Latten-Bohrungen praezise. Saeulenbohrmaschine ideal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Bohrlehre selbstgebaut</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Eigenbau</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Sperrholz-Rest</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>MUSS-HAVE: 5 mm Bohrloch, Anschlag fuer Wiederholgenauigkeit. Selbst in 1 Std gebaut.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Bohraufsaetze M5+M6</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Wuerth PT</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Edelstahl-tauglich, scharf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Akku-Hobel ELEKTRISCH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Miete</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Bauhaus PT</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Latten-Oberflaeche glatt machen. 2 Wochen Miete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sortimentskasten Schrauben A4</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Wuerth</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>M5, M6, Spax 4x50, 5x80 Edelstahl A4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Schraubzwingen (Set 8 Stueck)</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Bauhaus</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Beim Khaana-Zusammenbau unentbehrlich.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Wasserwaage 2m</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Plattform-Aufbau, Tuer-Justierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Massband 5m + 8m</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Bauhaus</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Doppelpack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Erdraketen-Werkzeug Krinner</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Miete</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Mit Schraubpfahl-Lieferung mitbestellen</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Spezial-Werkzeug fuer Krinner-Schrauben. 8 Pfaehle 1 Tag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Sicherheitsausruestung (Brille+Gehoer+Maske)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>PFLICHT</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Bauhaus</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Pflicht fuer Saege+Hobel+Plane-Naehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Leiter 3 m</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Empfohlen</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Miete oder Kauf</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Tono-Aufbau (4,20 m hoch). Klappleiter ausreichend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>4-8 Helfer fuer Aufbau</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Empfohlen</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Bekanntenkreis</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Tono+Uni-Aufbau allein nicht moeglich. Pizza &amp; Bier statt Geld.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sattler-Werkzeug fuer Schlaufen</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Optional</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Sattlerei PT</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Falls Du Lederband statt Bolzen am Khaana willst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Industrie-Naehmaschine</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>OPTIONAL (nur wenn selber naehen)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Miete</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Sattlerei lokal</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Du wolltest Plane bei Fachbetrieb beauftragen -&gt; nicht noetig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Tacker fuer Innenliner</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Empfohlen</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Hand-Tacker mit 10 mm Klammern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Schraubendreher-Set</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Empfohlen</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Bauhaus</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Wera/Wiha Premium - lebenslange Investition.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Beize/Imprägnierung Holz (Hartoel)</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Empfohlen</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Kauf</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus Auro/Osmo</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Auro/Osmo Hartoel statt Lack - atmungsaktiv. ca. 4 Dosen fuer 8m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>WERKZEUG GESAMT</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E22" s="10" t="n"/>
+      <c r="F22" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>DIY 8m Jurte - Vollkostenrechnung + Vergleich Casa dos Sonhos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Block A: Material (siehe Sheet 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Khaana Edelkastanie + Bolzen</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="n">
+        <v>1455</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>PT-Saegerei. Hauptbauteil Wand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Tono fertig + Versand</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Hartholz-Kronenring + Spedition aus DE/HU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Uni Sibir. Laerche + Befestigung</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>982</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>60 Dachstangen incl. Niete + Lederschlaufen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Kuriye Spannband + Spannschloesser</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>192</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Wand-Zugring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Tuer + Tuerbeschlaege A4</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>1350</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Robinie/Eiche, Doppeltuer mit Doppelverglasung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="23" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Plattform komplett (Pfaehle, Tragwerk, Daemmung, Decke, Schrauben)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>4040</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Schraubpfaehle Krinner + Kiefer KDI + Kork 30mm + Laerchen-Deck T+G.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Daemmung Wand+Dach (Schafwollfilz Isolena 16mm)</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>1680</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>105 m2 inkl. Aufschlag, Versand AT-&gt;PT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Innenliner Baumwolle</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>780</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>65 m2 Sergeant 200 g/m2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Solitex-Membran (Diffusionsoffen)</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>690</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>115 m2 fuer Algarve-Klima essentiell.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Aussenplane Sauleda Massanfertigung</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Komplett-Set Dach+Wand+Kuppel-Cover, Sauleda Solar Pro Acryl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Polycarbonat-Kuppel oeffenbar</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>750</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>1,2 m, klar, oeffnungs-faehig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sturm-Kit (Erdanker + Ratschen)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>456</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ALGARVE OBLIGATORISCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Kaminzug-Durchfuehrung</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>280</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Falls Holzofen geplant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Schattennetz Algarve</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Verlaengert Plane-Lebensdauer drastisch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Reserve (10%)</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Schraubenkauf, Lieferzuschlaege, Reparaturen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Werkzeug (Miete+Kauf, siehe Sheet 12)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>1378</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Tischkreissaege Miete + Akku-Tools Kauf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="8" customHeight="1"/>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>ZWISCHENSUMME MATERIAL+WERKZEUG</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n">
+        <v>20273</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Komplett-Materialliste + Werkzeug-Pauschale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="8" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Block B: Versand + Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Holz-Versand DE/AT-&gt;PT (Laerche, Robinie)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>600</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Spedition Sammelladung 2-3 Wochen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Filz-Versand AT-&gt;PT (Isolena)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Paketdienst, ~100 kg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Schraubpfaehle/Schrauben Inland PT</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Lokaler Einkauf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Plane-Lieferung</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>150</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Falls Auftrag bei ES-Sattler statt PT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Tono-Versand</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Sperrgut DE/HU-&gt;PT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="8" customHeight="1"/>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>ZWISCHENSUMME VERSAND</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Block C: Eigene Arbeitszeit (nicht monetarisiert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Geschaetzter Zeitaufwand</t>
+        </is>
+      </c>
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>350-450 Std</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Bei mittlerem Skill, einzeln + 4-8 Helfer-Tage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Zeit-Aequivalent bei 30 EUR/h (rechnerisch)</t>
+        </is>
+      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>10.500-13.500 EUR</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Bewertung: Hobby/Eigenleistung. Nicht in Kostenrechnung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="8" customHeight="1"/>
+    <row r="35" ht="23" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>GESAMTKOSTEN DIY (Material+Werkzeug+Versand)</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>21523</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Inklusive Werkzeug und Algarve-Sturm-Kit. OHNE eigene Arbeitszeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Vergleich mit Casa dos Sonhos (Hersteller)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Casa dos Sonhos 7,3m (42 m2)</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>15750</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Lieferung+Aufbau PT INKL. Aber: keine Plattform, kein Sturm-Kit, kein Kaminzug.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="23" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Casa Plattform separat</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Wenn man dasselbe Niveau will (Schraubpfaehle + Kork + Laerchen-Deck).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Casa Sturm-Kit (Optionspreis offen)</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Geschaetzt - bei Casa konkret abfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Casa Kaminzug (Optionspreis offen)</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>600</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Geschaetzt - bei Casa konkret abfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Casa Schattennetz</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Selbst lokal kaufen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>CASA TOTAL APPLES-TO-APPLES (7,3m)</t>
+        </is>
+      </c>
+      <c r="B43" s="14" t="n">
+        <v>21390</v>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Ueberraschung: DIY 8m und Casa 7,3m kommen aufs Gleiche raus!</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="8" customHeight="1"/>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Casa 9,1m (64 m2)</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Inkl. Aufbau, ohne Plattform/Sturm-Kit/Kamin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Casa 9,1m + Plattform + Sturm-Kit + Kamin</t>
+        </is>
+      </c>
+      <c r="B46" s="13" t="n">
+        <v>23640</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Komplett-Setup 9,1m vs DIY 8m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>FAZIT ENTSCHEIDUNG DIY VS CASA</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="23" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Material-Differenz DIY 8m vs Casa 7,3m all-in</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>-130 EUR (Casa minimal teurer)</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>DIY ist NICHT signifikant guenstiger wenn alles ehrlich gerechnet wird.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="23" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Was DIY trotzdem fuer dich bringen kann</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Lernen + 50m2 statt 42m2 + 8m statt 7,3m + volle Kontrolle Materialwahl + keine 100% Vorauszahlung</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Du baust 8m statt 7,3m = 8 m2 mehr Wohnflaeche fuer denselben Preis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Was DIY KOSTET (jenseits Geld)</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>350-450 Stunden Lebenszeit + Risiko Konstruktionsfehler + Werkzeug-Lernkurve</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Casa liefert Sicherheit (10-J. UV-Garantie schriftlich).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="25" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Empfehlung</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>Hybrid pruefen: Casa Plane+Daemmung kaufen, Plattform+Aufbau selbst</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Frage Casa, ob sie Komponenten ohne Aufbau verkaufen. Spart 30-50% Hersteller-Marge.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5411,4 +9464,1915 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>DIY 8m Jurte - Konstruktionsuebersicht (Algarve-optimiert)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Gesamtgeometrie</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="27" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Durchmesser</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>8,00 m</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Aussenmass Khaana ausgebreitet, plus 100 mm Plane-Ueberlappung pro Seite</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Wandhoehe (Khaana)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>2,00 m</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Casa-dos-Sonhos-Standard (vs. mongolisch traditionell 1,60-1,70 m) - mehr Stehhoehe + bessere Belueftung</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="25" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Hoehe Mittelring (Tono)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>4,20 m</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Ueber Plattform-Oberkante; Dachneigung am Eaves ca. 28-30 Grad</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Tono-Durchmesser</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>1,20 m</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Standard fuer 8m-Jurten mit ~60 Dachstangen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Anzahl Khaana-Sektionen</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Jede Sektion ca. 3,14 m breit ausgebreitet (= pi * 8m / 8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Anzahl Dachstangen (Uni)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Alle 6 Grad = 60 mm Abstand am Tono</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="25" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Wohnflaeche innen</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>~50 m2</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Inkl. 1,2 m Tono-Saeule-frei -&gt; volle Fussbodenflaeche nutzbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="8" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Konstruktionsprinzip</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Bauweise</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Traditionelle Khaana mit Tono+Uni</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Selbsttragend ohne Mittelsaeule - Wandgitter haelt unter Druck der Dachstangen-Schubspannung. Zwingend: stabiles Spannband (Kuriye) auf Wandkronenhoehe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Statik-Prinzip</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Druckring + Zugring</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Tono = Druckring (Dachstangen druecken nach innen). Spannband um Khaana-Top = Zugring (haelt Wand gegen Schub). Funktioniert seit 3000 Jahren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="43" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Sturmsicherung Algarve</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Sturm-Kit dringend</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Atlantik-Winterstuerme 80-100 km/h. Erdanker an 8 Punkten unter Plattform, 5-Tonnen Ratschen-Riemen ueber Aussenplane, Wand+Dach-Verstaerkung mit zusaetzlichen Querstaeben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="8" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Aufbau Schichten (innen nach aussen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Schicht 1 - Khaana-Rahmen</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Edelkastanie 30x10 mm</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Lokal in PT verfuegbar, naturlich tannin-/insektenresistent durch Gerbsaeure - Termiten-Schutz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="27" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Schicht 2 - Innenliner</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Baumwoll-Stoff 200 g/m2</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Aesthetisch + faengt Daemmwolle ein. Maemost in PT bei Sattlerei beziehbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Schicht 3 - Daemmung</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Schafwollfilz 16 mm (ISOLENA)</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>100% Wolle Ionic Protect, schimmelresistent, oeko. 50 m2 fuer Wand + 50 m2 fuer Dach = 100 m2 Gesamtbedarf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Schicht 4 - Atmungsoffene Membran</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Solitex Plus / Tyvek 'Soft'</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>OPTIONAL aber dringend empfohlen: zwischen Daemmung und Aussenplane, verhindert Kondensat in der Daemmwolle. Sebastian hat das auch bei Atilla geplant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Schicht 5 - Aussenplane</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Sauleda Solar Pro Acryl</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Marine-grade UV, salzluftbestaendig, atmungsaktiv, 290-340 g/m2. ca. 110 m2 Bedarf (Dach + Wand + Ueberlappung).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="8" customHeight="1"/>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Holzwahl - Algarve-optimiert</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Khaana (Lattengitter)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Edelkastanie (Castanho)</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Lokal in PT (Norden+Centro). Tannin-haltig = natuerlicher Termiten-/Insektenschutz. Leicht zu biegen, gut sägbar. Klasse 2 Dauerhaftigkeit nach EN 350.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Uni (Dachstangen)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Sibirische Laerche</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Hohe Festigkeit bei geringem Gewicht, harzhaltig = rotresistent. Aus AT/RU-Import via DE oder direkt von Siero Lam (ES/PT). Klasse 3-4 Dauerhaftigkeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Tono (Kronenring)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Gekauft - Hartholz</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Lieferant macht Wahl (typisch Eiche oder Esche laminiert). Achtung: Kontaktpartner fuer ALLE Bohrungen, weil die Geometrie 1.200 mm + 60 Bohrungen nicht einfach zu replizieren ist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="39" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Tuerrahmen + Tuer</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Robinie / Falsche Akazie</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Klasse 1-2 Dauerhaftigkeit (auch ohne Behandlung), extrem hart, salzwasserresistent. Aus AT/HU-Import. Alternative: portugiesische Edelkastanie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Plattform-Konstruktion</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Druckimpr. Kiefer + Laerchen-Deck</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Tragbalken Kiefer KDI (Klasse 4 Dauerhaftigkeit fuer Bodennaehe), Decke Laerche fuer Optik+Klima. Alternativ Robinie als Premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="35" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Plattform-Schraubpfaehle</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Stahl verzinkt Krinner / Stop</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Erdschrauben 800-1.000 mm tief, 8 Stueck fuer 8m-Plattform. Loest die Frage 'Beton oder nicht' (du wolltest keinen Beton).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Plane / Aussenhuelle</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="29" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Sauleda Solar Pro 300 g/m2 (Acryl)</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Spanischer Hersteller seit 1897, Marine-grade. Solrain-Variante zusaetzlich impraegniert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Alternative Tempotest Parà (IT)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Tempotest Marine 290 g/m2</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Italienisches Premium, 6-J. Farbtreue-Garantie, Teflon EXTREME Finish. Vergleichbar Sauleda.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Auftragsfertigung</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Lokaler Persenningmacher / Sattlerei in PT</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Du lieferst die Stoffrolle, der Fachbetrieb naeht zu. Suchbegriffe PT: 'oficina de toldos', 'velejaria' (Sailmaker), 'persenning'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Aussenflaeche Gesamt</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>~110 m2 (mit Ueberlappung)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Dach: 50 m2 Kegelmantel + 10% Ueberlappung. Wand: 8 x pi x 2,2 m = 55 m2. Plus Verschnitt 15% Reserve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Plane-Lebensdauer</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>10-15 Jahre</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Sauleda/Tempotest mit Schattennetz darueber. OHNE Schattennetz in Algarve: 5-8 Jahre realistic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="8" customHeight="1"/>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Plattform / Foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="33" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Geschraubte Pfahl-Plattform</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Krinner-Schraubpfaehle KSF-M 800mm. Kein Beton. Reversibel. Belueftung darunter verhindert Feuchte+Termiten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Tragwerk</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Doppel-T aus 50x200 mm Kiefer KDI</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Konzentrische Rahmen-Konstruktion + radiale Balken alle 45 Grad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Bodenaufbau (innen nach aussen)</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Estrich-Vlies + Kork 30mm + Laerchen-Deck 27mm</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Trittschall, Kaelte-Pufferung, schoene Optik. Kork = portugiesisches Material par excellence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Diameter</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>8,20 m (10 cm Ueberstand)</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Verhindert Regenwasser-Hochzug ins Innere; passt Plane-Wand-Saum exakt.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Bauteil</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Material/Spezifikation</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Menge</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Einheit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Einzelpreis EUR</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Gesamtpreis EUR</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Bezugsquelle Vorschlag</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Khaana Latten Edelkastanie</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>30x10 mm, getrocknet, gehobelt, 2,1 m Laenge</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1260</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Mil Martins &amp; Irmao (PT-Norden) / Industria de Madeiras / Albano Leite</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>8 Sektionen x ~35 Latten/Sektion. 10% Verschnitt eingerechnet. Wahlweise auch in 30x12 mm fuer mehr Stabilitaet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Khaana Nieten/Bolzen</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>M5 x 30 mm Senkkopf Edelstahl A4 + Hutmuttern</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>350</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Wuerth PT / Bauhaus PT / Schraubenking.de</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Pro Khaana-Kreuzung 1 Bolzen. ~38 Kreuzungen pro Sektion * 8 = 304 + Reserve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Khaana Hanfband / Lederband</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Hanfgurt 25 mm breit ODER Leder-Streifen</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Meter</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>125</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>tipiwakan.com / handweber-PT / Saddlery Lousa</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Optional fuer traditionelle Optik statt Bolzen. Sebastian: Bolzen empfohlen (haltbarer in Salzluft).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Tono - Kronenring fertig</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>1,20 m Durchmesser, 60 Bohrungen für Uni, Eiche/Esche laminiert</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Camping Yurts (UK) / FAMTENTS (CZ) / Adorjan Jurta (HU) / Atilla (HU)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Inkl. Sicherheitslackierung und Bohrungen. Versand DE/HU-&gt;PT ca. 150-300 EUR extra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Tono Versand nach PT</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Spedition Übermass</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Logistik-Anbieter Wahl Lieferant</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Bei Anfrage einkalkulieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Uni Dachstangen Sibir. Laerche</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>30x30 mm gehobelt, 4,0 m Laenge, leicht gebogen</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Holz Schiller AT / Siero Lam (PT) / Holz Possling DE</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>60 + 5 Reserve. Konisch oder gerade. Wenn gerade: muss am unteren Ende leicht angefast werden fuer den Khaana-Sattel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Uni-Befestigung am Tono</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Edelstahl-Niet M6 x 40 mm A4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Wuerth PT / Bauhaus</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Eine Bohrung im Uni-Kopf + Tono-Bohrung verbinden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Uni-Auflage auf Khaana</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Lederband / Hanfschlaufe alle 60 cm an Wandkrone</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Meter</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>150</v>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Sattlerei PT / Lederhandwerk</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>Pro Sektion 8 Uni werden aufgelegt. Bestens: durchgehende Schlaufen-Schnur (Kuriye-Funktion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Kuriye - Spannband Wandkrone</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Polypropylen-Gurt 50 mm, 8 Tonnen Zugfest</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Meter</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Industriebedarf PT / Wuerth / Schraubenking.de</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2 komplette Umrundungen (8m Durchmesser * pi = 25,1 m je Lage). Mit Klemmschnalle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Spannschloesser Edelstahl</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>M10 Spannschloss A4</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Wuerth / Bootsbedarf PT (Acastillaje)</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>An 4 Stellen Spannung einstellbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Tuerrahmen Robinie</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Pfosten 100x100 mm, Sturz 100x150 mm</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Meter</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Holz Henkel AT / Forstamt PT / Holz Schiller</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Trockene Robinie, gehobelt. Alternative PT: Edelkastanie Bohlenware.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>5.1</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Tuerblatt Doppeltuer</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>2x je 90x200 cm Robinie/Eiche mit Doppelverglasung</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Lokale Schreinerei PT (Tischlerei) / Bauhaus IKEA-Tueren als Basis</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Selber bauen oder bei lokalem Tischler in PT in Auftrag geben. UPVC waere guenstiger aber waermer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>5.2</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Tuerbeschlaege Edelstahl A4</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Bandscharniere x 6 + Schloss + Drueckergarnitur</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Wuerth PT / Brico Marche</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>A4 statt A2 wegen Salzluft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Schraubpfaehle Krinner KSF-M</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>M-Profil, 800 mm Laenge, verzinkt</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>280</v>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Krinner GmbH DE / Bauhaus PT / Acreditados.pt</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Statt Beton. 8 Punkte alle 45 Grad auf 8m-Kreis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>6.1</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Tragbalken Kiefer KDI Klasse 4</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>50 x 200 mm, 4,0 m Laenge</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>560</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Leroy Merlin PT / AKI / lokales Saege-werk</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Doppel-T-Rahmen + Radial-Balken. KDI = Kesseldruckimpragniert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>6.2</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Laerchen-Deck T+G</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>27 x 137 mm Nut+Feder, 4 m Laenge</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>1900</v>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Mil Martins / Maderterraneo (ES) / Holz Possling</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>ca. 50 m2 zu verlegen plus 10% Verschnitt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>6.3</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Kork-Daemmung Plattform</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>30 mm gepresst Naturkork</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Amorim Cork (PT national) / Sofalca / Maderterraneo</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Portugiesisches Material par excellence. Zwischen Tragbalken und Decke.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estrich-Vlies + Dampfsperre</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>PE Folie 200 my + Geo-Vlies 300 g/m2</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>200</v>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus PT / AKI</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Unter Plattform gegen aufsteigende Feuchte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Plattform-Schrauben Edelstahl</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Spax A4 5x80 mm + 4x50 mm</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Wuerth PT / Schraubenking.de</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>A4 wegen Salzluft. Pauschal Sortiment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Schafwollfilz Isolena 16 mm</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>100% Schafwolle Ionic Protect, 1,2 m breit</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>105</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>1680</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>ISOLENA AT direkt / baustoffplus.de / DAEMWOOL AT</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Wand 55 m2 + Dach 50 m2 = 105 m2. Bei Bestellung in DE: USt-IdNr nutzen fuer IC-Lieferung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Innenliner Baumwoll-Sergeant</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>200 g/m2, naturweiss/decorativ, 1,5 m breit</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>780</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Toldum.es / Sattlerei PT / Stoffhandel-Industrie</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Wand 55 m2 + Dach 50 m2 - Verschnitt = 65 m2 Stoffbedarf bei Verzug. Wird unterhalb Filz montiert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>8.0</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Membran Solitex Plus / Tyvek Soft</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Diffusionsoffen, wasserdicht, 1,5 m breit</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>690</v>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Pro Clima AT / Tyvek via Bauhaus PT</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Zwischen Filz und Aussenplane. WICHTIG fuer Algarve: verhindert Kondensat in Daemmwolle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>9.0</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Aussenplane MASSANFERTIG</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Sauleda Solar Pro 300 g/m2 / oder Tempotest Marine, Beige/Sand</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Coartal (ES Sauleda Distri) / Lokaler Persenningmacher PT / Yurt Workshop ES (Cadiar)</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Komplett-Set: Dach + Wand + Kuppel-Cover. Inkl. Saeume, Tunnel fuer Spannband, Verstaerkungen an Eaves. Sturm-Kit-Option (Verstaerkte Eckpunkte) +200 EUR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Kuppel-Oberlicht (Polycarbonat)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Klar, oeffenbar, 1,2 m Durchmesser</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>750</v>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus PT / Atilla Jurte (HU) / Custom</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>Wahlweise von Tono-Lieferant gleich mitbestellen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>10.0</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Erdanker Sturm-Kit</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Schraubanker M16 1.000 mm + Stahlseil 6 mm</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Krinner / Wuerth PT</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Algarve-Atlantik OBLIGATORISCH. 8 Anker um Plattform, Seil ueber Dach gespannt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>10.1</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Ratschen-Riemen 5 Tonnen</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Polypropylen 50 mm / 8 m Laenge</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>176</v>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Wuerth PT</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Pro Erdanker 1 Ratsche.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Kaminzug-Durchfuehrung</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Hitze-Manschette Silikon 600 Grad C, Adapter 150 mm</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>280</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Ofenbedarf PT / Heimdesign DE / Bauhaus</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Falls Holzofen geplant. Silikon hitzefest, an Plane verschweissbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Werkzeug-Pauschale</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>siehe Sheet 'DIY 12 Werkzeuge'</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Mietkauf / lokale Vermietung</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>Inkl. Tischkreissaege Miete, Bohrer-Aufsaetze, Hobel-Verleih, Sicherheitsausruestung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Schattennetz Algarve</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>6 m breit, 90% Sonnenschutz</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>240</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Agrar-Kooperative Algarve / Cooperativa Agricola</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>WICHTIG fuer Algarve. Ueber Plane gespannt = verdoppelt Plane-Lebensdauer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>13.1</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Reserve / Unvorhergesehenes</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>10% des Materialbudgets</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>Schrauben-Nachkauf, Reparaturen, Lieferzuschlaege.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="10" t="n"/>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>GESAMTKOSTEN</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>19695</v>
+      </c>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1580,12 +1580,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Bet Yurts (Algarve - Nadav &amp; Noga)</t>
+          <t>Bet Yurts (Algarve - Noga Shimshon)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Portugal (Algarve)</t>
+          <t>Portugal (Algarve, Aljezur)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1595,54 +1595,54 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5/6/7/8/9 m Durchmesser</t>
+          <t>6 m=28m2 / 7 m=38,5m2 / 9 m=63,5m2 (Quote-PDFs Mai 2026)</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Basispreise auf https://www.betyurts.com/pricing (als Bild) - Aufpreis 800 EUR pro zusaetzlicher Oeffnung bestaetigt</t>
+          <t>Jurte netto: 6m=12.600 / 7m=14.400 / 9m=19.800 EUR. Plattform: 6m=6.500 / 7m=7.200 / 9m=11.500 EUR. Zus. Tueren/Fenster: 800 EUR/Stk. Transport zur Aljezur: 6m=700 / 7m=900 / 9m=1.500. Installation: 6m=1.900 / 7m=2.500 / 9m=2.900. Alle Preise zzgl. 23% IVA.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Gitterwand Nordische Kiefer (Wandhoehe 2,20 m), Innenwand 100% Baumwolle, Daemmung 8 cm recyceltes PET-Vlies, Aussenplane Acryl MARINE-GRADE UV-/schimmelfest mit PVC-Schuerze, Plexikuppel oeffenbar, Silikon-Kaminmanschette Standard, Glastuer Zedernholz-Rahmen doppelverglast</t>
+          <t>Quote-PDF nennt nur 'Nordic Pine roof rafters + lattice walls', 'Outer canvas with stove outlet', '80mm Insulation material', 'Inner cotton linen', '1.20m central ring'. KEINE Hersteller-/Markennennung trotz Marketing 'marine-grade' auf Website.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>SEHR GUT FUER ALGARVE-KUESTE: Marine-grade UV-Plane (explizit kuestentauglich), PET-Daemmung (schimmel-/feuchteresistenter als Schafwolle in Salzluft), Kronenring 1,20 m / Hoehe 2,90-3,70 m</t>
+          <t>Mittel-Gut: Pine-Rahmen (NICHT Laerche/Kastanie!). 'Outer canvas' ohne Spezifikation. NUR 2 JAHRE GARANTIE auf Plane + 1 J. Verarbeitung = NICHT marine-grade-Niveau (Sauleda waere 5-10 J. Garantie).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Inland Algarve - Transport+Aufbau gegen Aufpreis (Distanzabhaengig). Vorgefertigte gedaemmte Plattform mit Erdschrauben + Kiefer-Sperrholzboden im Angebot.</t>
+          <t>Inland Algarve, Transport+Aufbau gegen Aufpreis ausgewiesen. Vorgefertigte gedaemmte Plattform mit Erdschrauben + Vinyl-Top-Flooring (kann selbst gebaut werden, dann Plattform-Preis sparen).</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Schreiner Nadav + Produktdesignerin Noga - lebt selbst was sie baut. Standard inkl.: doppelverglaste Glastuer, Plexikuppel, Kaminmanschette. Optionen: 800 EUR/Oeffnung. Kontakt: noga@betyurts.com / +351 961 592 792</t>
+          <t>NIF 307460320 (Empresario em Nome Individual, registriert auf Noga Shimshon). Bank: Privatkonto Noga Shimshon. ZAHLUNG: 50% NICHT-RUECKZAHLBAR upfront, 50% vor Lieferung. AUGUST 2026 SLOT verfuegbar. Werkstatt-Besuch nach 3 Wochen Reise. Kontakt: noga@betyurts.com / +351 961 592 792</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Basispreis aus Web nicht extrahierbar (Bild); Anfrage gestellt, Erwartung 12.000-18.000 EUR fuer 7-9m mit Plattform+Aufbau</t>
+          <t>6m all-in (2 Fenster+Plattform+Transport+Install): ~28.060 / 7m: ~31.940 / 9m: ~44.870 EUR. DOPPELT SO TEUER WIE CASA DOS SONHOS bei kuerzerer Garantie.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos Yurts (Alto Alentejo, Besteiros de Cima/Portalegre)</t>
+          <t>Casa dos Sonhos Yurts (Sarah &amp; Vladimir, Alegrete)</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Portugal (Alto Alentejo)</t>
+          <t>Portugal (Alto Alentejo, Besteiros de Cima 7300-320 Alegrete)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>https://www.casadossonhos.co.uk/copy-of-environmental-policy</t>
+          <t>https://www.casadossonhos.co.uk/  |  https://www.facebook.com/yurtscasadossonhos/</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 (delivered+erected PT)</t>
+          <t>5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 EUR (delivered+erected PT). Konkretes Quote Mai 2026: 6,1m + 2.Tuer 850 + Flue-Kit 100 = 10.650 EUR all-in.</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1667,17 +1667,17 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>Innerhalb Festland-PT INKL. Lieferung+Aufbau im Preis</t>
+          <t>Innerhalb Festland-PT INKL. Lieferung+Aufbau im Preis. Plattform NICHT enthalten (Kunde stellt 'a base').</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>STANDARD inkl.: 1x1 m doppelverglastes Alu-Fenster (9,1m: 120x120cm) ODER Vollglas-UPVC-Tuer, Standardtuer mit Fenster+Holzladen, moderne Daemmung, Innenliner, oeffenbares Kuppel-Oberlicht. Selbsttragend ohne Mittelsaeule, Wand &gt;2 m, Mittelring min. 3,5 m. Solarwerkstatt. OPTIONEN (Preis offen): groessere/Vollhoehe-Fenster, STURM-KIT (storm-prone areas), Extra-Daemmlagen, franz. Doppeltueren 3/4-Glas+Lade, Vollhoehe-UPVC-Doppeltueren, Kaminzug, MEZZANINE-Ebenen</t>
+          <t>Inhaber: Sarah (UK-Englisch) + Vladimir, Tochter 3J, leben in Alegrete. NIPC 260282812 (Empresario em Nome Individual - persoenlicher NIF als Geschaefts-NIPC). Slot Oktober 2026 wurde 15.05.2026 an anderen Kunden vergeben. Naechster Slot: 2027. Zahlung: 1.000 EUR Anzahlung + Restbetrag 2 Monate vor Lieferung (3 Monate beim 9m). Refs: Brett bei Quinta Glamping (https://www.quintaglamping.com), Paula Young verkauft gebrauchte 7,3m (FB 'Paula Vegan Chef')</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>5m: 7.900 / 6,1m: 9.700 / 7,3m: 15.750 / 9,1m: 18.000 EUR alles inkl. PT-Lieferung+Aufbau</t>
+          <t>5m: 7.900 / 6,1m: 9.700 / 7,3m: 15.750 / 9,1m: 18.000 EUR alles inkl. PT-Lieferung+Aufbau. ACHTUNG: 6,1m all-in mit Plattform DIY 4.000 + Schattennetz 240 = 14.890 EUR. STATUS: Oktober 2026 SLOT WEG (15.05.2026), nur 2027 verfuegbar.</t>
         </is>
       </c>
     </row>
@@ -2094,6 +2094,474 @@
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>ca. 6.000-15.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Portugal Yurts (Yonatan / Natural Habitat)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Portugal (Centro)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>https://portugalyurts.com/</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Natural Building Approach: Holz + Lehm + Stroh + lokale Materialien</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Hoch fuer humide Algarve - natuerliche Baustoffe, lokal beschafft, ca. 20 J. Erfahrung Yonatan in EU</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Innerhalb PT - kein Import-Zoll</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>PT-LOKAL-OPTION #3 nach Casa und Bēt. Gruender Yonatan hat 'Natural Habitat'-Hintergrund. Eigenes Tradesmen-Team von Kauf bis Komplettinstallation. Keine oeffentlichen Preise - Direktanfrage erforderlich.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage (Schaetzung 12.000-18.000 EUR fuer 6-7m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>YourTent.com (Praha CZ)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Tschechien (Praha)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yourtent.com/  |  https://cz.yourtent.com/cenik</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>4-8 m, individuell konfigurierbar</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Online-Kalkulator</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Laerchenholz-Rahmen, 50mm Schafwoll-Filz, 180cm Standard-Wandhoehe, franz. Doppeltuer Laerche, Skylight 150/180cm zweischichtig oeffenbar, Ofen-Vorbereitung</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Sehr gut - 5 JAHRE PLANE-GARANTIE (60 Monate fabric warranty), Mediterranean Track Record bis Kanarische Inseln + Polarkreis</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>CZ-&gt;PT 1.500-2.500 EUR Spedition</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>150 Jurten in 12 Jahren gebaut. BESTE LAERCHE-WAHL fuer Algarve nach Casa. Vergleichbar mit Casa-Qualitaet aber laengere Reise. 5-J. Garantie schlaegt Bēt (2 J.).</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage (Schaetzung 12.000-16.000 EUR 6m all-in inkl. Versand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ZenYurts Belgium</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Belgien (Vlaanderen)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>https://zenyurts.be/en/</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>5,80m / 6,80m=35m2 / 7,80m=47m2</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Online transparent</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Schafwoll-Filz 15mm + Baumwoll-Canvas UV-impraegniert, UV-Holz-Oel-Behandlung, UV-Plexikuppel</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Mittel - mongolisch-traditioneller Stil, Plane-Garantie unklar</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>BE-&gt;PT 1.500-2.000 EUR Spedition</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Sehr transparente Online-Preise mit SKU-Codes (z.B. SW10011.1). 7,80m mit Setup+Plattform = ca. 15.800 EUR. Halb so teuer wie Bēt Yurts bei aehnlicher Spec.</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>ca. 14.000-17.000 EUR 6,80m all-in inkl. Versand+Sturm-Kit</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Yurts4ever (Y4E, Transylvania)</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Rumaenien (Siebenbuergen)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>https://yurts4ever.ro/</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>5-8m typisch</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Handgefertigt, traditionelle mongolische Bauweise, ca. 1 Monat Produktion</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>Mittel - kontinentaler Klimaerfahrung, mediterrane Tracks (Italien)</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>RO-&gt;PT 1.500-2.000 EUR Spedition</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Verkauft in RO, HU, DK, IT. Adorján-Klasse Preisniveau erwartbar bei Handwerksqualitaet. Neuer Player.</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage (Schaetzung 8.000-12.000 EUR 6m all-in)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Yurts Hellas (Athens)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Griechenland</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurts-hellas.gr/</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>diverse 4-8m</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Mediterranean climate-experienced</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Sehr gut - direkte mediterrane Klima-Erfahrung</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>GR-&gt;PT 1.800-2.500 EUR Spedition (See/Sammelladung)</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Telefon +30 210 8317431. Konkrete Preise via Anfrage. Versand-Kosten sind der Nachteil vs PT-lokal.</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Tiny Homes Greece</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Griechenland</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.tinyhomes.gr/</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Mediterran, Erfahrung GR+UK</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Sehr gut - 17 Jahre Erfahrung Mittelmeerklima</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>GR-&gt;PT teuer (1.800-2.500 EUR)</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Verkauft Jurten fuer GR und UK Markt seit 17 J. Versand-Kostennachteil vs PT-Lokal.</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Streetgy (AT vertreibt CZ)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Tschechien / vertrieb Oesterreich</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>https://streetgy.at/jurte-kaufen-und-erfahrungen/</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Diverse</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Online-Preisliste pro m2</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Mongolische Jurten via CZ-Hersteller</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Mittel - marketing 'bis zu 30% guenstiger' (gegenueber wem?)</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>CZ-&gt;PT 1.500-2.500 EUR</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Bewerben sich als guenstige Alternative. Preisliste online vorhanden. Garantie unklar. Anfrage lohnt sich evtl.</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Mongolian Magic (Niederlande)</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Niederlande</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>https://mongolianmagic.com/mongolian-magic-ger-yurt/?lang=en</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>diverse 5-8m</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Direktimport aus Mongolei mit EU-Anpassung</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Mittel - mongolische Bauweise, Anpassung an EU-Klima</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>NL-&gt;PT 1.800-2.200 EUR</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Aehnlich Silk Road Yurts. Lokale Service-Vertretung in NL.</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Yin Yang Yurt (Belgium)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Belgien (Brasschaat / Rochefort)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>https://yinyangyurt.com/en/</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>diverse mongolisch</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Mongolische Jurten, Daemmung gegen Kaelte+Naesse</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Mittel - europ. Wettererfahrung</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>BE-&gt;PT ca. 1.500-2.000 EUR</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>EU-angepasste mongolische Jurten. Weniger transparent als ZenYurts.</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2900,812 +3368,1071 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Plane-Fachbetrieb</t>
+          <t>Plane-Algarve-LOKAL</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Lokaler Persenningmacher PT</t>
+          <t>Dune Algarve Sailmakers</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>PT (Vilamoura)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Auftragsnaeherei</t>
+          <t>Bootssegel + Marine-Persenningen + Schatten-Segel; Sauleda-Marine-Acryl</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Suche: 'oficina de toldos Algarve', 'velejaria PT'</t>
+          <t>https://www.dunesailmakers.com/en/</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Innerhalb PT</t>
+          <t>Innerhalb PT (Algarve direkt)</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Du lieferst Stoff, sie naehen. Risiko: noch nie Jurte genaht. Skizzen mitbringen.</t>
+          <t>PRIORITAET #1 FUER JURTEN-COVER-COMMISSION. Beste fachliche Eignung (3D-Persenning-Erfahrung, Sauleda im Sortiment). Persoenlicher Besuch leicht moeglich von Aljezur.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Tono</t>
+          <t>Plane-Algarve-LOKAL</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Camping Yurts</t>
+          <t>Toldos Etapaveloz Lda</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>PT (Loule, seit 2007)</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Tono fertig gebohrt</t>
+          <t>Toldos, Markisen, Sicht-/Schutz-beschattungen Spezialfertigung</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>https://www.campingyurts.com/yurt-parts/</t>
+          <t>https://www.toldosetapaveloz.com/en</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Ja, UK-&gt;PT post-Brexit Zoll</t>
+          <t>Innerhalb PT (naehe Aljezur)</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Pre-drilled, sealed, varnished. Direkt online bestellbar.</t>
+          <t>BACKUP #1: Aelteste Loule-Werkstatt, geographisch am naechsten. Toldos = Acryl-Markisen-Erfahrung = Sauleda-Verarbeitung. Frage: Erfahrung mit 3D-/Jurten-Form?</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Tono</t>
+          <t>Plane-Algarve-LOKAL</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Groovy Yurts (CA, exportiert global)</t>
+          <t>Textilux</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>PT (Algarve)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sibir.-Kiefer Tono Mongolian-style</t>
+          <t>Markisen + Stoff-Sonderanfertigung Veranden/Terrassen</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.groovyyurts.com/accessories-and-add-ons/toono-dome</t>
+          <t>https://www.textilux.com/en/</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Versand teuer</t>
+          <t>Innerhalb PT</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Authentisch mongolisch, eher teuer fuer EU.</t>
+          <t>BACKUP #2: spezialisiert auf grossflaechige Verarbeitung. Sauleda-kompatibel.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Tono</t>
+          <t>Plane-Algarve-LOKAL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>FAMTENTS</t>
+          <t>Toldos Chique</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>PT (Algarve)</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Tschechische Laerche Tono</t>
+          <t>Pergolas, Markisen, Outdoor-Beschattungs-Loesungen massgefertigt</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>https://www.famtents.com/yurts</t>
+          <t>https://toldos-chique.com/awnings/</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Ja, EU-Spedition</t>
+          <t>Innerhalb PT</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>Premium-Hersteller EU, Tono separat anfragen.</t>
+          <t>BACKUP #3: auch automatisierte Markisen, gut etabliert.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Tono</t>
+          <t>Plane-Algarve-LOKAL</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Atilla Jurtak (HU)</t>
+          <t>Toldegarve</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>PT (Algarve)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tono separat moeglich (Anfrage)</t>
+          <t>Markisen vertikal/horizontal manuell/elektrisch</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://jurtak.hu/</t>
+          <t>https://www.toldegarve.pt/en/</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Ja, HU-Versand</t>
+          <t>Innerhalb PT</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Custom in Hartholz. Anfragen ob er nur Tono+Uni verkauft.</t>
+          <t>BACKUP #4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Tono</t>
+          <t>Plane-Algarve-LOKAL</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Adorjan Jurta (HU)</t>
+          <t>algartoldos SOMBRIARTE Lda</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>PT (Algarve)</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Tradi. mongolisch Tono</t>
+          <t>Markisen Herstellung</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>https://adorjan-jurta.hu/</t>
+          <t>https://www.toldosombriarte.com/</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Ja, HU-Versand</t>
+          <t>Innerhalb PT</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Hartholz, traditionell, lange Lieferzeit (bookings 1J voraus).</t>
+          <t>BACKUP #5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Schraubpfaehle</t>
+          <t>Plane-Algarve-LOKAL</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Krinner GmbH</t>
+          <t>Sombra&amp;Constroi</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PT (Portimao)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Schraubpfaehle Marktfuehrer</t>
+          <t>Toldos, Estores, Pergolas</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.krinner.de/</t>
+          <t>Caminho Horta de Sao Francisco 8500-145 Portimao</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Ja, EU-Spedition</t>
+          <t>Innerhalb PT</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>KSF-M Profil 800-1000 mm, alle EU-baurelevanten Zulassungen.</t>
+          <t>BACKUP #6 - in Portimao naehe Aljezur</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Schraubpfaehle</t>
+          <t>Plane-Fachbetrieb-EU</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Stop Schraubfundamente</t>
+          <t>Lokaler Persenningmacher PT (Backup-Suche)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Alternative zu Krinner</t>
+          <t>Auftragsnaeherei</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>https://www.stop-schraubfundamente.de/</t>
+          <t>Suche: 'oficina de toldos Algarve', 'velejaria PT'</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Ja, EU-Spedition</t>
+          <t>Innerhalb PT</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Etwas guenstiger als Krinner.</t>
+          <t>Generelle Suchbegriffe falls obige Liste nicht weiterhilft. Skizzen mitbringen, Maße ueber bereits aufgebautes Skelett nehmen.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Schraubpfaehle</t>
+          <t>Tono</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Bauhaus / Leroy Merlin PT</t>
+          <t>Camping Yurts</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Krinner-Lager+Vertrieb</t>
+          <t>Tono fertig gebohrt</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.bauhaus.pt/  |  https://www.leroymerlin.pt/</t>
+          <t>https://www.campingyurts.com/yurt-parts/</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Innerhalb PT</t>
+          <t>Ja, UK-&gt;PT post-Brexit Zoll</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Lokales Lager, schneller als DE-Direkt.</t>
+          <t>Pre-drilled, sealed, varnished. Direkt online bestellbar.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Beschlaege</t>
+          <t>Tono</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Wuerth Portugal</t>
+          <t>Groovy Yurts (CA, exportiert global)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Industrie-Schrauben/Beschlaege</t>
+          <t>Sibir.-Kiefer Tono Mongolian-style</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>https://www.wurth.pt/</t>
+          <t>https://www.groovyyurts.com/accessories-and-add-ons/toono-dome</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Innerhalb PT, oft Same-Day</t>
+          <t>Versand teuer</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Edelstahl A4 fuer Algarve obligatorisch. Schraubenmusterbox empfehlenswert.</t>
+          <t>Authentisch mongolisch, eher teuer fuer EU.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Beschlaege</t>
+          <t>Tono</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Bauhaus PT</t>
+          <t>FAMTENTS</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>DIY-Sortiment</t>
+          <t>Tschechische Laerche Tono</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.bauhaus.pt/</t>
+          <t>https://www.famtents.com/yurts</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Innerhalb PT</t>
+          <t>Ja, EU-Spedition</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Gut fuer Standard-Sortiment. A4-Schrauben anfragen.</t>
+          <t>Premium-Hersteller EU, Tono separat anfragen.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Beschlaege</t>
+          <t>Tono</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Brico Marche</t>
+          <t>Atilla Jurtak (HU)</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>DIY landesweit</t>
+          <t>Tono separat moeglich (Anfrage)</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>https://www.bricomarche.pt/</t>
+          <t>https://jurtak.hu/</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Innerhalb PT</t>
+          <t>Ja, HU-Versand</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>Bauhaus-Alternative.</t>
+          <t>Custom in Hartholz. Anfragen ob er nur Tono+Uni verkauft.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Beschlaege</t>
+          <t>Tono</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Acastillaje (Bootsbedarf)</t>
+          <t>Adorjan Jurta (HU)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Marine-Edelstahl Spannschloss</t>
+          <t>Tradi. mongolisch Tono</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Suche 'acastillaje algarve'</t>
+          <t>https://adorjan-jurta.hu/</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Lokal</t>
+          <t>Ja, HU-Versand</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Spezialisiert auf Salzluft. Spannschlossglieder, Edelstahl-Karabiner.</t>
+          <t>Hartholz, traditionell, lange Lieferzeit (bookings 1J voraus).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Werkzeug-Verleih</t>
+          <t>Schraubpfaehle</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Bauhaus PT Mietservice</t>
+          <t>Krinner GmbH</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>Tischkreissaege, Bohrer-Profi</t>
+          <t>Schraubpfaehle Marktfuehrer</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>https://www.bauhaus.pt/leihservice</t>
+          <t>https://www.krinner.de/</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Lokal</t>
+          <t>Ja, EU-Spedition</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Tages-/Wochenmiete. Tischkreissaege 25-40 EUR/Tag.</t>
+          <t>KSF-M Profil 800-1000 mm, alle EU-baurelevanten Zulassungen.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Werkzeug-Verleih</t>
+          <t>Schraubpfaehle</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Lokale Aluguer-Equipamentos Algarve</t>
+          <t>Stop Schraubfundamente</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Bau-Maschinen-Verleih</t>
+          <t>Alternative zu Krinner</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Suche 'aluguer equipamentos Algarve'</t>
+          <t>https://www.stop-schraubfundamente.de/</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Lokal</t>
+          <t>Ja, EU-Spedition</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Oft Wochenpakete guenstiger.</t>
+          <t>Etwas guenstiger als Krinner.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Literatur</t>
+          <t>Schraubpfaehle</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Paul King - The Complete Yurt Handbook</t>
+          <t>Bauhaus / Leroy Merlin PT</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>Standard-Werk Bauanleitung</t>
+          <t>Krinner-Lager+Vertrieb</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Amazon / Yurtinfo.org</t>
+          <t>https://www.bauhaus.pt/  |  https://www.leroymerlin.pt/</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>PDF/Print</t>
+          <t>Innerhalb PT</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>ca. 25 EUR. Pflichtlektuere fuer DIY. Kein 8m-Plan, aber Skalierungs-Anleitung.</t>
+          <t>Lokales Lager, schneller als DE-Direkt.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Literatur</t>
+          <t>Beschlaege</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Paul King - Build Your Own Yurt (kostenloses PDF)</t>
+          <t>Wuerth Portugal</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Frueheres Werk, online</t>
+          <t>Industrie-Schrauben/Beschlaege</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://azinelibrary.org/approved/build-your-own-yurt-1.pdf</t>
+          <t>https://www.wurth.pt/</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>PDF kostenlos</t>
+          <t>Innerhalb PT, oft Same-Day</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Aelter aber kostenlos. 3m Yurte als Skalierungs-Basis.</t>
+          <t>Edelstahl A4 fuer Algarve obligatorisch. Schraubenmusterbox empfehlenswert.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Literatur</t>
+          <t>Beschlaege</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>SimplyDifferently Yurt Calculator</t>
+          <t>Bauhaus PT</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>Onlinerechner Bemassung</t>
+          <t>DIY-Sortiment</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>https://simplydifferently.org/Yurt_Notes</t>
+          <t>https://www.bauhaus.pt/</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>kostenlos</t>
+          <t>Innerhalb PT</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>GOLD-STANDARD: Exakte Bohrwinkel, Latten-Anzahlen, Uni-Laengen fuer beliebige Durchmesser.</t>
+          <t>Gut fuer Standard-Sortiment. A4-Schrauben anfragen.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Literatur</t>
+          <t>Beschlaege</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Yurt Forum Community</t>
+          <t>Brico Marche</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>DIY-Erfahrungsaustausch</t>
+          <t>DIY landesweit</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.yurtforum.com/</t>
+          <t>https://www.bricomarche.pt/</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>kostenlos</t>
+          <t>Innerhalb PT</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Stelle Fragen, Bilder, Detail-Probleme.</t>
+          <t>Bauhaus-Alternative.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Literatur</t>
+          <t>Beschlaege</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Doit Yurtself</t>
+          <t>Acastillaje (Bootsbedarf)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>DIY-Schritte, Tipps</t>
+          <t>Marine-Edelstahl Spannschloss</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>https://doityurtself.com/</t>
+          <t>Suche 'acastillaje algarve'</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>kostenlos</t>
+          <t>Lokal</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Schreibblog mit Foto-Doku eines Komplett-Baus.</t>
+          <t>Spezialisiert auf Salzluft. Spannschlossglieder, Edelstahl-Karabiner.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Literatur</t>
+          <t>Werkzeug-Verleih</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Yurt Plans Library DryUrts</t>
+          <t>Bauhaus PT Mietservice</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plaene zum Kauf</t>
+          <t>Tischkreissaege, Bohrer-Profi</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.dryurts.com/yurt-plans.html</t>
+          <t>https://www.bauhaus.pt/leihservice</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>ca. 20-50 USD</t>
+          <t>Lokal</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Mehrere Yurten-Plaene downloadbar.</t>
+          <t>Tages-/Wochenmiete. Tischkreissaege 25-40 EUR/Tag.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t>Werkzeug-Verleih</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Lokale Aluguer-Equipamentos Algarve</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Bau-Maschinen-Verleih</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Suche 'aluguer equipamentos Algarve'</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Lokal</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Oft Wochenpakete guenstiger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Paul King - The Complete Yurt Handbook</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Standard-Werk Bauanleitung</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Amazon / Yurtinfo.org</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>PDF/Print</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>ca. 25 EUR. Pflichtlektuere fuer DIY. Kein 8m-Plan, aber Skalierungs-Anleitung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Paul King - Build Your Own Yurt (kostenloses PDF)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Frueheres Werk, online</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>https://azinelibrary.org/approved/build-your-own-yurt-1.pdf</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>PDF kostenlos</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>Aelter aber kostenlos. 3m Yurte als Skalierungs-Basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SimplyDifferently Yurt Calculator</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Onlinerechner Bemassung</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://simplydifferently.org/Yurt_Notes</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>kostenlos</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>GOLD-STANDARD: Exakte Bohrwinkel, Latten-Anzahlen, Uni-Laengen fuer beliebige Durchmesser.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Yurt Forum Community</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>DIY-Erfahrungsaustausch</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yurtforum.com/</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>kostenlos</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Stelle Fragen, Bilder, Detail-Probleme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Doit Yurtself</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>DIY-Schritte, Tipps</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://doityurtself.com/</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>kostenlos</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Schreibblog mit Foto-Doku eines Komplett-Baus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Literatur</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Yurt Plans Library DryUrts</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Plaene zum Kauf</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>https://www.dryurts.com/yurt-plans.html</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>ca. 20-50 USD</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Mehrere Yurten-Plaene downloadbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>Schattennetz</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Cooperativa Agricola Algarve</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>PT (lokal)</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Agrar-Schattennetz 90%</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Lokal vor Ort suchen z.B. Sao Bras de Alportel, Lagos</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Innerhalb PT</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Wichtigster Algarve-Tipp! 6m Breite Standard, 4-8 EUR/m2.</t>
         </is>
@@ -5486,7 +6213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6122,13 +6849,284 @@
         </is>
       </c>
     </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>NEU MAI 2026: DIY-MODIFY SZENARIO A (CHEAP BASE + PREMIUM UPGRADES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="38" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Konzept</t>
+        </is>
+      </c>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>Skelett guenstig + Plane Premium + lokal verbauen</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Du sparst beim Holzrahmen (Adorjan HU 1.750 EUR fuer 6m), zahlst Premium bei Plane (Sauleda Solar Pro lokal in Algarve gefertigt) und Daemmung (PET-Vlies / Wolle), baust Plattform selbst.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="25" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Adorjan 6m Rahmen (Khaana + Tono + Uni + Tuer)</t>
+        </is>
+      </c>
+      <c r="B56" s="13" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Ungarn, Direktanfrage. Lieferzeit oft 1J Wartezeit aber neuer/aktueller Preis erfragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Versand HU -&gt; Algarve (Sammelladung)</t>
+        </is>
+      </c>
+      <c r="B57" s="13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Spedition uebergross, 2-3 Wochen Lieferzeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="35" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Sauleda Solar Pro Plane BEI LOKALEM ALGARVE-SATTLER</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="n">
+        <v>2200</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>GAME-CHANGER: Dune Algarve Sailmakers in Vilamoura oder Toldos Etapaveloz in Loule. Schaetzung 1.800-2.500 EUR. PERSOENLICHE Auftragsfertigung + lokale Reparatur.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="29" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>PET-Vlies-Daemmung 8 cm (60 m2 Wand+Dach)</t>
+        </is>
+      </c>
+      <c r="B59" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Tobias Tumfart AT 8,16 EUR/m2 netto = 489 EUR fuer 60 m2. Modern, schimmelfest. Vergleichbar Bēt-Yurts-Daemmung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Solitex-Diffusions-Membran</t>
+        </is>
+      </c>
+      <c r="B60" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Pro Clima AT, 115 m2. Verhindert Kondensat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Tuer-Upgrade falls noetig (Glas-Doppeltuer)</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Adorjan-Standard-Tuer eventuell zu einfach - Upgrade pruefen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Plattform DIY (Schraubpfaehle + Holz)</t>
+        </is>
+      </c>
+      <c r="B62" s="13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Vereinfachte Plattform: Krinner-Pfaehle + Kiefer KDI + einfaches Laerchen-Deck. Kork-Daemmung weglassen wenn Budget eng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Sturm-Verankerung Algarve</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="n">
+        <v>400</v>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Erdanker + Ratschen lokal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Schattennetz Algarve</t>
+        </is>
+      </c>
+      <c r="B64" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Lokale Agrar-Kooperative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Reserve / Verschnitt / Schrauben</t>
+        </is>
+      </c>
+      <c r="B65" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66" ht="23" customHeight="1">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>ZWISCHENSUMME SZENARIO A</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="n">
+        <v>10690</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>OHNE Werkzeugkosten (Sebastian hat ggf. bereits Werkzeug oder mietet)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Werkzeug-Block bei DIY</t>
+        </is>
+      </c>
+      <c r="B67" s="13" t="n">
+        <v>1378</v>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Wenn neu zu beschaffen, siehe Sheet DIY 12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="27" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL SZENARIO A (mit Werkzeug)</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="n">
+        <v>12068</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>NEU EMPFEHLUNG #1 SEIT CASA-SLOT WEG: ca. 11.000-12.500 EUR all-in fuer 6m Algarve-Premium-Setup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="8" customHeight="1"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>VERGLEICH SZENARIO A vs CASA 2027er Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>DIY Modify Szenario A 6m</t>
+        </is>
+      </c>
+      <c r="B71" s="13" t="n">
+        <v>10690</v>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Material+Versand. Ohne Werkzeug-Kauf (haben oder mieten).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="25" customHeight="1">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Casa 6,1m (2027 Slot)</t>
+        </is>
+      </c>
+      <c r="B72" s="13" t="n">
+        <v>14890</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>9.700 Casa + 4.000 Plattform DIY + 240 Schattennetz + 950 Optionen (Tuer/Kamin).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>ERSPARNIS SZENARIO A</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="n">
+        <v>-4200</v>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>ca. 4.000-4.500 EUR weniger als Casa 2027, mit objektiv besseren Materialien (Sauleda Solar Pro vs unspezifiziertes Casa-Canvas). Du gibst Casa's 10-J. UV-Garantie auf, gewinnst dafuer Sauleda-Marken-Garantie (5-10 J. je nach Hersteller) + sofortige Verfuegbarkeit + lokale Reparatur-Quelle.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A70:C70"/>
     <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A54:C54"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6141,7 +7139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6385,64 +7383,64 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Kleinanzeigen - Jurte Suche</t>
+          <t>Paula Young (FB 'Paula Vegan Chef') - gebrauchte Casa-Jurte 7,3m</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>kleinanzeigen.de</t>
+          <t>Facebook (Direktverkauf)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Deutschland weit</t>
+          <t>Algarve / Monchique-Umgebung</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>42 m² (7,3 m / 24 ft Casa dos Sonhos)</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1.000-15.000</t>
+          <t>Anfrage (Schaetzung 8.000-11.000 EUR = 50-70% vom Neupreis 15.750)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Neu bis stark gebraucht</t>
+          <t>Gebraucht direkt vom Eigentuemer</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.kleinanzeigen.de/s-jurte/k0</t>
+          <t>Facebook-Suche 'Paula Vegan Chef' - kein Direktlink. Sarah von Casa kann Einfuehrung machen.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Ja - Spedition 500-1.500 EUR</t>
+          <t>Inland Algarve, Transport ca. 500-1.000 EUR</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Marktplatz, wechselnde Angebote, regelmaessig pruefen</t>
+          <t>TOP-EMPFEHLUNG seit Casa-Slot weg: gebrauchte Casa-Qualitaet, physisch verifizierbar, sofortige Verfuegbarkeit, kein Vorauszahlungs-Risiko. Wichtige Fragen: Alter? Zustand Plane/Filz? Grund Verkauf? Algarve-Erfahrung mit Sommer/Winter.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>eBay.de Jurten Kategorie</t>
+          <t>Kleinanzeigen - Jurte Suche</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>eBay.de</t>
+          <t>kleinanzeigen.de</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Deutschland weit</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -6452,44 +7450,44 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>200-10.000+</t>
+          <t>1.000-15.000</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Neu bis stark gebraucht</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebay.de/b/Jurte-Zelt/bn_7005694261</t>
+          <t>https://www.kleinanzeigen.de/s-jurte/k0</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Versand variiert</t>
+          <t>Ja - Spedition 500-1.500 EUR</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Auch Pfadfinder-Jurten (gross, billig, aber Plane nicht UV-fest)</t>
+          <t>Marktplatz, wechselnde Angebote, regelmaessig pruefen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>eBay.co.uk Yurt</t>
+          <t>eBay.de Jurten Kategorie</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>eBay UK</t>
+          <t>eBay.de</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -6499,54 +7497,54 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1.500-12.000</t>
+          <t>200-10.000+</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Gebraucht</t>
+          <t>Neu/gebraucht</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.co.uk/sch/i.html?_nkw=yurt</t>
+          <t>https://www.ebay.de/b/Jurte-Zelt/bn_7005694261</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Ja - Brexit-Zoll bei Import nach PT (~7% Zoll + 23% IVA)</t>
+          <t>Versand variiert</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Brexit verteuert UK-Importe stark</t>
+          <t>Auch Pfadfinder-Jurten (gross, billig, aber Plane nicht UV-fest)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>LeBonCoin Yourte</t>
+          <t>eBay.co.uk Yurt</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>leboncoin.fr</t>
+          <t>eBay UK</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Frankreich (variable)</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>10-50 m2</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1.500-20.000</t>
+          <t>1.500-12.000</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -6556,44 +7554,44 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>https://www.leboncoin.fr/ck/ventes_immobilieres/yourte</t>
+          <t>https://www.ebay.co.uk/sch/i.html?_nkw=yurt</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Ja - Spedition FR-&gt;PT 800-1.500 EUR</t>
+          <t>Ja - Brexit-Zoll bei Import nach PT (~7% Zoll + 23% IVA)</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Beispiel: 6m yourte mit Wollisolierung gelistet</t>
+          <t>Brexit verteuert UK-Importe stark</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Wallapop Yurtas</t>
+          <t>LeBonCoin Yourte</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>wallapop.com</t>
+          <t>leboncoin.fr</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Frankreich (variable)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>10-50 m2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5.000-25.000</t>
+          <t>1.500-20.000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -6603,29 +7601,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://es.wallapop.com/muebles-deco-y-jardin/yurtas</t>
+          <t>https://www.leboncoin.fr/ck/ventes_immobilieres/yourte</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Ja - ES-&gt;PT guenstig 500-1.000 EUR</t>
+          <t>Ja - Spedition FR-&gt;PT 800-1.500 EUR</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9 Eintraege typischerweise gelistet</t>
+          <t>Beispiel: 6m yourte mit Wollisolierung gelistet</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Milanuncios Yurta</t>
+          <t>Wallapop Yurtas</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>milanuncios.com</t>
+          <t>wallapop.com</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -6635,59 +7633,59 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>diverse 40-80 m2</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>22.500-42.000</t>
+          <t>5.000-25.000</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Gebraucht</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>https://www.milanuncios.com/anuncios/yurt-yurta.htm</t>
+          <t>https://es.wallapop.com/muebles-deco-y-jardin/yurtas</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Ja - ES-&gt;PT guenstig 500-1.000 EUR</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Komplett ausgestattet 27.500 EUR, ohne Moebel 22.500 EUR (Beispiel)</t>
+          <t>9 Eintraege typischerweise gelistet</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>OLX Portugal yurts (Kategorie-Uebersicht)</t>
+          <t>Milanuncios Yurta</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>olx.pt</t>
+          <t>milanuncios.com</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>diverse 40-80 m2</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>variabel</t>
+          <t>22.500-42.000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -6697,24 +7695,24 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/</t>
+          <t>https://www.milanuncios.com/anuncios/yurt-yurta.htm</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Ja - innerhalb PT</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>INLAND PT - keine Zoll, kein Auslandsversand</t>
+          <t>Komplett ausgestattet 27.500 EUR, ohne Moebel 22.500 EUR (Beispiel)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>OLX PT: Tenda Yurt Original Quirguistao (Palmela)</t>
+          <t>OLX Portugal yurts (Kategorie-Uebersicht)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -6724,190 +7722,190 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>PT - Palmela (Setubal)</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>28 m2 (ca. 6 m Durchmesser, 30 Personen)</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Anfrage</t>
+          <t>variabel</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Neu/handgefertigt (Originalimport Issyk-Kul Quirguistao)</t>
+          <t>Neu/gebraucht</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/d/anuncio/tenda-yurt-original-do-quirguisto-yurt-tent-original-from-kyrgystan-IDHEwz9.html</t>
+          <t>https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Ja - PT-inland, Versand EXTRA (Region Lissabon)</t>
+          <t>Ja - innerhalb PT</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Marke 'Yourta', Modell 'Serenity'. Komplette Originalausstattung: Schilf-Geflecht, Wolle/Filz, Shyrdak-Teppich, Baskur-Band, Korpe-Kissen, geschnitzte Holztuer. Hand-Applikation. Keine Baugenehmigung noetig.</t>
+          <t>INLAND PT - keine Zoll, kein Auslandsversand</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Yurt Workshop Secondhand</t>
+          <t>OLX PT: Tenda Yurt Original Quirguistao (Palmela)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>yurtworkshop.com (Spanien)</t>
+          <t>olx.pt</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Spanien Granada</t>
+          <t>PT - Palmela (Setubal)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5-7m</t>
+          <t>28 m2 (ca. 6 m Durchmesser, 30 Personen)</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3.000-10.000</t>
+          <t>Anfrage</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Gebraucht (vom Hersteller)</t>
+          <t>Neu/handgefertigt (Originalimport Issyk-Kul Quirguistao)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.yurtworkshop.com/Buy_Your_Yurt/Second-Hand-Yurts-For-Sale.html</t>
+          <t>https://www.olx.pt/d/anuncio/tenda-yurt-original-do-quirguisto-yurt-tent-original-from-kyrgystan-IDHEwz9.html</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Ja - ES-&gt;PT 600-1.200 EUR</t>
+          <t>Ja - PT-inland, Versand EXTRA (Region Lissabon)</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Vom Hersteller selbst - Qualitaet gepruef</t>
+          <t>Marke 'Yourta', Modell 'Serenity'. Komplette Originalausstattung: Schilf-Geflecht, Wolle/Filz, Shyrdak-Teppich, Baskur-Band, Korpe-Kissen, geschnitzte Holztuer. Hand-Applikation. Keine Baugenehmigung noetig.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Casa Dos Sonhos Secondhand</t>
+          <t>Yurt Workshop Secondhand</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Facebook Casa Dos Sonhos</t>
+          <t>yurtworkshop.com (Spanien)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Portugal (Alentejo)</t>
+          <t>Spanien Granada</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>5-7m</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Anfrage</t>
+          <t>3.000-10.000</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Gebraucht direkt vom Eigentuemer</t>
+          <t>Gebraucht (vom Hersteller)</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/yurtscasadossonhos/posts/3660919220624833/</t>
+          <t>https://www.yurtworkshop.com/Buy_Your_Yurt/Second-Hand-Yurts-For-Sale.html</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Ja - inland PT</t>
+          <t>Ja - ES-&gt;PT 600-1.200 EUR</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Hersteller direkt, ggf. Garantie</t>
+          <t>Vom Hersteller selbst - Qualitaet gepruef</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Yurt Market (worldwide)</t>
+          <t>Casa Dos Sonhos Secondhand</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>yurtmarket.com</t>
+          <t>Facebook Casa Dos Sonhos</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Portugal (Alentejo)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>variabel</t>
+          <t>Anfrage</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Gebraucht direkt vom Eigentuemer</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.yurtmarket.com/</t>
+          <t>https://www.facebook.com/yurtscasadossonhos/posts/3660919220624833/</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Versand variiert je Anbieter</t>
+          <t>Ja - inland PT</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Welt-Marktplatz</t>
+          <t>Hersteller direkt, ggf. Garantie</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Yurt Forum Classifieds</t>
+          <t>Yurt Market (worldwide)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>yurtforum.com</t>
+          <t>yurtmarket.com</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -6927,39 +7925,39 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Gebraucht</t>
+          <t>Neu/gebraucht</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>https://www.yurtforum.com/classifieds/</t>
+          <t>https://www.yurtmarket.com/</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Versand variiert</t>
+          <t>Versand variiert je Anbieter</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Community-Marktplatz, oft USA-fokussiert</t>
+          <t>Welt-Marktplatz</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Groovy Yurts Clearance</t>
+          <t>Yurt Forum Classifieds</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>groovyyurts.com</t>
+          <t>yurtforum.com</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Kanada/USA</t>
+          <t>International</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -6969,72 +7967,119 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>USD 2.790-18.950</t>
+          <t>variabel</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Restposten/leicht gebraucht</t>
+          <t>Gebraucht</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.groovyyurts.com/catalogue-clearance-and-sale</t>
+          <t>https://www.yurtforum.com/classifieds/</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Nein - hauptsaechlich Nordamerika; Versand teuer</t>
+          <t>Versand variiert</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Eher fuer US/CA - hohe Versandkosten nach EU/PT</t>
+          <t>Community-Marktplatz, oft USA-fokussiert</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
+          <t>Groovy Yurts Clearance</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>groovyyurts.com</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Kanada/USA</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>USD 2.790-18.950</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Restposten/leicht gebraucht</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.groovyyurts.com/catalogue-clearance-and-sale</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Nein - hauptsaechlich Nordamerika; Versand teuer</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>Eher fuer US/CA - hohe Versandkosten nach EU/PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Facebook Marketplace EU</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>facebook.com/marketplace</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Diverse EU</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>diverse</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>variabel</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Gebraucht</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.facebook.com/marketplace/category/search/?query=yurt</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Regional pruefen</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>Lokale Suche pro Land empfohlen</t>
         </is>
@@ -7465,7 +8510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7514,27 +8559,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos Yurts (Alto Alentejo)</t>
+          <t>DIY Modify Szenario A (Adorjan-Rahmen + Algarve-Sauleda-Sattler)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Hersteller PT - lokale Spitzenoption (BESTAETIGTE PREISE)</t>
+          <t>DIY-Hybrid - lokaler PT-Sattler + HU-Rahmen</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 EUR delivered+erected</t>
+          <t>ca. 10.300-11.000 EUR all-in (6m)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>BESTPREIS FUER KLEINE+MITTLERE GROESSEN MIT KLIMA-GARANTIE: 6,1m bei 9.700 EUR all-in (Lieferung+Aufbau PT inkl.) ist im Algarve-Markt kaum zu unterbieten. 10 Jahre UV-Garantie SCHRIFTLICH auf Aussenhuelle, kein Verrotten/Schimmel, keine Nachbehandlung noetig. SELBSTTRAGEND ohne Mittelsaeule, Waende &gt;2 m, Mittelring 3,5 m -&gt; super geraeumig. STANDARD inkl.: doppelverglastes Alu-Fenster oder Vollglas-UPVC-Tuer, Standardtuer mit Fenster+Laden, moderne Daemmung, Innenliner, oeffenbares Kuppel-Oberlicht, klima-angepasste Aussenhuelle. Portugiesisches Holz, Solarwerkstatt in Alto Alentejo (Portalegre). KEIN Import-Zoll/IVA, kein Versandstress. Optionen verfuegbar: Sturm-Kit (Algarve!), Vollhoehe-Fenster, Extra-Daemmung, franz. Doppeltueren, Kaminzug, MEZZANINE-Ebenen. HINWEIS 7,3m und 9,1m: Preis-Sprung ueberproportional - 6,1m bietet bestes EUR/m2.</t>
+          <t>NEUER SPITZENREITER seit Casa-Slot weg: Adorjan 6m Rahmen 1.750 + Versand 1.200 + Sauleda Marine-Acryl bei lokalem Algarve-Sattler 1.800-2.500 + PET-Daemmung 500 (Tobias Tumfart AT, 8,16€/m²) + Solitex 500 + Plattform DIY 3.000 + Sturm-Kit 400 + Schattennetz 240 + Reserve 500. PT-LOKALER SATTLER (z.B. Dune Algarve Sailmakers in Vilamoura) ist der Game-Changer: Sauleda Solar Pro Acryl ist objektiv BESSER als unspezifiziertes Casa-Canvas. 4.000-5.000 EUR Ersparnis vs Casa Wartezeit 2027. Sofortige Verfuegbarkeit. Volle Materialkontrolle. Risiko: Selbstaufbau-Skill, Maßabstimmung Rahmen-&gt;Plane, keine Komplett-Garantie.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.casadossonhos.co.uk/copy-of-environmental-policy  |  https://www.facebook.com/yurtscasadossonhos/</t>
+          <t>https://adorjan-jurta.hu/  |  https://www.dunesailmakers.com/</t>
         </is>
       </c>
     </row>
@@ -7544,27 +8589,27 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Bet Yurts</t>
+          <t>Paula Young - gebrauchte Casa-Jurte 7,3m</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Hersteller PT (Algarve direkt)</t>
+          <t>Used-Markt (Algarve direkt)</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ca. 10.000-15.000 (Anfrage)</t>
+          <t>Schaetzung 8.000-11.000 EUR + Transport 1.000</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>DIREKT IM ALGARVE: Schreiner+Designerin (Nadav &amp; Noga) bauen vor Ort, kennen das Klima persoenlich. Modern, helle Doppelglas-Tueren, modular 5-9m. Kein Versand-Risiko, kein Zoll, schnelle Wartung/Reparatur. Lokales Holz. Inkl. Plattform-Transport bei Anfrage.</t>
+          <t>ALGARVE-LEAD von Casa-Sarah selbst empfohlen: Paula Young (FB 'Paula Vegan Chef') verkauft 7,3m Casa-Jurte (42m²). Gebrauchte Casa-Qualitaet mit Original-Garantie-Resten. PHYSISCH VERIFIZIERBAR vor Kauf, kein Vorauszahlungs-Risiko, sofort verfuegbar, GROESSER als Casa 6,1m. Wichtige Pruefpunkte: Alter Plane (10-J. Casa-Garantie laeuft mit), Zustand Filz/Holz, Grund Verkauf, Algarve-Praxiserfahrung. Kontakt ueber Facebook-Suche oder Einfuehrung via Sarah Casa.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>https://www.betyurts.com/</t>
+          <t>Facebook: 'Paula Vegan Chef' / Sarah Casa als Vermittler</t>
         </is>
       </c>
     </row>
@@ -7574,27 +8619,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Yourtepoque (6,5m oder 8m)</t>
+          <t>Yurt Made in Portugal (Loures, OLX-Hersteller)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Hersteller FR - bestes Preis-Leistung</t>
+          <t>Hersteller PT (Lissabon-Region)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8.680 (6,5m) / 11.820 (8m)</t>
+          <t>5m 6.900 / 6m 8.400 / 7-8m Anfrage</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>TRANSPARENTE PREISE ONLINE - Yourtepoque listet alle Preise unverbluemt. Ehrliche europ. Bauweise, Mittelpreis-Klasse, im Budget. Mit Schatten-Netz (siehe Hinweise) klimatauglich. 6,5m = 33m2 fuer 8.680 EUR ist Top-Wert.</t>
+          <t>PT-LOKAL ALTERNATIVE zu Casa: junger Hersteller seit 2020 bei Lissabon. Kein Import-Zoll, kein Versandstress. Preise transparent auf OLX. Klima-Garantie &amp; UV-Spezifikation noch zu erfragen! Anfrage dringend lohnt sich, bevor andere Optionen verfolgt werden. Kontakt via OLX.pt.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://yourtepoque.com/</t>
+          <t>https://www.olx.pt/d/anuncio/yurt-made-in-portugal-IDIyzPL.html</t>
         </is>
       </c>
     </row>
@@ -7604,27 +8649,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yurt Workshop Spain (Cadiar)</t>
+          <t>YourTent.com CZ (Praha)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Hersteller ES (Andalusien)</t>
+          <t>Hersteller CZ - 5J-Plane-Garantie</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>ca. 8.000-13.000 nach Spezifikation</t>
+          <t>Schaetzung 12.000-16.000 EUR 6m inkl. Versand</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>NACHBARLAND-HERSTELLER: Rob Matthews seit 2004, baut in Alpujarras (mediterranes Klima vergleichbar Algarve). Spanisches Kastanienholz, flammenhemmendes Canvas. 3 Levels: standard/isoliert/Glaswand. Versand ES-&gt;PT guenstig (~600-1.200 EUR). Lokale Klima-Kompetenz.</t>
+          <t>BESTE PLANE-GARANTIE NACH CASA: 5 JAHRE Plane-Garantie (60 Monate). 150 Jurten in 12 Jahren gebaut, MEDITERRANEAN TRACK RECORD bis Kanarische Inseln + Polarkreis. LAERCHENHOLZ-Rahmen (Algarve-optimal). 180cm Standard-Wandhoehe, 50mm Schafwoll-Filz, franz. Doppeltuer Laerche, Skylight 150/180cm, Ofen-Vorbereitung. Online-Kalkulator + Anfrage. Versand CZ-&gt;PT ca. 1.500-2.500 EUR.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>http://yurtworkshop.es/</t>
+          <t>https://www.yourtent.com/</t>
         </is>
       </c>
     </row>
@@ -7634,27 +8679,57 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Jurte24 6m (Hr. Wendt)</t>
+          <t>Casa dos Sonhos Yurts (2027er Slot)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hersteller DE - mongolisch, deutsche Qualitaet</t>
+          <t>Hersteller PT - 10-J. UV-Garantie SCHRIFTLICH</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12.050 EUR (komplett, inkl. 19% MwSt)</t>
+          <t>6,1m 9.700 / 7,3m 15.750 EUR delivered+erected PT</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>DEUTSCHE QUALITAET: Festpreis komplett ausgestattet, winterfest, wasserdicht, 100% Schafwoll-Filz, 170 cm Wandhoehe. Im Budget mit Spedition (~13.500 EUR). Ergaenze mit Schatten-Netz fuer PT-Sommer.</t>
+          <t>BLEIBT TOP-OPTION FUER LAENGEREN ZEITHORIZONT (2027+): Oktober 2026-Slot wurde 15.05.2026 an anderen Kunden vergeben. Naechster verfuegbarer Slot in 2027. Trotzdem das technisch beste Angebot fuer Algarve mit 10 J. UV-Garantie auf Plane, alles inkl. Lieferung+Aufbau in Festland-PT, portugiesische Materialien. Sarah &amp; Vladimir (UK-Familien-Betrieb) etabliert seit Jahren in Alegrete. NIPC: Empresario em Nome Individual. Verifizieren via Brett bei Quinta Glamping + Werkstatt-Besuch.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.jurte24.de/</t>
+          <t>https://www.casadossonhos.co.uk/  |  https://www.facebook.com/yurtscasadossonhos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Bēt Yurts (August 2026 Slot)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Hersteller PT (Algarve direkt)</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>6m 28.060 / 7m 31.940 / 9m 44.870 EUR all-in</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>ALGARVE-LOKAL ABER PREMIUM-PREIS: Konkretes Quote-PDF erhalten. Halb so teuer waere besser - DOPPELT SO TEUER wie Casa. 50% NICHT-RUECKZAHLBAR upfront, nur 2 JAHRE Plane-Garantie. Material laut Quote: 'Nordic Pine + Outer canvas + 80mm Insulation' OHNE Marken-/Herstellernennung (Marketing 'marine-grade' nicht im Quote bestaetigt). AUGUST 2026 Slot verfuegbar - Zeit-Vorteil. Nur empfehlenswert wenn andere Optionen ausfallen + August-Lieferung zwingend.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.betyurts.com/</t>
         </is>
       </c>
     </row>
@@ -8306,7 +9381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -9163,7 +10238,7 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="54" customHeight="1">
+    <row r="86" ht="36" customHeight="1">
       <c r="A86" s="8" t="inlineStr">
         <is>
           <t>Bewertung</t>
@@ -9171,11 +10246,11 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>TOP-EMPFEHLUNG #1 BESTAETIGT - bei 6,1m fuer 9.700 EUR all-in nicht zu schlagen, einzigartige 10-J. UV-Garantie schriftlich, lokale Produktion, Lieferung+Aufbau inkl., portugiesische Materialien, kein Import-Risiko, kein Versandstress.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="34" customHeight="1">
+          <t>BLEIBT TOP-OPTION TECHNISCH - aber STATUS 15.05.2026: Oktober-2026-Slot wurde an anderen Kunden vergeben. Naechster Slot 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="47" customHeight="1">
       <c r="A87" s="8" t="inlineStr">
         <is>
           <t>Sweet Spot</t>
@@ -9183,19 +10258,67 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>6,1m / 30 m2 zu 9.700 EUR - DEUTLICH UNTER 15k Budget, laesst Raum fuer Sturm-Kit + Kaminzug + Plattform-Vorbereitung</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="57" customHeight="1">
+          <t>6,1m / 30 m2 zu 9.700 EUR delivered+erected. Konkretes Quote 15.05.2026: 9.700 Basis + 850 Extra-Tuer + 100 Flue-Kit = 10.650 EUR. + Plattform DIY 4.000 + Schattennetz 240 = ~14.890 EUR all-in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="51" customHeight="1">
       <c r="A88" s="8" t="inlineStr">
         <is>
+          <t>Konkretes Angebot in der Konversation</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>6,1m mit 2.Tuer und Flue-Kit = 10.650 EUR; 1.000 EUR Anzahlung sichert Slot, 9.650 EUR Restbetrag 1. August 2026 zu zahlen (= 2 Monate vor Lieferung). Lieferung war 2. Oktoberwoche 2026 vorgesehen - SLOT INZWISCHEN WEG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="58" customHeight="1">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>Inhaber-Hintergrund</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>Sarah (englisch) + Vladimir (Mann) + Tochter 3J, leben in Alegrete. Sarah operiert die Mail-Kommunikation. Auch ueber Casa dos Sonhos Cottage (Ferienvermietung) seit Jahren in PT etabliert - dokumentiert auf babyfriendlyboltholes, homeexchange, peoplelikeus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="60" customHeight="1">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>NIPC-Status</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>260282812 - Anfangsziffer '26' = persoenlicher NIF, der als NIPC verwendet wird = 'Empresario em Nome Individual' (Einzelunternehmer ohne Haftungsbeschraenkung). Sarah oder Vladimir persoenlich als Geschaeftsbetreiber. Standard fuer PT-Kleinhandwerker, kein Showstopper, aber kein Lda-Schutz fuer Kaeufer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>Verifikations-Optionen</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Brett bei Quinta Glamping (https://www.quintaglamping.com/) hat eine Casa-Jurte als Lake View Yurt - Uebernachtung dort moeglich zur Casa-Qualitaets-Pruefung. Paula Young (FB 'Paula Vegan Chef') verkauft eine gebrauchte 7,3m Casa-Jurte in der Algarve - kann besichtigt werden + Algarve-Praxiserfahrung in 1-2 Std Gespraech erhalten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="60" customHeight="1">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
           <t>Naechster Schritt</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>Konkretes schriftliches Angebot fuer 6,1m oder 7,3m inkl. Sturm-Kit + Kaminzug + Mezzanine-Option (falls fuer 7,3m relevant) anfragen. Zahlungskonditionen klaeren (Etappenzahlung). Show-Yurt-Besuch Portalegre verhandeln. Slot 2026 bestaetigen (nicht 2027).</t>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>1) Casa: Antwort auf 'Slot-weg'-Mail abwarten - 2027er-Optionen + ggf. Vermittlung Paula Young. 2) Quinta Glamping Lake View Yurt fuer Naechtigung buchen (Casa-Qualitaets-Test). 3) Paula Young direkt anschreiben - moeglicherweise sofortige Algarve-Loesung. 4) Parallel DIY-Modify-Szenario A verfolgen (siehe Sheet DIY Bauplan). 5) Wenn alle obigen ausfallen: 2027-Slot bei Casa annehmen oder Bēt August.</t>
         </is>
       </c>
     </row>
@@ -11040,7 +12163,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Sauleda Solar Pro 300 g/m2 / oder Tempotest Marine, Beige/Sand</t>
+          <t>Sauleda Solar Pro 290-340 g/m2 / oder Tempotest Marine, Beige/Sand</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
@@ -11052,19 +12175,19 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3500</v>
+        <v>2200</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3500</v>
+        <v>2200</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Coartal (ES Sauleda Distri) / Lokaler Persenningmacher PT / Yurt Workshop ES (Cadiar)</t>
+          <t>PRIORITAET: Dune Algarve Sailmakers (Vilamoura) / Toldos Etapaveloz (Loule) / Textilux (Algarve) / Toldos Chique / Toldegarve / SOMBRIARTE / Sombra&amp;Constroi (Portimao). BACKUP: Yurt Workshop ES (Cadiar) / Atilla HU.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Komplett-Set: Dach + Wand + Kuppel-Cover. Inkl. Saeume, Tunnel fuer Spannband, Verstaerkungen an Eaves. Sturm-Kit-Option (Verstaerkte Eckpunkte) +200 EUR.</t>
+          <t>GAME-CHANGER ERKENNTNIS: Lokale Algarve-Sattler arbeiten taeglich mit Sauleda Marine-Acryl, ideal fuer Jurten-Cover-Auftrag. Schaetzung 6m: 1.800-2.500 EUR (Material+Verarbeitung). Komplett-Set Dach+Wand+Kuppel-Cover, inkl. Saeume, Tunnel fuer Spannband, Verstaerkungen Eaves. PERSOENLICHER BESUCH MOEGLICH = Maßabstimmung perfekt + lokale Reparatur-Quelle.</t>
         </is>
       </c>
     </row>
@@ -11367,7 +12490,7 @@
         </is>
       </c>
       <c r="G32" s="12" t="n">
-        <v>19695</v>
+        <v>18395</v>
       </c>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -20,6 +20,7 @@
     <sheet name="DIY 11 Arbeitsschritte" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="DIY 12 Werkzeuge" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="DIY 13 Kostenrechnung" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="DIY 14 8m Modify Kalk" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7133,6 +7134,616 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>DIY 8m Yurt fuer Algarve - 'Modify Cheap Base' mit Algarve-Sattler (Sebastians Praeferenz Mai 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>AUSGANGSLAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sebastians Vorgabe</t>
+        </is>
+      </c>
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <t>8 m Durchmesser (50 m2)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Begrundung: deutlich groesser als Casa 7,3m (42m2). Wohnflaeche-Plus = 8 m2 (ca. ein Mini-Schlafalkoven).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Verfuegbare 8m-Anbieter</t>
+        </is>
+      </c>
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Yourtepoque, Atilla, Adorjan, jurte24, YourTent CZ, Yurts4ever, DIY</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Casa und Bēt Yurts haben KEIN 8m im Sortiment. Casa naechste: 7,3m oder 9,1m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="29" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Budget-Realitaet</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>8m all-in ca. 17.000-22.000 EUR</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Original Budget 15.000 EUR reicht NICHT fuer 8m. Bei 8m muss Budget auf 17-18k flexen ODER signifikante Kompromisse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="8" customHeight="1"/>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>KONZEPT DIY-MODIFY 8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="37" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Idee</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>Cheap Frame (HU) + Premium Plane (Sauleda lokal Algarve) + Selbst-Aufbau</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Wiederholt das 6m-Schema von Sheet 13, hochskaliert auf 8m. Hauptvorteile: lokaler Algarve-Sattler fuer Reparatur, volle Materialkontrolle, sofortige Verfuegbarkeit, kein Slot-Warten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Anbieter Frame</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Adorjan Jurta HU / Atilla HU / Yurts4ever RO</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Anfragen parallel. Adorjan + Atilla aktuell mit Frame-only-Anfrage angeschrieben Mai 2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="23" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Anbieter Plane</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Dune Algarve Sailmakers (Vilamoura) / Toldos Etapaveloz (Loule) / Textilux</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>3 Anfragen Mai 2026 abgesendet. Erwartung: 1-3 Wochen Antwortzeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="8" customHeight="1"/>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>MATERIAL-KOSTEN 8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Adorjan 8m Frame-only (Khaana + Tono + Uni + Tuer)</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>SCHAETZUNG (6m bei 1.750 - 8m Skalierung mit Material-Mehrbedarf + groesserem Tono). Konkreter Preis ueber laufende Anfrage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Versand HU -&gt; Algarve 8m (heavier)</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Spedition Uebergross, 2-3 Wochen. 8m benoetigt groesseres Fahrzeug als 6m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="49" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sauleda Solar Pro Plane 8m (~150 m2 Stoff)</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>DIE GROESSTE POSITION: 8m hat ca. 60 m2 Dach (Kegelmantel) + 50 m2 Wand + Verschnitt + Saum-/Tunnel-Verstaerkung = ca. 150 m2 Stoffbedarf. Bei 25-30 EUR/m2 + 50-100% Verarbeitungs-Aufschlag = 4.000-5.000 EUR komplett massgefertigt. Komplettes Set: Dach + Wand + Kuppel-Cap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>PET-Vlies-Daemmung 8 cm (~110 m2 Wand+Dach)</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>900</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Tobias Tumfart AT 8,16 EUR/m2 netto = 898 EUR fuer 110 m2. Modern, schimmelfest fuer Salzluft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Solitex Diffusions-Membran</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>700</v>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Pro Clima AT. ~120 m2 inkl. Ueberlappung. Verhindert Kondensat in Daemmwolle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="29" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Innenliner Baumwolle (~115 m2 Stoff)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>1380</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>200 g/m2 Sergeant fuer Aesthetik + Daemmwolle-Halt. Beim selben Sattler/Sattlerei mitbeauftragen oder online beziehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Kuppel-Oberlicht oeffenbar (Polycarbonat)</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>1,2-1,4 m Durchmesser bei 8m-Jurte (skaliert mit Tono). Bei Tono-Lieferant gleich mitbestellen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Tuer-Upgrade (Glas-Doppeltuer / franz. Doppeltuer)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>600</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Adorjan-Standard-Tuer kann zu einfach sein - Upgrade pruefen. Oder lokal bei PT-Schreiner massgefertigt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="8" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>PLATTFORM 8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="43" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Plattform-Konstruktion (~50 m2)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>10 Schraubpfaehle Krinner KSF-M 800mm = 350 EUR. Kiefer KDI Tragbalken 50x200 ca. 25 Stueck = 700 EUR. Laerchen-Deck T+G 27 mm fuer 50 m2 = 1.900 EUR. Kork-Daemmung 30mm 50 m2 = 900 EUR. Geo-Vlies + Schrauben + Sundries = 650 EUR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Vereinfachte Plattform (Budget-Variante)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Falls Budget eng: Kork weglassen, Standard-Druck-impr. Decking statt Laerche. Spart 1.500 EUR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>STURM + KLIMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="25" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sturm-Kit (Erdanker + Ratschen 5T)</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>500</v>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>ALGARVE-OBLIGATORISCH. 10 Anker statt 8 fuer 8m. Verstaerkter Spannband + Ratschen-Set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Schattennetz Algarve (~75 m2)</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>350</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Lokale Agrar-Kooperative. 8m braucht mehr Flaeche als 6m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="8" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>BUFFER</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Reserve / Verschnitt / Schrauben</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="n">
+        <v>800</v>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Bei 8m mehr Kleinteile, hoeheres Risiko von Anpassungen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1"/>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>GESAMTKOSTEN DIY-MODIFY 8M (mit Premium-Plattform)</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>22030</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>INKL. Werkzeug-Pauschale 1.378 EUR (siehe Sheet DIY 12). Bei eigenem Werkzeug-Bestand: -1.378 = 20.652 EUR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="27" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>GESAMTKOSTEN DIY-MODIFY 8M (Budget-Plattform, eigenes Werkzeug)</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>17652</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Mit der einfacheren Plattform-Variante und ohne neue Werkzeug-Kosten. UEBER 15k Budget aber UNTER 20k.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="8" customHeight="1"/>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>VERGLEICH 8M-OPTIONEN ALL-IN ALGARVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="25" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Yourtepoque 8m (FR) + Plattform + Sturm/Schatten</t>
+        </is>
+      </c>
+      <c r="B37" s="13" t="n">
+        <v>19170</v>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Einfachste 8m-Komplett-Loesung. ABER keine UV-Garantie auf Plane, Versand 2k FR-PT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="27" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>DIY-Modify 8m (Adorjan + Algarve-Sattler) Budget-Variante</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="n">
+        <v>17652</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>EMPFEHLUNG #1 FUER 8M. Schaerfster Preis bei premium Sauleda-Plane lokal. 350-450 h Eigenarbeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>DIY-Modify 8m Premium-Variante</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>22030</v>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Mit Premium-Plattform inkl. Kork-Daemmung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Atilla 8m + Eichen-Upgrade + Plattform DIY</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>21960</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Komplette Jurte mit Premium-Holz von Atilla, dann Plattform selbst. Versand 3.500 EUR ist der Kostentreiber.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>YourTent CZ 8m + Versand + Plattform</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>21350</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>5-J. Plane-Garantie ist Plus. Versand CZ-PT ca. 2k. Schaetzung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>jurte24 8m winterfest + Versand + Plattform</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>26250</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Teuerste 8m-Option. Kiefer-Rahmen (kritisch fuer Algarve), nur Werbe-Aussage statt schriftl. UV-Garantie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="8" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>ALTERNATIVE: SIZE-DOWN ZU 7,3M</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="32" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Casa 7,3m + Plattform DIY + Sturm/Schatten + Kamin</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>20700</v>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Casa hat keine 8m, aber 7,3m mit 10-J. UV-Garantie und Lieferung+Aufbau inkl. STATUS: Oktober 2026 Slot weg, fruehestens 2027 verfuegbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="8" customHeight="1"/>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>FAZIT 8M</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="32" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>8m unter 18k machbar?</t>
+        </is>
+      </c>
+      <c r="B48" s="15" t="inlineStr">
+        <is>
+          <t>JA - aber nur DIY-Modify Budget-Variante</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>17.652 EUR sind realistic fuer DIY-Modify 8m mit Sauleda-Plane und einfacherer Plattform. Sebastian muss 2-3k ueber Original-Budget gehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="29" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>8m unter 20k machbar?</t>
+        </is>
+      </c>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>JA - mehrere Wege</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>DIY-Modify Premium: 22k, DIY-Modify Budget: 17,6k, Yourtepoque: 19k. Bewegt sich im 17-22k-Korridor je nach Detailwahl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Empfohlene Strategie</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="inlineStr">
+        <is>
+          <t>Adorjan + Atilla parallel anfragen (Mai 2026 gesendet), Sattler-Antworten abwarten, dann finalkalkulieren</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Mit konkreten Adorjan-Frame-Preis und Sattler-Plane-Preis kann auf 500 EUR genau gerechnet werden. Aktuell noch Schaetzungen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="32" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Worst Case</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>8m geht nicht in Budget - dann Casa 7,3m als 2027-Slot oder Casa 6,1m sofort</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Falls Adorjan oder Sattler unverhaeltnismaessig teuer, ist 7,3m bei Casa der beste Kompromiss (Casa-Slot 2027 oder Paula Young gebraucht).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -21,6 +21,7 @@
     <sheet name="DIY 12 Werkzeuge" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="DIY 13 Kostenrechnung" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="DIY 14 8m Modify Kalk" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15 Kommunikations-Log" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -63,7 +64,7 @@
       <color rgb="00666666"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -80,6 +81,24 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+        <bgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCCCC"/>
+        <bgColor rgb="00FFCCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -143,6 +162,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3399,7 +3427,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>PRIORITAET #1 FUER JURTEN-COVER-COMMISSION. Beste fachliche Eignung (3D-Persenning-Erfahrung, Sauleda im Sortiment). Persoenlicher Besuch leicht moeglich von Aljezur.</t>
+          <t>STATUS Mai 2026: ANFRAGE GESENDET (PT). Antwort offen. PRIORITAET #1 FUER JURTEN-COVER-COMMISSION. Beste fachliche Eignung (3D-Persenning-Erfahrung, Sauleda im Sortiment). Persoenlicher Besuch leicht moeglich von Aljezur.</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3464,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>BACKUP #1: Aelteste Loule-Werkstatt, geographisch am naechsten. Toldos = Acryl-Markisen-Erfahrung = Sauleda-Verarbeitung. Frage: Erfahrung mit 3D-/Jurten-Form?</t>
+          <t>STATUS Mai 2026: ANFRAGE GESENDET (PT). Antwort offen. Aelteste Loule-Werkstatt, geographisch am naechsten zu Aljezur. Toldos = Acryl-Markisen-Erfahrung = Sauleda-Verarbeitung. Frage: Erfahrung mit 3D-/Jurten-Form?</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3501,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>BACKUP #2: spezialisiert auf grossflaechige Verarbeitung. Sauleda-kompatibel.</t>
+          <t>STATUS Mai 2026: ABGELEHNT - 'nao sao da nossa especialidade'. Klassischer Markisen-Hersteller, 3D-Persenning nicht im Programm. Datenpunkt: Toldos-Hersteller machen meist KEINE Jurten-Cover. Echte Kandidaten = Segelmacher (Dune) oder Atilla/Yurt Workshop als Cover-Only.</t>
         </is>
       </c>
     </row>
@@ -7740,6 +7768,695 @@
     <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Datum</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Anbieter</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Kanal</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Richtung</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Inhalt</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Naechste Aktion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>~10.05.2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Atilla es a Fehernep (HU)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>E-Mail</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Atilla</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Originale Anfrage 8m Komplett-Jurte</t>
+        </is>
+      </c>
+      <c r="F2" s="16" t="inlineStr">
+        <is>
+          <t>✓ Beantwortet</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Folgemail Frame-only-Anfrage senden (Entwurf liegt vor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>~10.05.2026</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Adorjan Jurta (HU)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>E-Mail</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Adorjan</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Frame-only Anfrage 8m, Larch optional, Oel-Finish, Versand PT</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>✓ Teilantwort</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Folgemail: 4 Punkte offen (Larch / Tuer-Variante / Lieferzeit / Eigener Spediteur / Werkstatt-Besuch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Adorjan Jurta (HU)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>E-Mail</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Adorjan -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8m Rahmen 3.220.000 HUF = 8.150 EUR netto. Spezifikation Top: 48 Rafters 5x10cm, Tono 170cm 4-lagig verleimt, Wand 2m, Pinie AT Biopin-impraegniert, isolierte Tuer Standard. Versand offen.</t>
+        </is>
+      </c>
+      <c r="F4" s="16" t="inlineStr">
+        <is>
+          <t>Info erhalten</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Folge-Fragen senden</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Adorjan Jurta (HU)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>E-Mail</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Adorjan -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Versand-Spediteur wird gesucht, kein Preis. 50% Anzahlung + 50% vor Versand. Installation extra (4 Pers + Fluege + Maschinen).</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>Info erhalten</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Folge-Fragen (Larch/Tuer/Lieferzeit) + Eigener-Spediteur-Option erfragen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>~10.05.2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Yourtetoiles &amp; Kontempobois (FR)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>E-Mail</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Yourtetoiles</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage 8m Yurte</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>✓ Teilantwort</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp-Videocall Termin festlegen, beide Linien (Klassisch + Kontempo) erfragen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Yourtetoiles &amp; Kontempobois (FR)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>E-Mail</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Yourtetoiles -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Empfehlen Kontempo (Holz-Rundhaus mit Zink-Dach) statt klassischer Jurte fuer Atlantik-Exposition. Devis komplett dauert noch. Bieten Visio-Call an.</t>
+        </is>
+      </c>
+      <c r="F7" s="16" t="inlineStr">
+        <is>
+          <t>Info erhalten</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Visio-Call vereinbaren (3 Terminvorschlaege schicken)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>~12.05.2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Casa dos Sonhos (Sarah &amp; Vladimir, PT)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Facebook Messenger</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Sarah</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage 5/6,1/7,3/9,1m Preise + Konditionen</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>✓ Beantwortet</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>~13.05.2026</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Casa dos Sonhos (Sarah &amp; Vladimir, PT)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Facebook Messenger</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sarah -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Preise bestaetigt: 5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 EUR delivered+erected PT. Refs Brett (Quinta Glamping) + Paula Young (verkauft 7,3m gebraucht).</t>
+        </is>
+      </c>
+      <c r="F9" s="16" t="inlineStr">
+        <is>
+          <t>Quote erhalten</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Nachfrage NIPC/IVA/Bankdaten/Material-Spec/Vermittlung Paula</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Casa dos Sonhos (Sarah &amp; Vladimir, PT)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>PDF Quote</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Sarah -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Quote 6,1m + 2.Tuer 850 + Flue-Kit 100 = 10.650 EUR. 1.000 EUR Anzahlung + 9.650 EUR am 1.8.2026. Lieferung 2. Oktoberwoche 2026.</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Quote erhalten</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Quote schwach dokumentiert (kein IVA-Split, kein Quote-Nr, keine Bank), Klaerung gefordert</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>15.05.2026</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Casa dos Sonhos (Sarah, PT)</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Facebook Messenger</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sarah -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>SLOT OKTOBER 2026 ist an anderen Kunden vergeben. Naechster Slot 2027.</t>
+        </is>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
+        <is>
+          <t>✗ Slot verloren</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Antwort raus: 2027er Slot + Preis-Bestaetigung + Paula-Vermittlung erfragen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>~10.05.2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Bēt Yurts (Noga &amp; Nadav, PT)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>E-Mail</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Noga</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage 6/7/9m Preise + Plattform + Aufbau Algarve</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>✓ Beantwortet</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>~12.05.2026</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Bēt Yurts (Noga, PT)</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>E-Mail + 3 PDF-Quotes</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Noga -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Preise: 6m=12.600 / 7m=14.400 / 9m=19.800 Jurte netto. Plattform separat: 6m=6.500 / 7m=7.200 / 9m=11.500. Transport+Install: 700/1.900, 900/2.500, 1.500/2.900. 23% IVA on top. 50% upfront NICHT-RUECKZAHLBAR. AUGUST 2026 Slot. Material laut Quote: Nordic Pine + Outer Canvas + 80mm Insulation (ohne Marken-Angabe). 2-J. Garantie auf Plane.</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Quote erhalten</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Mail raus: Konkurrenz-Preis + Material-Aufschluesselung (Sauleda? PET?) anfordern</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>~17.05.2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Dune Algarve Sailmakers (PT)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Web/E-Mail</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dune</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>⏳ Antwort offen</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5 Tage warten, dann WhatsApp/Tel.-Nachfrage. Telefon-Skript bereit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>~17.05.2026</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Toldos Etapaveloz (Loule, PT)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Web/E-Mail</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Etapaveloz</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>⏳ Antwort offen</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>5 Tage warten, dann Folgekontakt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>~17.05.2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Textilux (Algarve, PT)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Web/E-Mail</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Textilux</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
+        </is>
+      </c>
+      <c r="F16" s="17" t="inlineStr">
+        <is>
+          <t>✗ ABGELEHNT</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>'nao sao da nossa especialidade' - klassischer Markisen-Hersteller, kein 3D-Persenning. Keine weitere Aktion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Paula Young (FB 'Paula Vegan Chef')</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Facebook (offen)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Paula</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage zur gebrauchten 7,3m Casa-Jurte</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>⏳ Kontakt steht aus</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Ueber FB suchen ODER Sarah um Vermittlung bitten (in der naechsten Casa-Antwort mit aufnehmen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Brett, Quinta Glamping (Algarve)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Online-Buchung</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian (geplant)</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>⏳ noch nicht gebucht</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -7168,7 +7168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -7398,18 +7398,18 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
+    <row r="19" ht="43" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Kuppel-Oberlicht oeffenbar (Polycarbonat)</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>800</v>
+        <v>1500</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>1,2-1,4 m Durchmesser bei 8m-Jurte (skaliert mit Tono). Bei Tono-Lieferant gleich mitbestellen.</t>
+          <t>KORRIGIERT Mai 2026: Atilla+Adorjan bestaetigen Tono 170-180 cm fuer 8m (nicht 120 cm). Kuppel muss entsprechend 1,5-1,7 m gross sein. Polycarbonat in dieser Groesse: 1.200-1.800 EUR. Bei Frame-Lieferant gleich mitbestellen.</t>
         </is>
       </c>
     </row>
@@ -7528,154 +7528,178 @@
       </c>
     </row>
     <row r="32" ht="8" customHeight="1"/>
-    <row r="33" ht="28" customHeight="1">
+    <row r="33" ht="42" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>GESAMTKOSTEN DIY-MODIFY 8M (mit Premium-Plattform)</t>
+          <t>GESAMTKOSTEN DIY-MODIFY 8M (Budget-Plattform, eigenes Werkzeug)</t>
         </is>
       </c>
       <c r="B33" s="14" t="n">
+        <v>23780</v>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>AKTUALISIERT Mai 2026 nach Adorjan-Real-Quote + Atilla-Engineering-Feedback: Adorjan Frame 8.150 (statt 5.000 Schaetzung) + Tono+Kuppel 1.500 (statt 800 wegen 170-180 cm Tono) = +3.850 vs Original. 8,8k UEBER 15k Budget.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="33" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>GESAMTKOSTEN DIY-MODIFY 8M (Premium-Plattform + neues Werkzeug)</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>26658</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>AKTUALISIERT Mai 2026: mit Premium Plattform inkl. Kork 4.500 + Werkzeug-Pauschale 1.378. Realistisches Komplett-Setup wenn alles neu beschafft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="34" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Yourtepoque 8m bleibt PREISSIEGER 8m</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="n">
+        <v>19170</v>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>11.820 + 2.000 Versand + 4.500 Plattform + 850 Sturm/Schatten = 19.170 EUR. Keine UV-Garantie auf Plane aber 4.000-7.000 EUR guenstiger als DIY-Modify 8m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>BLEIBT die Kompromiss-Option Casa 7,3m</t>
+        </is>
+      </c>
+      <c r="B36" s="13" t="n">
+        <v>20700</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>15.750 inkl. Aufbau + 4.000 Plattform DIY + 850 Sturm/Schatten + 100 Kamin = 20.700. 10-J. UV-Garantie. 8m² kleiner als 8m DIY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="50" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>NEU ERKENNTNIS Mai 2026</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>Adorjan/Atilla Engineering ist solide aber teurer als gedacht</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>DIY-Modify 8m verliert seinen Preisvorteil gegenueber Yourtepoque (rein finanziell). Hauptargumente fuer DIY-Modify bleiben: 1) sofortige Verfuegbarkeit, 2) volle Materialkontrolle (Sauleda Marine-grade vs Yourtepoque-Standard-Canvas), 3) Lokaler PT-Reparatur-Service via Algarve-Sattler.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>VERGLEICH 8M-OPTIONEN ALL-IN ALGARVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="25" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Yourtepoque 8m (FR) + Plattform + Sturm/Schatten</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>19170</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Einfachste 8m-Komplett-Loesung. ABER keine UV-Garantie auf Plane, Versand 2k FR-PT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="27" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>DIY-Modify 8m (Adorjan + Algarve-Sattler) Budget-Variante</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>17652</v>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>EMPFEHLUNG #1 FUER 8M. Schaerfster Preis bei premium Sauleda-Plane lokal. 350-450 h Eigenarbeit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>DIY-Modify 8m Premium-Variante</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
         <v>22030</v>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>INKL. Werkzeug-Pauschale 1.378 EUR (siehe Sheet DIY 12). Bei eigenem Werkzeug-Bestand: -1.378 = 20.652 EUR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="27" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>GESAMTKOSTEN DIY-MODIFY 8M (Budget-Plattform, eigenes Werkzeug)</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="n">
-        <v>17652</v>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Mit der einfacheren Plattform-Variante und ohne neue Werkzeug-Kosten. UEBER 15k Budget aber UNTER 20k.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="8" customHeight="1"/>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>VERGLEICH 8M-OPTIONEN ALL-IN ALGARVE</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="25" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Yourtepoque 8m (FR) + Plattform + Sturm/Schatten</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="n">
-        <v>19170</v>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Einfachste 8m-Komplett-Loesung. ABER keine UV-Garantie auf Plane, Versand 2k FR-PT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="27" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>DIY-Modify 8m (Adorjan + Algarve-Sattler) Budget-Variante</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="n">
-        <v>17652</v>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>EMPFEHLUNG #1 FUER 8M. Schaerfster Preis bei premium Sauleda-Plane lokal. 350-450 h Eigenarbeit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>DIY-Modify 8m Premium-Variante</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="n">
-        <v>22030</v>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>Mit Premium-Plattform inkl. Kork-Daemmung.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="43" ht="28" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Atilla 8m + Eichen-Upgrade + Plattform DIY</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n">
+      <c r="B43" s="13" t="n">
         <v>21960</v>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Komplette Jurte mit Premium-Holz von Atilla, dann Plattform selbst. Versand 3.500 EUR ist der Kostentreiber.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>YourTent CZ 8m + Versand + Plattform</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n">
+      <c r="B44" s="13" t="n">
         <v>21350</v>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>5-J. Plane-Garantie ist Plus. Versand CZ-PT ca. 2k. Schaetzung.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="28" customHeight="1">
-      <c r="A42" s="3" t="inlineStr">
+    <row r="45" ht="28" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>jurte24 8m winterfest + Versand + Plattform</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n">
+      <c r="B45" s="13" t="n">
         <v>26250</v>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Teuerste 8m-Option. Kiefer-Rahmen (kritisch fuer Algarve), nur Werbe-Aussage statt schriftl. UV-Garantie.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="8" customHeight="1"/>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>ALTERNATIVE: SIZE-DOWN ZU 7,3M</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="32" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Casa 7,3m + Plattform DIY + Sturm/Schatten + Kamin</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="n">
-        <v>20700</v>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Casa hat keine 8m, aber 7,3m mit 10-J. UV-Garantie und Lieferung+Aufbau inkl. STATUS: Oktober 2026 Slot weg, fruehestens 2027 verfuegbar.</t>
         </is>
       </c>
     </row>
@@ -7683,73 +7707,96 @@
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>FAZIT 8M</t>
+          <t>ALTERNATIVE: SIZE-DOWN ZU 7,3M</t>
         </is>
       </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>8m unter 18k machbar?</t>
-        </is>
-      </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>JA - aber nur DIY-Modify Budget-Variante</t>
-        </is>
+          <t>Casa 7,3m + Plattform DIY + Sturm/Schatten + Kamin</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>20700</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>17.652 EUR sind realistic fuer DIY-Modify 8m mit Sauleda-Plane und einfacherer Plattform. Sebastian muss 2-3k ueber Original-Budget gehen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="29" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>8m unter 20k machbar?</t>
-        </is>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>JA - mehrere Wege</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>DIY-Modify Premium: 22k, DIY-Modify Budget: 17,6k, Yourtepoque: 19k. Bewegt sich im 17-22k-Korridor je nach Detailwahl.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>Empfohlene Strategie</t>
-        </is>
-      </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>Adorjan + Atilla parallel anfragen (Mai 2026 gesendet), Sattler-Antworten abwarten, dann finalkalkulieren</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Mit konkreten Adorjan-Frame-Preis und Sattler-Plane-Preis kann auf 500 EUR genau gerechnet werden. Aktuell noch Schaetzungen.</t>
+          <t>Casa hat keine 8m, aber 7,3m mit 10-J. UV-Garantie und Lieferung+Aufbau inkl. STATUS: Oktober 2026 Slot weg, fruehestens 2027 verfuegbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="8" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>FAZIT 8M</t>
         </is>
       </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>8m unter 18k machbar?</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>JA - aber nur DIY-Modify Budget-Variante</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>17.652 EUR sind realistic fuer DIY-Modify 8m mit Sauleda-Plane und einfacherer Plattform. Sebastian muss 2-3k ueber Original-Budget gehen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="29" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>8m unter 20k machbar?</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="inlineStr">
+        <is>
+          <t>JA - mehrere Wege</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>DIY-Modify Premium: 22k, DIY-Modify Budget: 17,6k, Yourtepoque: 19k. Bewegt sich im 17-22k-Korridor je nach Detailwahl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Empfohlene Strategie</t>
+        </is>
+      </c>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>Adorjan + Atilla parallel anfragen (Mai 2026 gesendet), Sattler-Antworten abwarten, dann finalkalkulieren</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Mit konkreten Adorjan-Frame-Preis und Sattler-Plane-Preis kann auf 500 EUR genau gerechnet werden. Aktuell noch Schaetzungen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
           <t>Worst Case</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>8m geht nicht in Budget - dann Casa 7,3m als 2027-Slot oder Casa 6,1m sofort</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>Falls Adorjan oder Sattler unverhaeltnismaessig teuer, ist 7,3m bei Casa der beste Kompromiss (Casa-Slot 2027 oder Paula Young gebraucht).</t>
         </is>
@@ -7757,12 +7804,12 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A36:C36"/>
-    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A50:C50"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A39:C39"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="A26:C26"/>
@@ -7778,7 +7825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7867,12 +7914,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>~10.05.2026</t>
+          <t>~18.05.2026</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Adorjan Jurta (HU)</t>
+          <t>Atilla es a Fehernep (HU)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -7882,34 +7929,34 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Adorjan</t>
+          <t>Sebastian -&gt; Atilla</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Frame-only Anfrage 8m, Larch optional, Oel-Finish, Versand PT</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>✓ Teilantwort</t>
+          <t>Frame-only Anfrage 8m (Khaana+Tono 120cm+60 Uni+Tuer)</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>✓ Beantwortet</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Folgemail: 4 Punkte offen (Larch / Tuer-Variante / Lieferzeit / Eigener Spediteur / Werkstatt-Besuch)</t>
+          <t>Atilla akzeptiert Frame-only ABER lehnt 120cm Tono ab</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>~19.05.2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Adorjan Jurta (HU)</t>
+          <t>Atilla es a Fehernep (HU)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -7919,29 +7966,29 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Adorjan -&gt; Sebastian</t>
+          <t>Atilla -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8m Rahmen 3.220.000 HUF = 8.150 EUR netto. Spezifikation Top: 48 Rafters 5x10cm, Tono 170cm 4-lagig verleimt, Wand 2m, Pinie AT Biopin-impraegniert, isolierte Tuer Standard. Versand offen.</t>
+          <t>ENGINEERING-KORREKTUR: 120cm Tono fuer 8m statisch zu klein (6cm Loch-Abstand). Atilla nutzt 180cm fuer 8m und 160cm fuer 6m. 60 Uni waeren auch zu wenig (schwache Wand bei 2m Hoehe). Fragt: jede Khaana-Spitze = ein Uni? Wuerde nur mit seinen Massen Verantwortung uebernehmen.</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>Info erhalten</t>
+          <t>Info erhalten - technisch wertvoll</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Folge-Fragen senden</t>
+          <t>Antwort: Atilla's Standard-Masse akzeptieren (180cm Tono, jede Khaana-Spitze=Uni). Quote neu erfragen + Larch/Skylight/Lieferzeit/Versand/Eigene-Spedition Fragen.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>~10.05.2026</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -7956,34 +8003,34 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Adorjan -&gt; Sebastian</t>
+          <t>Sebastian -&gt; Adorjan</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Versand-Spediteur wird gesucht, kein Preis. 50% Anzahlung + 50% vor Versand. Installation extra (4 Pers + Fluege + Maschinen).</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>Info erhalten</t>
+          <t>Frame-only Anfrage 8m, Larch optional, Oel-Finish, Versand PT</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>✓ Teilantwort</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Folge-Fragen (Larch/Tuer/Lieferzeit) + Eigener-Spediteur-Option erfragen</t>
+          <t>Folgemail: 4 Punkte offen (Larch / Tuer-Variante / Lieferzeit / Eigener Spediteur / Werkstatt-Besuch)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>~10.05.2026</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Yourtetoiles &amp; Kontempobois (FR)</t>
+          <t>Adorjan Jurta (HU)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -7993,22 +8040,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Yourtetoiles</t>
+          <t>Adorjan -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Anfrage 8m Yurte</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>✓ Teilantwort</t>
+          <t>8m Rahmen 3.220.000 HUF = 8.150 EUR netto. Spezifikation Top: 48 Rafters 5x10cm, Tono 170cm 4-lagig verleimt, Wand 2m, Pinie AT Biopin-impraegniert, isolierte Tuer Standard. Versand offen.</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>Info erhalten</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp-Videocall Termin festlegen, beide Linien (Klassisch + Kontempo) erfragen</t>
+          <t>Folge-Fragen senden</t>
         </is>
       </c>
     </row>
@@ -8020,7 +8067,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Yourtetoiles &amp; Kontempobois (FR)</t>
+          <t>Adorjan Jurta (HU)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -8030,12 +8077,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Yourtetoiles -&gt; Sebastian</t>
+          <t>Adorjan -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Empfehlen Kontempo (Holz-Rundhaus mit Zink-Dach) statt klassischer Jurte fuer Atlantik-Exposition. Devis komplett dauert noch. Bieten Visio-Call an.</t>
+          <t>Versand-Spediteur wird gesucht, kein Preis. 50% Anzahlung + 50% vor Versand. Installation extra (4 Pers + Fluege + Maschinen).</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -8045,88 +8092,88 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Visio-Call vereinbaren (3 Terminvorschlaege schicken)</t>
+          <t>Folge-Fragen (Larch/Tuer/Lieferzeit) + Eigener-Spediteur-Option erfragen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>~12.05.2026</t>
+          <t>~10.05.2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos (Sarah &amp; Vladimir, PT)</t>
+          <t>Yourtetoiles &amp; Kontempobois (FR)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Facebook Messenger</t>
+          <t>E-Mail</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Sarah</t>
+          <t>Sebastian -&gt; Yourtetoiles</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Anfrage 5/6,1/7,3/9,1m Preise + Konditionen</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>✓ Beantwortet</t>
+          <t>Anfrage 8m Yurte</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>✓ Teilantwort</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>WhatsApp-Videocall Termin festlegen, beide Linien (Klassisch + Kontempo) erfragen</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>~13.05.2026</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos (Sarah &amp; Vladimir, PT)</t>
+          <t>Yourtetoiles &amp; Kontempobois (FR)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Facebook Messenger</t>
+          <t>E-Mail</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Sarah -&gt; Sebastian</t>
+          <t>Yourtetoiles -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Preise bestaetigt: 5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 EUR delivered+erected PT. Refs Brett (Quinta Glamping) + Paula Young (verkauft 7,3m gebraucht).</t>
+          <t>Empfehlen Kontempo (Holz-Rundhaus mit Zink-Dach) statt klassischer Jurte fuer Atlantik-Exposition. Devis komplett dauert noch. Bieten Visio-Call an.</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>Quote erhalten</t>
+          <t>Info erhalten</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Nachfrage NIPC/IVA/Bankdaten/Material-Spec/Vermittlung Paula</t>
+          <t>Visio-Call vereinbaren (3 Terminvorschlaege schicken)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>~12.05.2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -8136,39 +8183,39 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>PDF Quote</t>
+          <t>Facebook Messenger</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sarah -&gt; Sebastian</t>
+          <t>Sebastian -&gt; Sarah</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Quote 6,1m + 2.Tuer 850 + Flue-Kit 100 = 10.650 EUR. 1.000 EUR Anzahlung + 9.650 EUR am 1.8.2026. Lieferung 2. Oktoberwoche 2026.</t>
+          <t>Anfrage 5/6,1/7,3/9,1m Preise + Konditionen</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>Quote erhalten</t>
+          <t>✓ Beantwortet</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Quote schwach dokumentiert (kein IVA-Split, kein Quote-Nr, keine Bank), Klaerung gefordert</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>~13.05.2026</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos (Sarah, PT)</t>
+          <t>Casa dos Sonhos (Sarah &amp; Vladimir, PT)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -8183,165 +8230,165 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>SLOT OKTOBER 2026 ist an anderen Kunden vergeben. Naechster Slot 2027.</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr">
-        <is>
-          <t>✗ Slot verloren</t>
+          <t>Preise bestaetigt: 5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 EUR delivered+erected PT. Refs Brett (Quinta Glamping) + Paula Young (verkauft 7,3m gebraucht).</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="inlineStr">
+        <is>
+          <t>Quote erhalten</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Antwort raus: 2027er Slot + Preis-Bestaetigung + Paula-Vermittlung erfragen</t>
+          <t>Nachfrage NIPC/IVA/Bankdaten/Material-Spec/Vermittlung Paula</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>~10.05.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Bēt Yurts (Noga &amp; Nadav, PT)</t>
+          <t>Casa dos Sonhos (Sarah &amp; Vladimir, PT)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>E-Mail</t>
+          <t>PDF Quote</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Noga</t>
+          <t>Sarah -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Anfrage 6/7/9m Preise + Plattform + Aufbau Algarve</t>
+          <t>Quote 6,1m + 2.Tuer 850 + Flue-Kit 100 = 10.650 EUR. 1.000 EUR Anzahlung + 9.650 EUR am 1.8.2026. Lieferung 2. Oktoberwoche 2026.</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>✓ Beantwortet</t>
+          <t>Quote erhalten</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Quote schwach dokumentiert (kein IVA-Split, kein Quote-Nr, keine Bank), Klaerung gefordert</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>~12.05.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Bēt Yurts (Noga, PT)</t>
+          <t>Casa dos Sonhos (Sarah, PT)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>E-Mail + 3 PDF-Quotes</t>
+          <t>Facebook Messenger</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>Noga -&gt; Sebastian</t>
+          <t>Sarah -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Preise: 6m=12.600 / 7m=14.400 / 9m=19.800 Jurte netto. Plattform separat: 6m=6.500 / 7m=7.200 / 9m=11.500. Transport+Install: 700/1.900, 900/2.500, 1.500/2.900. 23% IVA on top. 50% upfront NICHT-RUECKZAHLBAR. AUGUST 2026 Slot. Material laut Quote: Nordic Pine + Outer Canvas + 80mm Insulation (ohne Marken-Angabe). 2-J. Garantie auf Plane.</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>Quote erhalten</t>
+          <t>SLOT OKTOBER 2026 ist an anderen Kunden vergeben. Naechster Slot 2027.</t>
+        </is>
+      </c>
+      <c r="F13" s="17" t="inlineStr">
+        <is>
+          <t>✗ Slot verloren</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Mail raus: Konkurrenz-Preis + Material-Aufschluesselung (Sauleda? PET?) anfordern</t>
+          <t>Antwort raus: 2027er Slot + Preis-Bestaetigung + Paula-Vermittlung erfragen</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>~17.05.2026</t>
+          <t>~10.05.2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Dune Algarve Sailmakers (PT)</t>
+          <t>Bēt Yurts (Noga &amp; Nadav, PT)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Web/E-Mail</t>
+          <t>E-Mail</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dune</t>
+          <t>Sebastian -&gt; Noga</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>⏳ Antwort offen</t>
+          <t>Anfrage 6/7/9m Preise + Plattform + Aufbau Algarve</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>✓ Beantwortet</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5 Tage warten, dann WhatsApp/Tel.-Nachfrage. Telefon-Skript bereit.</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>~17.05.2026</t>
+          <t>~12.05.2026</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Toldos Etapaveloz (Loule, PT)</t>
+          <t>Bēt Yurts (Noga, PT)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Web/E-Mail</t>
+          <t>E-Mail + 3 PDF-Quotes</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Etapaveloz</t>
+          <t>Noga -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
-        </is>
-      </c>
-      <c r="F15" s="18" t="inlineStr">
-        <is>
-          <t>⏳ Antwort offen</t>
+          <t>Preise: 6m=12.600 / 7m=14.400 / 9m=19.800 Jurte netto. Plattform separat: 6m=6.500 / 7m=7.200 / 9m=11.500. Transport+Install: 700/1.900, 900/2.500, 1.500/2.900. 23% IVA on top. 50% upfront NICHT-RUECKZAHLBAR. AUGUST 2026 Slot. Material laut Quote: Nordic Pine + Outer Canvas + 80mm Insulation (ohne Marken-Angabe). 2-J. Garantie auf Plane.</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <t>Quote erhalten</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>5 Tage warten, dann Folgekontakt</t>
+          <t>Mail raus: Konkurrenz-Preis + Material-Aufschluesselung (Sauleda? PET?) anfordern</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8400,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Textilux (Algarve, PT)</t>
+          <t>Dune Algarve Sailmakers (PT)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -8363,7 +8410,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Textilux</t>
+          <t>Sebastian -&gt; Dune</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8371,86 +8418,160 @@
           <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
         </is>
       </c>
-      <c r="F16" s="17" t="inlineStr">
-        <is>
-          <t>✗ ABGELEHNT</t>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>⏳ Antwort offen</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>'nao sao da nossa especialidade' - klassischer Markisen-Hersteller, kein 3D-Persenning. Keine weitere Aktion.</t>
+          <t>5 Tage warten, dann WhatsApp/Tel.-Nachfrage. Telefon-Skript bereit.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>~17.05.2026</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Paula Young (FB 'Paula Vegan Chef')</t>
+          <t>Toldos Etapaveloz (Loule, PT)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Facebook (offen)</t>
+          <t>Web/E-Mail</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Paula</t>
+          <t>Sebastian -&gt; Etapaveloz</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>Anfrage zur gebrauchten 7,3m Casa-Jurte</t>
+          <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
         </is>
       </c>
       <c r="F17" s="18" t="inlineStr">
         <is>
-          <t>⏳ Kontakt steht aus</t>
+          <t>⏳ Antwort offen</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Ueber FB suchen ODER Sarah um Vermittlung bitten (in der naechsten Casa-Antwort mit aufnehmen)</t>
+          <t>5 Tage warten, dann Folgekontakt</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>~17.05.2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Textilux (Algarve, PT)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Web/E-Mail</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Textilux</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
+        <is>
+          <t>✗ ABGELEHNT</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>'nao sao da nossa especialidade' - klassischer Markisen-Hersteller, kein 3D-Persenning. Keine weitere Aktion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Paula Young (FB 'Paula Vegan Chef')</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Facebook (offen)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Paula</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage zur gebrauchten 7,3m Casa-Jurte</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>⏳ Kontakt steht aus</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Ueber FB suchen ODER Sarah um Vermittlung bitten (in der naechsten Casa-Antwort mit aufnehmen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F20" s="18" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -11996,7 +12117,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1">
+    <row r="6" ht="60" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Tono-Durchmesser</t>
@@ -12004,46 +12125,46 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1,20 m</t>
+          <t>170-180 cm</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Standard fuer 8m-Jurten mit ~60 Dachstangen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
+          <t>KORRIGIERT Mai 2026 nach technischem Feedback von Atilla + Adorjan: 120 cm fuer 8m ist statisch UNDERDIMENSIONIERT. Adorjan praktiziert 170 cm bei 8m (mit 48 Rafters 5x10cm), Atilla 180 cm (mit groesserer Anzahl Uni). Bei 60 Uni und 120 cm Tono waeren nur 6 cm Lochabstand am Ring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="43" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
+          <t>Anzahl Dachstangen (Uni)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>60-80 (je nach Tono-Wahl)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Bei 180 cm Tono mit jeder Khaana-Spitze=Uni: 64-80 Uni. Bei 170 cm Tono mit massiven 5x10cm Rafters (Adorjan-Bauart): 48 Uni reichen. Beides bewaehrte Engineering-Loesungen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
           <t>Anzahl Khaana-Sektionen</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Jede Sektion ca. 3,14 m breit ausgebreitet (= pi * 8m / 8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Anzahl Dachstangen (Uni)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Alle 6 Grad = 60 mm Abstand am Tono</t>
         </is>
       </c>
     </row>
@@ -12707,12 +12828,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tono - Kronenring fertig</t>
+          <t>Tono - Kronenring fertig (KORRIGIERT 2026)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>1,20 m Durchmesser, 60 Bohrungen für Uni, Eiche/Esche laminiert</t>
+          <t>170-180 cm Durchmesser, 60-80 Bohrungen Uni, 4-lagig verleimt (Adorjan-Standard) - NICHT 120 cm wie urspruenglich angenommen</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
@@ -12724,19 +12845,19 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Camping Yurts (UK) / FAMTENTS (CZ) / Adorjan Jurta (HU) / Atilla (HU)</t>
+          <t>Camping Yurts (UK) / FAMTENTS (CZ) / Adorjan Jurta (HU, 170 cm) / Atilla (HU, 180 cm)</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Inkl. Sicherheitslackierung und Bohrungen. Versand DE/HU-&gt;PT ca. 150-300 EUR extra.</t>
+          <t>WICHTIG: Atilla + Adorjan haben beide bestaetigt: 120 cm Tono fuer 8m statisch zu klein. 170-180 cm noetig. Preisaufschlag entsprechend (700-1.500 EUR). Adorjan baut komplettes Frame inkl. Tono fuer 8.150 EUR.</t>
         </is>
       </c>
     </row>
@@ -12789,16 +12910,16 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Uni Dachstangen Sibir. Laerche</t>
+          <t>Uni Dachstangen (KORRIGIERT 2026)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>30x30 mm gehobelt, 4,0 m Laenge, leicht gebogen</t>
+          <t>Bei 170 cm Tono (Adorjan-Bauart): 48 Stk mit 5x10 cm massiv / Bei 180 cm Tono (Atilla-Bauart): 64-80 Stk mit 3,5x3,5 cm, jede Khaana-Spitze</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -12806,19 +12927,19 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>780</v>
+        <v>1440</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Holz Schiller AT / Siero Lam (PT) / Holz Possling DE</t>
+          <t>Holz Schiller AT / Siero Lam (PT) / Holz Possling DE / Adorjan oder Atilla im Komplett-Frame</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>60 + 5 Reserve. Konisch oder gerade. Wenn gerade: muss am unteren Ende leicht angefast werden fuer den Khaana-Sattel.</t>
+          <t>WICHTIG: Wenn Adorjan/Atilla das ganze Frame liefert, sind Uni inklusive. Hier nur relevant fuer reines DIY. 5x10 cm massive Variante ist teurer aber statisch besser fuer 8m.</t>
         </is>
       </c>
     </row>
@@ -13818,7 +13939,7 @@
         </is>
       </c>
       <c r="G32" s="12" t="n">
-        <v>18395</v>
+        <v>19805</v>
       </c>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -7825,7 +7825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7988,12 +7988,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>~10.05.2026</t>
+          <t>20.05.2026</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Adorjan Jurta (HU)</t>
+          <t>Atilla es a Fehernep (HU)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -8003,29 +8003,29 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Adorjan</t>
+          <t>Sebastian -&gt; Atilla</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Frame-only Anfrage 8m, Larch optional, Oel-Finish, Versand PT</t>
+          <t>Akzeptiert Atilla's Engineering-Standards (180cm Tono, jede Khaana-Spitze=Uni, 2m Wand). Fragt nach: Frame-only-Quote mit Atilla's Massen, Laerche statt Buche/Kiefer, Skylight-Preis 180cm Tono, Lieferzeit, Versand frame-only Algarve, Eigene-Spedition-Option, Werkstatt-Besuch.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>✓ Teilantwort</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Folgemail: 4 Punkte offen (Larch / Tuer-Variante / Lieferzeit / Eigener Spediteur / Werkstatt-Besuch)</t>
+          <t>Antwort abwarten (3-7 Tage). Bei Verzug nach 10 Tagen WhatsApp +36 30 657 0740.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>~10.05.2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -8040,22 +8040,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Adorjan -&gt; Sebastian</t>
+          <t>Sebastian -&gt; Adorjan</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8m Rahmen 3.220.000 HUF = 8.150 EUR netto. Spezifikation Top: 48 Rafters 5x10cm, Tono 170cm 4-lagig verleimt, Wand 2m, Pinie AT Biopin-impraegniert, isolierte Tuer Standard. Versand offen.</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>Info erhalten</t>
+          <t>Frame-only Anfrage 8m, Larch optional, Oel-Finish, Versand PT</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>✓ Teilantwort</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Folge-Fragen senden</t>
+          <t>Folgemail: 4 Punkte offen (Larch / Tuer-Variante / Lieferzeit / Eigener Spediteur / Werkstatt-Besuch)</t>
         </is>
       </c>
     </row>
@@ -8082,7 +8082,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Versand-Spediteur wird gesucht, kein Preis. 50% Anzahlung + 50% vor Versand. Installation extra (4 Pers + Fluege + Maschinen).</t>
+          <t>8m Rahmen 3.220.000 HUF = 8.150 EUR netto. Spezifikation Top: 48 Rafters 5x10cm, Tono 170cm 4-lagig verleimt, Wand 2m, Pinie AT Biopin-impraegniert, isolierte Tuer Standard. Versand offen.</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -8092,19 +8092,19 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Folge-Fragen (Larch/Tuer/Lieferzeit) + Eigener-Spediteur-Option erfragen</t>
+          <t>Folge-Fragen senden</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>~10.05.2026</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Yourtetoiles &amp; Kontempobois (FR)</t>
+          <t>Adorjan Jurta (HU)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -8114,29 +8114,29 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Yourtetoiles</t>
+          <t>Adorjan -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Anfrage 8m Yurte</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>✓ Teilantwort</t>
+          <t>Versand-Spediteur wird gesucht, kein Preis. 50% Anzahlung + 50% vor Versand. Installation extra (4 Pers + Fluege + Maschinen).</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="inlineStr">
+        <is>
+          <t>Info erhalten</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>WhatsApp-Videocall Termin festlegen, beide Linien (Klassisch + Kontempo) erfragen</t>
+          <t>Folge-Fragen (Larch/Tuer/Lieferzeit) + Eigener-Spediteur-Option erfragen</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>~10.05.2026</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -8151,66 +8151,66 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>Yourtetoiles -&gt; Sebastian</t>
+          <t>Sebastian -&gt; Yourtetoiles</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Empfehlen Kontempo (Holz-Rundhaus mit Zink-Dach) statt klassischer Jurte fuer Atlantik-Exposition. Devis komplett dauert noch. Bieten Visio-Call an.</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>Info erhalten</t>
+          <t>Anfrage 8m Yurte</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>✓ Teilantwort</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Visio-Call vereinbaren (3 Terminvorschlaege schicken)</t>
+          <t>WhatsApp-Videocall Termin festlegen, beide Linien (Klassisch + Kontempo) erfragen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>~12.05.2026</t>
+          <t>?</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos (Sarah &amp; Vladimir, PT)</t>
+          <t>Yourtetoiles &amp; Kontempobois (FR)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Facebook Messenger</t>
+          <t>E-Mail</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Sarah</t>
+          <t>Yourtetoiles -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Anfrage 5/6,1/7,3/9,1m Preise + Konditionen</t>
+          <t>Empfehlen Kontempo (Holz-Rundhaus mit Zink-Dach) statt klassischer Jurte fuer Atlantik-Exposition. Devis komplett dauert noch. Bieten Visio-Call an.</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>✓ Beantwortet</t>
+          <t>Info erhalten</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Visio-Call vereinbaren (3 Terminvorschlaege schicken)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>~13.05.2026</t>
+          <t>~12.05.2026</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -8225,29 +8225,29 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Sarah -&gt; Sebastian</t>
+          <t>Sebastian -&gt; Sarah</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Preise bestaetigt: 5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 EUR delivered+erected PT. Refs Brett (Quinta Glamping) + Paula Young (verkauft 7,3m gebraucht).</t>
+          <t>Anfrage 5/6,1/7,3/9,1m Preise + Konditionen</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>Quote erhalten</t>
+          <t>✓ Beantwortet</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Nachfrage NIPC/IVA/Bankdaten/Material-Spec/Vermittlung Paula</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>15.05.2026</t>
+          <t>~13.05.2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -8257,7 +8257,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>PDF Quote</t>
+          <t>Facebook Messenger</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Quote 6,1m + 2.Tuer 850 + Flue-Kit 100 = 10.650 EUR. 1.000 EUR Anzahlung + 9.650 EUR am 1.8.2026. Lieferung 2. Oktoberwoche 2026.</t>
+          <t>Preise bestaetigt: 5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 EUR delivered+erected PT. Refs Brett (Quinta Glamping) + Paula Young (verkauft 7,3m gebraucht).</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Quote schwach dokumentiert (kein IVA-Split, kein Quote-Nr, keine Bank), Klaerung gefordert</t>
+          <t>Nachfrage NIPC/IVA/Bankdaten/Material-Spec/Vermittlung Paula</t>
         </is>
       </c>
     </row>
@@ -8289,12 +8289,12 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos (Sarah, PT)</t>
+          <t>Casa dos Sonhos (Sarah &amp; Vladimir, PT)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Facebook Messenger</t>
+          <t>PDF Quote</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -8304,128 +8304,128 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>SLOT OKTOBER 2026 ist an anderen Kunden vergeben. Naechster Slot 2027.</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr">
-        <is>
-          <t>✗ Slot verloren</t>
+          <t>Quote 6,1m + 2.Tuer 850 + Flue-Kit 100 = 10.650 EUR. 1.000 EUR Anzahlung + 9.650 EUR am 1.8.2026. Lieferung 2. Oktoberwoche 2026.</t>
+        </is>
+      </c>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <t>Quote erhalten</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Antwort raus: 2027er Slot + Preis-Bestaetigung + Paula-Vermittlung erfragen</t>
+          <t>Quote schwach dokumentiert (kein IVA-Split, kein Quote-Nr, keine Bank), Klaerung gefordert</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>~10.05.2026</t>
+          <t>15.05.2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Bēt Yurts (Noga &amp; Nadav, PT)</t>
+          <t>Casa dos Sonhos (Sarah, PT)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>E-Mail</t>
+          <t>Facebook Messenger</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Noga</t>
+          <t>Sarah -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Anfrage 6/7/9m Preise + Plattform + Aufbau Algarve</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>✓ Beantwortet</t>
+          <t>SLOT OKTOBER 2026 ist an anderen Kunden vergeben. Naechster Slot 2027.</t>
+        </is>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
+        <is>
+          <t>✗ Slot verloren</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Antwort raus: 2027er Slot + Preis-Bestaetigung + Paula-Vermittlung erfragen</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>~12.05.2026</t>
+          <t>~10.05.2026</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Bēt Yurts (Noga, PT)</t>
+          <t>Bēt Yurts (Noga &amp; Nadav, PT)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>E-Mail + 3 PDF-Quotes</t>
+          <t>E-Mail</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>Noga -&gt; Sebastian</t>
+          <t>Sebastian -&gt; Noga</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Preise: 6m=12.600 / 7m=14.400 / 9m=19.800 Jurte netto. Plattform separat: 6m=6.500 / 7m=7.200 / 9m=11.500. Transport+Install: 700/1.900, 900/2.500, 1.500/2.900. 23% IVA on top. 50% upfront NICHT-RUECKZAHLBAR. AUGUST 2026 Slot. Material laut Quote: Nordic Pine + Outer Canvas + 80mm Insulation (ohne Marken-Angabe). 2-J. Garantie auf Plane.</t>
+          <t>Anfrage 6/7/9m Preise + Plattform + Aufbau Algarve</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>Quote erhalten</t>
+          <t>✓ Beantwortet</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Mail raus: Konkurrenz-Preis + Material-Aufschluesselung (Sauleda? PET?) anfordern</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>~17.05.2026</t>
+          <t>~12.05.2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Dune Algarve Sailmakers (PT)</t>
+          <t>Bēt Yurts (Noga, PT)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Web/E-Mail</t>
+          <t>E-Mail + 3 PDF-Quotes</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dune</t>
+          <t>Noga -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
-        </is>
-      </c>
-      <c r="F16" s="18" t="inlineStr">
-        <is>
-          <t>⏳ Antwort offen</t>
+          <t>Preise: 6m=12.600 / 7m=14.400 / 9m=19.800 Jurte netto. Plattform separat: 6m=6.500 / 7m=7.200 / 9m=11.500. Transport+Install: 700/1.900, 900/2.500, 1.500/2.900. 23% IVA on top. 50% upfront NICHT-RUECKZAHLBAR. AUGUST 2026 Slot. Material laut Quote: Nordic Pine + Outer Canvas + 80mm Insulation (ohne Marken-Angabe). 2-J. Garantie auf Plane.</t>
+        </is>
+      </c>
+      <c r="F16" s="16" t="inlineStr">
+        <is>
+          <t>Quote erhalten</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5 Tage warten, dann WhatsApp/Tel.-Nachfrage. Telefon-Skript bereit.</t>
+          <t>Mail raus: Konkurrenz-Preis + Material-Aufschluesselung (Sauleda? PET?) anfordern</t>
         </is>
       </c>
     </row>
@@ -8437,7 +8437,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Toldos Etapaveloz (Loule, PT)</t>
+          <t>Dune Algarve Sailmakers (PT)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Etapaveloz</t>
+          <t>Sebastian -&gt; Dune</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>5 Tage warten, dann Folgekontakt</t>
+          <t>5 Tage warten, dann WhatsApp/Tel.-Nachfrage. Telefon-Skript bereit.</t>
         </is>
       </c>
     </row>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Textilux (Algarve, PT)</t>
+          <t>Toldos Etapaveloz (Loule, PT)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Textilux</t>
+          <t>Sebastian -&gt; Etapaveloz</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8492,51 +8492,51 @@
           <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
         </is>
       </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>✗ ABGELEHNT</t>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>⏳ Antwort offen</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>'nao sao da nossa especialidade' - klassischer Markisen-Hersteller, kein 3D-Persenning. Keine weitere Aktion.</t>
+          <t>5 Tage warten, dann Folgekontakt</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>~17.05.2026</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Paula Young (FB 'Paula Vegan Chef')</t>
+          <t>Textilux (Algarve, PT)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Facebook (offen)</t>
+          <t>Web/E-Mail</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Paula</t>
+          <t>Sebastian -&gt; Textilux</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Anfrage zur gebrauchten 7,3m Casa-Jurte</t>
-        </is>
-      </c>
-      <c r="F19" s="18" t="inlineStr">
-        <is>
-          <t>⏳ Kontakt steht aus</t>
+          <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
+        </is>
+      </c>
+      <c r="F19" s="17" t="inlineStr">
+        <is>
+          <t>✗ ABGELEHNT</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Ueber FB suchen ODER Sarah um Vermittlung bitten (in der naechsten Casa-Antwort mit aufnehmen)</t>
+          <t>'nao sao da nossa especialidade' - klassischer Markisen-Hersteller, kein 3D-Persenning. Keine weitere Aktion.</t>
         </is>
       </c>
     </row>
@@ -8548,30 +8548,67 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
+          <t>Paula Young (FB 'Paula Vegan Chef')</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Facebook (offen)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Paula</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage zur gebrauchten 7,3m Casa-Jurte</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>⏳ Kontakt steht aus</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Ueber FB suchen ODER Sarah um Vermittlung bitten (in der naechsten Casa-Antwort mit aufnehmen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F21" s="18" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -33,7 +33,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;EUR&quot;"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,6 +62,10 @@
     <font>
       <i val="1"/>
       <color rgb="00666666"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="002E5C8A"/>
     </font>
   </fonts>
   <fills count="7">
@@ -128,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -149,6 +153,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6218,18 +6225,18 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="10" t="n"/>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>WERKZEUG GESAMT</t>
         </is>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="D22" s="13" t="n">
         <v>1560</v>
       </c>
-      <c r="E22" s="10" t="n"/>
-      <c r="F22" s="10" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6270,7 +6277,7 @@
           <t>Khaana Edelkastanie + Bolzen</t>
         </is>
       </c>
-      <c r="B3" s="13" t="n">
+      <c r="B3" s="14" t="n">
         <v>1455</v>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -6285,7 +6292,7 @@
           <t>Tono fertig + Versand</t>
         </is>
       </c>
-      <c r="B4" s="13" t="n">
+      <c r="B4" s="14" t="n">
         <v>1000</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -6300,7 +6307,7 @@
           <t>Uni Sibir. Laerche + Befestigung</t>
         </is>
       </c>
-      <c r="B5" s="13" t="n">
+      <c r="B5" s="14" t="n">
         <v>982</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -6315,7 +6322,7 @@
           <t>Kuriye Spannband + Spannschloesser</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="14" t="n">
         <v>192</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -6330,7 +6337,7 @@
           <t>Tuer + Tuerbeschlaege A4</t>
         </is>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="14" t="n">
         <v>1350</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -6345,7 +6352,7 @@
           <t>Plattform komplett (Pfaehle, Tragwerk, Daemmung, Decke, Schrauben)</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>4040</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -6360,7 +6367,7 @@
           <t>Daemmung Wand+Dach (Schafwollfilz Isolena 16mm)</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>1680</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -6375,7 +6382,7 @@
           <t>Innenliner Baumwolle</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>780</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -6390,7 +6397,7 @@
           <t>Solitex-Membran (Diffusionsoffen)</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="14" t="n">
         <v>690</v>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -6405,7 +6412,7 @@
           <t>Aussenplane Sauleda Massanfertigung</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="14" t="n">
         <v>3500</v>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -6420,7 +6427,7 @@
           <t>Polycarbonat-Kuppel oeffenbar</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>750</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -6435,7 +6442,7 @@
           <t>Sturm-Kit (Erdanker + Ratschen)</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
         <v>456</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -6450,7 +6457,7 @@
           <t>Kaminzug-Durchfuehrung</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>280</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -6465,7 +6472,7 @@
           <t>Schattennetz Algarve</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>240</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -6480,7 +6487,7 @@
           <t>Reserve (10%)</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <v>1500</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -6495,7 +6502,7 @@
           <t>Werkzeug (Miete+Kauf, siehe Sheet 12)</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="14" t="n">
         <v>1378</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -6511,7 +6518,7 @@
           <t>ZWISCHENSUMME MATERIAL+WERKZEUG</t>
         </is>
       </c>
-      <c r="B20" s="14" t="n">
+      <c r="B20" s="15" t="n">
         <v>20273</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -6534,7 +6541,7 @@
           <t>Holz-Versand DE/AT-&gt;PT (Laerche, Robinie)</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="14" t="n">
         <v>600</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -6549,7 +6556,7 @@
           <t>Filz-Versand AT-&gt;PT (Isolena)</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="14" t="n">
         <v>250</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -6564,7 +6571,7 @@
           <t>Schraubpfaehle/Schrauben Inland PT</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -6579,7 +6586,7 @@
           <t>Plane-Lieferung</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="14" t="n">
         <v>150</v>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -6594,7 +6601,7 @@
           <t>Tono-Versand</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B27" s="14" t="n">
         <v>250</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -6610,7 +6617,7 @@
           <t>ZWISCHENSUMME VERSAND</t>
         </is>
       </c>
-      <c r="B29" s="14" t="n">
+      <c r="B29" s="15" t="n">
         <v>1250</v>
       </c>
       <c r="C29" s="3" t="inlineStr"/>
@@ -6629,7 +6636,7 @@
           <t>Geschaetzter Zeitaufwand</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="16" t="inlineStr">
         <is>
           <t>350-450 Std</t>
         </is>
@@ -6646,7 +6653,7 @@
           <t>Zeit-Aequivalent bei 30 EUR/h (rechnerisch)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>10.500-13.500 EUR</t>
         </is>
@@ -6664,7 +6671,7 @@
           <t>GESAMTKOSTEN DIY (Material+Werkzeug+Versand)</t>
         </is>
       </c>
-      <c r="B35" s="14" t="n">
+      <c r="B35" s="15" t="n">
         <v>21523</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -6687,7 +6694,7 @@
           <t>Casa dos Sonhos 7,3m (42 m2)</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n">
+      <c r="B38" s="14" t="n">
         <v>15750</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6702,7 +6709,7 @@
           <t>Casa Plattform separat</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n">
+      <c r="B39" s="14" t="n">
         <v>4000</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -6717,7 +6724,7 @@
           <t>Casa Sturm-Kit (Optionspreis offen)</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n">
+      <c r="B40" s="14" t="n">
         <v>800</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6732,7 +6739,7 @@
           <t>Casa Kaminzug (Optionspreis offen)</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n">
+      <c r="B41" s="14" t="n">
         <v>600</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -6747,7 +6754,7 @@
           <t>Casa Schattennetz</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n">
+      <c r="B42" s="14" t="n">
         <v>240</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6762,7 +6769,7 @@
           <t>CASA TOTAL APPLES-TO-APPLES (7,3m)</t>
         </is>
       </c>
-      <c r="B43" s="14" t="n">
+      <c r="B43" s="15" t="n">
         <v>21390</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -6778,7 +6785,7 @@
           <t>Casa 9,1m (64 m2)</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n">
+      <c r="B45" s="14" t="n">
         <v>18000</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -6793,7 +6800,7 @@
           <t>Casa 9,1m + Plattform + Sturm-Kit + Kamin</t>
         </is>
       </c>
-      <c r="B46" s="13" t="n">
+      <c r="B46" s="14" t="n">
         <v>23640</v>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -6816,7 +6823,7 @@
           <t>Material-Differenz DIY 8m vs Casa 7,3m all-in</t>
         </is>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>-130 EUR (Casa minimal teurer)</t>
         </is>
@@ -6833,7 +6840,7 @@
           <t>Was DIY trotzdem fuer dich bringen kann</t>
         </is>
       </c>
-      <c r="B50" s="15" t="inlineStr">
+      <c r="B50" s="16" t="inlineStr">
         <is>
           <t>Lernen + 50m2 statt 42m2 + 8m statt 7,3m + volle Kontrolle Materialwahl + keine 100% Vorauszahlung</t>
         </is>
@@ -6850,7 +6857,7 @@
           <t>Was DIY KOSTET (jenseits Geld)</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>350-450 Stunden Lebenszeit + Risiko Konstruktionsfehler + Werkzeug-Lernkurve</t>
         </is>
@@ -6867,7 +6874,7 @@
           <t>Empfehlung</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>Hybrid pruefen: Casa Plane+Daemmung kaufen, Plattform+Aufbau selbst</t>
         </is>
@@ -6892,7 +6899,7 @@
           <t>Konzept</t>
         </is>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>Skelett guenstig + Plane Premium + lokal verbauen</t>
         </is>
@@ -6909,7 +6916,7 @@
           <t>Adorjan 6m Rahmen (Khaana + Tono + Uni + Tuer)</t>
         </is>
       </c>
-      <c r="B56" s="13" t="n">
+      <c r="B56" s="14" t="n">
         <v>1750</v>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -6924,7 +6931,7 @@
           <t>Versand HU -&gt; Algarve (Sammelladung)</t>
         </is>
       </c>
-      <c r="B57" s="13" t="n">
+      <c r="B57" s="14" t="n">
         <v>1200</v>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -6939,7 +6946,7 @@
           <t>Sauleda Solar Pro Plane BEI LOKALEM ALGARVE-SATTLER</t>
         </is>
       </c>
-      <c r="B58" s="13" t="n">
+      <c r="B58" s="14" t="n">
         <v>2200</v>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -6954,7 +6961,7 @@
           <t>PET-Vlies-Daemmung 8 cm (60 m2 Wand+Dach)</t>
         </is>
       </c>
-      <c r="B59" s="13" t="n">
+      <c r="B59" s="14" t="n">
         <v>500</v>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -6969,7 +6976,7 @@
           <t>Solitex-Diffusions-Membran</t>
         </is>
       </c>
-      <c r="B60" s="13" t="n">
+      <c r="B60" s="14" t="n">
         <v>500</v>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -6984,7 +6991,7 @@
           <t>Tuer-Upgrade falls noetig (Glas-Doppeltuer)</t>
         </is>
       </c>
-      <c r="B61" s="13" t="n">
+      <c r="B61" s="14" t="n">
         <v>400</v>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -6999,7 +7006,7 @@
           <t>Plattform DIY (Schraubpfaehle + Holz)</t>
         </is>
       </c>
-      <c r="B62" s="13" t="n">
+      <c r="B62" s="14" t="n">
         <v>3000</v>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -7014,7 +7021,7 @@
           <t>Sturm-Verankerung Algarve</t>
         </is>
       </c>
-      <c r="B63" s="13" t="n">
+      <c r="B63" s="14" t="n">
         <v>400</v>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -7029,7 +7036,7 @@
           <t>Schattennetz Algarve</t>
         </is>
       </c>
-      <c r="B64" s="13" t="n">
+      <c r="B64" s="14" t="n">
         <v>240</v>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -7044,7 +7051,7 @@
           <t>Reserve / Verschnitt / Schrauben</t>
         </is>
       </c>
-      <c r="B65" s="13" t="n">
+      <c r="B65" s="14" t="n">
         <v>500</v>
       </c>
       <c r="C65" s="3" t="inlineStr"/>
@@ -7055,7 +7062,7 @@
           <t>ZWISCHENSUMME SZENARIO A</t>
         </is>
       </c>
-      <c r="B66" s="14" t="n">
+      <c r="B66" s="15" t="n">
         <v>10690</v>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -7070,7 +7077,7 @@
           <t>Werkzeug-Block bei DIY</t>
         </is>
       </c>
-      <c r="B67" s="13" t="n">
+      <c r="B67" s="14" t="n">
         <v>1378</v>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -7085,7 +7092,7 @@
           <t>TOTAL SZENARIO A (mit Werkzeug)</t>
         </is>
       </c>
-      <c r="B68" s="13" t="n">
+      <c r="B68" s="14" t="n">
         <v>12068</v>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -7108,7 +7115,7 @@
           <t>DIY Modify Szenario A 6m</t>
         </is>
       </c>
-      <c r="B71" s="13" t="n">
+      <c r="B71" s="14" t="n">
         <v>10690</v>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -7123,7 +7130,7 @@
           <t>Casa 6,1m (2027 Slot)</t>
         </is>
       </c>
-      <c r="B72" s="13" t="n">
+      <c r="B72" s="14" t="n">
         <v>14890</v>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -7138,7 +7145,7 @@
           <t>ERSPARNIS SZENARIO A</t>
         </is>
       </c>
-      <c r="B73" s="13" t="n">
+      <c r="B73" s="14" t="n">
         <v>-4200</v>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -7196,7 +7203,7 @@
           <t>Sebastians Vorgabe</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>8 m Durchmesser (50 m2)</t>
         </is>
@@ -7213,7 +7220,7 @@
           <t>Verfuegbare 8m-Anbieter</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Yourtepoque, Atilla, Adorjan, jurte24, YourTent CZ, Yurts4ever, DIY</t>
         </is>
@@ -7230,7 +7237,7 @@
           <t>Budget-Realitaet</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>8m all-in ca. 17.000-22.000 EUR</t>
         </is>
@@ -7255,7 +7262,7 @@
           <t>Idee</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Cheap Frame (HU) + Premium Plane (Sauleda lokal Algarve) + Selbst-Aufbau</t>
         </is>
@@ -7272,7 +7279,7 @@
           <t>Anbieter Frame</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Adorjan Jurta HU / Atilla HU / Yurts4ever RO</t>
         </is>
@@ -7289,7 +7296,7 @@
           <t>Anbieter Plane</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Dune Algarve Sailmakers (Vilamoura) / Toldos Etapaveloz (Loule) / Textilux</t>
         </is>
@@ -7314,7 +7321,7 @@
           <t>Adorjan 8m Frame-only (Khaana + Tono + Uni + Tuer)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>5000</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -7329,7 +7336,7 @@
           <t>Versand HU -&gt; Algarve 8m (heavier)</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="14" t="n">
         <v>2000</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -7344,7 +7351,7 @@
           <t>Sauleda Solar Pro Plane 8m (~150 m2 Stoff)</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>4500</v>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -7359,7 +7366,7 @@
           <t>PET-Vlies-Daemmung 8 cm (~110 m2 Wand+Dach)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="14" t="n">
         <v>900</v>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -7374,7 +7381,7 @@
           <t>Solitex Diffusions-Membran</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n">
+      <c r="B17" s="14" t="n">
         <v>700</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -7389,7 +7396,7 @@
           <t>Innenliner Baumwolle (~115 m2 Stoff)</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n">
+      <c r="B18" s="14" t="n">
         <v>1380</v>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -7404,7 +7411,7 @@
           <t>Kuppel-Oberlicht oeffenbar (Polycarbonat)</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="14" t="n">
         <v>1500</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -7419,7 +7426,7 @@
           <t>Tuer-Upgrade (Glas-Doppeltuer / franz. Doppeltuer)</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B20" s="14" t="n">
         <v>600</v>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -7442,7 +7449,7 @@
           <t>Plattform-Konstruktion (~50 m2)</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n">
+      <c r="B23" s="14" t="n">
         <v>4500</v>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -7457,7 +7464,7 @@
           <t>Vereinfachte Plattform (Budget-Variante)</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n">
+      <c r="B24" s="14" t="n">
         <v>3000</v>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -7480,7 +7487,7 @@
           <t>Sturm-Kit (Erdanker + Ratschen 5T)</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n">
+      <c r="B27" s="14" t="n">
         <v>500</v>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -7495,7 +7502,7 @@
           <t>Schattennetz Algarve (~75 m2)</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n">
+      <c r="B28" s="14" t="n">
         <v>350</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -7518,7 +7525,7 @@
           <t>Reserve / Verschnitt / Schrauben</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n">
+      <c r="B31" s="14" t="n">
         <v>800</v>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -7534,7 +7541,7 @@
           <t>GESAMTKOSTEN DIY-MODIFY 8M (Budget-Plattform, eigenes Werkzeug)</t>
         </is>
       </c>
-      <c r="B33" s="14" t="n">
+      <c r="B33" s="15" t="n">
         <v>23780</v>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -7549,7 +7556,7 @@
           <t>GESAMTKOSTEN DIY-MODIFY 8M (Premium-Plattform + neues Werkzeug)</t>
         </is>
       </c>
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="15" t="n">
         <v>26658</v>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -7564,7 +7571,7 @@
           <t>Yourtepoque 8m bleibt PREISSIEGER 8m</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="14" t="n">
         <v>19170</v>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -7579,7 +7586,7 @@
           <t>BLEIBT die Kompromiss-Option Casa 7,3m</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n">
+      <c r="B36" s="14" t="n">
         <v>20700</v>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -7594,7 +7601,7 @@
           <t>NEU ERKENNTNIS Mai 2026</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Adorjan/Atilla Engineering ist solide aber teurer als gedacht</t>
         </is>
@@ -7619,7 +7626,7 @@
           <t>Yourtepoque 8m (FR) + Plattform + Sturm/Schatten</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n">
+      <c r="B40" s="14" t="n">
         <v>19170</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -7634,7 +7641,7 @@
           <t>DIY-Modify 8m (Adorjan + Algarve-Sattler) Budget-Variante</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n">
+      <c r="B41" s="14" t="n">
         <v>17652</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -7649,7 +7656,7 @@
           <t>DIY-Modify 8m Premium-Variante</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n">
+      <c r="B42" s="14" t="n">
         <v>22030</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -7664,7 +7671,7 @@
           <t>Atilla 8m + Eichen-Upgrade + Plattform DIY</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="14" t="n">
         <v>21960</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -7679,7 +7686,7 @@
           <t>YourTent CZ 8m + Versand + Plattform</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="14" t="n">
         <v>21350</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7694,7 +7701,7 @@
           <t>jurte24 8m winterfest + Versand + Plattform</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n">
+      <c r="B45" s="14" t="n">
         <v>26250</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7717,7 +7724,7 @@
           <t>Casa 7,3m + Plattform DIY + Sturm/Schatten + Kamin</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
+      <c r="B48" s="14" t="n">
         <v>20700</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7740,7 +7747,7 @@
           <t>8m unter 18k machbar?</t>
         </is>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>JA - aber nur DIY-Modify Budget-Variante</t>
         </is>
@@ -7757,7 +7764,7 @@
           <t>8m unter 20k machbar?</t>
         </is>
       </c>
-      <c r="B52" s="15" t="inlineStr">
+      <c r="B52" s="16" t="inlineStr">
         <is>
           <t>JA - mehrere Wege</t>
         </is>
@@ -7774,7 +7781,7 @@
           <t>Empfohlene Strategie</t>
         </is>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>Adorjan + Atilla parallel anfragen (Mai 2026 gesendet), Sattler-Antworten abwarten, dann finalkalkulieren</t>
         </is>
@@ -7791,7 +7798,7 @@
           <t>Worst Case</t>
         </is>
       </c>
-      <c r="B54" s="15" t="inlineStr">
+      <c r="B54" s="16" t="inlineStr">
         <is>
           <t>8m geht nicht in Budget - dann Casa 7,3m als 2027-Slot oder Casa 6,1m sofort</t>
         </is>
@@ -7900,7 +7907,7 @@
           <t>Originale Anfrage 8m Komplett-Jurte</t>
         </is>
       </c>
-      <c r="F2" s="16" t="inlineStr">
+      <c r="F2" s="17" t="inlineStr">
         <is>
           <t>✓ Beantwortet</t>
         </is>
@@ -7937,7 +7944,7 @@
           <t>Frame-only Anfrage 8m (Khaana+Tono 120cm+60 Uni+Tuer)</t>
         </is>
       </c>
-      <c r="F3" s="16" t="inlineStr">
+      <c r="F3" s="17" t="inlineStr">
         <is>
           <t>✓ Beantwortet</t>
         </is>
@@ -7974,7 +7981,7 @@
           <t>ENGINEERING-KORREKTUR: 120cm Tono fuer 8m statisch zu klein (6cm Loch-Abstand). Atilla nutzt 180cm fuer 8m und 160cm fuer 6m. 60 Uni waeren auch zu wenig (schwache Wand bei 2m Hoehe). Fragt: jede Khaana-Spitze = ein Uni? Wuerde nur mit seinen Massen Verantwortung uebernehmen.</t>
         </is>
       </c>
-      <c r="F4" s="16" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
         <is>
           <t>Info erhalten - technisch wertvoll</t>
         </is>
@@ -8085,7 +8092,7 @@
           <t>8m Rahmen 3.220.000 HUF = 8.150 EUR netto. Spezifikation Top: 48 Rafters 5x10cm, Tono 170cm 4-lagig verleimt, Wand 2m, Pinie AT Biopin-impraegniert, isolierte Tuer Standard. Versand offen.</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F7" s="17" t="inlineStr">
         <is>
           <t>Info erhalten</t>
         </is>
@@ -8122,7 +8129,7 @@
           <t>Versand-Spediteur wird gesucht, kein Preis. 50% Anzahlung + 50% vor Versand. Installation extra (4 Pers + Fluege + Maschinen).</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Info erhalten</t>
         </is>
@@ -8196,7 +8203,7 @@
           <t>Empfehlen Kontempo (Holz-Rundhaus mit Zink-Dach) statt klassischer Jurte fuer Atlantik-Exposition. Devis komplett dauert noch. Bieten Visio-Call an.</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F10" s="17" t="inlineStr">
         <is>
           <t>Info erhalten</t>
         </is>
@@ -8233,7 +8240,7 @@
           <t>Anfrage 5/6,1/7,3/9,1m Preise + Konditionen</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>✓ Beantwortet</t>
         </is>
@@ -8270,7 +8277,7 @@
           <t>Preise bestaetigt: 5m 7.900 / 6,1m 9.700 / 7,3m 15.750 / 9,1m 18.000 EUR delivered+erected PT. Refs Brett (Quinta Glamping) + Paula Young (verkauft 7,3m gebraucht).</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F12" s="17" t="inlineStr">
         <is>
           <t>Quote erhalten</t>
         </is>
@@ -8307,7 +8314,7 @@
           <t>Quote 6,1m + 2.Tuer 850 + Flue-Kit 100 = 10.650 EUR. 1.000 EUR Anzahlung + 9.650 EUR am 1.8.2026. Lieferung 2. Oktoberwoche 2026.</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>Quote erhalten</t>
         </is>
@@ -8344,7 +8351,7 @@
           <t>SLOT OKTOBER 2026 ist an anderen Kunden vergeben. Naechster Slot 2027.</t>
         </is>
       </c>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="F14" s="18" t="inlineStr">
         <is>
           <t>✗ Slot verloren</t>
         </is>
@@ -8381,7 +8388,7 @@
           <t>Anfrage 6/7/9m Preise + Plattform + Aufbau Algarve</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F15" s="17" t="inlineStr">
         <is>
           <t>✓ Beantwortet</t>
         </is>
@@ -8418,7 +8425,7 @@
           <t>Preise: 6m=12.600 / 7m=14.400 / 9m=19.800 Jurte netto. Plattform separat: 6m=6.500 / 7m=7.200 / 9m=11.500. Transport+Install: 700/1.900, 900/2.500, 1.500/2.900. 23% IVA on top. 50% upfront NICHT-RUECKZAHLBAR. AUGUST 2026 Slot. Material laut Quote: Nordic Pine + Outer Canvas + 80mm Insulation (ohne Marken-Angabe). 2-J. Garantie auf Plane.</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F16" s="17" t="inlineStr">
         <is>
           <t>Quote erhalten</t>
         </is>
@@ -8455,7 +8462,7 @@
           <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
         </is>
       </c>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="F17" s="19" t="inlineStr">
         <is>
           <t>⏳ Antwort offen</t>
         </is>
@@ -8492,7 +8499,7 @@
           <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="19" t="inlineStr">
         <is>
           <t>⏳ Antwort offen</t>
         </is>
@@ -8529,7 +8536,7 @@
           <t>Anfrage Sauleda-Plane 8m Massanfertigung</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F19" s="18" t="inlineStr">
         <is>
           <t>✗ ABGELEHNT</t>
         </is>
@@ -8566,7 +8573,7 @@
           <t>Anfrage zur gebrauchten 7,3m Casa-Jurte</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="19" t="inlineStr">
         <is>
           <t>⏳ Kontakt steht aus</t>
         </is>
@@ -8603,7 +8610,7 @@
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="F21" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
@@ -8625,7 +8632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -8916,111 +8923,106 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Kleinanzeigen - Jurte Suche</t>
+          <t>PT-Marktanalyse: Kategorie 1-5 Uebersicht</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>kleinanzeigen.de</t>
+          <t>Multi-Plattform</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Deutschland weit</t>
+          <t>Portugal komplett</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>Marktreport</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1.000-15.000</t>
+          <t>Marktbeobachtung</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Neu bis stark gebraucht</t>
+          <t>Kategorisiert nach 5 Kategorien (Sofortkauf / Anfrage lohnt / Vorsicht / Plattform-Uebersicht / Spezielle Quellen)</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>https://www.kleinanzeigen.de/s-jurte/k0</t>
+          <t>Siehe einzelne Eintraege</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Ja - Spedition 500-1.500 EUR</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>Marktplatz, wechselnde Angebote, regelmaessig pruefen</t>
+          <t>ANALYSE: PT-Used-Markt klein - 3-5 aktive &gt;=6m Listings gleichzeitig. Konzentration Mafra/Lissabon, kaum Algarve-Lokal. Off-OLX-Leads (Sarah-Vermittlung) wertvoller als oeffentliche Marktplaetze. Empfehlung: OLX-Daily-Alert + FB-Gruppe Algarve 'Wanted'-Post + Sarah um weitere Vermittler bitten.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>eBay.de Jurten Kategorie</t>
+          <t>FB Gruppe 'For Sale or Swap in the Algarve'</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>eBay.de</t>
+          <t>facebook.com/groups</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Deutschland</t>
+          <t>Algarve - lokale Expat-Community</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>Variabel</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>200-10.000+</t>
+          <t>Variabel</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Variabel - meist neu/gebraucht aus Expat-Besitz</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.ebay.de/b/Jurte-Zelt/bn_7005694261</t>
+          <t>https://www.facebook.com/groups/FORSALEORSWAPINTHEALGARVE/</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Versand variiert</t>
+          <t>Lokal Algarve - kein Versand</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Auch Pfadfinder-Jurten (gross, billig, aber Plane nicht UV-fest)</t>
+          <t>Eigenen 'Wanted: 6-8m yurt' Post aufgeben. Beste Chance auf lokale Algarve-Funde direkt. Gross genug fuer Sichtbarkeit, lokal genug fuer Transport-Vorteil.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>eBay.co.uk Yurt</t>
+          <t>CustoJusto.pt</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>eBay UK</t>
+          <t>custojusto.pt</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Portugal weit</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -9030,91 +9032,91 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1.500-12.000</t>
+          <t>selten - meist &lt;500 EUR</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Gebraucht</t>
+          <t>Meist Spielzelte oder kleine Hobby-Jurten</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>https://www.ebay.co.uk/sch/i.html?_nkw=yurt</t>
+          <t>https://www.custojusto.pt/portugal?o=1&amp;q=yurt</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Ja - Brexit-Zoll bei Import nach PT (~7% Zoll + 23% IVA)</t>
+          <t>Inland PT</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Brexit verteuert UK-Importe stark</t>
+          <t>Sekundaerplattform, deutlich weniger Listings als OLX. 1-2 Listings typisch. Beobachten alle 2-4 Wochen.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>LeBonCoin Yourte</t>
+          <t>Kleinanzeigen - Jurte Suche</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>leboncoin.fr</t>
+          <t>kleinanzeigen.de</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Frankreich (variable)</t>
+          <t>Deutschland weit</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>10-50 m2</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1.500-20.000</t>
+          <t>1.000-15.000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Gebraucht</t>
+          <t>Neu bis stark gebraucht</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>https://www.leboncoin.fr/ck/ventes_immobilieres/yourte</t>
+          <t>https://www.kleinanzeigen.de/s-jurte/k0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Ja - Spedition FR-&gt;PT 800-1.500 EUR</t>
+          <t>Ja - Spedition 500-1.500 EUR</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Beispiel: 6m yourte mit Wollisolierung gelistet</t>
+          <t>Marktplatz, wechselnde Angebote, regelmaessig pruefen</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Wallapop Yurtas</t>
+          <t>eBay.de Jurten Kategorie</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>wallapop.com</t>
+          <t>eBay.de</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>Deutschland</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -9124,448 +9126,589 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>5.000-25.000</t>
+          <t>200-10.000+</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Gebraucht</t>
+          <t>Neu/gebraucht</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>https://es.wallapop.com/muebles-deco-y-jardin/yurtas</t>
+          <t>https://www.ebay.de/b/Jurte-Zelt/bn_7005694261</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>Ja - ES-&gt;PT guenstig 500-1.000 EUR</t>
+          <t>Versand variiert</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>9 Eintraege typischerweise gelistet</t>
+          <t>Auch Pfadfinder-Jurten (gross, billig, aber Plane nicht UV-fest)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Milanuncios Yurta</t>
+          <t>eBay.co.uk Yurt</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>milanuncios.com</t>
+          <t>eBay UK</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Spanien</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>diverse 40-80 m2</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22.500-42.000</t>
+          <t>1.500-12.000</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Gebraucht</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.milanuncios.com/anuncios/yurt-yurta.htm</t>
+          <t>https://www.ebay.co.uk/sch/i.html?_nkw=yurt</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Ja - Brexit-Zoll bei Import nach PT (~7% Zoll + 23% IVA)</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Komplett ausgestattet 27.500 EUR, ohne Moebel 22.500 EUR (Beispiel)</t>
+          <t>Brexit verteuert UK-Importe stark</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>OLX Portugal yurts (Kategorie-Uebersicht)</t>
+          <t>LeBonCoin Yourte</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>olx.pt</t>
+          <t>leboncoin.fr</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Frankreich (variable)</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>10-50 m2</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>variabel</t>
+          <t>1.500-20.000</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Gebraucht</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/</t>
+          <t>https://www.leboncoin.fr/ck/ventes_immobilieres/yourte</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Ja - innerhalb PT</t>
+          <t>Ja - Spedition FR-&gt;PT 800-1.500 EUR</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>INLAND PT - keine Zoll, kein Auslandsversand</t>
+          <t>Beispiel: 6m yourte mit Wollisolierung gelistet</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>OLX PT: Tenda Yurt Original Quirguistao (Palmela)</t>
+          <t>Wallapop Yurtas</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>olx.pt</t>
+          <t>wallapop.com</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>PT - Palmela (Setubal)</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28 m2 (ca. 6 m Durchmesser, 30 Personen)</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Anfrage</t>
+          <t>5.000-25.000</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Neu/handgefertigt (Originalimport Issyk-Kul Quirguistao)</t>
+          <t>Gebraucht</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/d/anuncio/tenda-yurt-original-do-quirguisto-yurt-tent-original-from-kyrgystan-IDHEwz9.html</t>
+          <t>https://es.wallapop.com/muebles-deco-y-jardin/yurtas</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Ja - PT-inland, Versand EXTRA (Region Lissabon)</t>
+          <t>Ja - ES-&gt;PT guenstig 500-1.000 EUR</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Marke 'Yourta', Modell 'Serenity'. Komplette Originalausstattung: Schilf-Geflecht, Wolle/Filz, Shyrdak-Teppich, Baskur-Band, Korpe-Kissen, geschnitzte Holztuer. Hand-Applikation. Keine Baugenehmigung noetig.</t>
+          <t>9 Eintraege typischerweise gelistet</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Yurt Workshop Secondhand</t>
+          <t>Milanuncios Yurta</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>yurtworkshop.com (Spanien)</t>
+          <t>milanuncios.com</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Spanien Granada</t>
+          <t>Spanien</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>5-7m</t>
+          <t>diverse 40-80 m2</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>3.000-10.000</t>
+          <t>22.500-42.000</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Gebraucht (vom Hersteller)</t>
+          <t>Neu/gebraucht</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>https://www.yurtworkshop.com/Buy_Your_Yurt/Second-Hand-Yurts-For-Sale.html</t>
+          <t>https://www.milanuncios.com/anuncios/yurt-yurta.htm</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Ja - ES-&gt;PT 600-1.200 EUR</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Vom Hersteller selbst - Qualitaet gepruef</t>
+          <t>Komplett ausgestattet 27.500 EUR, ohne Moebel 22.500 EUR (Beispiel)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Casa Dos Sonhos Secondhand</t>
+          <t>OLX Portugal yurts (Kategorie-Uebersicht)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Facebook Casa Dos Sonhos</t>
+          <t>olx.pt</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Portugal (Alentejo)</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5m</t>
+          <t>diverse</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Anfrage</t>
+          <t>variabel</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Gebraucht direkt vom Eigentuemer</t>
+          <t>Neu/gebraucht</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/yurtscasadossonhos/posts/3660919220624833/</t>
+          <t>https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Ja - inland PT</t>
+          <t>Ja - innerhalb PT</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Hersteller direkt, ggf. Garantie</t>
+          <t>INLAND PT - keine Zoll, kein Auslandsversand</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Yurt Market (worldwide)</t>
+          <t>OLX PT: Tenda Yurt Original Quirguistao (Palmela)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>yurtmarket.com</t>
+          <t>olx.pt</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>PT - Palmela (Setubal)</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>28 m2 (ca. 6 m Durchmesser, 30 Personen)</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>variabel</t>
+          <t>Anfrage</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Neu/gebraucht</t>
+          <t>Neu/handgefertigt (Originalimport Issyk-Kul Quirguistao)</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>https://www.yurtmarket.com/</t>
+          <t>https://www.olx.pt/d/anuncio/tenda-yurt-original-do-quirguisto-yurt-tent-original-from-kyrgystan-IDHEwz9.html</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Versand variiert je Anbieter</t>
+          <t>Ja - PT-inland, Versand EXTRA (Region Lissabon)</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Welt-Marktplatz</t>
+          <t>Marke 'Yourta', Modell 'Serenity'. Komplette Originalausstattung: Schilf-Geflecht, Wolle/Filz, Shyrdak-Teppich, Baskur-Band, Korpe-Kissen, geschnitzte Holztuer. Hand-Applikation. Keine Baugenehmigung noetig.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Yurt Forum Classifieds</t>
+          <t>Yurt Workshop Secondhand</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>yurtforum.com</t>
+          <t>yurtworkshop.com (Spanien)</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Spanien Granada</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>5-7m</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>variabel</t>
+          <t>3.000-10.000</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Gebraucht</t>
+          <t>Gebraucht (vom Hersteller)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.yurtforum.com/classifieds/</t>
+          <t>https://www.yurtworkshop.com/Buy_Your_Yurt/Second-Hand-Yurts-For-Sale.html</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Versand variiert</t>
+          <t>Ja - ES-&gt;PT 600-1.200 EUR</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Community-Marktplatz, oft USA-fokussiert</t>
+          <t>Vom Hersteller selbst - Qualitaet gepruef</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Groovy Yurts Clearance</t>
+          <t>Casa Dos Sonhos Secondhand</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>groovyyurts.com</t>
+          <t>Facebook Casa Dos Sonhos</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Kanada/USA</t>
+          <t>Portugal (Alentejo)</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>diverse</t>
+          <t>5m</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>USD 2.790-18.950</t>
+          <t>Anfrage</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Restposten/leicht gebraucht</t>
+          <t>Gebraucht direkt vom Eigentuemer</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>https://www.groovyyurts.com/catalogue-clearance-and-sale</t>
+          <t>https://www.facebook.com/yurtscasadossonhos/posts/3660919220624833/</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>Nein - hauptsaechlich Nordamerika; Versand teuer</t>
+          <t>Ja - inland PT</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Eher fuer US/CA - hohe Versandkosten nach EU/PT</t>
+          <t>Hersteller direkt, ggf. Garantie</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>Yurt Market (worldwide)</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>yurtmarket.com</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>variabel</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Neu/gebraucht</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurtmarket.com/</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Versand variiert je Anbieter</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Welt-Marktplatz</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Yurt Forum Classifieds</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>yurtforum.com</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>variabel</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Gebraucht</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yurtforum.com/classifieds/</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Versand variiert</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>Community-Marktplatz, oft USA-fokussiert</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Groovy Yurts Clearance</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>groovyyurts.com</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Kanada/USA</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>USD 2.790-18.950</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Restposten/leicht gebraucht</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.groovyyurts.com/catalogue-clearance-and-sale</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Nein - hauptsaechlich Nordamerika; Versand teuer</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Eher fuer US/CA - hohe Versandkosten nach EU/PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>Facebook Marketplace EU</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>facebook.com/marketplace</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Diverse EU</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>diverse</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>variabel</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>Gebraucht</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>https://www.facebook.com/marketplace/category/search/?query=yurt</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>Regional pruefen</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>Lokale Suche pro Land empfohlen</t>
         </is>
@@ -11833,7 +11976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -12021,10 +12164,8 @@
           <t>28 m2 (Kapazitaet 30 Personen)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Anfrage (Region Lissabon)</t>
-        </is>
+      <c r="E4" s="2" t="n">
+        <v>13000</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -12048,7 +12189,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>HOHE AUTHENTIZITAET: Originalimport aus Quirguistao, traditionelle Stickerei und Applikationen. PROBLEM ALGARVE: traditioneller Filz/Wolle nicht fuer 40C+ ausgelegt; Plane unter UV-Belastung anfaellig. Sehr dekorativ - eher fuer kuehlere Bergstandorte als heisse Algarve geeignet. Inserent in PT, kein Importzoll.</t>
+          <t>KATEGORIE ROT (NICHT EMPFOHLEN ALGARVE): HOHE AUTHENTIZITAET aber NICHT fuer Atlantikkueste. Traditioneller Filz/Wolle nicht fuer 40C+ ausgelegt; Plane unter UV-Belastung anfaellig; Salzluft schimmelt Wolle. Sehr dekorativ - eher fuer kuehlere Bergstandorte. 13.000 EUR fuer eine Deko-Jurte ist viel.</t>
         </is>
       </c>
     </row>
@@ -12062,13 +12203,21 @@
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>WICHTIG: OLX-Angebote aendern sich taeglich. Vor Anfrage Live-Suche unter https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/ pruefen. Recherche-Stand: 2026-05-11.</t>
+          <t>WICHTIG: OLX-Angebote aendern sich taeglich. Vor Anfrage Live-Suche unter https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/ pruefen. Recherche-Stand: 2026-05-21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>PT-USED-MARKT TIEFENSCAN MAI 2026: Markt ist klein - max 3-5 aktive &gt;=6m Listings gleichzeitig. Konzentration Mafra/Lissabon, kaum direkt in Algarve. EMPFOHLENE PLATTFORMEN ZUM BEOBACHTEN: 1) OLX.pt https://www.olx.pt/moveis-casa-e-jardim/q-yurts/ (Hauptkanal); 2) Facebook Marketplace Portugal + 'For Sale or Swap in the Algarve' Gruppe https://www.facebook.com/groups/FORSALEORSWAPINTHEALGARVE/ (eigenen Wanted-Post aufgeben!); 3) CustoJusto.pt https://www.custojusto.pt/ (selten); 4) Casa dos Sonhos Facebook https://www.facebook.com/yurtscasadossonhos/ (sporadische Secondhand-Posts); 5) Hipcamp + Workaway Algarve-Hosts direkt fragen (Glamping-Sites verkaufen manchmal). WICHTIGSTES OFF-MARKT-LEAD: Paula Young via Sarah-Vermittlung (gebrauchte 7,3m Casa-Jurte). EXPERTEN-FAZIT: Casa-Jurten kommen kaum auf Used-Markt (Hersteller-Wartelisten + Eigentuemer halten Jahre). Off-OLX-Leads (Sarah-Vermittlung, FB-Gruppe Wanted-Post) sind wertvoller als oeffentliche Marktplaetze.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A10:J10"/>
     <mergeCell ref="A8:J8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13965,21 +14114,21 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>GESAMTKOSTEN</t>
         </is>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="G32" s="13" t="n">
         <v>19805</v>
       </c>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -22,6 +22,7 @@
     <sheet name="DIY 13 Kostenrechnung" sheetId="13" state="visible" r:id="rId13"/>
     <sheet name="DIY 14 8m Modify Kalk" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="15 Kommunikations-Log" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="16 DIY Bauplan-Quellen" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8626,6 +8627,1692 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Kategorie</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Typ</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Sprache</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Bewertung 6-9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1 Pflicht-Quelle</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Paul King: 'The Complete Yurt Handbook'</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Buch (~25 EUR)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/Complete-Yurt-Handbook-Paul-King/dp/1899233083</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Standardwerk: 121 Seiten, 3 Jurten-Typen in mehreren Groessen, Materiallisten, Worked Examples. UNVERZICHTBAR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1 Pflicht-Quelle</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Paul King: 'Build Your Own Yurt' (Vorgaengerwerk)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Free PDF</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>https://azinelibrary.org/approved/build-your-own-yurt-1.pdf</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Kostenlos. 3m-Beispiel aber Logik skalierbar. Idealerweise VOR Buchkauf lesen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1 Pflicht-Quelle</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SimplyDifferently.org Yurt Calculator</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Web-Tool kostenlos</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://simplydifferently.org/Yurt_Notes</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>GOLDSTANDARD. Du gibst Durchmesser ein -&gt; exakte Latten-Anzahl, Bohrwinkel, Uni-Laengen, Tono-Bemassung. Pflicht.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>1 Pflicht-Quelle</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SimplyDifferently Construction PDF</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Free PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>https://simplydifferently.org/DL/yurt_construction_document.pdf</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Vertieftes PDF mit Konstruktions-Detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2 Plattform</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Pacific Yurts: 20 ft / 6,1 m Plattform-Plan</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Free PDF</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurts.com/wp-content/uploads/2023/12/20ft-Pacific-Yurts-Platform-Plan.pdf</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Direkt fuer 6,1m verwendbar. Standard-USA-Bauweise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>2 Plattform</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Yurts: 24 ft / 7,3 m Plattform-Plan</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Free PDF</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yurts.com/wp-content/uploads/2023/12/24ft-Pacific-Yurts-Platform-Plan.pdf</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Direkt fuer 7,3m. Fuer 8m um ~10% skalieren.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2 Plattform</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Pacific Yurts Setup Manual 20/24/30 ft</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Free PDF</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurts.com/wp-content/uploads/2023/12/Set-Up-Manual_20-24-30-Yurts.pdf</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Komplettes Aufbau-Manual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>2 Plattform</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Yurts Download-Hub</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Web-Hub</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yurts.com/downloads/</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Alle Pacific-Yurts-PDFs zentral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2 Plattform</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>That Yurt Blog: Foundations, Beams, Blocking</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Web-Artikel</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thatyurt.com/yurt-journal/yurt-platform-building-1/</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Detaillierte Foto-Doku Plattform-Aufbau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>2 Plattform</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Krinner Ground Screws</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Hersteller-Website</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Englisch/Deutsch</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.krinner.io/en/</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Schraubpfaehle-Marktfuehrer. KSF-M 800mm Standard fuer 8m-Yurte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2 Plattform</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Krinner Foundation Construction Guide</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Hersteller-Tutorial</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.krinner.io/en/foundation-construction/ground-screws/</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Schritt-fuer-Schritt Schraubpfahl-Einbau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2 Plattform</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Shelter Designs Platform Guide</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Web-Artikel</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shelterdesigns.net/learn-about-yurts/how-to-plan-your-yurt/how-to-build-a-yurt-platform/</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Alternative Plattform-Bauweise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>3 Khaana</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>The Delmer Yurt Blog: Khana</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Web-Foto-Doku</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>http://thedelmeryurt.blogspot.com/p/khana.html</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Detaillierte Foto-Schritte Khaana-Konstruktion. Sehr nuetzlich.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>3 Khaana</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>The Yurt Is Born: Assembling Lattice Wall</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Web-Tutorial</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>https://theyurtisborn.wordpress.com/2013/01/15/assembling-the-lattice-wall-section/</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Schritt-fuer-Schritt mit Tipps zur Bohr-Schablone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>3 Khaana</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ThePlywood.com - How to Make a Yurt</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Web-Tutorial</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://theplywood.com/yurt/</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Materialliste + Bauanleitung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>3 Khaana</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Outdoor Happens Homestead - Build a Yurt</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Web-Artikel</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.outdoorhappens.com/how-to-build-a-yurt/</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Materialliste + Kosten + DIY-Kit-Anbieter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>3 Khaana</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Instructables: Yurt Without Steel (10 Steps)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Web-Tutorial</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instructables.com/Yurt/</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Holz-only-Variante ohne Stahl-Schrauben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>4 Tono</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>The Delmer Yurt Blog: Crown</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Web-Foto-Doku</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>http://thedelmeryurt.blogspot.com/p/crown.html</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Tono-Konstruktion: 4-lagig verleimt, Bohrwinkel-Schablone, Dichtung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>4 Tono</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Solaripedia: Yurt Roof Ring</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Web-Artikel</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.solaripedia.com/13/318/3704/yurt_roof_ring.html</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Architektonische Detail-Beschreibung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>4 Tono</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Felting and Fiber Studio: Yurt Tono</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Blog-Artikel</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>https://feltingandfiberstudio.com/2013/08/29/yurt-tono-and-a-felting-party/amp/</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Tono-Bau Schritt-fuer-Schritt mit Filz-Detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>4 Tono</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Yurt Forum: DIY Center Ring</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Forum-Diskussion</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurtforum.com/forums/building-a-yurt-f3/diy-yurt-center-ring-any-ideas-529.html</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Community-Erfahrungen Tono selbst bauen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>5 Plane</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>The Delmer Yurt Blog: Canvas Exterior</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Web-Foto-Doku</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>http://thedelmeryurt.blogspot.com/p/canvas-exterior.html</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Schnittmuster + Naehtechnik. WICHTIG fuer Maß-Konsistenz.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>5 Plane</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Outdoor Sewing Solutions UK: Designing Your Yurt</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Web-Tutorial</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://outdoorsewingsolutions.co.uk/designing-your-yurt/</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Pattern-Designer-Tutorial mit Bemassungs-Logik.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>5 Plane</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Yurting: Sewing Canvas with Sailrite</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Blog-Artikel</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>https://diyode.com/blog/2014/01/yurting-sewing-the-canvas-with-the-sailrite-and-yurt-dwelling-tips/</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Industrie-Naehmaschinen-Tipps + Yurten-Leben.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>5 Plane</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Beowulf Industrial Sewing: Yurt Covers</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Web-Anbieter</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.beowulfsewing.com/yurt-covers</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Professionelle Cover-Naeher in USA. Konzepte uebertragbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>5 Plane</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Yurtcovers.com Broker Advice</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Web-Artikel</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>http://yurtcovers.com/yurtbroker-advice/</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Cover-Profi-Tipps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>6 Video</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Kents of Cornwall: Full Tutorial 5m</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=tBRt4yEqwYA</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Klassisch 5m, Logik fuer 6-8m uebertragbar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>6 Video</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>How to Build an ORON Yurt - Full Step by Step</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=8p_-3X1C7jA</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Moderne Bauweise, Komplett-Anleitung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>6 Video</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Building Yurt Platform &amp; Raising Playlist (30ft)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>YouTube Playlist</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/playlist?list=PLCu9QeIvVTyZjdRf3cY-y2CHOzrMahXHY</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>30-ft (9m) komplette Doku - direkt anwendbar fuer Sebastians 8m.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>6 Video</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Inside DIY Yurt - Registered Home in Germany</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=wNWlieH2ha0</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Wohnnutzung-Beispiel mit Bau-Genehmigung. Inspirations-Video.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>6 Video</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Strongest Yurt - Full Build</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=zIcRn50oh_E</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Robuste Bauweise fuer extremes Klima.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>6 Video</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Shelter Designs Video Library</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Web-Hub</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shelterdesigns.net/learn-about-yurts/yurt-building-videos/</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Mehrere Videos: Flooring, Framing, Wiring, Plumbing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>6 Video</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Couple Building YURT Timelapse</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/watch?v=-6f_GIqqZ8Y</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Komplett-Aufbau visualisiert in 15min Timelapse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>7 Step-by-Step Guide</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>HomeBiogas: DIY Yurt Complete Guide</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Web-Guide</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.homebiogas.com/blog/diy-yurt/</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Kompakte Komplett-Anleitung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>7 Step-by-Step Guide</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Outdoor Happens: Build a Yurt</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Web-Guide</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.outdoorhappens.com/how-to-build-a-yurt/</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Materialliste, Kosten, DIY-Kit-Anbieter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>7 Step-by-Step Guide</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Woodworkers Institute: Traditional Yurt</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Web-Guide</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>https://woodworkersinstitute.com/how-to-make-a-yurt/</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Handwerker-Perspektive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>7 Step-by-Step Guide</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Yurtnotes.com Illustrated Guide</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Web-Guide</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://yurtnotes.com/yurt-construction-a-helpful-illustrated-guide/</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Illustrierte Schritte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>7 Step-by-Step Guide</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Milkwood Permaculture: Yurt Resources</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Web-Guide</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.milkwood.net/2012/07/04/building-a-yurt-from-scratch-resources/</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Permakultur-Perspektive auf Bau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>8 Community</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Yurt Forum</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Forum</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurtforum.com/</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Hauptforum fuer DIY-Fragen, Bauprobleme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>8 Community</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Felting and Fiber Studio - Yurt Series</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Blog-Serie</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>https://feltingandfiberstudio.com/category/yurt/</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>51-Tage-Bau-Dokumentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>8 Community</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>YurtInfo.org - Plans</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Web-Hub</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurtinfo.org/yurt-plans</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Linkliste zu Plaenen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>8 Community</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>YurtInfo.org - Resources</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Web-Hub</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.yurtinfo.org/yurt-resources</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Allgemeine Ressourcen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>8 Community</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>YurtInfo.org - Bookstore</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Web-Hub</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.yurtinfo.org/yurt-bookstore</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Buch-Empfehlungen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>9 Engineering Wind</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Structural Basics: Wind Loads on Pitched Roofs</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Web-Artikel</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>https://structuralbasics.substack.com/p/wind-loads-on-pitched-roofs</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Wind-Last-Berechnung Schraegdach. Algarve-Atlantik-Wind kritisch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>9 Engineering Wind</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Omnicalculator: Wind Load Calculator</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Online-Rechner</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Englisch</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.omnicalculator.com/physics/wind-load</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Quick-Calc fuer Sturm-Auslegung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>10 Sebastian-Specs (8m)</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Tono Durchmesser</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>180 cm (Atilla-Standard, mit jeder Khaana-Spitze=Uni) oder 170 cm (Adorjan-Standard, mit 48 massiven 5x10cm Rafters)</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>EXTRA WICHTIG: 120 cm waere zu klein! Mehrfach bestaetigt durch Atilla + Adorjan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>10 Sebastian-Specs (8m)</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Uni Anzahl</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>48 (5x10cm massiv) ODER 64-80 (3,5x3,5cm klassisch)</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Wahl haengt von Tono-Bauart ab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>10 Sebastian-Specs (8m)</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Khaana-Latten</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>~380 Stueck, 30x10 mm, 2,1 m Laenge</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>8 Sektionen. Edelkastanie ideal fuer Algarve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>10 Sebastian-Specs (8m)</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Wandhoehe</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>2,00 m (Casa-Standard)</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Hoeher als traditionell mongolisch (1,70m).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>10 Sebastian-Specs (8m)</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Bohrwinkel Tono fuer Uni</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>30 Grad</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Mit Bohrlehre arbeiten - Wiederholgenauigkeit kritisch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>10 Sebastian-Specs (8m)</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Sturm-Verankerung Algarve</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Spec</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>8-10 Erdanker + 5-Tonnen Ratschen ueber Dach</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Atlantik-Wind bis 100 km/h - obligatorisch.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2597,6 +2597,162 @@
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Green World (Ukraine, Liefert PT)</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Ukraine, Vertrieb weltweit</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>https://greenworld.house/pt/yurts/</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>24 / 50 / 56 / 78 / 113 / 254 m2 (50m2 = 8m Durchmesser)</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage (Preisliste ab 01.01.2024)</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Vorgefertigter Holz-Frame, modular, durchnummeriert, mit Anleitung</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>10 JAHRE STRUKTUR-GARANTIE + 12 Mon. versteckte Maengel</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Lieferung in 9 Laender weltweit, auch PT. Versand ab UA per Spedition.</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>VERDACHT: moeglicher Verkaeufer hinter OLX-Listings IDJatvu + IDJbO7n (beide 8m). Produktion 2 Monate. Plane-Spec unklar (vermutlich Standard, nicht marine-grade). Ukraine-Hersteller -&gt; Versand- und politisches Risiko abklaeren. 8m / 50m2 koennte sehr wettbewerbsfaehig sein wenn Plane Algarve-tauglich ist.</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage (Schaetzung 8m/50m2 ca. 8.000-14.000 EUR + Versand)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Woodspot Solutions (PT)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.woodspotsolutions.com/pt/yurts-pt</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Inspiriert traditionellem Design, modernisiert fuer mehr Komfort</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Mittel - PT-lokal aber wenig Info im Netz</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Innerhalb PT - kein Import-Zoll</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Weiterer PT-Anbieter, weniger sichtbar als Casa/Bēt/Yonatan. Direktanfrage erforderlich.</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Anfrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Celtic Yurts (Galicia, ES)</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Spanien (Galicia, NW Iberia)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.celticyurts.com/en</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>diverse</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Preisliste auf Website</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Hochwertige Materialien, Strapazierfaehigkeit</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>Mittel - Galicien-Klima vergleichbar Nord-PT/Atlantikkueste</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>ES-&gt;PT relativ guenstig 500-1.500 EUR (Galicien grenzt an PT)</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Optional Selbstbau-Workshop (2-3 Wochen Werkstatt + fertige Jurte zum Mitnehmen).</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Anfrage</t>
         </is>
@@ -7833,7 +7989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8588,35 +8744,146 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>21.05.2026</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>OLX 8m Listing IDJatvu</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>OLX Direktansicht</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Sebastian (Recherche)</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Yurt 8m mit Panoramafenster - Listing entdeckt</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Details fehlen</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian muss Preis/Verkaeufer/Standort/Material teilen (Sandbox kann OLX nicht lesen). Verdacht: Green World UA Vertrieb.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>21.05.2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>OLX 8m Listing IDJbO7n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>OLX Direktansicht</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Sebastian (Recherche)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Yurt luxuosa NOVA 8m - Listing entdeckt (gleicher Verkaeufer wie IDJatvu?)</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>⏳ Details fehlen</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian muss Listing-Details teilen. Beide Listings wahrscheinlich derselbe Anbieter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Green World (Ukraine)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Web/E-Mail (zu pruefen)</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Green World</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Anfrage 8m / 50m2 Yurte fuer Algarve, 10-J. Strukturgarantie, Versandkosten PT, Plane-Spezifikation</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Anfrage moeglich</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>WENN OLX-Listings nicht von ihnen: trotzdem direkt anfragen ueber greenworld.house/pt/yurts/ - moeglicher 4. PT-Lieferant neben Casa/Bēt/Yonatan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F24" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -13663,7 +13930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -13880,22 +14147,126 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Ausgeschlossen (unter 6 m Mindestgroesse): 'Yurt mongol autentico Mafra' (5,5 m, 8.000 EUR) - https://www.olx.pt/d/anuncio/yurt-mongol-autntico-IDIR7sZ.html</t>
+    <row r="5" ht="110" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Yurt de 8 metros com janela panoramica (OLX neu Mai 2026)</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Standort tbd (Sebastian: Details bitte teilen)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>8 m</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>ca. 50 m2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Preis tbd</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Neu, mit Panoramafenster</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Konstruktion tbd - Sebastian Details aus Listing bitte teilen</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>tbd</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.olx.pt/d/anuncio/yurt-de-8-metros-de-dimetro-com-janela-panormica-IDJatvu.html</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>NEUFUND Mai 2026: 8m mit Panoramafenster. Wahrscheinlich vom selben Verkaeufer wie IDJbO7n (beide 8m Listings). MOEGLICHER ANBIETER: Green World (UA, Yurts ab 50m2/8m verfuegbar, 10-J. Struktur-Garantie). Details fehlen - Sebastian muss Preis/Verkaeufer/Standort teilen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Yurt luxuosa NOVA 8 metros (OLX neu Mai 2026)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Standort tbd (Sebastian: Details bitte teilen)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8 m</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>ca. 50 m2</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Preis tbd</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>NEU - Luxus-Variante</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Konstruktion tbd - Sebastian Details aus Listing bitte teilen</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>tbd</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.olx.pt/d/anuncio/yurt-luxuosa-nova-8-metros-de-dimetro-IDJbO7n.html</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>NEUFUND Mai 2026: 'Luxus' + 'NEU' 8m. Wahrscheinlich vom selben Verkaeufer wie IDJatvu (zwei verschiedene Stueck auf Lager). MOEGLICHER ANBIETER: Green World UA. Details fehlen - Sebastian muss Preis/Verkaeufer/Standort teilen.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
+          <t>Ausgeschlossen (unter 6 m Mindestgroesse): 'Yurt mongol autentico Mafra' (5,5 m, 8.000 EUR) - https://www.olx.pt/d/anuncio/yurt-mongol-autntico-IDIR7sZ.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
           <t>WICHTIG: OLX-Angebote aendern sich taeglich. Vor Anfrage Live-Suche unter https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/ pruefen. Recherche-Stand: 2026-05-21.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="120" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>PT-USED-MARKT TIEFENSCAN MAI 2026: Markt ist klein - max 3-5 aktive &gt;=6m Listings gleichzeitig. Konzentration Mafra/Lissabon, kaum direkt in Algarve. EMPFOHLENE PLATTFORMEN ZUM BEOBACHTEN: 1) OLX.pt https://www.olx.pt/moveis-casa-e-jardim/q-yurts/ (Hauptkanal); 2) Facebook Marketplace Portugal + 'For Sale or Swap in the Algarve' Gruppe https://www.facebook.com/groups/FORSALEORSWAPINTHEALGARVE/ (eigenen Wanted-Post aufgeben!); 3) CustoJusto.pt https://www.custojusto.pt/ (selten); 4) Casa dos Sonhos Facebook https://www.facebook.com/yurtscasadossonhos/ (sporadische Secondhand-Posts); 5) Hipcamp + Workaway Algarve-Hosts direkt fragen (Glamping-Sites verkaufen manchmal). WICHTIGSTES OFF-MARKT-LEAD: Paula Young via Sarah-Vermittlung (gebrauchte 7,3m Casa-Jurte). EXPERTEN-FAZIT: Casa-Jurten kommen kaum auf Used-Markt (Hersteller-Wartelisten + Eigentuemer halten Jahre). Off-OLX-Leads (Sarah-Vermittlung, FB-Gruppe Wanted-Post) sind wertvoller als oeffentliche Marktplaetze.</t>
         </is>
@@ -13903,7 +14274,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A12:J12"/>
     <mergeCell ref="A10:J10"/>
     <mergeCell ref="A8:J8"/>
   </mergeCells>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8749,7 +8749,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>OLX 8m Listing IDJatvu</t>
+          <t>OLX 8m Listing IDJatvu (Benedikt 'Yury')</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -8764,17 +8764,17 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Yurt 8m mit Panoramafenster - Listing entdeckt</t>
+          <t>Yurt 8m / 50m2 / 15.000 EUR / Gouveia / Verkaeufer Benedikt / Modell 'Yury' / NEU / inkl. Tuer+2 Fenster+weisser Innenstoff+Filzisolierung+'Gruendach'</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>⏳ Details fehlen</t>
+          <t>✓ Details bestaetigt</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Sebastian muss Preis/Verkaeufer/Standort/Material teilen (Sandbox kann OLX nicht lesen). Verdacht: Green World UA Vertrieb.</t>
+          <t>BENEDIKT KONTAKTIEREN: 11 konkrete Fragen (Hersteller? Plane-Material/UV? Filz-Typ? was ist 'Gruendach'? Holz? Tono-Durchmesser? Transport Aljezur? Aufbau? Garantie? Verkaufsgrund? Besichtigungstermin?). KRITISCH: vor Anzahlung physische Besichtigung Gouveia.</t>
         </is>
       </c>
     </row>
@@ -8786,7 +8786,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>OLX 8m Listing IDJbO7n</t>
+          <t>OLX 8m Listing IDJbO7n ('luxuosa nova')</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Yurt luxuosa NOVA 8m - Listing entdeckt (gleicher Verkaeufer wie IDJatvu?)</t>
+          <t>Yurt luxuosa NOVA 8m - vermutlich gleicher Verkaeufer (Benedikt?) - Sebastian muss Details teilen</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Sebastian muss Listing-Details teilen. Beide Listings wahrscheinlich derselbe Anbieter.</t>
+          <t>Wenn 2 Listings vom selben Verkaeufer = Benedikt ist Reseller mit Lager. Wichtig: 'luxuosa' Differenz zu 'Yury' verstehen (Material? Groesse? Preis?)</t>
         </is>
       </c>
     </row>
@@ -12093,7 +12093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12142,27 +12142,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>DIY Modify Szenario A (Adorjan-Rahmen + Algarve-Sauleda-Sattler)</t>
+          <t>OLX Benedikt 8m 'Yury' (Gouveia, Zentral-PT)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>DIY-Hybrid - lokaler PT-Sattler + HU-Rahmen</t>
+          <t>Privatverkauf NEU - 8m Komplett-Setup</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ca. 10.300-11.000 EUR all-in (6m)</t>
+          <t>15.000 EUR (inkl. Tuer + 2 Fenster + weisser Innenstoff + Filzisolierung + 'Gruendach')</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>NEUER SPITZENREITER seit Casa-Slot weg: Adorjan 6m Rahmen 1.750 + Versand 1.200 + Sauleda Marine-Acryl bei lokalem Algarve-Sattler 1.800-2.500 + PET-Daemmung 500 (Tobias Tumfart AT, 8,16€/m²) + Solitex 500 + Plattform DIY 3.000 + Sturm-Kit 400 + Schattennetz 240 + Reserve 500. PT-LOKALER SATTLER (z.B. Dune Algarve Sailmakers in Vilamoura) ist der Game-Changer: Sauleda Solar Pro Acryl ist objektiv BESSER als unspezifiziertes Casa-Canvas. 4.000-5.000 EUR Ersparnis vs Casa Wartezeit 2027. Sofortige Verfuegbarkeit. Volle Materialkontrolle. Risiko: Selbstaufbau-Skill, Maßabstimmung Rahmen-&gt;Plane, keine Komplett-Garantie.</t>
+          <t>BESTER 8M-PREIS IM MARKT (Mai 2026 entdeckt) - 50 m2 Wohnflaeche fuer 15k all-in passt EXAKT in Sebastian's Budget. Verkaeufer Benedikt = deutscher Reseller in Gouveia (Serra da Estrela), Inserat auf Deutsch = einfache Kommunikation. NEUWARE. Standort 4-5 h von Aljezur - Besichtigung machbar. ACHTUNG: Privatverkauf ohne Verbraucherschutz - vor Anzahlung: Besichtigung + Klaerung Plane-UV/Hersteller/Transport+Aufbau/Garantie/was-bedeutet-'Gruendach'. Modell 'Yury' deutet auf Green World UA Hersteller hin (10-J. Strukturgarantie wenn so).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://adorjan-jurta.hu/  |  https://www.dunesailmakers.com/</t>
+          <t>https://www.olx.pt/d/anuncio/yurt-de-8-metros-de-dimetro-com-janela-panormica-IDJatvu.html</t>
         </is>
       </c>
     </row>
@@ -12172,27 +12172,27 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Paula Young - gebrauchte Casa-Jurte 7,3m</t>
+          <t>DIY Modify Szenario A (Adorjan-Rahmen + Algarve-Sauleda-Sattler)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Used-Markt (Algarve direkt)</t>
+          <t>DIY-Hybrid - lokaler PT-Sattler + HU-Rahmen</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Schaetzung 8.000-11.000 EUR + Transport 1.000</t>
+          <t>ca. 10.300-11.000 EUR all-in (6m)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>ALGARVE-LEAD von Casa-Sarah selbst empfohlen: Paula Young (FB 'Paula Vegan Chef') verkauft 7,3m Casa-Jurte (42m²). Gebrauchte Casa-Qualitaet mit Original-Garantie-Resten. PHYSISCH VERIFIZIERBAR vor Kauf, kein Vorauszahlungs-Risiko, sofort verfuegbar, GROESSER als Casa 6,1m. Wichtige Pruefpunkte: Alter Plane (10-J. Casa-Garantie laeuft mit), Zustand Filz/Holz, Grund Verkauf, Algarve-Praxiserfahrung. Kontakt ueber Facebook-Suche oder Einfuehrung via Sarah Casa.</t>
+          <t>NEUER SPITZENREITER seit Casa-Slot weg: Adorjan 6m Rahmen 1.750 + Versand 1.200 + Sauleda Marine-Acryl bei lokalem Algarve-Sattler 1.800-2.500 + PET-Daemmung 500 (Tobias Tumfart AT, 8,16€/m²) + Solitex 500 + Plattform DIY 3.000 + Sturm-Kit 400 + Schattennetz 240 + Reserve 500. PT-LOKALER SATTLER (z.B. Dune Algarve Sailmakers in Vilamoura) ist der Game-Changer: Sauleda Solar Pro Acryl ist objektiv BESSER als unspezifiziertes Casa-Canvas. 4.000-5.000 EUR Ersparnis vs Casa Wartezeit 2027. Sofortige Verfuegbarkeit. Volle Materialkontrolle. Risiko: Selbstaufbau-Skill, Maßabstimmung Rahmen-&gt;Plane, keine Komplett-Garantie.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Facebook: 'Paula Vegan Chef' / Sarah Casa als Vermittler</t>
+          <t>https://adorjan-jurta.hu/  |  https://www.dunesailmakers.com/</t>
         </is>
       </c>
     </row>
@@ -12202,27 +12202,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Yurt Made in Portugal (Loures, OLX-Hersteller)</t>
+          <t>Paula Young - gebrauchte Casa-Jurte 7,3m</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Hersteller PT (Lissabon-Region)</t>
+          <t>Used-Markt (Algarve direkt)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5m 6.900 / 6m 8.400 / 7-8m Anfrage</t>
+          <t>Schaetzung 8.000-11.000 EUR + Transport 1.000</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>PT-LOKAL ALTERNATIVE zu Casa: junger Hersteller seit 2020 bei Lissabon. Kein Import-Zoll, kein Versandstress. Preise transparent auf OLX. Klima-Garantie &amp; UV-Spezifikation noch zu erfragen! Anfrage dringend lohnt sich, bevor andere Optionen verfolgt werden. Kontakt via OLX.pt.</t>
+          <t>ALGARVE-LEAD von Casa-Sarah selbst empfohlen: Paula Young (FB 'Paula Vegan Chef') verkauft 7,3m Casa-Jurte (42m²). Gebrauchte Casa-Qualitaet mit Original-Garantie-Resten. PHYSISCH VERIFIZIERBAR vor Kauf, kein Vorauszahlungs-Risiko, sofort verfuegbar, GROESSER als Casa 6,1m. Wichtige Pruefpunkte: Alter Plane (10-J. Casa-Garantie laeuft mit), Zustand Filz/Holz, Grund Verkauf, Algarve-Praxiserfahrung. Kontakt ueber Facebook-Suche oder Einfuehrung via Sarah Casa.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/d/anuncio/yurt-made-in-portugal-IDIyzPL.html</t>
+          <t>Facebook: 'Paula Vegan Chef' / Sarah Casa als Vermittler</t>
         </is>
       </c>
     </row>
@@ -12232,27 +12232,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>YourTent.com CZ (Praha)</t>
+          <t>Yurt Made in Portugal (Loures, OLX-Hersteller)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Hersteller CZ - 5J-Plane-Garantie</t>
+          <t>Hersteller PT (Lissabon-Region)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Schaetzung 12.000-16.000 EUR 6m inkl. Versand</t>
+          <t>5m 6.900 / 6m 8.400 / 7-8m Anfrage</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>BESTE PLANE-GARANTIE NACH CASA: 5 JAHRE Plane-Garantie (60 Monate). 150 Jurten in 12 Jahren gebaut, MEDITERRANEAN TRACK RECORD bis Kanarische Inseln + Polarkreis. LAERCHENHOLZ-Rahmen (Algarve-optimal). 180cm Standard-Wandhoehe, 50mm Schafwoll-Filz, franz. Doppeltuer Laerche, Skylight 150/180cm, Ofen-Vorbereitung. Online-Kalkulator + Anfrage. Versand CZ-&gt;PT ca. 1.500-2.500 EUR.</t>
+          <t>PT-LOKAL ALTERNATIVE zu Casa: junger Hersteller seit 2020 bei Lissabon. Kein Import-Zoll, kein Versandstress. Preise transparent auf OLX. Klima-Garantie &amp; UV-Spezifikation noch zu erfragen! Anfrage dringend lohnt sich, bevor andere Optionen verfolgt werden. Kontakt via OLX.pt.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>https://www.yourtent.com/</t>
+          <t>https://www.olx.pt/d/anuncio/yurt-made-in-portugal-IDIyzPL.html</t>
         </is>
       </c>
     </row>
@@ -12262,27 +12262,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos Yurts (2027er Slot)</t>
+          <t>YourTent.com CZ (Praha)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hersteller PT - 10-J. UV-Garantie SCHRIFTLICH</t>
+          <t>Hersteller CZ - 5J-Plane-Garantie</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6,1m 9.700 / 7,3m 15.750 EUR delivered+erected PT</t>
+          <t>Schaetzung 12.000-16.000 EUR 6m inkl. Versand</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>BLEIBT TOP-OPTION FUER LAENGEREN ZEITHORIZONT (2027+): Oktober 2026-Slot wurde 15.05.2026 an anderen Kunden vergeben. Naechster verfuegbarer Slot in 2027. Trotzdem das technisch beste Angebot fuer Algarve mit 10 J. UV-Garantie auf Plane, alles inkl. Lieferung+Aufbau in Festland-PT, portugiesische Materialien. Sarah &amp; Vladimir (UK-Familien-Betrieb) etabliert seit Jahren in Alegrete. NIPC: Empresario em Nome Individual. Verifizieren via Brett bei Quinta Glamping + Werkstatt-Besuch.</t>
+          <t>BESTE PLANE-GARANTIE NACH CASA: 5 JAHRE Plane-Garantie (60 Monate). 150 Jurten in 12 Jahren gebaut, MEDITERRANEAN TRACK RECORD bis Kanarische Inseln + Polarkreis. LAERCHENHOLZ-Rahmen (Algarve-optimal). 180cm Standard-Wandhoehe, 50mm Schafwoll-Filz, franz. Doppeltuer Laerche, Skylight 150/180cm, Ofen-Vorbereitung. Online-Kalkulator + Anfrage. Versand CZ-&gt;PT ca. 1.500-2.500 EUR.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.casadossonhos.co.uk/  |  https://www.facebook.com/yurtscasadossonhos/</t>
+          <t>https://www.yourtent.com/</t>
         </is>
       </c>
     </row>
@@ -12292,25 +12292,55 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>Casa dos Sonhos Yurts (2027er Slot)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Hersteller PT - 10-J. UV-Garantie SCHRIFTLICH</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>6,1m 9.700 / 7,3m 15.750 EUR delivered+erected PT</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>BLEIBT TOP-OPTION FUER LAENGEREN ZEITHORIZONT (2027+): Oktober 2026-Slot wurde 15.05.2026 an anderen Kunden vergeben. Naechster verfuegbarer Slot in 2027. Trotzdem das technisch beste Angebot fuer Algarve mit 10 J. UV-Garantie auf Plane, alles inkl. Lieferung+Aufbau in Festland-PT, portugiesische Materialien. Sarah &amp; Vladimir (UK-Familien-Betrieb) etabliert seit Jahren in Alegrete. NIPC: Empresario em Nome Individual. Verifizieren via Brett bei Quinta Glamping + Werkstatt-Besuch.</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.casadossonhos.co.uk/  |  https://www.facebook.com/yurtscasadossonhos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>Bēt Yurts (August 2026 Slot)</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Hersteller PT (Algarve direkt)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>6m 28.060 / 7m 31.940 / 9m 44.870 EUR all-in</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>ALGARVE-LOKAL ABER PREMIUM-PREIS: Konkretes Quote-PDF erhalten. Halb so teuer waere besser - DOPPELT SO TEUER wie Casa. 50% NICHT-RUECKZAHLBAR upfront, nur 2 JAHRE Plane-Garantie. Material laut Quote: 'Nordic Pine + Outer canvas + 80mm Insulation' OHNE Marken-/Herstellernennung (Marketing 'marine-grade' nicht im Quote bestaetigt). AUGUST 2026 Slot verfuegbar - Zeit-Vorteil. Nur empfehlenswert wenn andere Optionen ausfallen + August-Lieferung zwingend.</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>https://www.betyurts.com/</t>
         </is>
@@ -14150,12 +14180,12 @@
     <row r="5" ht="110" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Yurt de 8 metros com janela panoramica (OLX neu Mai 2026)</t>
+          <t>Yurt de 8 metros com janela panoramica (OLX neu Mai 2026) - Modell 'Yury' von Benedikt</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Standort tbd (Sebastian: Details bitte teilen)</t>
+          <t>Gouveia (Sao Pedro / Sao Juliao) - Serra da Estrela, Zentral-PT</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -14165,27 +14195,25 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>ca. 50 m2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Preis tbd</t>
-        </is>
+          <t>50 m2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>15000</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Neu, mit Panoramafenster</t>
+          <t>NEU (Neuware) - veroeffentlicht 06.05.2026, Verkaeufer Benedikt seit 07.2025 auf OLX</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Konstruktion tbd - Sebastian Details aus Listing bitte teilen</t>
+          <t>STANDARD INKL.: Tuer + 2 transparente Fenster + WEISSER INNENSTOFF + FILZISOLIERUNG + GRUENDACH (?). Modell 'Yury' (vermutlich Green World UA oder vergleichbar). Hersteller-Spezifikation muss erfragt werden.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>tbd</t>
+          <t>Innerhalb PT (Gouveia ~400 km von Aljezur). Transport/Aufbau muss erfragt werden ob enthalten.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -14195,7 +14223,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>NEUFUND Mai 2026: 8m mit Panoramafenster. Wahrscheinlich vom selben Verkaeufer wie IDJbO7n (beide 8m Listings). MOEGLICHER ANBIETER: Green World (UA, Yurts ab 50m2/8m verfuegbar, 10-J. Struktur-Garantie). Details fehlen - Sebastian muss Preis/Verkaeufer/Standort teilen.</t>
+          <t>SEHR STARKES ANGEBOT FUER 8M! 15.000 EUR ist GUENSTIGSTER 8m-PREIS AM MARKT (vs Yourtepoque 19k / Atilla 22k / DIY 24k / Casa 7,3m 20,7k). Verkaeufer Benedikt = deutscher Reseller in PT, deutsche Inserat-Sprache = einfache Kommunikation. ACHTUNG: Privatverkauf ohne Verbraucherschutz - vor Kauf besichtigen + Spec klaeren (Plane-Material/UV-Garantie, was ist 'Gruendach', Hersteller, Garantie, Transport+Aufbau).</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -545,7 +545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2755,6 +2755,53 @@
       <c r="J43" s="3" t="inlineStr">
         <is>
           <t>Anfrage</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Dani's Community-Projekt (Telegram-Kontakt Mai 2026, 7m im Bau)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Standort tbd (vermutlich PT, zu erfragen)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Aktuell 7m im Bau, lebt selbst in 8m, hat 6m als Gaeste-Jurte</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>tbd (Preis-Anfrage offen)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Eigenes Design seit 8 Jahren bewohnt - Familien-Projekt/Community. Bauen selbst. 7m war fuer daenische Familie geplant, jetzt verfuegbar.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Sehr gut potentiell - 8 Jahre eigene Praxiserfahrung mit dem Modell. Materialspec noch zu erfragen (Plane, Daemmung, Holz).</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Standort + Transport zu erfragen</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/ (Telegram-Gruppe Jurten Portugal - Direkt-Kontakt 'Dani')</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>BEMERKENSWERT: KEIN klassischer Hersteller/Reseller, sondern echtes Community-Projekt. 7m fertig August/September 2026 = schneller als Casa 2027. Du kannst noch Spezifikationen mitbestimmen wahrend Bau. 'Personal plans changed'-Story verifizierbar (daenische Familie blieb in DK). Anpassbar - Sebastian kann Algarve-spezifische Materialwuensche einbringen. PARALLEL HALTEN ZU BENEDIKT 8M (15k) UND CASA 2027.</t>
         </is>
       </c>
     </row>
@@ -7989,7 +8036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8855,35 +8902,146 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>~22.05.2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Telegram-Gruppe 'Jurten Portugal'</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Telegram-Post (DE)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Gruppe</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Eigene Wanted-Anfrage 6-8m Jurte fuer dauerhaftes Wohnen West-Algarve, 15k Budget</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>✓ Gepostet</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Auf Antworten warten - bisher 1 konkrete Antwort von 'Dani'</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026 07:00</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Dani (Telegram, Community-Projekt PT?)</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Dani -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Verkauft 7m Custom-Build noch im Bau. Eigenes Design, seit 8J in 8m gewohnt. Hatte fuer daenische Familie geplant - jetzt verfuegbar. 200cm Wand, 150cm Skylight, Schafwoll-Filz, 2 Doppeltueren. Fertig August/September 2026.</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>✓ Antwort erhalten</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian hat zurueckgeschrieben mit Standort+Specs+Preisfrage - warten auf Folge-Antwort</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026 07:07</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Dani (Telegram)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dani</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Standort? Algarve? Selbst gebaut? Materialspec (Fenster, Daemmungsdicke)? Preisvorstellung?</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>✓ Gesendet</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Auf Antwort warten - dann Material-/Preis-Bewertung</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
+      <c r="F27" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -2761,47 +2761,47 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Dani's Community-Projekt (Telegram-Kontakt Mai 2026, 7m im Bau)</t>
+          <t>Dani's Community-Projekt 7m Custom (Castelo de Vide, Alentejo)</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Standort tbd (vermutlich PT, zu erfragen)</t>
+          <t>Portugal - Castelo de Vide (Alto Alentejo, ca. 400 km von Aljezur)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Aktuell 7m im Bau, lebt selbst in 8m, hat 6m als Gaeste-Jurte</t>
+          <t>7m Innenflaeche ca. 38 m2, Mittelhoehe 360 cm, Dachneigung 28 Grad</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>tbd (Preis-Anfrage offen)</t>
+          <t>16.000 EUR inkl. Aufbau (Transport+Plattform extra)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Eigenes Design seit 8 Jahren bewohnt - Familien-Projekt/Community. Bauen selbst. 7m war fuer daenische Familie geplant, jetzt verfuegbar.</t>
+          <t>Khaana: PINIE-Scherengitter, 200cm Wandhoehe. Dachring (Tono): DOUGLASIE. Dachkuppel 150cm doppeltes Plexiglas (stufenlos oeffenbar, windfest). Tueren: 2 Hartholz-Doppeltueren 155x200cm zweifach verglast. Daemmung: NUR 4cm Schafwolle (duenn!). Innenstoff: 100% Biobaumwolltuch. Aussenstoff: BW/Polyester 50/50 Canvas (NICHT UV-langlebig).</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Sehr gut potentiell - 8 Jahre eigene Praxiserfahrung mit dem Modell. Materialspec noch zu erfragen (Plane, Daemmung, Holz).</t>
+          <t>GEMISCHT FUER ALGARVE: Konstruktion super (200cm Wand, atmungsaktiv, anti-Schimmel-Design, 28 Grad Dachneigung), ABER Aussenplane BW/Poly 50/50 haelt in Algarve-Sonne nur 3-5 Jahre ohne UV-Schutz. Dani gibt das SELBST ZU + empfiehlt UV-Schutz drueber legen oder regelmaessigen Canvas-Tausch. 4cm Schafwolle ist duenn (Vergleich Bēt 8cm PET, jurte24 dicker).</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Standort + Transport zu erfragen</t>
+          <t>Transport Castelo de Vide -&gt; Aljezur: 800-1.500 EUR. Aufbau IM 16k-Preis. Plattform bauen sie KEINE (Sebastian baut lokal: 3.000-4.500 EUR).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://t.me/ (Telegram-Gruppe Jurten Portugal - Direkt-Kontakt 'Dani')</t>
+          <t>Telegram Direkt-Kontakt 'Dani' (Gruppe Jurten Portugal)</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>BEMERKENSWERT: KEIN klassischer Hersteller/Reseller, sondern echtes Community-Projekt. 7m fertig August/September 2026 = schneller als Casa 2027. Du kannst noch Spezifikationen mitbestimmen wahrend Bau. 'Personal plans changed'-Story verifizierbar (daenische Familie blieb in DK). Anpassbar - Sebastian kann Algarve-spezifische Materialwuensche einbringen. PARALLEL HALTEN ZU BENEDIKT 8M (15k) UND CASA 2027.</t>
+          <t>STRATEGISCH WICHTIG: Probeschlafen im 6m-Modell ANGEBOTEN (= Casa-Style Verifikation moeglich!). Anpassbar waehrend Bau (Sebastian kann Sauleda-Plane statt Canvas vorschlagen = Hybrid-Idee). Fertig August/September 2026. Sebastian wohnt selbst seit 8 J. in einer baugleichen Jurte = echte Praxis. ABER all-in 20-22k + Canvas-Erneuerung alle 5-7 J. (+2-3,5k pro Zyklus) macht es teurer als Benedikt Yury 15k und Casa 7,3m bei 10-J. UV-Garantie. NUR EMPFEHLENSWERT mit Plane-Upgrade auf Sauleda/Tempotest.</t>
         </is>
       </c>
     </row>
@@ -8036,7 +8036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9013,35 +9013,109 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Dani (Castelo de Vide)</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Dani -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>FULL SPECS+PREIS: 16k inkl. Aufbau. Standort Castelo de Vide. Khaana Pinie 200cm Wand, Tono Douglasie 150cm, 2 Hartholz-Doppeltueren 155x200, Mittelhoehe 360cm, 28 Grad Dachneigung, 4cm Schafwolle, BW-Innenliner Bio, Canvas Aussen BW/Poly 50/50. Plattform/Transport extra. UV-Schutz Empfehlung drueber legen. PROBESCHLAFEN IM 6M-MODELL ANGEBOTEN!</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>✓ Volle Spec erhalten</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Antwort raus: Probeschlafen-Termin (Juni) + Plane-Upgrade-Anfrage (Sauleda statt Canvas) + Dickere Daemmung erfragen</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Dani (Castelo de Vide)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dani</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Wertschaetzende Antwort. Probeschlafen-Termin Juni Woche 2 oder 3 vorschlagen. Hybrid-Idee: Sauleda Marine-grade statt BW/Poly anfragen (ggf. ueber Algarve-Sattler in Vilamoura). Daemmungs-Upgrade auf 8cm erfragen.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Sebastians naechste Aktion - Antwort raus, Termin festlegen</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F27" s="19" t="inlineStr">
+      <c r="F29" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8036,7 +8036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Wertschaetzende Antwort. Probeschlafen-Termin Juni Woche 2 oder 3 vorschlagen. Hybrid-Idee: Sauleda Marine-grade statt BW/Poly anfragen (ggf. ueber Algarve-Sattler in Vilamoura). Daemmungs-Upgrade auf 8cm erfragen.</t>
+          <t>Wertschaetzende Antwort. Probeschlafen-Termin Juni Woche 2 oder 3 vorschlagen. Hybrid-Idee: Sauleda Marine-grade statt BW/Poly anfragen (ggf. ueber Algarve-Sattler in Vilamoura). Daemmungs-Upgrade auf 8cm erfragen (geschaetzt +600-800 EUR).</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -9087,35 +9087,72 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F29" s="19" t="inlineStr">
+      <c r="F30" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -23,6 +23,7 @@
     <sheet name="DIY 14 8m Modify Kalk" sheetId="14" state="visible" r:id="rId14"/>
     <sheet name="15 Kommunikations-Log" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="16 DIY Bauplan-Quellen" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="17 Plattform 7m Kostenrechnung" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -133,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -179,6 +180,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10849,6 +10853,823 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Guenstigste isolierte Plattform 7m fuer Algarve-Winter (Sebastians Wunsch Mai 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Menge</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Einheit</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Gesamt EUR</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>VARIANTE A - Absolut guenstig EPS-Daemmung</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Cheapest fuer 41 m² Plattform; Schimmel-Risiko langfristig</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Plattform-Durchmesser 7,2 m (41 m² Flaeche)</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>7,2 m</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Aussen</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Yurt 7m + 10cm Ueberstand</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Fundament Stein-/min. Beton 8 Punkte</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>145</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Lokal beschaffbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Tragbalken Kiefer KDI 50x200x4m</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>700</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Leroy Merlin / AKI / Bauhaus PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Schrauben+Beschlaege A4</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Wuerth PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PE-Folie 200 µ</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus 2 EUR/m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>EPS 100mm WLG 035 (R~2,8)</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>205</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Cheapest aber nicht atmungsaktiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>OSB-Verlegeplatte 22mm Deck</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>410</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Bedeckbar mit Teppich</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Boden-Schrauben Spax A4</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Reserve 10%</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>175</v>
+      </c>
+      <c r="E12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>VARIANTE A TOTAL</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="15" t="n">
+        <v>1925</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Absolutes Minimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="8" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>VARIANTE B - Eco-guenstig mit KORK EMPFEHLUNG</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>Portugiesisches Material, atmungsaktiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Fundament Stein-/Beton 8 Punkte</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>145</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Tragbalken Kiefer KDI 50x200x4m</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n">
+        <v>25</v>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>700</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Schrauben+Beschlaege A4</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>PE-Folie 200 µ</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>KORK 80mm Sofalca/Amorim (R~2,0)</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="n">
+        <v>738</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Portugiesisches Material, diffusionsoffen</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Kiefer KDI T+G Boden 22mm</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n">
+        <v>738</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Schoenere Optik</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Boden-Schrauben</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Reserve 10%</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n">
+        <v>270</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>VARIANTE B TOTAL</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="15" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>EMPFEHLUNG - 955 mehr als A, dafuer oeko+atmungsaktiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>VARIANTE C - Variante B + Krinner statt Beton</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Kein Beton, vollstaendig reversibel</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Krinner KSF-M 800mm Schraubpfaehle</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>Stueck</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="n">
+        <v>280</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Statt Stein/Beton</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Erdraketen-Miete oder Eigenhand</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Pauschal</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus PT, oder per Hand 4 Std Arbeit gratis</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Rest wie Variante B (Tragwerk+Kork+Deck+Schrauben+Reserve)</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr"/>
+      <c r="C29" s="20" t="inlineStr"/>
+      <c r="D29" s="14" t="n">
+        <v>2735</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>VARIANTE C TOTAL</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="15" t="n">
+        <v>3095</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Top-Setup: kein Beton + oeko + Kork</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="8" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>R-WERT VERGLEICH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>EPS 100mm Plattform</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr"/>
+      <c r="C33" s="20" t="inlineStr"/>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>R~2,8</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Sehr gut thermisch nicht atmungsaktiv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Kork 80mm Plattform</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr"/>
+      <c r="C34" s="20" t="inlineStr"/>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>R~2,0</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Gut + diffusionsoffen</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="27" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Dani Wand 4cm Schafwolle</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="20" t="inlineStr"/>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>R~1,0</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Plattform mit Kork ist DOPPELT so gut wie Danis Wand - kompensiert kalte Fuesse im Algarve-Winter</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>PT-LIEFERANTEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Kiefer KDI Tragwerk</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="20" t="inlineStr"/>
+      <c r="D38" s="16" t="inlineStr"/>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Leroy Merlin / AKI / Bauhaus PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Kork 80mm</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="20" t="inlineStr"/>
+      <c r="D39" s="16" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Sofalca (Coruche) https://www.sofalca.pt/ ODER Amorim (Santa Maria) https://www.amorim.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>OSB / Kiefer-Boden</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="20" t="inlineStr"/>
+      <c r="D40" s="16" t="inlineStr"/>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Bauhaus / Leroy Merlin / AKI</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Schrauben A4</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr"/>
+      <c r="C41" s="20" t="inlineStr"/>
+      <c r="D41" s="16" t="inlineStr"/>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Wuerth Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Krinner-Pfaehle</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr"/>
+      <c r="C42" s="20" t="inlineStr"/>
+      <c r="D42" s="16" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Krinner DE-Versand oder Bauhaus PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="8" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>INTEGRATION DANI 7M + KORK-PLATTFORM</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Dani 7m mit Aufbau</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="inlineStr"/>
+      <c r="C45" s="20" t="inlineStr"/>
+      <c r="D45" s="14" t="n">
+        <v>16000</v>
+      </c>
+      <c r="E45" s="3" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Plattform Variante B (Kork DIY)</t>
+        </is>
+      </c>
+      <c r="B46" s="20" t="inlineStr"/>
+      <c r="C46" s="20" t="inlineStr"/>
+      <c r="D46" s="14" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Transport Castelo de Vide -&gt; Aljezur</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="inlineStr"/>
+      <c r="C47" s="20" t="inlineStr"/>
+      <c r="D47" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Schaetzung 400km</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Werkzeug-Block (falls neu)</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr"/>
+      <c r="C48" s="20" t="inlineStr"/>
+      <c r="D48" s="14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>0 wenn vorhanden</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Schattennetz Algarve</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr"/>
+      <c r="C49" s="20" t="inlineStr"/>
+      <c r="D49" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="E49" s="3" t="inlineStr"/>
+    </row>
+    <row r="50" ht="29" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL ALL-IN</t>
+        </is>
+      </c>
+      <c r="B50" s="20" t="inlineStr"/>
+      <c r="C50" s="20" t="inlineStr"/>
+      <c r="D50" s="15" t="n">
+        <v>20420</v>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Kork-Plattform spart 1.000-2.000 vs Casa-Style Premium-Plattform = Spielraum fuer 8cm Schafwolle-Upgrade bei Dani</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A44:E44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -2780,22 +2780,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>16.000 EUR inkl. Aufbau (Transport+Plattform extra)</t>
+          <t>16.000 EUR inkl. Aufbau (Transport+Plattform extra). UPGRADES MOEGLICH: Sauleda-Plane +1.100 EUR Material, 8cm Wolle +400 EUR Material</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Khaana: PINIE-Scherengitter, 200cm Wandhoehe. Dachring (Tono): DOUGLASIE. Dachkuppel 150cm doppeltes Plexiglas (stufenlos oeffenbar, windfest). Tueren: 2 Hartholz-Doppeltueren 155x200cm zweifach verglast. Daemmung: NUR 4cm Schafwolle (duenn!). Innenstoff: 100% Biobaumwolltuch. Aussenstoff: BW/Polyester 50/50 Canvas (NICHT UV-langlebig).</t>
+          <t>Khaana: PINIE-Scherengitter, 200cm Wandhoehe. Dachring (Tono): DOUGLASIE. Dachkuppel 150cm doppeltes Plexiglas (stufenlos oeffenbar, windfest). Tueren: 2 Hartholz-Doppeltueren 155x200cm zweifach verglast. Daemmung: Standard 4cm Schafwolle (8cm Upgrade moeglich wenn Sebastian Material besorgt). Innenstoff: 100% Biobaumwolltuch. Aussenstoff: BW/Polyester 50/50 Canvas Standard ueber ESVO NL (1.400 EUR fuer 7m); ALTERNATIVE STOFFE wenn unter 420g/m² (Sauleda Solar Pro 290-340g/m² oder Tempotest Marine ✓) - Sebastian besorgt selbst, Dani naeht.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>GEMISCHT FUER ALGARVE: Konstruktion super (200cm Wand, atmungsaktiv, anti-Schimmel-Design, 28 Grad Dachneigung), ABER Aussenplane BW/Poly 50/50 haelt in Algarve-Sonne nur 3-5 Jahre ohne UV-Schutz. Dani gibt das SELBST ZU + empfiehlt UV-Schutz drueber legen oder regelmaessigen Canvas-Tausch. 4cm Schafwolle ist duenn (Vergleich Bēt 8cm PET, jurte24 dicker).</t>
+          <t>VERHANDELBAR: Dani ist sehr flexibel - naeht gerne anderen Stoff bis 420g/m² Maschinen-Limit, macht gerne dickere Daemmung wenn Sebastian Material liefert. SAULEDA SOLAR PRO ist langfristig guenstiger als 5-Jahres-Canvas-Tausch.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Transport Castelo de Vide -&gt; Aljezur: 800-1.500 EUR. Aufbau IM 16k-Preis. Plattform bauen sie KEINE (Sebastian baut lokal: 3.000-4.500 EUR).</t>
+          <t>Transport Castelo de Vide -&gt; Aljezur: 800-1.500 EUR. Aufbau IM 16k-Preis. Plattform bauen sie KEINE (Sebastian baut lokal: 2.880 EUR Kork-Variante, siehe Sheet 17).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>STRATEGISCH WICHTIG: Probeschlafen im 6m-Modell ANGEBOTEN (= Casa-Style Verifikation moeglich!). Anpassbar waehrend Bau (Sebastian kann Sauleda-Plane statt Canvas vorschlagen = Hybrid-Idee). Fertig August/September 2026. Sebastian wohnt selbst seit 8 J. in einer baugleichen Jurte = echte Praxis. ABER all-in 20-22k + Canvas-Erneuerung alle 5-7 J. (+2-3,5k pro Zyklus) macht es teurer als Benedikt Yury 15k und Casa 7,3m bei 10-J. UV-Garantie. NUR EMPFEHLENSWERT mit Plane-Upgrade auf Sauleda/Tempotest.</t>
+          <t>TOP-EMPFEHLUNG WENN UPGRADES MACHBAR: Dani 16k + Sauleda-Upgrade 1.100 + 8cm-Wolle 400 + Plattform Kork 2.880 + Transport 1.000 + Schattennetz 240 = ~21.620 EUR all-in. Spar gegenueber Canvas-5J-Tausch ueber 10J ca. 1.200 EUR. PLUS: 4 Familien-Community vor Ort fuer Sebastians Familie sehr willkommen.</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9054,7 +9054,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>23.05.2026 08:20</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -9074,89 +9074,163 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Wertschaetzende Antwort. Probeschlafen-Termin Juni Woche 2 oder 3 vorschlagen. Hybrid-Idee: Sauleda Marine-grade statt BW/Poly anfragen (ggf. ueber Algarve-Sattler in Vilamoura). Daemmungs-Upgrade auf 8cm erfragen (geschaetzt +600-800 EUR).</t>
+          <t>Unverbindliche Anfrage: alternative Aussenhuelle moeglich? Falls nein - Lebensdauer/Erneuerung/Kosten Canvas-Tausch nach 5J? 8cm Schafwolle moeglich+Aufpreis? Probeschlafen mit Frau+2 Kindern - Wann passt es bei euch?</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Sebastians naechste Aktion - Antwort raus, Termin festlegen</t>
+          <t>Antwort erhalten 12:47</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>23.05.2026 12:47</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dani -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>EXTREM HILFREICHE ANTWORT: 1) Plane: naeht gerne anderen Stoff bis MASCHINEN-LIMIT 420g/m². Standard ueber ESVO NL = 1.400 EUR fuer 7m. UV-Schutz drueber laesst Stoff laenger halten. 2) Daemmung: 8cm prinzipiell ok, Sebastian muss selbst Material besorgen (aktuell kein AT-Bezug). 3) Sommer-Tipps: Fallschirm/Schattennetz drueber, Kuppel-Ueberzieher gegen direkte Einstrahlung. 4) Probeschlafen: 6m-Jurte besetzt bis Mitte Juni, danach evtl. Luecke. Besuch jederzeit ok. 4 Familien+Kinder vor Ort.</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Vollantwort - sehr flexibel</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian antwortet: Sauleda/Tempotest erwaehnen (passt unter 420g/m²), 8cm Wolle selber besorgen (Isolena/Tumfart), Besuch in 2./3. Juniwoche vorschlagen</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Dani (Castelo de Vide)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dani</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Lockere Antwort in Sebastian-Stil: Sauleda/Tempotest checken (290-340g/m²), 8cm Schafwolle selber besorgen, Kuppel-Ueberzieher-Tipp aufgenommen, Besuch 2./3. Juniwoche vorschlagen (Wohnwagen/Hotel falls noetig), bei Glueck spaeter Uebernachtung in 6m.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian's Antwort raus - Termin warten</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F30" s="19" t="inlineStr">
+      <c r="F32" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -13183,7 +13257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -13232,27 +13306,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>OLX Benedikt 8m 'Yury' (Gouveia, Zentral-PT)</t>
+          <t>Dani Castelo de Vide 7m + Sauleda-Upgrade + 8cm Schafwolle + Kork-Plattform</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Privatverkauf NEU - 8m Komplett-Setup</t>
+          <t>Custom-Bau PT (Community-Projekt) - flexibel verhandelbar</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>15.000 EUR (inkl. Tuer + 2 Fenster + weisser Innenstoff + Filzisolierung + 'Gruendach')</t>
+          <t>~21.620 EUR all-in (16k Dani + 1.100 Sauleda + 400 Wolle 8cm + 2.880 Plattform + 1.000 Transport + 240 Schatten)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>BESTER 8M-PREIS IM MARKT (Mai 2026 entdeckt) - 50 m2 Wohnflaeche fuer 15k all-in passt EXAKT in Sebastian's Budget. Verkaeufer Benedikt = deutscher Reseller in Gouveia (Serra da Estrela), Inserat auf Deutsch = einfache Kommunikation. NEUWARE. Standort 4-5 h von Aljezur - Besichtigung machbar. ACHTUNG: Privatverkauf ohne Verbraucherschutz - vor Anzahlung: Besichtigung + Klaerung Plane-UV/Hersteller/Transport+Aufbau/Garantie/was-bedeutet-'Gruendach'. Modell 'Yury' deutet auf Green World UA Hersteller hin (10-J. Strukturgarantie wenn so).</t>
+          <t>NEUE TOP-EMPFEHLUNG seit Dani 23.05.2026: Maximum-flexibler Custom-Bau bei einer 8-Jahre-erfahrenen Familie in PT. Spec aushandelbar: Sauleda Solar Pro (290-340g/m², passt unter 420g/m² Maschinen-Limit) statt Standard-Canvas + 8cm Schafwolle statt 4cm (Sebastian besorgt selbst). Probeschlafen-Option, Community-Kontakt fuer Sebastians Familie. Casa-Wartezeit 2027 entfaellt, Lieferung bereits Aug/Sep 2026. STRUKTUR: 200cm Wand, 360cm Mittelhoehe, 150cm Tono Douglasie, 28° Dachneigung, 2 Hartholz-Doppeltueren 155x200cm. Standort Castelo de Vide ca. 400km - Transport ueberschaubar.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/d/anuncio/yurt-de-8-metros-de-dimetro-com-janela-panormica-IDJatvu.html</t>
+          <t>https://t.me/ (Telegram Direktkontakt 'Dani' in Gruppe 'Jurten Portugal')</t>
         </is>
       </c>
     </row>
@@ -13262,27 +13336,27 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>DIY Modify Szenario A (Adorjan-Rahmen + Algarve-Sauleda-Sattler)</t>
+          <t>OLX Benedikt 8m 'Yury' (Gouveia, Zentral-PT)</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>DIY-Hybrid - lokaler PT-Sattler + HU-Rahmen</t>
+          <t>Privatverkauf NEU - 8m Komplett-Setup</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>ca. 10.300-11.000 EUR all-in (6m)</t>
+          <t>15.000 EUR (inkl. Tuer + 2 Fenster + weisser Innenstoff + Filzisolierung + 'Gruendach')</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>NEUER SPITZENREITER seit Casa-Slot weg: Adorjan 6m Rahmen 1.750 + Versand 1.200 + Sauleda Marine-Acryl bei lokalem Algarve-Sattler 1.800-2.500 + PET-Daemmung 500 (Tobias Tumfart AT, 8,16€/m²) + Solitex 500 + Plattform DIY 3.000 + Sturm-Kit 400 + Schattennetz 240 + Reserve 500. PT-LOKALER SATTLER (z.B. Dune Algarve Sailmakers in Vilamoura) ist der Game-Changer: Sauleda Solar Pro Acryl ist objektiv BESSER als unspezifiziertes Casa-Canvas. 4.000-5.000 EUR Ersparnis vs Casa Wartezeit 2027. Sofortige Verfuegbarkeit. Volle Materialkontrolle. Risiko: Selbstaufbau-Skill, Maßabstimmung Rahmen-&gt;Plane, keine Komplett-Garantie.</t>
+          <t>BESTER 8M-PREIS IM MARKT (Mai 2026 entdeckt) - 50 m2 Wohnflaeche fuer 15k all-in. Verkaeufer Benedikt = deutscher Reseller in Gouveia (Serra da Estrela), Inserat auf Deutsch. NEUWARE. Standort 4-5 h von Aljezur. ACHTUNG: Privatverkauf ohne Verbraucherschutz - vor Anzahlung: Besichtigung + Klaerung Plane-UV/Hersteller/Transport/Garantie/'Gruendach'. Modell 'Yury' deutet auf Green World UA Hersteller hin.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>https://adorjan-jurta.hu/  |  https://www.dunesailmakers.com/</t>
+          <t>https://www.olx.pt/d/anuncio/yurt-de-8-metros-de-dimetro-com-janela-panormica-IDJatvu.html</t>
         </is>
       </c>
     </row>
@@ -13292,27 +13366,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Paula Young - gebrauchte Casa-Jurte 7,3m</t>
+          <t>DIY Modify Szenario A (Adorjan-Rahmen + Algarve-Sauleda-Sattler)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Used-Markt (Algarve direkt)</t>
+          <t>DIY-Hybrid - lokaler PT-Sattler + HU-Rahmen</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Schaetzung 8.000-11.000 EUR + Transport 1.000</t>
+          <t>ca. 10.300-11.000 EUR all-in (6m)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>ALGARVE-LEAD von Casa-Sarah selbst empfohlen: Paula Young (FB 'Paula Vegan Chef') verkauft 7,3m Casa-Jurte (42m²). Gebrauchte Casa-Qualitaet mit Original-Garantie-Resten. PHYSISCH VERIFIZIERBAR vor Kauf, kein Vorauszahlungs-Risiko, sofort verfuegbar, GROESSER als Casa 6,1m. Wichtige Pruefpunkte: Alter Plane (10-J. Casa-Garantie laeuft mit), Zustand Filz/Holz, Grund Verkauf, Algarve-Praxiserfahrung. Kontakt ueber Facebook-Suche oder Einfuehrung via Sarah Casa.</t>
+          <t>NEUER SPITZENREITER seit Casa-Slot weg: Adorjan 6m Rahmen 1.750 + Versand 1.200 + Sauleda Marine-Acryl bei lokalem Algarve-Sattler 1.800-2.500 + PET-Daemmung 500 (Tobias Tumfart AT, 8,16€/m²) + Solitex 500 + Plattform DIY 3.000 + Sturm-Kit 400 + Schattennetz 240 + Reserve 500. PT-LOKALER SATTLER (z.B. Dune Algarve Sailmakers in Vilamoura) ist der Game-Changer: Sauleda Solar Pro Acryl ist objektiv BESSER als unspezifiziertes Casa-Canvas. 4.000-5.000 EUR Ersparnis vs Casa Wartezeit 2027. Sofortige Verfuegbarkeit. Volle Materialkontrolle. Risiko: Selbstaufbau-Skill, Maßabstimmung Rahmen-&gt;Plane, keine Komplett-Garantie.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Facebook: 'Paula Vegan Chef' / Sarah Casa als Vermittler</t>
+          <t>https://adorjan-jurta.hu/  |  https://www.dunesailmakers.com/</t>
         </is>
       </c>
     </row>
@@ -13322,27 +13396,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Yurt Made in Portugal (Loures, OLX-Hersteller)</t>
+          <t>Paula Young - gebrauchte Casa-Jurte 7,3m</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Hersteller PT (Lissabon-Region)</t>
+          <t>Used-Markt (Algarve direkt)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>5m 6.900 / 6m 8.400 / 7-8m Anfrage</t>
+          <t>Schaetzung 8.000-11.000 EUR + Transport 1.000</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>PT-LOKAL ALTERNATIVE zu Casa: junger Hersteller seit 2020 bei Lissabon. Kein Import-Zoll, kein Versandstress. Preise transparent auf OLX. Klima-Garantie &amp; UV-Spezifikation noch zu erfragen! Anfrage dringend lohnt sich, bevor andere Optionen verfolgt werden. Kontakt via OLX.pt.</t>
+          <t>ALGARVE-LEAD von Casa-Sarah selbst empfohlen: Paula Young (FB 'Paula Vegan Chef') verkauft 7,3m Casa-Jurte (42m²). Gebrauchte Casa-Qualitaet mit Original-Garantie-Resten. PHYSISCH VERIFIZIERBAR vor Kauf, kein Vorauszahlungs-Risiko, sofort verfuegbar, GROESSER als Casa 6,1m. Wichtige Pruefpunkte: Alter Plane (10-J. Casa-Garantie laeuft mit), Zustand Filz/Holz, Grund Verkauf, Algarve-Praxiserfahrung. Kontakt ueber Facebook-Suche oder Einfuehrung via Sarah Casa.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/d/anuncio/yurt-made-in-portugal-IDIyzPL.html</t>
+          <t>Facebook: 'Paula Vegan Chef' / Sarah Casa als Vermittler</t>
         </is>
       </c>
     </row>
@@ -13352,27 +13426,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>YourTent.com CZ (Praha)</t>
+          <t>Yurt Made in Portugal (Loures, OLX-Hersteller)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hersteller CZ - 5J-Plane-Garantie</t>
+          <t>Hersteller PT (Lissabon-Region)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Schaetzung 12.000-16.000 EUR 6m inkl. Versand</t>
+          <t>5m 6.900 / 6m 8.400 / 7-8m Anfrage</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>BESTE PLANE-GARANTIE NACH CASA: 5 JAHRE Plane-Garantie (60 Monate). 150 Jurten in 12 Jahren gebaut, MEDITERRANEAN TRACK RECORD bis Kanarische Inseln + Polarkreis. LAERCHENHOLZ-Rahmen (Algarve-optimal). 180cm Standard-Wandhoehe, 50mm Schafwoll-Filz, franz. Doppeltuer Laerche, Skylight 150/180cm, Ofen-Vorbereitung. Online-Kalkulator + Anfrage. Versand CZ-&gt;PT ca. 1.500-2.500 EUR.</t>
+          <t>PT-LOKAL ALTERNATIVE zu Casa: junger Hersteller seit 2020 bei Lissabon. Kein Import-Zoll, kein Versandstress. Preise transparent auf OLX. Klima-Garantie &amp; UV-Spezifikation noch zu erfragen! Anfrage dringend lohnt sich, bevor andere Optionen verfolgt werden. Kontakt via OLX.pt.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.yourtent.com/</t>
+          <t>https://www.olx.pt/d/anuncio/yurt-made-in-portugal-IDIyzPL.html</t>
         </is>
       </c>
     </row>
@@ -13382,27 +13456,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos Yurts (2027er Slot)</t>
+          <t>YourTent.com CZ (Praha)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Hersteller PT - 10-J. UV-Garantie SCHRIFTLICH</t>
+          <t>Hersteller CZ - 5J-Plane-Garantie</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>6,1m 9.700 / 7,3m 15.750 EUR delivered+erected PT</t>
+          <t>Schaetzung 12.000-16.000 EUR 6m inkl. Versand</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>BLEIBT TOP-OPTION FUER LAENGEREN ZEITHORIZONT (2027+): Oktober 2026-Slot wurde 15.05.2026 an anderen Kunden vergeben. Naechster verfuegbarer Slot in 2027. Trotzdem das technisch beste Angebot fuer Algarve mit 10 J. UV-Garantie auf Plane, alles inkl. Lieferung+Aufbau in Festland-PT, portugiesische Materialien. Sarah &amp; Vladimir (UK-Familien-Betrieb) etabliert seit Jahren in Alegrete. NIPC: Empresario em Nome Individual. Verifizieren via Brett bei Quinta Glamping + Werkstatt-Besuch.</t>
+          <t>BESTE PLANE-GARANTIE NACH CASA: 5 JAHRE Plane-Garantie (60 Monate). 150 Jurten in 12 Jahren gebaut, MEDITERRANEAN TRACK RECORD bis Kanarische Inseln + Polarkreis. LAERCHENHOLZ-Rahmen (Algarve-optimal). 180cm Standard-Wandhoehe, 50mm Schafwoll-Filz, franz. Doppeltuer Laerche, Skylight 150/180cm, Ofen-Vorbereitung. Online-Kalkulator + Anfrage. Versand CZ-&gt;PT ca. 1.500-2.500 EUR.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>https://www.casadossonhos.co.uk/  |  https://www.facebook.com/yurtscasadossonhos/</t>
+          <t>https://www.yourtent.com/</t>
         </is>
       </c>
     </row>
@@ -13412,25 +13486,55 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>Casa dos Sonhos Yurts (2027er Slot)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Hersteller PT - 10-J. UV-Garantie SCHRIFTLICH</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,1m 9.700 / 7,3m 15.750 EUR delivered+erected PT</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>BLEIBT TOP-OPTION FUER LAENGEREN ZEITHORIZONT (2027+): Oktober 2026-Slot wurde 15.05.2026 an anderen Kunden vergeben. Naechster verfuegbarer Slot in 2027. Trotzdem das technisch beste Angebot fuer Algarve mit 10 J. UV-Garantie auf Plane, alles inkl. Lieferung+Aufbau in Festland-PT, portugiesische Materialien. Sarah &amp; Vladimir (UK-Familien-Betrieb) etabliert seit Jahren in Alegrete. NIPC: Empresario em Nome Individual. Verifizieren via Brett bei Quinta Glamping + Werkstatt-Besuch.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.casadossonhos.co.uk/  |  https://www.facebook.com/yurtscasadossonhos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>Bēt Yurts (August 2026 Slot)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Hersteller PT (Algarve direkt)</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>6m 28.060 / 7m 31.940 / 9m 44.870 EUR all-in</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>ALGARVE-LOKAL ABER PREMIUM-PREIS: Konkretes Quote-PDF erhalten. Halb so teuer waere besser - DOPPELT SO TEUER wie Casa. 50% NICHT-RUECKZAHLBAR upfront, nur 2 JAHRE Plane-Garantie. Material laut Quote: 'Nordic Pine + Outer canvas + 80mm Insulation' OHNE Marken-/Herstellernennung (Marketing 'marine-grade' nicht im Quote bestaetigt). AUGUST 2026 Slot verfuegbar - Zeit-Vorteil. Nur empfehlenswert wenn andere Optionen ausfallen + August-Lieferung zwingend.</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>https://www.betyurts.com/</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -2780,12 +2780,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>16.000 EUR inkl. Aufbau (Transport+Plattform extra). UPGRADES MOEGLICH: Sauleda-Plane +1.100 EUR Material, 8cm Wolle +400 EUR Material</t>
+          <t>16.000 EUR inkl. Aufbau (Transport+Plattform extra). UPGRADES MOEGLICH: Sauleda-Plane +1.100 EUR Material, 8cm Wolle +400 EUR Material. NICHT moeglich: zusaetzliche Fenster (Waende schon fertig).</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Khaana: PINIE-Scherengitter, 200cm Wandhoehe. Dachring (Tono): DOUGLASIE. Dachkuppel 150cm doppeltes Plexiglas (stufenlos oeffenbar, windfest). Tueren: 2 Hartholz-Doppeltueren 155x200cm zweifach verglast. Daemmung: Standard 4cm Schafwolle (8cm Upgrade moeglich wenn Sebastian Material besorgt). Innenstoff: 100% Biobaumwolltuch. Aussenstoff: BW/Polyester 50/50 Canvas Standard ueber ESVO NL (1.400 EUR fuer 7m); ALTERNATIVE STOFFE wenn unter 420g/m² (Sauleda Solar Pro 290-340g/m² oder Tempotest Marine ✓) - Sebastian besorgt selbst, Dani naeht.</t>
+          <t>Khaana: PINIE-Scherengitter, 200cm Wandhoehe. Dachring (Tono): DOUGLASIE. Dachkuppel 150cm doppeltes Plexiglas (stufenlos oeffenbar, windfest). Tueren: 2 Hartholz-Doppeltueren 155x200cm zweifach verglast (= 4,8 m² Glasflaeche durch Tueren, plus 1,77 m² Skylight). KEINE zusaetzlichen Wandfenster moeglich. Daemmung: Standard 4cm Schafwolle (8cm Upgrade moeglich wenn Sebastian Material besorgt - Schafwolle PT-Bezug schwierig, Kontakt 'Chris' via Dani-Vermittlung). Innenstoff: 100% Biobaumwolltuch. Aussenstoff: BW/Polyester 50/50 Canvas Standard ueber ESVO NL (1.400 EUR fuer 7m); ALTERNATIVE STOFFE wenn unter 420g/m² (Sauleda Solar Pro 290-340g/m² oder Tempotest Marine ✓) - Sebastian besorgt selbst, Dani naeht.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Telegram Direkt-Kontakt 'Dani' (Gruppe Jurten Portugal)</t>
+          <t>Telegram Direkt-Kontakt 'Dani' (Gruppe Jurten Portugal). RECHTSFORM: AKTUELL Privatverkauf an Freunde (Verein in Gruendung). Zahlung: Anzahlung als Commitment + flexible Teilzahlungen, ueberweisen ODER PAYPAL (= PayPal-Kaeuferschutz potentiell nutzbar). Kontakt Chris (PT-Schafwolle) via Dani vermittelbar.</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>TOP-EMPFEHLUNG WENN UPGRADES MACHBAR: Dani 16k + Sauleda-Upgrade 1.100 + 8cm-Wolle 400 + Plattform Kork 2.880 + Transport 1.000 + Schattennetz 240 = ~21.620 EUR all-in. Spar gegenueber Canvas-5J-Tausch ueber 10J ca. 1.200 EUR. PLUS: 4 Familien-Community vor Ort fuer Sebastians Familie sehr willkommen.</t>
+          <t>TOP-EMPFEHLUNG WENN UPGRADES MACHBAR: Dani 16k + Sauleda-Upgrade 1.100 + 8cm-Wolle 400 + Plattform Kork 2.880 + Transport 1.000 + Schattennetz 240 = ~21.620 EUR all-in. Spar gegenueber Canvas-5J-Tausch ueber 10J ca. 1.200 EUR. PLUS: 4 Familien-Community vor Ort fuer Sebastians Familie sehr willkommen. PAYPAL-OPTION fuer Anzahlung = wichtiges Sicherheitsnetz fuer Privatverkauf.</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9165,72 +9165,331 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>23.05.2026 12:53</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Sebastian -&gt; Dani</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Findet alles super, Frau kommt naechste Woche, meldet sich dann fuer Termin. Daemmung kann auch in PT bezogen werden (Recherche). Aug/Sep-Lieferzeit passt. Fragt: Bezahlung? Aufpreis zusaetzliches Fenster?</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Antwort erhalten 14:06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>23.05.2026 14:06</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Dani (Castelo de Vide)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Dani -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>WICHTIGE EINSCHRAENKUNG: ZUSAETZLICHES FENSTER NICHT MOEGLICH - Waende sind schon fertig. Umbau bis September nicht machbar. Schafwolle-Bezug schwierig - neuer Anbieter 'Chris' hat in Schafwolldaemmungs-Post in Gruppe geantwortet. Dani bietet Chris-Kontakt-Vermittlung an.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>✓ Eingeschraenkt aber transparent</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Chris-Vermittlung annehmen!</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026 14:09</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Dani (Castelo de Vide)</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dani</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Fragt nach Bezahlungsmoeglichkeiten und Firmenstruktur</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>✓ Gesendet</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>Antwort 14:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026 14:11</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Dani (Castelo de Vide)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Dani -&gt; Sebastian</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>ZAHLUNG: Anzahlung als Commitment, danach Teilbetraege verhandelbar. UEBERWEISUNG ODER PAYPAL (aufteilbar!) - PayPal-Kaeuferschutz potentiell nutzbar. AKTUELL: Privatverkauf an Freunde (kein Gewerbe, keine MwSt., keine Verbraucher-Rechte). Verein in Gruendung - dann ueber Verein.</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>✓ Flexibel + PayPal-Option</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>PayPal als Risiko-Absicherung wichtig</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026 15:29</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Dani (Castelo de Vide)</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dani</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>'Super 👍🏼' - kurzes Acknowledgement</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>✓ Gesendet</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>FOLGE: Chris-Vermittlung explizit annehmen + Anfang-Juni Besuchstermin avisieren</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>24.05.2026 (Sebastians Folge)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Dani (Castelo de Vide)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dani</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Chris-Vermittlung annehmen + Anfang Juni Besuchstermin avisieren (mit Frau)</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Wartet auf Frauen-Rueckkehr fuer Termin-Fixierung</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>Chris (PT-Schafwoll-Anbieter via Dani)</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Telegram (geplant)</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Chris</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Schafwolle 8cm fuer 7m Jurte, Liefermenge ca. 50 m², Algarve-Klima beraten, Aufpreis vs 4cm</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Vermittlung steht aus</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>Wenn Dani vermittelt: Chris direkt anschreiben</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F32" s="19" t="inlineStr">
+      <c r="F39" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9429,67 +9429,215 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Mikael (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Mikael -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Bietet NEUE komplette 8m Jurte an, 2.10m Wandhoehe, sofort lieferbar, auch Massanfertigung anderer moeglich</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Angebot erhalten</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Mikael DM: Standort? Preis? Cover-Material UV? Fotos? Hersteller oder privat?</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>Mikael (Telegram)</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Mikael</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Antwort kurz: 8m mit 2.10m Wand passt zu Plaenen Algarve. Frage: Standort? Preis? Cover-Material (UV-resistent?)? Fotos? Hersteller oder privat?</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>Wartet auf Mikaels Antwort mit Specs+Preis</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Dror (Telegram-Gruppe)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Telegram-Post</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Dror -&gt; Gruppe</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>✓ Wertvoller Kontakt</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F39" s="19" t="inlineStr">
+      <c r="F43" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G43" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9486,12 +9486,12 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>Wartet auf Mikaels Antwort mit Specs+Preis</t>
+          <t>Antwort von Mikael erhalten</t>
         </is>
       </c>
     </row>
@@ -9503,44 +9503,44 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Mickaël) Gouveia/Guarda</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>VOLLSPEC + 3 FOTOS: 8m Yurt, 15.000 EUR + Versand. Standort GOUVEIA/GUARDA (gleicher Ort wie Benedikt 'Yury'!). Material: Canvas Standard mit EXTRA VINYL-OVERLAY-OPTION (Vinyl-Dach hat 2 zusaetzliche Oeffnungen, muesste 2 extra Fenster bauen). KONSTRUKTION: HOLZWAND-Style (vertikale Bretter, NICHT traditionelle Khaana - sieht nach Pacific-Yurts-Style aus). AC4-LAMINAT-FLOORING INKLUSIVE. Empfiehlt Sommer-Schattennetz.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Erste Daten erhalten</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>VERDACHT: Mikael+Benedikt selber Verkaeufer oder verbunden (Gouveia+15k+8m). Sebastian fragt direkt nach. Folge-Fragen: Hersteller? Holz? Was in 15k? Versand-Schaetzung? Aufgebaut/neu? Mehr Fotos? Besuch Anfang Juni?</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Mickaël)</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Folge-Fragen: Verbindung zu Benedikt direkt erfragt + Hersteller/Wandholz/Behandlung + was genau in 15k + Versand-Schaetzung Aljezur + aufgebaut/neu + mehr Innenfotos + Besuch Anfang Juni in Gouveia</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Bei Antwort: Vergleich mit Benedikt machen, ggf. kombinierte Besichtigung</t>
         </is>
       </c>
     </row>
@@ -9577,67 +9577,141 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F43" s="19" t="inlineStr">
+      <c r="F45" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -15561,7 +15635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -15880,22 +15954,74 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+    <row r="7" ht="110" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Mikael (Mickaël) - Telegram-Gruppe Yurts PT (Gouveia/Guarda)</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Portugal (Gouveia, Guarda - selber Ort wie Benedikt!)</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>8 m, 2.10 m Wandhoehe</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>ca. 50 m2</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>15.000 EUR + Versand</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>NEU (sofort lieferbar)</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>HOLZWAND-Style (vertikale Bretter, NICHT traditionelle Khaana - sieht nach Pacific-Yurts-aehnlicher Bauart aus). Canvas-Dach Standard + EXTRA VINYL-OVERLAY-OPTION (Vinyl-Dach hat 2 zusaetzliche Oeffnungen, braucht 2 zusaetzliche Fenster). AC4-LAMINAT-FLOORING INKLUSIVE. Empfiehlt Sommer-Schattennetz.</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Versand NICHT in 15k - separat. Standort Gouveia 400 km von Aljezur. Vermutlich 800-1.500 EUR.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Telegram Direkt-Kontakt 'Mickaël' (Gruppe Jurten Portugal)</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>VERDACHT: VERBUNDEN MIT BENEDIKT 'YURY' (selber Standort Gouveia, selber Preis 15k, selbe Groesse 8m). Sebastian fragt direkt nach. PROS: Holzwand stabiler+windfester als Khaana, AC4-Boden im Preis. CONS: Vinyl heizt in Algarve auf, Canvas nur 3-5 J. Lebensdauer, kein Hinweis auf Hersteller/Garantie. Mikael spricht englisch+franzoesisch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Ausgeschlossen (unter 6 m Mindestgroesse): 'Yurt mongol autentico Mafra' (5,5 m, 8.000 EUR) - https://www.olx.pt/d/anuncio/yurt-mongol-autntico-IDIR7sZ.html</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>WICHTIG: OLX-Angebote aendern sich taeglich. Vor Anfrage Live-Suche unter https://www.olx.pt/moveis-casa-e-jardim/jardim-e-bricolage/q-yurts/ pruefen. Recherche-Stand: 2026-05-21.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="120" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>PT-USED-MARKT TIEFENSCAN MAI 2026: Markt ist klein - max 3-5 aktive &gt;=6m Listings gleichzeitig. Konzentration Mafra/Lissabon, kaum direkt in Algarve. EMPFOHLENE PLATTFORMEN ZUM BEOBACHTEN: 1) OLX.pt https://www.olx.pt/moveis-casa-e-jardim/q-yurts/ (Hauptkanal); 2) Facebook Marketplace Portugal + 'For Sale or Swap in the Algarve' Gruppe https://www.facebook.com/groups/FORSALEORSWAPINTHEALGARVE/ (eigenen Wanted-Post aufgeben!); 3) CustoJusto.pt https://www.custojusto.pt/ (selten); 4) Casa dos Sonhos Facebook https://www.facebook.com/yurtscasadossonhos/ (sporadische Secondhand-Posts); 5) Hipcamp + Workaway Algarve-Hosts direkt fragen (Glamping-Sites verkaufen manchmal). WICHTIGSTES OFF-MARKT-LEAD: Paula Young via Sarah-Vermittlung (gebrauchte 7,3m Casa-Jurte). EXPERTEN-FAZIT: Casa-Jurten kommen kaum auf Used-Markt (Hersteller-Wartelisten + Eigentuemer halten Jahre). Off-OLX-Leads (Sarah-Vermittlung, FB-Gruppe Wanted-Post) sind wertvoller als oeffentliche Marktplaetze.</t>
         </is>
@@ -15903,9 +16029,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -9555,7 +9555,7 @@
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>Folge-Fragen: Verbindung zu Benedikt direkt erfragt + Hersteller/Wandholz/Behandlung + was genau in 15k + Versand-Schaetzung Aljezur + aufgebaut/neu + mehr Innenfotos + Besuch Anfang Juni in Gouveia</t>
+          <t>Detaillierte Folge-Fragen in 4 Bloecken: 1) HOLZ: Wand/Tono/Uni/Tueren-Holz+Behandlung. 2) ISOLIERUNG: Material/Dicke Wand/Dach/Innenliner-Spec. 3) WAS IN 15k: Anzahl Tueren+Fenster, Skylight-Groesse, Canvas vs Vinyl, AC4-Flaeche/Verlegung. 4) PRAKTISCH: Hersteller+Garantie, Versand-Schaetzung, neu/aufgebaut. Plus: mehr Innenfotos, Besuchstermin Gouveia Anfang Juni. VERDACHT BENEDIKT-VERBINDUNG direkt angesprochen.</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Bei Antwort: Vergleich mit Benedikt machen, ggf. kombinierte Besichtigung</t>
+          <t>Antwort wird Vergleich mit Benedikt entscheiden + ggf. kombinierte Besichtigung Anfang Juni</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9560,61 +9560,61 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>Antwort wird Vergleich mit Benedikt entscheiden + ggf. kombinierte Besichtigung Anfang Juni</t>
+          <t>Antwort 13:15 erhalten</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 13:15</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Mickaël) Gouveia</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>ANTWORT: Hersteller PACIFIC YURTS USA, nie aufgebaut, customized. Holz: solid wood vermutlich Nordische Kiefer mit klarem Lack OHNE Insektizid (selbst behandeln noetig!). Isolierung: Schafwoll-Filz 1.1 kg/m² 'Dicke 0.7mm' (unklar). Skylight 1.40m Kiefer+Eisen. AC4 Boden inkl., Sebastian installiert selbst. Konfiguration: 1 Tuer + 1 Fenster pro Seite. Kennt Benedikt ANGEBLICH NICHT, bittet um OLX-Link.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Vollantwort erhalten</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>WICHTIG: Pacific Yurts = Premium-Hersteller. ABER: Kein Termiten-Schutz, Filz-Dicke unklar, nur 1 Tuer. Sebastian Folge-Fragen + OLX-Link senden.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Mickaël)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Folge-Klarstellungs-Fragen: 1) OLX-Link Benedikt mitgeschickt zur Pruefung. 2) Filz-Dicke 0.7mm = was genau (Canvas/Filz/Schreibfehler 7mm)? 3) Termiten-Behandlung in Algarve obligatorisch, was empfiehlt er + Kosten? 4) Pacific Yurts Modell-Jahr + Serie? Original Sunforger 13oz Canvas oder anders? 5) Genaue Fenster-Anzahl + Groesse. 6) Versand-Schaetzung Aljezur. 7) Besuch Anfang Juni Gouveia (ggf. mit Benedikt zusammen).</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Antwort wird klaeren ob ernsthafte Option oder durchfallen</t>
         </is>
       </c>
     </row>
@@ -9651,67 +9651,141 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F45" s="19" t="inlineStr">
+      <c r="F47" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G47" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -15982,17 +16056,17 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>NEU (sofort lieferbar)</t>
+          <t>NEU (sofort lieferbar, NIE aufgebaut)</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>HOLZWAND-Style (vertikale Bretter, NICHT traditionelle Khaana - sieht nach Pacific-Yurts-aehnlicher Bauart aus). Canvas-Dach Standard + EXTRA VINYL-OVERLAY-OPTION (Vinyl-Dach hat 2 zusaetzliche Oeffnungen, braucht 2 zusaetzliche Fenster). AC4-LAMINAT-FLOORING INKLUSIVE. Empfiehlt Sommer-Schattennetz.</t>
+          <t>HERSTELLER: PACIFIC YURTS USA (Oregon, seit 1978, Industrie-Standard moderne Jurten). KONSTRUKTION: HOLZWAND-Style (vertikale Bretter, Massiv-Holz Nordische Kiefer, klar lackiert OHNE Insektizid - SEBASTIAN MUSS SELBST GEGEN TERMITEN BEHANDELN!). Canvas-Dach Standard + EXTRA VINYL-OVERLAY-OPTION (Vinyl-Dach hat 2 zusaetzliche Oeffnungen, braucht 2 zusaetzliche Fenster). ISOLIERUNG: Schafwoll-Filz 1.1 kg/m² Dichte - Dicke 0.7mm angegeben (verdaechtig duenn - muss geklaert werden ob 0.7mm Filz oder Canvas oder Schreibfehler 7mm). SKYLIGHT: 1.40 m Kiefer+Eisen. KONFIGURATION: 1 Tuer + 1 Fenster pro Seite = 2 Fenster total. AC4-LAMINAT-FLOORING INKLUSIVE (schwimmend verlegt, Sebastian installiert).</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Versand NICHT in 15k - separat. Standort Gouveia 400 km von Aljezur. Vermutlich 800-1.500 EUR.</t>
+          <t>Versand NICHT in 15k - separat. Standort Gouveia 400 km von Aljezur. Vermutlich 800-1.500 EUR. ALGARVE-RISIKO: Termiten-Behandlung obligatorisch (Borax oder professionell ~200-500 EUR + 2 Tage Arbeit).</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
@@ -16002,7 +16076,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>VERDACHT: VERBUNDEN MIT BENEDIKT 'YURY' (selber Standort Gouveia, selber Preis 15k, selbe Groesse 8m). Sebastian fragt direkt nach. PROS: Holzwand stabiler+windfester als Khaana, AC4-Boden im Preis. CONS: Vinyl heizt in Algarve auf, Canvas nur 3-5 J. Lebensdauer, kein Hinweis auf Hersteller/Garantie. Mikael spricht englisch+franzoesisch.</t>
+          <t>PACIFIC YURTS = PREMIUM-HERSTELLER (Pluspunkt!). ABER 3 KRITISCHE PUNKTE: 1) KEIN Insektizid-Schutz - Algarve-Termiten-Risiko. 2) Filz-Dicke unklar (0.7mm zu duenn fuer Daemmung). 3) Nur 1 Tuer + 2 Fenster vs Danis 2 Doppeltueren. CONNECTION BENEDIKT: Mikael sagt 'kennt ihn nicht' und will OLX-Link sehen - vermutlich genuin separate Verkaeufer, Pacific-Yurts-Hersteller-Naehe ist Indiz dass Benedikt evtl. anderes Modell hat.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>Folge-Klarstellungs-Fragen: 1) OLX-Link Benedikt mitgeschickt zur Pruefung. 2) Filz-Dicke 0.7mm = was genau (Canvas/Filz/Schreibfehler 7mm)? 3) Termiten-Behandlung in Algarve obligatorisch, was empfiehlt er + Kosten? 4) Pacific Yurts Modell-Jahr + Serie? Original Sunforger 13oz Canvas oder anders? 5) Genaue Fenster-Anzahl + Groesse. 6) Versand-Schaetzung Aljezur. 7) Besuch Anfang Juni Gouveia (ggf. mit Benedikt zusammen).</t>
+          <t>Folge-Klarstellungs-Fragen + Fotos analysiert: 1) OLX-Link Benedikt mitgeschickt zur Pruefung. 2) Filz-Dicke 0.7mm = was genau (Canvas/Filz/Schreibfehler 7mm)? 3) Termiten-Behandlung in Algarve obligatorisch, was empfiehlt er + Kosten? 4) Pacific Yurts Modell-Jahr + Serie? Original Sunforger 13oz Canvas oder anders? 5) Genaue Fenster-Anzahl + Groesse. 6) Versand-Schaetzung Aljezur. 7) Besuch Anfang Juni Gouveia (ggf. mit Benedikt zusammen). 8) PLATTFORM-INKLUSION bestaetigen (sichtbar in Fotos).</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -9639,44 +9639,44 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>Antwort wird klaeren ob ernsthafte Option oder durchfallen</t>
+          <t>Antwort wird klaeren ob ernsthafte Option oder durchfallen. PLATTFORM-KLAERUNG ist kritisch (spart 2.880 EUR)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Mickaël) Gouveia</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian (4 FOTOS)</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>FOTO-UPDATE: Foto 1 = Jurte im Aufbau mit Canvas-Dach + Doppeltuer + AUFGESTAENDERTE PLATTFORM auf Holzpfaehlen. Foto 2 = TRADITIONELLE KHAANA-SCHEREN-GITTER (nicht Vertikal-Holzwand!) mit 2 Glas-Fenstern + Doppeltuer. Foto 3 = Innenansicht mit weißem Vlies + Uni-Dachsparren radial. Foto 4 = Pacific Yurts offizielles 'Traditional Structure' Marketing-Bild.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Fotos erhalten</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>WICHTIG: Construction IST traditionelle Khaana (wie Dani), nur maschinen-praezise von Pacific Yurts. Plattform sichtbar im Preis enthalten. Verarbeitung sehr ordentlich. RESET vorherige Annahme 'Vertikal-Holzwand' = FALSCH.</t>
         </is>
       </c>
     </row>
@@ -9688,32 +9688,32 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Telegram DM</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
@@ -9725,67 +9725,104 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Sebastian -&gt; Dror</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F47" s="19" t="inlineStr">
+      <c r="F48" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -16031,7 +16068,7 @@
     <row r="7" ht="110" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mikael (Mickaël) - Telegram-Gruppe Yurts PT (Gouveia/Guarda)</t>
+          <t>Mikael (Mickaël) - Pacific Yurts 8m Traditional (Gouveia/Guarda)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -16051,7 +16088,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>15.000 EUR + Versand</t>
+          <t>15.000 EUR + Versand (Plattform vermutlich INKL. - Bestaetigung ausstehend!)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -16061,7 +16098,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>HERSTELLER: PACIFIC YURTS USA (Oregon, seit 1978, Industrie-Standard moderne Jurten). KONSTRUKTION: HOLZWAND-Style (vertikale Bretter, Massiv-Holz Nordische Kiefer, klar lackiert OHNE Insektizid - SEBASTIAN MUSS SELBST GEGEN TERMITEN BEHANDELN!). Canvas-Dach Standard + EXTRA VINYL-OVERLAY-OPTION (Vinyl-Dach hat 2 zusaetzliche Oeffnungen, braucht 2 zusaetzliche Fenster). ISOLIERUNG: Schafwoll-Filz 1.1 kg/m² Dichte - Dicke 0.7mm angegeben (verdaechtig duenn - muss geklaert werden ob 0.7mm Filz oder Canvas oder Schreibfehler 7mm). SKYLIGHT: 1.40 m Kiefer+Eisen. KONFIGURATION: 1 Tuer + 1 Fenster pro Seite = 2 Fenster total. AC4-LAMINAT-FLOORING INKLUSIVE (schwimmend verlegt, Sebastian installiert).</t>
+          <t>HERSTELLER: PACIFIC YURTS USA (Oregon, seit 1978). KORRIGIERT NACH FOTOS: Konstruktion ist NICHT vertikale Holzwand wie zunaechst angenommen, sondern TRADITIONELLE KHAANA-SCHEREN-GITTER (maschinen-praezise, Massiv-Holz Nordische Kiefer, klar lackiert OHNE Insektizid - SEBASTIAN MUSS SELBST GEGEN TERMITEN BEHANDELN!). Canvas-Dach Standard + EXTRA VINYL-OVERLAY-OPTION. ISOLIERUNG: Schafwoll-Filz 1.1 kg/m² Dichte - Dicke 0.7mm angegeben (verdaechtig duenn - Klarstellung 0.7 vs 7 mm noetig). SKYLIGHT: 1.40 m Kiefer+Eisen. KONFIGURATION: 1 Doppeltuer mit Glas-Oberteil + 2 Glas-Fenster bereits in Khaana INTEGRIERT. AC4-LAMINAT-FLOORING INKLUSIVE. PLATTFORM AUFGESTAENDERT AUF HOLZPFAEHLEN sichtbar in Fotos (vermutlich inklusive - bestaetigen!).</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -16076,7 +16113,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>PACIFIC YURTS = PREMIUM-HERSTELLER (Pluspunkt!). ABER 3 KRITISCHE PUNKTE: 1) KEIN Insektizid-Schutz - Algarve-Termiten-Risiko. 2) Filz-Dicke unklar (0.7mm zu duenn fuer Daemmung). 3) Nur 1 Tuer + 2 Fenster vs Danis 2 Doppeltueren. CONNECTION BENEDIKT: Mikael sagt 'kennt ihn nicht' und will OLX-Link sehen - vermutlich genuin separate Verkaeufer, Pacific-Yurts-Hersteller-Naehe ist Indiz dass Benedikt evtl. anderes Modell hat.</t>
+          <t>PACIFIC YURTS = PREMIUM-HERSTELLER (Pluspunkt!). FOTO-UPDATE 24.05.2026: Sehr ordentliche Verarbeitung sichtbar, traditionelle Khaana (wie Dani) mit Pacific-Praezision, AUFGESTAENDERTE PLATTFORM sichtbar = potentiell 2.880 EUR Plattform-Eigenbau gespart! OPEN POINTS: 1) Plattform-Inklusion bestaetigen. 2) Filz-Dicke 0.7 vs 7 mm. 3) Termiten-Behandlung-Plan. 4) Pacific-Yurts-Modell+Jahr+Canvas-Spec. 5) Versand-Schaetzung. CONNECTION BENEDIKT: Mikael sagt 'kennt ihn nicht', will OLX-Link - separate Verkaeufer wahrscheinlich. WENN PLATTFORM INKLUSIVE bestaetigt: All-in ~17.500 EUR (Pacific Yurts 15k + Versand 1k + Termiten 500 + Schatten 240 + Schrauben/Reserve 500) = potentiell guenstigste seriöse 8m-Option!</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9683,49 +9683,49 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 13:42</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Mickaël) = Bento</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>KLARSTELLUNGEN: 1) ER IST DER OLX-VERKAEUFER (Bento, nicht Benedikt - Translator-Fehler). EINE Person, nicht zwei! 2) Filz BESTAETIGT 7mm (traditional thickness). 3) Termiten-Behandlung obligatorisch. 4) Modell 'European Modern' (Pacific Yurts Variante). 5) NEUES PROBLEM: SCHRAUBEN ROSTIG an Khaana-Waenden - muessen ersetzt werden, 'hence the price'. 6) Besuch jederzeit willkommen.</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Klargestellt + Mangelinfo</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>WICHTIG: Mikael war komplett ehrlich ueber Rost-Mangel = Vertrauensbeweis. PREIS 15K IST MAENGELPREIS. Rost-Ausmass muss vor Ort gepruefen werden. ~30 Std Eigenarbeit Schrauben-Tausch + 200 EUR Material Edelstahl A4.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Konkrete Rost-Fragen: 1) Wie extensiv ist Rost (Verfaerbung vs Materialfrass)? 2) Welche Schrauben betroffen (nur Khaana oder auch Tono/Uni/Tuer)? 3) Original-Material (verzinkt/Edelstahl/normal)? 4) Anzahl Schrauben zu ersetzen? Plus: Pacific Yurts Modell-Name exakt, Sunforger 13oz Canvas?, Plattform-Inklusion bestaetigen, Termin-Vorschlag Mitte Juni mit Familie.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9750,7 +9750,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Vor Anreise nach Gouveia: Rost-Ausmass und Plattform-Inklusion bestaetigen lassen</t>
         </is>
       </c>
     </row>
@@ -9762,67 +9762,141 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F48" s="19" t="inlineStr">
+      <c r="F50" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -16068,12 +16142,12 @@
     <row r="7" ht="110" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mikael (Mickaël) - Pacific Yurts 8m Traditional (Gouveia/Guarda)</t>
+          <t>Mikael (Mickaël) = Bento - Pacific Yurts 8m 'European Modern' (Gouveia)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Portugal (Gouveia, Guarda - selber Ort wie Benedikt!)</t>
+          <t>Portugal (Gouveia, Guarda)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -16088,32 +16162,32 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>15.000 EUR + Versand (Plattform vermutlich INKL. - Bestaetigung ausstehend!)</t>
+          <t>15.000 EUR + Versand (MAENGELPREIS wegen Rost an Khaana-Schrauben)</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>NEU (sofort lieferbar, NIE aufgebaut)</t>
+          <t>NEU (sofort lieferbar, NIE aufgebaut) - aber ROSTPROBLEM an Schrauben</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>HERSTELLER: PACIFIC YURTS USA (Oregon, seit 1978). KORRIGIERT NACH FOTOS: Konstruktion ist NICHT vertikale Holzwand wie zunaechst angenommen, sondern TRADITIONELLE KHAANA-SCHEREN-GITTER (maschinen-praezise, Massiv-Holz Nordische Kiefer, klar lackiert OHNE Insektizid - SEBASTIAN MUSS SELBST GEGEN TERMITEN BEHANDELN!). Canvas-Dach Standard + EXTRA VINYL-OVERLAY-OPTION. ISOLIERUNG: Schafwoll-Filz 1.1 kg/m² Dichte - Dicke 0.7mm angegeben (verdaechtig duenn - Klarstellung 0.7 vs 7 mm noetig). SKYLIGHT: 1.40 m Kiefer+Eisen. KONFIGURATION: 1 Doppeltuer mit Glas-Oberteil + 2 Glas-Fenster bereits in Khaana INTEGRIERT. AC4-LAMINAT-FLOORING INKLUSIVE. PLATTFORM AUFGESTAENDERT AUF HOLZPFAEHLEN sichtbar in Fotos (vermutlich inklusive - bestaetigen!).</t>
+          <t>HERSTELLER: PACIFIC YURTS USA Modell 'European Modern' (vage Bezeichnung). KONSTRUKTION: TRADITIONELLE KHAANA-SCHEREN-GITTER (maschinen-praezise). Holz: Massiv Nordische Kiefer, klar lackiert OHNE Insektizid - SEBASTIAN MUSS TERMITEN BEHANDELN. ISOLIERUNG: Schafwoll-Filz 7mm (KORRIGIERT - traditioneller Standard, OK) Dichte 1.1 kg/m². Canvas-Dach Standard + Vinyl-Overlay-Option. SKYLIGHT: 1.40m Kiefer+Eisen. KONFIGURATION: 1 Doppeltuer + 2 Glas-Fenster integriert in Khaana. AC4-LAMINAT-FLOORING INKLUSIVE. PLATTFORM AUFGESTAENDERT sichtbar.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Versand NICHT in 15k - separat. Standort Gouveia 400 km von Aljezur. Vermutlich 800-1.500 EUR. ALGARVE-RISIKO: Termiten-Behandlung obligatorisch (Borax oder professionell ~200-500 EUR + 2 Tage Arbeit).</t>
+          <t>Versand NICHT in 15k - separat (vermutlich 800-1.500). ALGARVE-RISIKO: Termiten obligatorisch (~500 EUR). MAENGEL: Schrauben rostig - Komplett-Ersatz noetig (Edelstahl A4) - ~200 EUR Material + 30 Std Arbeit Selbstaufbau.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Telegram Direkt-Kontakt 'Mickaël' (Gruppe Jurten Portugal)</t>
+          <t>Telegram Direkt-Kontakt 'Mickaël' = Bento (OLX-Verkaeufer - Uebersetzer-Fehler hatte 'Benedikt' gemacht).</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>PACIFIC YURTS = PREMIUM-HERSTELLER (Pluspunkt!). FOTO-UPDATE 24.05.2026: Sehr ordentliche Verarbeitung sichtbar, traditionelle Khaana (wie Dani) mit Pacific-Praezision, AUFGESTAENDERTE PLATTFORM sichtbar = potentiell 2.880 EUR Plattform-Eigenbau gespart! OPEN POINTS: 1) Plattform-Inklusion bestaetigen. 2) Filz-Dicke 0.7 vs 7 mm. 3) Termiten-Behandlung-Plan. 4) Pacific-Yurts-Modell+Jahr+Canvas-Spec. 5) Versand-Schaetzung. CONNECTION BENEDIKT: Mikael sagt 'kennt ihn nicht', will OLX-Link - separate Verkaeufer wahrscheinlich. WENN PLATTFORM INKLUSIVE bestaetigt: All-in ~17.500 EUR (Pacific Yurts 15k + Versand 1k + Termiten 500 + Schatten 240 + Schrauben/Reserve 500) = potentiell guenstigste seriöse 8m-Option!</t>
+          <t>GAME-CHANGER UPDATE 24.05.2026: Mikael IST der OLX-Verkaeufer (Bento - Uebersetzer-Verwirrung). Mikael ehrlich ueber Maengel (Rost) - das spricht fuer Vertrauen. Filz 7mm bestaetigt (OK). Modell-Name vage. ALL-IN ~17.440 EUR (mit Schrauben-Ersatz 200 + Termiten 500 + Versand 1000 + Schatten 240 + Reserve 500) - PLUS 30 Std Eigenarbeit Schrauben-Tausch. WICHTIG: vor Anzahlung Rost-Ausmass vor Ort pruefen + Pacific-Yurts-Modell-Name + Sunforger-Canvas-Spec klaeren.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9720,7 +9720,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>24.05.2026 (Sebastians Folge)</t>
+          <t>24.05.2026 13:59</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -9735,59 +9735,59 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Mikael</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Konkrete Rost-Fragen: 1) Wie extensiv ist Rost (Verfaerbung vs Materialfrass)? 2) Welche Schrauben betroffen (nur Khaana oder auch Tono/Uni/Tuer)? 3) Original-Material (verzinkt/Edelstahl/normal)? 4) Anzahl Schrauben zu ersetzen? Plus: Pacific Yurts Modell-Name exakt, Sunforger 13oz Canvas?, Plattform-Inklusion bestaetigen, Termin-Vorschlag Mitte Juni mit Familie.</t>
+          <t>Begeistert ueber geplanten Besuch ('Are you coming to Gouveia? That's great, you can see the yurt and its components 👍')</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Termin-Bereitschaft</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Vor Anreise nach Gouveia: Rost-Ausmass und Plattform-Inklusion bestaetigen lassen</t>
+          <t>Konkreten Datums-Vorschlag + Vorab-Fragen senden</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>Besuchsbestaetigung + 2 Datum-Optionen (Sa 13. oder Sa 20. Juni mit Frau+Kindern) + Vorab-Fragen: Rost-Ausmass (Verfaerbung vs durchgerostet?), welche Schrauben betroffen (nur Khaana oder auch Tono/Uni?), Original-Material (verzinkt?), Pacific Yurts Modell-Name+Jahr, Plattform-Inklusion bestaetigen. Hinweis: bringen Lunch mit, schlafen in Pension.</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Bei Termin-Fixierung: gleiches Wochenende auch Dani Castelo de Vide besuchen (~130 km zwischen den Orten)</t>
         </is>
       </c>
     </row>
@@ -9799,32 +9799,32 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Telegram DM</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
@@ -9836,67 +9836,104 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Sebastian -&gt; Dror</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F50" s="19" t="inlineStr">
+      <c r="F51" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9794,49 +9794,49 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 spaeter</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>KORREKTUR: AC4-Boden 52 m² NICHT in 15k - extra 700 EUR (Selbstkostenpreis). Plattform NICHT in 15k - Sebastian baut selbst aus Saegewerk-Holz lokal (guenstiger). KLARSTELLUNG DAEMMUNG: '7mm refers to the thickness of the insulation, density 1,100 kg/m²' (vermutlich PT-Komma: 1,1 kg/m² = 157 kg/m³ Dichte = normal aber 7mm KRITISCH DUENN).</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Wichtige Klarstellungen</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>KRITISCH: 7mm Daemmung ist halb so viel wie Industrie-Standard fuer ganzjaehrigen Wohnen. Sebastian muss zusaetzlich daemmen ODER aktiv heizen.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -9846,12 +9846,12 @@
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Bestaetigungs-Frage Daemmungs-Wert (1,1 vs 1.100 - Komma-Dezimal-Klaerung) + Erfahrungs-Frage: andere Pacific-Yurts-Besitzer in PT haben zusaetzlich gedaemmt? OK fuer Sebastian eine 8mm Zusatz-Schicht draufzulegen?</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -9861,7 +9861,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Bei Antwort: bei Besuch Daemmungs-Realitaet anfassen</t>
         </is>
       </c>
     </row>
@@ -9873,67 +9873,141 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F51" s="19" t="inlineStr">
+      <c r="F53" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -14039,27 +14113,27 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>OLX Benedikt 8m 'Yury' (Gouveia, Zentral-PT)</t>
+          <t>Mikael/Bento Pacific Yurts 8m (Gouveia) = OLX 'Yury'</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Privatverkauf NEU - 8m Komplett-Setup</t>
+          <t>Pacific Yurts USA Modell 'European Modern' - NEU mit Maengeln</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>15.000 EUR (inkl. Tuer + 2 Fenster + weisser Innenstoff + Filzisolierung + 'Gruendach')</t>
+          <t>~22.040 EUR all-in (15k Pacific + 700 AC4 + 3.300 Plattform Premium + 600 Zusatz-Daemmung + 1k Versand + 500 Termiten + 200 Schrauben + 240 Schatten + 500 Reserve)</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>BESTER 8M-PREIS IM MARKT (Mai 2026 entdeckt) - 50 m2 Wohnflaeche fuer 15k all-in. Verkaeufer Benedikt = deutscher Reseller in Gouveia (Serra da Estrela), Inserat auf Deutsch. NEUWARE. Standort 4-5 h von Aljezur. ACHTUNG: Privatverkauf ohne Verbraucherschutz - vor Anzahlung: Besichtigung + Klaerung Plane-UV/Hersteller/Transport/Garantie/'Gruendach'. Modell 'Yury' deutet auf Green World UA Hersteller hin.</t>
+          <t>STARK aber TEURER ALS DANI: 50 m² Pacific Yurts Premium-Marke, Mikael=Bento (1 Person 2 Channels: Telegram+OLX). EHRLICHER Verkaeufer (Rost offen kommuniziert). PROBLEME: 1) Schrauben-Rost - Komplett-Ersatz Edelstahl A4 (~200 EUR + 30 Std Arbeit). 2) NUR 7mm Schafwoll-Filz (R~0,18) - 5x DUENNER als Dani's 4cm. Zusatz-Daemmung in Algarve obligatorisch (+600 EUR). 3) Pinie ohne Insektizid = Termiten-Behandlung selbst (+500 EUR + 2 Tage). PLATTFORM nicht inklusive (Sebastian baut). AC4-Boden 700 EUR optional fair. Konstruktion: traditionelle Khaana, hochpraezise gefertigt. 1 Doppeltuer + 2 Glas-Fenster integriert.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/d/anuncio/yurt-de-8-metros-de-dimetro-com-janela-panormica-IDJatvu.html</t>
+          <t>https://www.olx.pt/d/anuncio/yurt-de-8-metros-de-dimetro-com-janela-panormica-IDJatvu.html | Telegram 'Mickaël'</t>
         </is>
       </c>
     </row>
@@ -16199,32 +16273,32 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>15.000 EUR + Versand (MAENGELPREIS wegen Rost an Khaana-Schrauben)</t>
+          <t>15.000 EUR (Jurte only) + 700 EUR optional AC4 + Versand. PLATTFORM NICHT INKL! DAEMMUNG-NACHRUESTUNG noetig fuer Algarve.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>NEU (sofort lieferbar, NIE aufgebaut) - aber ROSTPROBLEM an Schrauben</t>
+          <t>NEU (sofort lieferbar, NIE aufgebaut) - ROSTPROBLEM an Schrauben + KRITISCH DUENNE DAEMMUNG 7mm</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>HERSTELLER: PACIFIC YURTS USA Modell 'European Modern' (vage Bezeichnung). KONSTRUKTION: TRADITIONELLE KHAANA-SCHEREN-GITTER (maschinen-praezise). Holz: Massiv Nordische Kiefer, klar lackiert OHNE Insektizid - SEBASTIAN MUSS TERMITEN BEHANDELN. ISOLIERUNG: Schafwoll-Filz 7mm (KORRIGIERT - traditioneller Standard, OK) Dichte 1.1 kg/m². Canvas-Dach Standard + Vinyl-Overlay-Option. SKYLIGHT: 1.40m Kiefer+Eisen. KONFIGURATION: 1 Doppeltuer + 2 Glas-Fenster integriert in Khaana. AC4-LAMINAT-FLOORING INKLUSIVE. PLATTFORM AUFGESTAENDERT sichtbar.</t>
+          <t>HERSTELLER: PACIFIC YURTS USA Modell 'European Modern' (vage Bezeichnung). KONSTRUKTION: TRADITIONELLE KHAANA-SCHEREN-GITTER (maschinen-praezise). Holz: Massiv Nordische Kiefer, klar lackiert OHNE Insektizid. ISOLIERUNG: NUR 7mm Schafwoll-Filz, 1,1 kg/m² Flaechengewicht (= 157 kg/m³ Dichte normal, aber DICKE KRITISCH DUENN fuer Algarve-Winter). R-Wert ~0,18 (Dani 40mm: R~1,0 = 5x besser). Pacific Yurts Standard ist fuer US-West-Klima ausgelegt, nicht Atlantik-Winter. SEBASTIAN MUSS ZUSAETZLICHE 8mm Schafwoll-Filz NACHRUESTEN (~600 EUR Material, von Chris PT). Canvas-Dach Standard + Vinyl-Overlay-Option. SKYLIGHT: 1.40m Kiefer+Eisen. KONFIGURATION: 1 Doppeltuer + 2 Glas-Fenster integriert in Khaana. AC4-LAMINAT-BODEN OPTIONAL 700 EUR fuer 52 m² (Selbstkostenpreis, fair). PLATTFORM NICHT enthalten - Sebastian baut selbst (Empfehlung Mikael: Saegewerk-Holz lokal).</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Versand NICHT in 15k - separat (vermutlich 800-1.500). ALGARVE-RISIKO: Termiten obligatorisch (~500 EUR). MAENGEL: Schrauben rostig - Komplett-Ersatz noetig (Edelstahl A4) - ~200 EUR Material + 30 Std Arbeit Selbstaufbau.</t>
+          <t>Versand NICHT in 15k - separat (vermutlich 800-1.500). ALGARVE-RISIKO: Termiten obligatorisch (~500 EUR). MAENGEL: Schrauben rostig - Komplett-Ersatz noetig (Edelstahl A4) - ~200 EUR Material + 30 Std Arbeit. ZUSAETZLICHE DAEMMUNG ~600 EUR.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Telegram Direkt-Kontakt 'Mickaël' = Bento (OLX-Verkaeufer - Uebersetzer-Fehler hatte 'Benedikt' gemacht).</t>
+          <t>Telegram Direkt-Kontakt 'Mickaël' = Bento (OLX-Verkaeufer)</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>GAME-CHANGER UPDATE 24.05.2026: Mikael IST der OLX-Verkaeufer (Bento - Uebersetzer-Verwirrung). Mikael ehrlich ueber Maengel (Rost) - das spricht fuer Vertrauen. Filz 7mm bestaetigt (OK). Modell-Name vage. ALL-IN ~17.440 EUR (mit Schrauben-Ersatz 200 + Termiten 500 + Versand 1000 + Schatten 240 + Reserve 500) - PLUS 30 Std Eigenarbeit Schrauben-Tausch. WICHTIG: vor Anzahlung Rost-Ausmass vor Ort pruefen + Pacific-Yurts-Modell-Name + Sunforger-Canvas-Spec klaeren.</t>
+          <t>REZENTE KOSTEN-AKTUALISIERUNG 24.05.2026: KRITISCH dunne Daemmung 7mm = Nachruest-Bedarf. ALL-IN ~22.040 EUR (Pacific Yurts 15k + AC4 700 + Plattform Kork-Premium 3.300 + Zusatz-Daemmung 600 + Versand 1k + Termiten 500 + Schrauben 200 + Schatten 240 + Reserve 500). ~80-100 Std Eigenarbeit. JETZT TEURER ALS DANI 7m (21,6k). VERGLEICH Mikael (50m², Pacific Brand, dünne Daemmung+Rost+Termiten-Risiko, sofort verfuegbar) vs DANI (38m², Community+Probeschlafen+atmungsaktiv+5x bessere Daemmung+anpassbar Sauleda). DANI klar im Vorteil wenn Wohnkomfort &gt; 12m² Mehrflaeche.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9868,49 +9868,49 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 spaeter</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Bento) Gouveia</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>TRAGISCHE HINTERGRUNDGESCHICHTE: Pacific Yurts gekauft AUGUST 2025 (10 Mon. her), seitdem in einem Van gelagert. GROSSER BRAND zerstoerte ihre Grundstuecks-Plaene - haben deshalb nichts installiert. Erklaert: Verkaufsgrund (echtes Schicksal), Rost-Schrauben (Van-Lagerung mit Temperatur+Feuchte-Wechsel), nie aufgebaut. Empfiehlt Holz-Behandlung vor Installation.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Vollkontext geklaert</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>MENSCHLICH stark - tragische Verkaufsmotivation. STRATEGISCH neues Risiko: 10 Mon. Van-Lagerung koennte Filz/Plane/Holz beeinflusst haben (Schimmel/Verzug).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians empathische Folge)</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -9920,12 +9920,12 @@
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Empathische Antwort zum Brand. Bestaetigung Verstaendnis (15k + 700 AC4 + DIY Plattform + DIY Daemmungs-Nachruest+Termiten-Behandlung). Termin-Vorschlag Sa 14. oder Sa 21. Juni mit Familie+Pension. Wichtige Vorab-Fragen: 1) Lagerungs-Zustand Canvas/Filz/Holz nach 10 Mon. Van (Feuchte/Schimmel/Verzug?). 2) Rost-Ausmass: 10/50/100% der Schrauben?</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -9935,79 +9935,227 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Vor dem Besuch: Lagerungs-Zustand und Rost-Quantitaet abklaeren, um Trip-Aufwand zu rechtfertigen</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 spaeter</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram DM (PT)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>VERSAND-REFERENZ: Vorheriger Kunde aus Sebastians Naehe hat Jurte selbst mit gemietetem grossem Van abgeholt - Kosten 750 EUR. Real-Referenz Selbst-Abholung billiger als Spedition.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Konkrete Versand-Option</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian Antwort: Frage nach Groesse der anderen Jurte (7m/8m?) und ob Mikael beim Beladen hilft</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
+          <t>24.05.2026 (Sebastians Folge)</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Mikael (Bento)</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Mikael</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Versand-Optionen: 750 EUR Selbst-Abholung wird in Sebastians Plan integriert. Klaerung-Fragen: Welche Groesse hat die andere Jurte gekostet? Hilfst du beim Beladen? Plus Idee: Besuch und Abholung kombinieren in 1-2 Wochenenden</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>Bei Bestaetigung: Van-Miete in Aljezur recherchieren (typisch Renault Master 13-17 m³ ~80-150 EUR/Tag)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Dror (Telegram-Gruppe)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Telegram-Post</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Dror -&gt; Gruppe</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>✓ Wertvoller Kontakt</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F53" s="19" t="inlineStr">
+      <c r="F57" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr">
+      <c r="G57" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -16258,7 +16406,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Portugal (Gouveia, Guarda)</t>
+          <t>Portugal (Gouveia, Guarda) - 10 Mon. in Van gelagert nach Grundstueck-Brand</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -16273,32 +16421,32 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>15.000 EUR (Jurte only) + 700 EUR optional AC4 + Versand. PLATTFORM NICHT INKL! DAEMMUNG-NACHRUESTUNG noetig fuer Algarve.</t>
+          <t>15.000 EUR (Jurte only) + 700 EUR optional AC4 + 750 EUR Selbst-Abholung Van. PLATTFORM NICHT INKL!</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>NEU (sofort lieferbar, NIE aufgebaut) - ROSTPROBLEM an Schrauben + KRITISCH DUENNE DAEMMUNG 7mm</t>
+          <t>NEU - August 2025 gekauft Pacific Yurts, BIG FIRE zerstoerte ihre Plaene, seitdem in einem Van gelagert (10 Mon). ROSTPROBLEM an Khaana-Schrauben (vermutlich Van-Lagerung+Feuchte). NIE aufgebaut.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>HERSTELLER: PACIFIC YURTS USA Modell 'European Modern' (vage Bezeichnung). KONSTRUKTION: TRADITIONELLE KHAANA-SCHEREN-GITTER (maschinen-praezise). Holz: Massiv Nordische Kiefer, klar lackiert OHNE Insektizid. ISOLIERUNG: NUR 7mm Schafwoll-Filz, 1,1 kg/m² Flaechengewicht (= 157 kg/m³ Dichte normal, aber DICKE KRITISCH DUENN fuer Algarve-Winter). R-Wert ~0,18 (Dani 40mm: R~1,0 = 5x besser). Pacific Yurts Standard ist fuer US-West-Klima ausgelegt, nicht Atlantik-Winter. SEBASTIAN MUSS ZUSAETZLICHE 8mm Schafwoll-Filz NACHRUESTEN (~600 EUR Material, von Chris PT). Canvas-Dach Standard + Vinyl-Overlay-Option. SKYLIGHT: 1.40m Kiefer+Eisen. KONFIGURATION: 1 Doppeltuer + 2 Glas-Fenster integriert in Khaana. AC4-LAMINAT-BODEN OPTIONAL 700 EUR fuer 52 m² (Selbstkostenpreis, fair). PLATTFORM NICHT enthalten - Sebastian baut selbst (Empfehlung Mikael: Saegewerk-Holz lokal).</t>
+          <t>HERSTELLER: PACIFIC YURTS USA Modell 'European Modern' (Aug 2025 gekauft, also 2025er Spec). KONSTRUKTION: TRADITIONELLE KHAANA-SCHEREN-GITTER. Holz: Massiv Nordische Kiefer, klar lackiert OHNE Insektizid. ISOLIERUNG: 7mm Schafwoll-Filz, 1,1 kg/m² Flaechengewicht (= 157 kg/m³ Dichte normal, aber DICKE KRITISCH DUENN fuer Algarve). R-Wert ~0,18 (Dani 40mm R~1,0 = 5x besser). Pacific Yurts Standard fuer US-West-Klima. Sebastian muss zusaetzliche 8mm Schafwoll-Filz NACHRUESTEN (+600 EUR). Canvas-Dach Standard + Vinyl-Overlay-Option. SKYLIGHT: 1.40m Kiefer+Eisen. KONFIGURATION: 1 Doppeltuer + 2 Glas-Fenster integriert. AC4-LAMINAT-BODEN OPTIONAL 700 EUR fuer 52 m². PLATTFORM NICHT enthalten - Sebastian baut selbst.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>Versand NICHT in 15k - separat (vermutlich 800-1.500). ALGARVE-RISIKO: Termiten obligatorisch (~500 EUR). MAENGEL: Schrauben rostig - Komplett-Ersatz noetig (Edelstahl A4) - ~200 EUR Material + 30 Std Arbeit. ZUSAETZLICHE DAEMMUNG ~600 EUR.</t>
+          <t>VERSAND BESTAETIGT: 750 EUR Selbst-Abholung mit gemietetem Van (Real-Referenz von anderem Kunden in Sebastians Naehe). Spedition vermutlich 1k-1.5k. ALGARVE-RISIKO: Termiten obligatorisch (+500), Schrauben-Ersatz Edelstahl A4 (+200 + 30 Std), Zusatz-Daemmung 8mm (+600 + 5 Std).</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Telegram Direkt-Kontakt 'Mickaël' = Bento (OLX-Verkaeufer)</t>
+          <t>Telegram Direkt-Kontakt 'Mickaël' = Bento (OLX-Verkaeufer). Tragische Geschichte: Brand-Opfer.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>REZENTE KOSTEN-AKTUALISIERUNG 24.05.2026: KRITISCH dunne Daemmung 7mm = Nachruest-Bedarf. ALL-IN ~22.040 EUR (Pacific Yurts 15k + AC4 700 + Plattform Kork-Premium 3.300 + Zusatz-Daemmung 600 + Versand 1k + Termiten 500 + Schrauben 200 + Schatten 240 + Reserve 500). ~80-100 Std Eigenarbeit. JETZT TEURER ALS DANI 7m (21,6k). VERGLEICH Mikael (50m², Pacific Brand, dünne Daemmung+Rost+Termiten-Risiko, sofort verfuegbar) vs DANI (38m², Community+Probeschlafen+atmungsaktiv+5x bessere Daemmung+anpassbar Sauleda). DANI klar im Vorteil wenn Wohnkomfort &gt; 12m² Mehrflaeche.</t>
+          <t>AKTUALISIERTE KOSTEN 24.05.2026 mit echtem Versand 750: ALL-IN ~21.790 EUR (Pacific Yurts 15k + AC4 700 + Plattform Kork 3.300 + Zusatz-Daemmung 600 + Versand Selbst-Abholung 750 + Termiten 500 + Schrauben 200 + Schatten 240 + Reserve 500). PRAKTISCH GLEICH MIT DANI (21,6k). VERGLEICH bleibt: Mikael 50m² Pacific-Brand aber 7mm Daemmung+Rost+Termiten+10Mon-Van-Lagerung-Risiko vs DANI 38m² mit 40mm Daemmung+Community+Probeschlafen+anpassbar Sauleda.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8040,7 +8040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G57"/>
+  <dimension ref="A1:G59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10016,49 +10016,49 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 spaeter</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>NEUES ANGEBOT: Mikael hat sowieso Lieferung nach Castelo Branco geplant - bietet an, Sebastians Jurte direkt nach Aljezur mitzunehmen mit Preisanpassung. Gouveia -&gt; Castelo Branco ~110 km, dann Zusatz Castelo Branco -&gt; Aljezur ~400 km.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Liefer-Option erhalten</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Sebastian Fragen: 1) Wann ist Castelo-Branco-Lieferung geplant (vor oder nach Juni-Besuch)? 2) Konkreter Aufpreis fuer Lieferung Aljezur? 3) Hilft Mikael beim Abladen?</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Ja zur Liefer-Option grundsaetzlich interessiert. Wann ist Castelo-Branco-Termin? Wie viel Aufpreis fuer Aljezur? Wenn nach Mitte Juni: ideal - Besuch + Lieferung kombinieren.</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Wenn Mikaels Liefertermin VOR Mitte Juni: Konflikt mit Besuch. Falls NACH Mitte Juni: ideal.</t>
         </is>
       </c>
     </row>
@@ -10095,67 +10095,141 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F57" s="19" t="inlineStr">
+      <c r="F59" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -24,6 +24,7 @@
     <sheet name="15 Kommunikations-Log" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="16 DIY Bauplan-Quellen" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="17 Plattform 7m Kostenrechnung" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="18 Mikael 3 Szenarien" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8040,7 +8041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10090,37 +10091,37 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 KONSOLIDIERT</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>KONSOLIDIERTE NACHRICHT MIT 8 BLOECKEN: 1) Lagerungs-Zustand 10 Mon Van (Canvas/Filz/Holz). 2) Rost-Quantifizierung (%/Position/Material). 3) Pacific Yurts Modell+Sunforger-Canvas+Vinyl-Inkl. 4) DAEMMUNG-UPGRADE moeglich (14mm oder doppelt)? Falls nein: ok wenn Sebastian 8mm Zusatzschicht selbst macht? 5) HOLZ-BEHANDLUNG durch Mikael vor Lieferung moeglich+Preis? Falls nein: Produkt-Empfehlung. 6) LIEFERUNG Castelo Branco Datum+Aufpreis Aljezur+Hilfe Abladen. 7) Visit-Termin Sa 14 vs Sa 21 Juni. 8) Andere Jurte 7m/8m, Mikael Beladen-Hilfe?</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Mit diesen Antworten kann Sebastian Vollkosten kalkulieren in 3 Szenarien (A=Selbst, B=Mittlerer Service, C=Max Komfort). Total 21,1k-22,4k je Szenario.</t>
         </is>
       </c>
     </row>
@@ -10132,32 +10133,32 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Telegram DM</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
@@ -10169,67 +10170,104 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Sebastian -&gt; Dror</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F59" s="19" t="inlineStr">
+      <c r="F60" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G59" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -12738,6 +12776,585 @@
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="A44:E44"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Mikael Pacific Yurts 8m - 3 Szenarien Vollkosten (Mai 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>A: Selbst max</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>B: Mittel</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>C: Komfort</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Pacific Yurts 8m (Mikael Basis)</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C3" s="14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D3" s="14" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Jurte selbst, alle Komponenten</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>AC4-Boden 52 m² optional</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="n">
+        <v>700</v>
+      </c>
+      <c r="C4" s="14" t="n">
+        <v>700</v>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>700</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Mikaels Selbstkosten-Preis fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Lieferung Castelo-Branco-Mitnahme (Schaetzung)</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Mit Aufbauhilfe in Szenario C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Zusatz-Daemmung 8mm Schafwoll-Filz Material</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <v>800</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>C: Mikael waehlt dickeres Filz</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Termiten-Behandlung Holz</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>A: Material+Selbstarbeit / B+C: durch Mikael+Oel-Auffrischung</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="21" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Schrauben-Ersatz Edelstahl A4</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>200</v>
+      </c>
+      <c r="C8" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>600</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>A: Material+Selbstarbeit 30 Std / B+C: durch Mikael</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Plattform DIY Kork (Sheet 17)</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="n">
+        <v>2880</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>3300</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>C: Premium Variante</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Schattennetz Algarve</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>240</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Lokale Agrar-Koop</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Reserve / Werkzeug</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>500</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12" ht="8" customHeight="1"/>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL ALL-IN</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>21120</v>
+      </c>
+      <c r="C13" s="15" t="n">
+        <v>21420</v>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>22440</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Spannweite 1.320 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Eigenarbeit (Stunden)</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>~80 h</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>~50 h</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>~20 h</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="8" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>VERGLEICH MIT DANI 7m Premium (21.620 EUR)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Mikael Szenario A vs Dani</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>-500</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr"/>
+      <c r="D17" s="16" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Mikael 500 EUR guenstiger als Dani</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Mikael Szenario B vs Dani</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr"/>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>-200</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Praktisch gleich</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Mikael Szenario C vs Dani</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr"/>
+      <c r="C19" s="16" t="inlineStr"/>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>+820</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Komfort kostet 820 EUR Aufpreis</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>ABER: Dani Vorteile</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Daemmung</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>7+8 mm</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>7+8 mm</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>bis 14 mm</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Dani 40mm = 2x dicker als Mikael max</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Probeschlafen</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Dani JA - Live-Verifikation</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Dani: 4 Familien vor Ort</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Rost-Risiko</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>moderat</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>behoben</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>behoben</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Dani: keiner</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Termiten-Risiko</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>moderat</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>behoben</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>behoben</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Dani: keiner (atmungsaktive Bauweise)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Lagerungs-Risiko 10 Mon Van</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Dani: frisch gebaut Aug/Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Wohnflaeche</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>50 m²</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>50 m²</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>50 m²</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Dani: 38 m²</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Markenwert</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Pacific Yurts Premium</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>Pacific Yurts Premium</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>Pacific Yurts Premium</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Dani: Selbstbau 8J Erfahrung</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A21:E21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8041,7 +8041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10116,61 +10116,61 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Mit diesen Antworten kann Sebastian Vollkosten kalkulieren in 3 Szenarien (A=Selbst, B=Mittlerer Service, C=Max Komfort). Total 21,1k-22,4k je Szenario.</t>
+          <t>Vollantwort 15:02 erhalten</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 15:02</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Bento) Gouveia</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>VOLLANTWORT auf 8-Block-Nachricht: 1) LAGERUNG: 'Nothing rusty, moldy, mildew anymore, smells brand new' - TOP Zustand. 2) ROST: 30% Schrauben oberflaechlich, Ursache: REGULAR STEEL statt verzinkt (Fertigungsfehler!) - implizit ALLE Schrauben gefaehrdet. 3) Pacific Yurts komplett bestaetigt. NORMALPREIS 8m Panoramic = 18.500 EUR (15k ist 3.500 EUR Rabatt fuer Schrauben). 4) Dickere Daemmung kann Mikael beschaffen (Sheep wool, 'treated properly'). 5) Holz-Behandlung: Initial bereits erfolgt + Spray am Abholtag (kein Aufpreis erwaehnt). 6) LIEFERUNG CASTELO BRANCO AM 1. JUNI! Vor Sebastians Besuch (14./21. Juni). 7) Visit-Termin offen. 8) Vinyl-Overlay 8m = EXTRA 1.000 EUR (nicht in 15k). AC4 = 700 EUR. Mikael hilft beim Beladen mit Maschine, Lieferung kommt mit Helfer.</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Vollantwort</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>TIMING-PROBLEM: 1. Juni Lieferung vor Juni-Besuch = unmoeglich kombinierbar. Sebastian muss Selbst-Abholung wahlen oder spaeteren Termin verhandeln.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Bedauert dass 1. Juni zu frueh - Frau kommt erst naechste Woche zurueck. Zwei Optionen: A) Selbst-Abholung Mietvan ~750 EUR Ende Juni/Anfang Juli nach Besuch. B) Mikael macht spaetere Liefertour im Mitte/Ende Juni nach Algarve mit Aufpreis. Plus: ALLE Schrauben durch Mikael ersetzen lassen (nicht nur 30%) + Vinyl-Overlay-Preis 1k fuer welche Variante genau?</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Bei Mikael's Antwort: Logistik-Entscheidung + Final-Kalkulation Vinyl-Overlay</t>
         </is>
       </c>
     </row>
@@ -10207,67 +10207,141 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F60" s="19" t="inlineStr">
+      <c r="F62" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -17092,7 +17166,7 @@
     <row r="7" ht="110" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Mikael (Mickaël) = Bento - Pacific Yurts 8m 'European Modern' (Gouveia)</t>
+          <t>Mikael (Mickaël) = Bento - Pacific Yurts 8m Panoramic (Gouveia)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -17112,32 +17186,32 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>15.000 EUR (Jurte only) + 700 EUR optional AC4 + 750 EUR Selbst-Abholung Van. PLATTFORM NICHT INKL!</t>
+          <t>15.000 EUR (NORMALPREIS 18.500 = 3.500 EUR Rabatt fuer Rost) + 700 AC4 + 1.000 Vinyl-Overlay optional + 500-800 Lieferung. PLATTFORM NICHT INKL!</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>NEU - August 2025 gekauft Pacific Yurts, BIG FIRE zerstoerte ihre Plaene, seitdem in einem Van gelagert (10 Mon). ROSTPROBLEM an Khaana-Schrauben (vermutlich Van-Lagerung+Feuchte). NIE aufgebaut.</t>
+          <t>NEU - August/Oktober 2025 gekauft Pacific Yurts. BIG FIRE zerstoerte Grundstueck. 10 Mon in Van: lagerung TOP (kein Schimmel/Geruch/Verzug). Aber: 30% Schrauben sichtbar rostig + ALLE Schrauben sind 'regular steel' (Fertigungsfehler statt verzinkt) = ALLE bedrohlich in Algarve-Salzluft.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>HERSTELLER: PACIFIC YURTS USA Modell 'European Modern' (Aug 2025 gekauft, also 2025er Spec). KONSTRUKTION: TRADITIONELLE KHAANA-SCHEREN-GITTER. Holz: Massiv Nordische Kiefer, klar lackiert OHNE Insektizid. ISOLIERUNG: 7mm Schafwoll-Filz, 1,1 kg/m² Flaechengewicht (= 157 kg/m³ Dichte normal, aber DICKE KRITISCH DUENN fuer Algarve). R-Wert ~0,18 (Dani 40mm R~1,0 = 5x besser). Pacific Yurts Standard fuer US-West-Klima. Sebastian muss zusaetzliche 8mm Schafwoll-Filz NACHRUESTEN (+600 EUR). Canvas-Dach Standard + Vinyl-Overlay-Option. SKYLIGHT: 1.40m Kiefer+Eisen. KONFIGURATION: 1 Doppeltuer + 2 Glas-Fenster integriert. AC4-LAMINAT-BODEN OPTIONAL 700 EUR fuer 52 m². PLATTFORM NICHT enthalten - Sebastian baut selbst.</t>
+          <t>HERSTELLER: PACIFIC YURTS USA - 8m Panoramic Model. KONSTRUKTION: TRADITIONELLE KHAANA-SCHEREN-GITTER. Holz: Massiv Nordische Kiefer, klar lackiert + INITIAL Insektenschutz-Spray bereits durchgefuehrt. Mikael macht zweite Spray-Anwendung am Abholtag (inkl.). ISOLIERUNG: 7mm Schafwoll-Filz Dichte 1.1 kg/m² (Standard Pacific Yurts, fuer Algarve duenn - Mikael kann dickere Daemmung beschaffen). Canvas-Dach Standard + Vinyl-Overlay-Option (NICHT in 15k, +1.000 EUR fuer 8m Variante, hat 2 zusaetzliche Oeffnungen). SKYLIGHT: 1.40m Kiefer+Eisen. KONFIG: 1 Doppeltuer + 2 Glas-Fenster in Khaana. AC4-Boden OPTIONAL 700 EUR (feuchtigkeitsresistent). PLATTFORM Sebastian baut selbst.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>VERSAND BESTAETIGT: 750 EUR Selbst-Abholung mit gemietetem Van (Real-Referenz von anderem Kunden in Sebastians Naehe). Spedition vermutlich 1k-1.5k. ALGARVE-RISIKO: Termiten obligatorisch (+500), Schrauben-Ersatz Edelstahl A4 (+200 + 30 Std), Zusatz-Daemmung 8mm (+600 + 5 Std).</t>
+          <t>Selbst-Abholung Mietvan 750 EUR (Real-Referenz). Mikael-Lieferung Castelo-Branco-Mitnahme 1. Juni (vor Sebastians Besuch = nicht nutzbar). Mikael hilft beim Beladen mit Maschine, Helfer auch beim Abladen.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Telegram Direkt-Kontakt 'Mickaël' = Bento (OLX-Verkaeufer). Tragische Geschichte: Brand-Opfer.</t>
+          <t>Telegram 'Mickaël' = Bento (OLX-Verkaeufer). Tragischer Brand-Opfer-Hintergrund.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>AKTUALISIERTE KOSTEN 24.05.2026 mit echtem Versand 750: ALL-IN ~21.790 EUR (Pacific Yurts 15k + AC4 700 + Plattform Kork 3.300 + Zusatz-Daemmung 600 + Versand Selbst-Abholung 750 + Termiten 500 + Schrauben 200 + Schatten 240 + Reserve 500). PRAKTISCH GLEICH MIT DANI (21,6k). VERGLEICH bleibt: Mikael 50m² Pacific-Brand aber 7mm Daemmung+Rost+Termiten+10Mon-Van-Lagerung-Risiko vs DANI 38m² mit 40mm Daemmung+Community+Probeschlafen+anpassbar Sauleda.</t>
+          <t>AKTUALISIERT 24.05.2026 nach voller Antwort: NORMALPREIS waere 18.500, sebastian zahlt 15k = 3.500 EUR fuer Rost. ALLE Schrauben muessen ersetzt werden (Mikael ~800 EUR oder Sebastian ~300 EUR + 50 Std). MIT VINYL-OVERLAY: ALL-IN ~22.320 EUR. OHNE VINYL: ~21.320 EUR. TIMING-KONFLIKT: 1. Juni Lieferung vs 14./21. Juni Besuch = unmoeglich kombiniert. Sebastian schlaegt Selbst-Abholung Ende Juni oder spaetere Liefertour vor.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8041,7 +8041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10190,61 +10190,61 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Bei Mikael's Antwort: Logistik-Entscheidung + Final-Kalkulation Vinyl-Overlay</t>
+          <t>Antwort 19:31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 19:31</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>WEITERE KLAERUNGEN: 1) Selbst-Abholung: nur Mietvan zahlen, kein Mikael-Aufpreis. 2) Vinyl ist 'vinyl coating' (Detail noch unklar). 3) Schrauben-Tausch durch Mikael: ER IST AUF REISEN, koennte jemand anderen organisieren. 4) Schrauben verkaufen wenn Sebastian sie nicht hat: ja. 5) LIEFERUNG ALJEZUR MINIMUM 1.000 EUR (van+sprit+maut+tageslohn) - nicht 500 wie geschaetzt! 6) Andere Pacific Yurts kosten ihn ~19.000 EUR. 7) WICHTIG MENSCHLICH: DRITTE TOCHTER DIESE WOCHE GEBOREN! Familien-Verkaufsdruck.</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Klar - Lieferung teurer als gedacht</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Korrigierte Kalkulation: Mikael-Lieferung 1.000 (statt 500 geschaetzt), Selbst-Abholung 750. Diff nur 250 EUR fuer 3 Tage Aufwand. NEU: Vinyl-Frage klar definieren (coating vs alternativ-Dach). Schrauben selbst tauschen ist besser (Sebastian lernt Jurte kennen).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Empathische Antwort: Glueckwunsch zur Geburt der 3. Tochter. KLARER PLAN in 5 Punkten: 1) Visit Sa 14 oder 21 Juni mit Familie. 2) Selbst-Abholung mit Mietvan nach Besuch. 3) Schrauben Edelstahl A4 selbst kaufen in Algarve (Wuerth PT) + selbst tauschen vor Aufbau. 4) Vinyl-Frage: ist es Beschichtung auf Canvas (a) oder Alternativ-Dach (b)? Bei (a) ja nehmen, bei (b) lieber Canvas+Schattennetz. 5) Zusatz-Daemmung 8mm Schafwolle - Mikael Preis oder Chris PT?</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Bei Antwort: Vinyl-Klaerung entscheidet ob +1.000 EUR sinnvoll oder besser Canvas+Schatten</t>
         </is>
       </c>
     </row>
@@ -10281,67 +10281,141 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F62" s="19" t="inlineStr">
+      <c r="F64" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8041,7 +8041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10276,49 +10276,49 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 - KRITISCH</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Sebastian Cashflow-Realitaet</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Selbst-Klaerung</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian intern</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>WICHTIG: Sebastian hat aktuell nur 5.000 EUR sofort verfuegbar! Differenz ~16.000 EUR muss bis August angespart werden (~5.300 EUR/Monat). Realistische Frage: ist das machbar? Alternativen: A) Mikael Etappenzahlung 5/5/5/6k bis 15. August (transparente Bitte). B) Dani Custom-Bau passt natuerlich zum Bauzeit-Cashflow (Aug/Sep Fertigstellung). C) Konsumkredit PT-Bank 5-15k bei guter Bonitaet (5-7% Zinsen). D) Familien-Darlehen DE. E) Warten bis Sep/Okt mit mehr Eigenanteil.</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>Strategischer Wendepunkt</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>ENTSCHEIDET FINALE STRATEGIE: Sebastian sollte Mikael ehrlich Cashflow kommunizieren + Etappenzahlung 5/5/5/6 bis 15.08 vorschlagen. Lieferung erst nach Vollzahlung (Sicherheit fuer Mikael). Dani's Custom-Bau ist Plan B = passt naturgemaess zum Cashflow.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -10328,12 +10328,12 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
         </is>
       </c>
     </row>
@@ -10355,67 +10355,141 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F64" s="19" t="inlineStr">
+      <c r="F66" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -2781,22 +2781,22 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>16.000 EUR inkl. Aufbau (Transport+Plattform extra). UPGRADES MOEGLICH: Sauleda-Plane +1.100 EUR Material, 8cm Wolle +400 EUR Material. NICHT moeglich: zusaetzliche Fenster (Waende schon fertig).</t>
+          <t>16.000 EUR inkl. Aufbau (Standard mit BW/Poly Canvas+4cm Wolle). Transport+Plattform NICHT inkl. OPTIONAL (Sebastian beschafft selbst): andere Stoffe bis 420g/m² (Dani naeht), dickere Daemmung. NICHT moeglich: zusaetzliche Fenster (Waende schon fertig).</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Khaana: PINIE-Scherengitter, 200cm Wandhoehe. Dachring (Tono): DOUGLASIE. Dachkuppel 150cm doppeltes Plexiglas (stufenlos oeffenbar, windfest). Tueren: 2 Hartholz-Doppeltueren 155x200cm zweifach verglast (= 4,8 m² Glasflaeche durch Tueren, plus 1,77 m² Skylight). KEINE zusaetzlichen Wandfenster moeglich. Daemmung: Standard 4cm Schafwolle (8cm Upgrade moeglich wenn Sebastian Material besorgt - Schafwolle PT-Bezug schwierig, Kontakt 'Chris' via Dani-Vermittlung). Innenstoff: 100% Biobaumwolltuch. Aussenstoff: BW/Polyester 50/50 Canvas Standard ueber ESVO NL (1.400 EUR fuer 7m); ALTERNATIVE STOFFE wenn unter 420g/m² (Sauleda Solar Pro 290-340g/m² oder Tempotest Marine ✓) - Sebastian besorgt selbst, Dani naeht.</t>
+          <t>Khaana: PINIE-Scherengitter, 200cm Wandhoehe. Dachring (Tono): DOUGLASIE. Dachkuppel 150cm doppeltes Plexiglas (stufenlos oeffenbar, windfest). Tueren: 2 Hartholz-Doppeltueren 155x200cm zweifach verglast (= 4,8 m² Glasflaeche durch Tueren, plus 1,77 m² Skylight). KEINE zusaetzlichen Wandfenster moeglich. Daemmung Standard: 4cm Schafwolle. Innenstoff: 100% Biobaumwolltuch. Aussenstoff STANDARD: BW/Polyester 50/50 Canvas ueber ESVO NL.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>VERHANDELBAR: Dani ist sehr flexibel - naeht gerne anderen Stoff bis 420g/m² Maschinen-Limit, macht gerne dickere Daemmung wenn Sebastian Material liefert. SAULEDA SOLAR PRO ist langfristig guenstiger als 5-Jahres-Canvas-Tausch.</t>
+          <t>VERHANDELBAR: Dani naeht andere Stoffe bis 420g/m² wenn Sebastian sie SELBST besorgt+liefert (NICHT aktiv von Dani angeboten als Upgrade). Mein Vorschlag Sauleda Solar Pro/Tempotest waere Sebastians Eigeninitiative fuer Algarve-UV. Aehnlich: dickere Daemmung wenn Sebastian Material organisiert.</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Transport Castelo de Vide -&gt; Aljezur: 800-1.500 EUR. Aufbau IM 16k-Preis. Plattform bauen sie KEINE (Sebastian baut lokal: 2.880 EUR Kork-Variante, siehe Sheet 17).</t>
+          <t>Transport Castelo de Vide -&gt; Aljezur: 800-1.500 EUR (zu klaeren - 'Aufbau' inklusive, aber wo? Bei Dani oder Sebastian?). Aufbau IM 16k-Preis. Plattform bauen sie KEINE (Sebastian baut lokal: 1.925 EUR EPS-Variante oder 2.880 EUR Kork-Variante, siehe Sheet 17).</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>TOP-EMPFEHLUNG WENN UPGRADES MACHBAR: Dani 16k + Sauleda-Upgrade 1.100 + 8cm-Wolle 400 + Plattform Kork 2.880 + Transport 1.000 + Schattennetz 240 = ~21.620 EUR all-in. Spar gegenueber Canvas-5J-Tausch ueber 10J ca. 1.200 EUR. PLUS: 4 Familien-Community vor Ort fuer Sebastians Familie sehr willkommen. PAYPAL-OPTION fuer Anzahlung = wichtiges Sicherheitsnetz fuer Privatverkauf.</t>
+          <t>DREI VARIANTEN ALL-IN: 1) MINIMUM (Standard-Canvas, EPS-Plattform): 16k + 1k Transport + 1.925 + 240 = 19.165 EUR. 2) MITTEL (Standard-Canvas, Kork-Plattform): 16k + 1k + 2.880 + 240 = 20.120 EUR. 3) PREMIUM (Sauleda + 8cm Wolle, Kork-Plattform): 16k + 1k + 2.880 + 240 + 1.100 Sauleda + 400 8cm = 21.620 EUR. ACHTUNG Standard-Canvas haelt nur 3-5J in Algarve = alle 5J 1.400 EUR Plane-Tausch. Premium-Sauleda haelt 10-15J. CASHFLOW: Minimum 3.540 EUR/Mon machbar, Premium 4.155 EUR/Mon knapper.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8041,7 +8041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10313,86 +10313,86 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
+          <t>24.05.2026 spaeter</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Mikael (Bento)</t>
+          <t>Sebastian KORREKTUR-NOTIZ</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Telegram DM</t>
+          <t>Selbst-Klaerung</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Mikael</t>
+          <t>Sebastian intern</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
+          <t>Sebastian-Korrektur: Sauleda-Upgrade ist MEIN VORSCHLAG, Dani hat das NICHT aktiv angeboten. Sie sagte nur 'naehe gerne anderen Stoff wenn IHR ihn selbst besorgt'. Dani's BASIS ist 16k Standard mit BW/Poly Canvas + 4cm Wolle. 3 Varianten ALL-IN: MIN 19.165 EUR (EPS-Plattform), MITTEL 20.120 EUR (Kork-Plattform), PREMIUM 21.620 EUR (mit Sauleda+8cm).</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>Klarstellung</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
+          <t>Korrigierte Cashflow-Bedarfe: MIN 3.540/Mon, MITTEL 3.780/Mon, PREMIUM 4.155/Mon - alle realistischer als Mikael 5.300/Mon.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>~25.05.2026 (Sebastians naechste Mail)</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Dani</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>KONSOLIDIERTE 5-Punkte-Anfrage: 1) AUFBAU WO? Bei euch in Castelo de Vide (ich hole ab) oder bei mir in Aljezur (Transport extra/inkl?)? 2) ANZAHLUNG-Hoehe + Etappenzahlung 5k jetzt + Rest bis September moeglich? 3) HOLZ-Behandlung Termiten was machen sie / was muss Sebastian nachbehandeln? 4) PLATTFORM-Masse fuer Sebastians DIY-Bau (Aussendurchmesser, Verankerung Khaana, Ueberstand)? 5) LIEFERZEIT konkret August oder September Woche X? PROBESCHLAFEN-Termin nach Mitte Juni?</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>5 Kernfragen vor Anzahlung. Sekundaere Fragen (Aufbau-Crew Logistik, Versicherung, Chris-Vermittlung, Garantie) kommen spaeter.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -10402,12 +10402,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
         </is>
       </c>
     </row>
@@ -10429,67 +10429,141 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F66" s="19" t="inlineStr">
+      <c r="F68" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8041,7 +8041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9408,17 +9408,17 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>Schafwolle 8cm fuer 7m Jurte, Liefermenge ca. 50 m², Algarve-Klima beraten, Aufpreis vs 4cm</t>
+          <t>Erstanfrage: Selbst-Vorstellung mit Dani's Vermittlung als Referenz. Bedarf: 50-60 m² Schafwoll-Filz (8mm oder 16mm) fuer Algarve-Atlantikkueste. Fragen: Preis pro m², Lieferung 8650 Aljezur, Lieferzeit, Mengenrabatt, Motten-/Insekten-Behandlung, Algarve-Referenzkunden.</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>⏳ Vermittlung steht aus</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>Wenn Dani vermittelt: Chris direkt anschreiben</t>
+          <t>Bei Antwort: Vergleich mit Isolena AT (~16 EUR/m² netto) und Tobias Tumfart AT (~8 EUR/m² 8mm netto). Chris als lokale PT-Quelle koennte Versand-Vorteil haben.</t>
         </is>
       </c>
     </row>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>KONSOLIDIERTE 5-Punkte-Anfrage: 1) AUFBAU WO? Bei euch in Castelo de Vide (ich hole ab) oder bei mir in Aljezur (Transport extra/inkl?)? 2) ANZAHLUNG-Hoehe + Etappenzahlung 5k jetzt + Rest bis September moeglich? 3) HOLZ-Behandlung Termiten was machen sie / was muss Sebastian nachbehandeln? 4) PLATTFORM-Masse fuer Sebastians DIY-Bau (Aussendurchmesser, Verankerung Khaana, Ueberstand)? 5) LIEFERZEIT konkret August oder September Woche X? PROBESCHLAFEN-Termin nach Mitte Juni?</t>
+          <t>INHALTLICHE 4-Punkte-Anfrage (OHNE Anzahlung-Thema - kommt spaeter separat): 1) AUFBAU WO? Bei euch in Castelo de Vide (ich hole ab) oder bei mir in Aljezur (Transport extra/inkl?)? 2) HOLZ-Behandlung Termiten was machen sie / was muss Sebastian nachbehandeln? 3) PLATTFORM-Masse fuer Sebastians DIY-Bau (Aussendurchmesser, Verankerung Khaana, Ueberstand)? 4) LIEFERZEIT konkret August oder September Woche X? Plus: PROBESCHLAFEN-Termin nach Mitte Juni?</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -10380,19 +10380,19 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>5 Kernfragen vor Anzahlung. Sekundaere Fragen (Aufbau-Crew Logistik, Versicherung, Chris-Vermittlung, Garantie) kommen spaeter.</t>
+          <t>Strategisch: erst inhaltliche Fragen + Vertrauen, dann separat Geld-Thema (Anzahlung+Etappen). Sebastian-Style: 'erst die Sache, dann das Geld'.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
+          <t>~25.05.2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Mikael (Bento)</t>
+          <t>Chris (PT-Schafwoll-Anbieter via Dani)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -10402,12 +10402,12 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Mikael</t>
+          <t>Sebastian -&gt; Chris</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
+          <t>Erstanfrage Deutsch: Selbst-Vorstellung + Dani's Vermittlung als Referenz. Bedarf: 50-60 m² Schafwoll-Filz (8mm/16mm) fuer Algarve-Atlantikkueste. Fragen: Preis pro m², Lieferung 8650 Aljezur, Lieferzeit, Mengenrabatt, Motten-/Insekten-Behandlung, Algarve-Referenzkunden.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -10417,44 +10417,44 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
+          <t>Bei Antwort: Vergleich mit Isolena AT und Tobias Tumfart AT. Chris als lokale PT-Quelle koennte Versand-Vorteil haben.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
         </is>
       </c>
     </row>
@@ -10466,32 +10466,32 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Telegram DM</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
@@ -10503,67 +10503,104 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Sebastian -&gt; Dror</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F68" s="19" t="inlineStr">
+      <c r="F69" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G69" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -2766,12 +2766,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Dani's Community-Projekt 7m Custom (Castelo de Vide, Alentejo)</t>
+          <t>Dani + Chris (Castelo de Vide Community-Projekt) - 7m Custom</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Portugal - Castelo de Vide (Alto Alentejo, ca. 400 km von Aljezur)</t>
+          <t>Portugal - Castelo de Vide (Alto Alentejo, ca. 400 km von Aljezur). Dani=Frau (Kommunikation), Chris=Mann (technisch+Schafwolle)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -10375,12 +10375,12 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>🔄 Umgeleitet an Chris (Danis Mann)</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>Strategisch: erst inhaltliche Fragen + Vertrauen, dann separat Geld-Thema (Anzahlung+Etappen). Sebastian-Style: 'erst die Sache, dann das Geld'.</t>
+          <t>Sebastian's Entscheidung: 4 inhaltliche Punkte direkt an Chris (Danis Mann, technisch-fokussierte Person, hat auch Schafwoll-Expertise). Eine Mail an Chris statt zwei separate Threads.</t>
         </is>
       </c>
     </row>
@@ -10392,7 +10392,7 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Chris (PT-Schafwoll-Anbieter via Dani)</t>
+          <t>Chris (Danis Mann, Castelo de Vide)</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Erstanfrage Deutsch: Selbst-Vorstellung + Dani's Vermittlung als Referenz. Bedarf: 50-60 m² Schafwoll-Filz (8mm/16mm) fuer Algarve-Atlantikkueste. Fragen: Preis pro m², Lieferung 8650 Aljezur, Lieferzeit, Mengenrabatt, Motten-/Insekten-Behandlung, Algarve-Referenzkunden.</t>
+          <t>Persoenliche Einleitung + 4 inhaltliche Punkte (von urspruenglicher Dani-Mail): 1) Aufbau wo+Transport, 2) Holz-Behandlung Termiten, 3) Plattform-Masse fuer DIY, 4) Lieferzeit Aug/Sep konkret. PLUS integriert: Schafwoll-Frage (Chris ist Wolle-Quelle laut Dani). Plus Probeschlafen-Termin.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Bei Antwort: Vergleich mit Isolena AT und Tobias Tumfart AT. Chris als lokale PT-Quelle koennte Versand-Vorteil haben.</t>
+          <t>WICHTIGE KORREKTUR: Chris ist Danis Mann (Partner), nicht externer Anbieter! Sebastian schreibt direkt an ihn als technische Person des Paars. Beide getrennten Mails (Dani 4 Punkte + Chris Schafwoll) in EINE konsolidierte Chris-Mail integriert. Eine Person zu kontaktieren ist effizienter.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Persoenliche Einleitung + 4 inhaltliche Punkte (von urspruenglicher Dani-Mail): 1) Aufbau wo+Transport, 2) Holz-Behandlung Termiten, 3) Plattform-Masse fuer DIY, 4) Lieferzeit Aug/Sep konkret. PLUS integriert: Schafwoll-Frage (Chris ist Wolle-Quelle laut Dani). Plus Probeschlafen-Termin.</t>
+          <t>FINAL 4-Punkte-Mail an Chris: 1) AUFBAU - anerkennt Danis Aussage 'inkl. Aufbau', fragt KONKRETISIERUNG: liefert ihr zu mir nach Aljezur+Aufbau vor Ort? Transport extra/inkl? 2) Holz-Behandlung Termiten 3) Plattform-Masse fuer DIY 4) Lieferzeit Aug/Sep + Probeschlafen-Termin. Schafwoll-Frage bewusst NICHT in dieser Mail (kommt spaeter wenn naehere Klaerung).</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>WICHTIGE KORREKTUR: Chris ist Danis Mann (Partner), nicht externer Anbieter! Sebastian schreibt direkt an ihn als technische Person des Paars. Beide getrennten Mails (Dani 4 Punkte + Chris Schafwoll) in EINE konsolidierte Chris-Mail integriert. Eine Person zu kontaktieren ist effizienter.</t>
+          <t>Persoenlich+praezise: 'Dani hatte gesagt' zeigt Sebastian geht nicht hinter Dani's Ruecken vorbei. Aufbau-Frage konkretisierend statt offen. 'euch' anerkennt Paar-Team.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>FINAL 4-Punkte-Mail an Chris: 1) AUFBAU - anerkennt Danis Aussage 'inkl. Aufbau', fragt KONKRETISIERUNG: liefert ihr zu mir nach Aljezur+Aufbau vor Ort? Transport extra/inkl? 2) Holz-Behandlung Termiten 3) Plattform-Masse fuer DIY 4) Lieferzeit Aug/Sep + Probeschlafen-Termin. Schafwoll-Frage bewusst NICHT in dieser Mail (kommt spaeter wenn naehere Klaerung).</t>
+          <t>FOLGE-MAIL (kein Selbst-Vorstellung mehr - bereits Kontakt). 5 Punkte: 1) AUFBAU - konkretisiert Danis Aussage 'inkl. Aufbau' (liefert ihr zu Aljezur? Transport extra?). 2) Holz-Behandlung Termiten. 3) Plattform-Masse fuer DIY. 4) Lieferzeit Aug/Sep konkret. 5) AUSSENHUELLE: Sebastian erwaehnt Marine-Acryl-Stoff-Recherche + 10-J-Garantie-Hinweis bei PT-Herstellern, fragt ob Alternative zum BW/Poly Standard moeglich (Aufpreis traegt Sebastian). Plus Probeschlafen-Termin.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Persoenlich+praezise: 'Dani hatte gesagt' zeigt Sebastian geht nicht hinter Dani's Ruecken vorbei. Aufbau-Frage konkretisierend statt offen. 'euch' anerkennt Paar-Team.</t>
+          <t>Sebastians Recherche-Hinweis (Sauleda subtil) als ELEGANTES Anregen: Casa-dos-Sonhos-Referenz im Hintergrund ohne Wettbewerbsdruck-Gefuehl. 'Aufpreis traegt Sebastian' entwaffnet die Frage.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -1954,32 +1954,32 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8m Rahmen 6.600 + 4 Fenster + Kuppel = 9.410 netto / +Plane (Sauleda+Airtex) 2.200 / +Versand PT 3.500</t>
+          <t>8m Frame-only KONKRET 25.05.2026: Buche-Basis 6.600 + EICHE-Upgrade 410 + OEL-Behandlung 340 = 7.350 EUR netto. Versand selbst-Spediteur OK.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Rahmen Buche (Standard) oder Eiche/Laerche (Upgrade), Rest Sibirische Kiefer lackiert (Sebastian wuenscht Oel-Finish), Plane Sauleda PVC Dach + Airtex Acryl Wand, Standard-Daemmung Spiegelfolie+Vatelin (fuer Algarve NICHT empfohlen - Sebastian sourct Wollfilz+Tyvek selbst)</t>
+          <t>Rahmen WAEHLBAR: Eiche (Empfehlung, Algarve-optimal) statt Buche (Standard). Rest Sibirische Kiefer. ALLES OEL-BEHANDELT (atmungsaktiv, fuer Algarve perfekt!). Plane + Kuppel + Filz Sebastian besorgt selbst (Algarve-Sattler/Chris).</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Mittel: Erfahrung ES/BE/DE/PL aber NICHT explizit Atlantik-Kueste. Buche-Standard fuer humide Algarve ungeeignet -&gt; Holz-Upgrade obligatorisch.</t>
+          <t>Sehr gut: EICHE (Klasse 2 Dauerhaftigkeit, Termiten-resistent durch Gerbstoffe) + OEL (diffusionsoffen) = optimal fuer humide Atlantikkueste.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Versand HU-&gt;Algarve 3.500 EUR (hoch). EU-USt-IdNr noetig fuer steuerfreie IC-Lieferung (sonst 27% MwSt HU). Lieferzeit 1-2 Monate. Foundation-Plaene inkl.</t>
+          <t>Versand HU-&gt;Algarve via Sebastians eigener Spediteur (Atilla bestaetigt 'positive') ca. 800 EUR. Lieferzeit 2 Mon. Aufbau Sebastian selbst (mit 4-6 Helfern).</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Atilla Berki, Jurtenbauer seit 1996, erster kommerzieller HU-Hersteller. Sozial: Rahmen aus Therapieprogramm fuer Drogenabhaengige/Jugendstraftaeter. Ehrlich (sagt selbst Airtex nicht atmungsaktiv). Kontakt: jurtak@gmail.com / +36 30 657 0740</t>
+          <t>Atilla Berki, Jurtenbauer seit 1996, erster kommerzieller HU-Hersteller. Sozial: Rahmen aus Therapieprogramm. Ehrlich+praezise Kommunikation. Kontakt: jurtak@gmail.com / +36 30 657 0740</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>8m mit Eichen-Upgrade+Premium-Daemmung+Versand: 17.700-20.500 netto (UEBER 15k Budget)</t>
+          <t>DIY-MODIFY 8M VOLLKOSTEN MIT ATILLA-EICHE: 7.350 Frame + 800 Versand + 2.500 Sauleda-Plane lokal + 1.000 Wolle + 700 Solitex + 800 Innenliner + 800 Kuppel + 200 Schrauben + 2.880 Plattform DIY + 500 Sturm-Kit + 240 Schatten + 500 Reserve = ~18.270 EUR. 100+ Std Eigenarbeit. PREIS-KOENIG fuer 8m wenn DIY-Lust + Cashflow-Tauglichkeit. Eiche statt Pinie/Buche ist STRUKTURELLER VORTEIL fuer Algarve.</t>
         </is>
       </c>
     </row>
@@ -8041,7 +8041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10424,86 +10424,86 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>Mikael (Bento)</t>
+          <t>Atilla es a Fehernep</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Telegram DM</t>
+          <t>E-Mail</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Mikael</t>
+          <t>Atilla -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
+          <t>KONKRETES FRAME-ONLY-ANGEBOT: Buche-Basis 6.600 + Eiche-Upgrade 410 + Oel-Behandlung 340 = 7.350 EUR netto. KEINE Acryl-Kuppel verfuegbar (nur mit seinem Cover kompatibel). Lieferzeit ~2 Monate. Versand: gleiches Auto noetig (kein Volumen-Rabatt), aber Sebastians EIGENER SPEDITEUR OK (Antwort positiv). Eiche besser als Laerche (in HU schwer zu bekommen). Oel-Behandlung statt Lack.</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Klares konkretes Angebot</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
+          <t>ATILLA WIRD ZUM PREISKOENIG fuer DIY-Modify 8m: 18.270 EUR all-in mit Eiche+Oel+Sauleda+Wolle+Plattform DIY. 100 Std Eigenarbeit. Eiche+Oel = STRUKTURELL BESSER fuer Algarve als Pinie+Lack bei Mikael.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>25.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Atilla es a Fehernep</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>E-Mail</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Atilla</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>Klarstellungs-Fragen: 1) Was genau in 7.350 inkludiert (Khana? Tono? Uni? Tuer)? 2) Dimensionen-Standard 8m: Wandhoehe, Tono-Durchmesser, Uni-Anzahl+Querschnitt? 3) Timing: bei Bestellung Mitte Juni, wann Pickup ready? Plus: Kuppel besorgt Sebastian lokal mit Plane-Sattler.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Bei Antwort: finale Liste fuer Sebastian's Eigenkoordination der separaten Komponenten (Kuppel, Plane, Filz, Innenliner)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -10513,12 +10513,12 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -10528,7 +10528,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
         </is>
       </c>
     </row>
@@ -10540,67 +10540,141 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E69" s="3" t="inlineStr">
+      <c r="E71" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F69" s="19" t="inlineStr">
+      <c r="F71" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G71" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>
@@ -15206,7 +15280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -15315,27 +15389,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>DIY Modify Szenario A (Adorjan-Rahmen + Algarve-Sauleda-Sattler)</t>
+          <t>Atilla 8m Frame-only (Eiche+Oel) + Algarve-Sauleda-Sattler + Chris-Wolle</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DIY-Hybrid - lokaler PT-Sattler + HU-Rahmen</t>
+          <t>DIY-Hybrid - HU Premium-Frame + Algarve-Service</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>ca. 10.300-11.000 EUR all-in (6m)</t>
+          <t>~18.270 EUR all-in (Atilla 7.350 + Versand 800 + Sauleda 2.500 + Wolle 1.000 + Solitex 700 + Innenliner 800 + Kuppel 800 + Schrauben 200 + Plattform Kork 2.880 + Sturm 500 + Schatten 240 + Reserve 500)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>NEUER SPITZENREITER seit Casa-Slot weg: Adorjan 6m Rahmen 1.750 + Versand 1.200 + Sauleda Marine-Acryl bei lokalem Algarve-Sattler 1.800-2.500 + PET-Daemmung 500 (Tobias Tumfart AT, 8,16€/m²) + Solitex 500 + Plattform DIY 3.000 + Sturm-Kit 400 + Schattennetz 240 + Reserve 500. PT-LOKALER SATTLER (z.B. Dune Algarve Sailmakers in Vilamoura) ist der Game-Changer: Sauleda Solar Pro Acryl ist objektiv BESSER als unspezifiziertes Casa-Canvas. 4.000-5.000 EUR Ersparnis vs Casa Wartezeit 2027. Sofortige Verfuegbarkeit. Volle Materialkontrolle. Risiko: Selbstaufbau-Skill, Maßabstimmung Rahmen-&gt;Plane, keine Komplett-Garantie.</t>
+          <t>PREIS-KOENIG fuer 8m DIY-Modify (Mai 2026): Atilla Frame-only-Angebot 7.350 EUR netto (6.600 Buche-Basis + 410 EICHE-Upgrade + 340 OEL-Behandlung) - Eiche+Oel ist STRUKTURELLER VORTEIL fuer Algarve (Klasse 2 Dauerhaftigkeit, atmungsaktiv, Termiten-resistent durch Gerbstoffe). Versand via Sebastians eigener Spediteur OK. 50 m² Wohnflaeche. 100 Std Eigenarbeit. ABER: Atilla liefert KEINE Acryl-Kuppel (Sebastian besorgt separat), KEIN Cover (Sebastian beauftragt Dune Algarve Sailmakers fuer Sauleda Solar Pro). Lieferzeit 2 Monate. Atilla seit 1996 etabliert, ehrlich+praezise.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>https://adorjan-jurta.hu/  |  https://www.dunesailmakers.com/</t>
+          <t>https://jurtak.hu/ | Sauleda lokal Algarve: https://www.dunesailmakers.com/</t>
         </is>
       </c>
     </row>
@@ -15345,27 +15419,27 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Paula Young - gebrauchte Casa-Jurte 7,3m</t>
+          <t>DIY Modify Szenario A (Adorjan-Rahmen + Algarve-Sauleda-Sattler)</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Used-Markt (Algarve direkt)</t>
+          <t>DIY-Hybrid - lokaler PT-Sattler + HU-Rahmen</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Schaetzung 8.000-11.000 EUR + Transport 1.000</t>
+          <t>ca. 10.300-11.000 EUR all-in (6m)</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ALGARVE-LEAD von Casa-Sarah selbst empfohlen: Paula Young (FB 'Paula Vegan Chef') verkauft 7,3m Casa-Jurte (42m²). Gebrauchte Casa-Qualitaet mit Original-Garantie-Resten. PHYSISCH VERIFIZIERBAR vor Kauf, kein Vorauszahlungs-Risiko, sofort verfuegbar, GROESSER als Casa 6,1m. Wichtige Pruefpunkte: Alter Plane (10-J. Casa-Garantie laeuft mit), Zustand Filz/Holz, Grund Verkauf, Algarve-Praxiserfahrung. Kontakt ueber Facebook-Suche oder Einfuehrung via Sarah Casa.</t>
+          <t>NEUER SPITZENREITER seit Casa-Slot weg: Adorjan 6m Rahmen 1.750 + Versand 1.200 + Sauleda Marine-Acryl bei lokalem Algarve-Sattler 1.800-2.500 + PET-Daemmung 500 (Tobias Tumfart AT, 8,16€/m²) + Solitex 500 + Plattform DIY 3.000 + Sturm-Kit 400 + Schattennetz 240 + Reserve 500. PT-LOKALER SATTLER (z.B. Dune Algarve Sailmakers in Vilamoura) ist der Game-Changer: Sauleda Solar Pro Acryl ist objektiv BESSER als unspezifiziertes Casa-Canvas. 4.000-5.000 EUR Ersparnis vs Casa Wartezeit 2027. Sofortige Verfuegbarkeit. Volle Materialkontrolle. Risiko: Selbstaufbau-Skill, Maßabstimmung Rahmen-&gt;Plane, keine Komplett-Garantie.</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Facebook: 'Paula Vegan Chef' / Sarah Casa als Vermittler</t>
+          <t>https://adorjan-jurta.hu/  |  https://www.dunesailmakers.com/</t>
         </is>
       </c>
     </row>
@@ -15375,27 +15449,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Yurt Made in Portugal (Loures, OLX-Hersteller)</t>
+          <t>Paula Young - gebrauchte Casa-Jurte 7,3m</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Hersteller PT (Lissabon-Region)</t>
+          <t>Used-Markt (Algarve direkt)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5m 6.900 / 6m 8.400 / 7-8m Anfrage</t>
+          <t>Schaetzung 8.000-11.000 EUR + Transport 1.000</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>PT-LOKAL ALTERNATIVE zu Casa: junger Hersteller seit 2020 bei Lissabon. Kein Import-Zoll, kein Versandstress. Preise transparent auf OLX. Klima-Garantie &amp; UV-Spezifikation noch zu erfragen! Anfrage dringend lohnt sich, bevor andere Optionen verfolgt werden. Kontakt via OLX.pt.</t>
+          <t>ALGARVE-LEAD von Casa-Sarah selbst empfohlen: Paula Young (FB 'Paula Vegan Chef') verkauft 7,3m Casa-Jurte (42m²). Gebrauchte Casa-Qualitaet mit Original-Garantie-Resten. PHYSISCH VERIFIZIERBAR vor Kauf, kein Vorauszahlungs-Risiko, sofort verfuegbar, GROESSER als Casa 6,1m. Wichtige Pruefpunkte: Alter Plane (10-J. Casa-Garantie laeuft mit), Zustand Filz/Holz, Grund Verkauf, Algarve-Praxiserfahrung. Kontakt ueber Facebook-Suche oder Einfuehrung via Sarah Casa.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>https://www.olx.pt/d/anuncio/yurt-made-in-portugal-IDIyzPL.html</t>
+          <t>Facebook: 'Paula Vegan Chef' / Sarah Casa als Vermittler</t>
         </is>
       </c>
     </row>
@@ -15405,27 +15479,27 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>YourTent.com CZ (Praha)</t>
+          <t>Yurt Made in Portugal (Loures, OLX-Hersteller)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Hersteller CZ - 5J-Plane-Garantie</t>
+          <t>Hersteller PT (Lissabon-Region)</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>Schaetzung 12.000-16.000 EUR 6m inkl. Versand</t>
+          <t>5m 6.900 / 6m 8.400 / 7-8m Anfrage</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>BESTE PLANE-GARANTIE NACH CASA: 5 JAHRE Plane-Garantie (60 Monate). 150 Jurten in 12 Jahren gebaut, MEDITERRANEAN TRACK RECORD bis Kanarische Inseln + Polarkreis. LAERCHENHOLZ-Rahmen (Algarve-optimal). 180cm Standard-Wandhoehe, 50mm Schafwoll-Filz, franz. Doppeltuer Laerche, Skylight 150/180cm, Ofen-Vorbereitung. Online-Kalkulator + Anfrage. Versand CZ-&gt;PT ca. 1.500-2.500 EUR.</t>
+          <t>PT-LOKAL ALTERNATIVE zu Casa: junger Hersteller seit 2020 bei Lissabon. Kein Import-Zoll, kein Versandstress. Preise transparent auf OLX. Klima-Garantie &amp; UV-Spezifikation noch zu erfragen! Anfrage dringend lohnt sich, bevor andere Optionen verfolgt werden. Kontakt via OLX.pt.</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>https://www.yourtent.com/</t>
+          <t>https://www.olx.pt/d/anuncio/yurt-made-in-portugal-IDIyzPL.html</t>
         </is>
       </c>
     </row>
@@ -15435,27 +15509,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Casa dos Sonhos Yurts (2027er Slot)</t>
+          <t>YourTent.com CZ (Praha)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Hersteller PT - 10-J. UV-Garantie SCHRIFTLICH</t>
+          <t>Hersteller CZ - 5J-Plane-Garantie</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6,1m 9.700 / 7,3m 15.750 EUR delivered+erected PT</t>
+          <t>Schaetzung 12.000-16.000 EUR 6m inkl. Versand</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>BLEIBT TOP-OPTION FUER LAENGEREN ZEITHORIZONT (2027+): Oktober 2026-Slot wurde 15.05.2026 an anderen Kunden vergeben. Naechster verfuegbarer Slot in 2027. Trotzdem das technisch beste Angebot fuer Algarve mit 10 J. UV-Garantie auf Plane, alles inkl. Lieferung+Aufbau in Festland-PT, portugiesische Materialien. Sarah &amp; Vladimir (UK-Familien-Betrieb) etabliert seit Jahren in Alegrete. NIPC: Empresario em Nome Individual. Verifizieren via Brett bei Quinta Glamping + Werkstatt-Besuch.</t>
+          <t>BESTE PLANE-GARANTIE NACH CASA: 5 JAHRE Plane-Garantie (60 Monate). 150 Jurten in 12 Jahren gebaut, MEDITERRANEAN TRACK RECORD bis Kanarische Inseln + Polarkreis. LAERCHENHOLZ-Rahmen (Algarve-optimal). 180cm Standard-Wandhoehe, 50mm Schafwoll-Filz, franz. Doppeltuer Laerche, Skylight 150/180cm, Ofen-Vorbereitung. Online-Kalkulator + Anfrage. Versand CZ-&gt;PT ca. 1.500-2.500 EUR.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>https://www.casadossonhos.co.uk/  |  https://www.facebook.com/yurtscasadossonhos/</t>
+          <t>https://www.yourtent.com/</t>
         </is>
       </c>
     </row>
@@ -15465,25 +15539,55 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>Casa dos Sonhos Yurts (2027er Slot)</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Hersteller PT - 10-J. UV-Garantie SCHRIFTLICH</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>6,1m 9.700 / 7,3m 15.750 EUR delivered+erected PT</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>BLEIBT TOP-OPTION FUER LAENGEREN ZEITHORIZONT (2027+): Oktober 2026-Slot wurde 15.05.2026 an anderen Kunden vergeben. Naechster verfuegbarer Slot in 2027. Trotzdem das technisch beste Angebot fuer Algarve mit 10 J. UV-Garantie auf Plane, alles inkl. Lieferung+Aufbau in Festland-PT, portugiesische Materialien. Sarah &amp; Vladimir (UK-Familien-Betrieb) etabliert seit Jahren in Alegrete. NIPC: Empresario em Nome Individual. Verifizieren via Brett bei Quinta Glamping + Werkstatt-Besuch.</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.casadossonhos.co.uk/  |  https://www.facebook.com/yurtscasadossonhos/</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>Bēt Yurts (August 2026 Slot)</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Hersteller PT (Algarve direkt)</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>6m 28.060 / 7m 31.940 / 9m 44.870 EUR all-in</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>ALGARVE-LOKAL ABER PREMIUM-PREIS: Konkretes Quote-PDF erhalten. Halb so teuer waere besser - DOPPELT SO TEUER wie Casa. 50% NICHT-RUECKZAHLBAR upfront, nur 2 JAHRE Plane-Garantie. Material laut Quote: 'Nordic Pine + Outer canvas + 80mm Insulation' OHNE Marken-/Herstellernennung (Marketing 'marine-grade' nicht im Quote bestaetigt). AUGUST 2026 Slot verfuegbar - Zeit-Vorteil. Nur empfehlenswert wenn andere Optionen ausfallen + August-Lieferung zwingend.</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>https://www.betyurts.com/</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8041,7 +8041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10498,12 +10498,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>Mikael (Bento)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -10513,71 +10513,71 @@
       </c>
       <c r="D67" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Mikael</t>
+          <t>Dani -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
+          <t>Chris hat ihr erzaehlt dass Sebastian Marinestoff von PT-Shop im Auge hat. Dani fragt: 'kannst du Link senden? Will pruefen ob meine Maschine das schafft (Limit 420g/m²)'</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Stoff-Frage offen</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
+          <t>POSITIV: Dani technisch offen fuer Sauleda/Tempotest wenn Material kompatibel! Aber: Sebastian hat tatsaechlich noch keinen konkreten PT-Shop, nur Marken-Recherche. Muss ehrlich klarstellen.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>25.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Dani</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>Ehrliche Korrektur: 'Chris hat mich besser gemacht als ich bin - hab keinen festen Shop, nur Marken-Recherche.' Konkret: Sauleda Solar Pro/Nautic (290-340 g/m²), Tempotest Para Marine (290-310 g/m²) - beide klar unter 420g/m² Limit. PT-Direktshop keiner bekannt, aber Sauleda via spanischen Distributoren (Coartal, Toldum.es) oder via Dune Algarve Sailmakers Vilamoura. Dani's Lieferanten-Empfehlung erfragt. Demuetig: 'will euch nicht zwingen mit neuem Material'.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Drei moegliche Reaktionen: a) Dani prueft Datenblatt = positiv, b) Dani kennt eigenen Lieferanten = Bonus, c) Dani bleibt bei ESVO Standard = Sebastian akzeptiert BW/Poly.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -10587,12 +10587,12 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -10602,7 +10602,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
         </is>
       </c>
     </row>
@@ -10614,67 +10614,141 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E71" s="3" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F71" s="19" t="inlineStr">
+      <c r="F73" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G73" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -25,6 +25,7 @@
     <sheet name="16 DIY Bauplan-Quellen" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="17 Plattform 7m Kostenrechnung" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="18 Mikael 3 Szenarien" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="19 Atilla DIY Stunden" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +37,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;EUR&quot;"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,6 +69,10 @@
     </font>
     <font>
       <i val="1"/>
+      <color rgb="002E5C8A"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="002E5C8A"/>
     </font>
   </fonts>
@@ -135,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -183,6 +188,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -13841,6 +13849,905 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Atilla DIY-Modify 8m - Stunden-Aufschluesselung Eigenarbeit (Sebastians Frage Mai 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Taetigkeit</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Stunden</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Bemerkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>BLOCK 1: PLATTFORM DIY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Schraubpfaehle setzen (8x Krinner KSF-M)</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>4-6 Std</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Mit Hand-Erdrakete oder hydraulisches Eindrehgeraet</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Tragwerk Doppel-T + Radial-Balken</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>8-12 Std</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Kiefer KDI 50x200, Schrauben</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Kork-Daemmung einlegen (PE-Folie+Kork 80mm)</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>4 Std</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Plattform-Daemmung Sheet 17 Variante B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Laerchen-Deck T+G verlegen 50 m²</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>8-12 Std</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Bohren, schrauben, schneiden</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Schrauben + Kanten-Arbeiten + Aufmass</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>2-3 Std</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>PLATTFORM-TOTAL</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>26-37 Std</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10" ht="8" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>BLOCK 2: FRAME-AUFBAU (mit 4-6 Helfern)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Khaana entfalten + im Kreis stellen</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>4-6 Std</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Mit 4 Helfern</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Tuerrahmen einsetzen + Spannband</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>3-4 Std</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Kuriye-Band Wandkrone</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Tono hochheben + 60+ Uni einsetzen</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>6-8 Std</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>ALLE Helfer aktiv, Leitern, kritischer Schritt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Tuerblatt einhaengen + justieren</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>2-3 Std</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Zwei-Personen-Arbeit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>AUFBAU-TOTAL</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>15-21 Std</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Sebastians Stunden gezaehlt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="8" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>BLOCK 3: PLANE + MEMBRAN + DAEMMUNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Innenliner Baumwolle befestigen</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>3-4 Std</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Tacker, Naehnadel an Khaana</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Wollfilz auflegen (Wand + Dach)</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>4-6 Std</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>8mm Filz auf Khaana</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Solitex-Membran ueberlappend</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>2-3 Std</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Diffusionsoffene Schicht</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Aussenplane Sauleda hochziehen+spannen</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>4-6 Std</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Mit 4 Helfern und Leitern</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Kuppel-Oberlicht einsetzen</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>1-2 Std</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Polycarbonat 1.40 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>PLANE/DAEMMUNG-TOTAL</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>14-21 Std</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="8" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>BLOCK 4: STURM-KIT + SCHATTENNETZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>8-10 Erdanker setzen fuer Sturm</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>2-3 Std</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Krinner M16 1m Anker</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Ratschen-Riemen ueber Dach spannen</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
+        <is>
+          <t>2 Std</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Algarve-Wind-Schutz</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Schattennetz drueber montieren</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
+        <is>
+          <t>2-3 Std</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Wichtig fuer Plane-Lebensdauer</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>STURM/SCHATTEN-TOTAL</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>6-8 Std</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="8" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>BLOCK 5: TERMITEN-BEHANDLUNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Borax-Loesung anruehren + Khaana behandeln</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
+        <is>
+          <t>4-6 Std</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Pinsel, alle Holzflaechen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Trocknen + 2. Anstrich falls noetig</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
+        <is>
+          <t>2 Std</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>TERMITEN-TOTAL</t>
+        </is>
+      </c>
+      <c r="B35" s="21" t="inlineStr">
+        <is>
+          <t>6-8 Std</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Vor Aufbau machen!</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="8" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>BLOCK 6: KOORDINATIONS-ARBEIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Atilla-Bestellung + Versand-Logistik HU-&gt;PT</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>3-5 Std</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Eigener Spediteur + Maut/Versicherung</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sauleda-Material bestellen ES oder PT</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>3-5 Std</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Lieferanten-Vergleich + Bestellung</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Sattler-Termin koordinieren</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>2-4 Std</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Vilamoura - Mass+Naeh-Termin</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Chris-Wolle bestellen + Lieferung</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>1-2 Std</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>PT-Direkt oder Isolena AT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Kuppel separat bestellen</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>1-2 Std</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Polycarbonat-Anbieter PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Schrauben + Beschlaege Wuerth PT</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="inlineStr">
+        <is>
+          <t>2-3 Std</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Edelstahl A4 zusammenstellen</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Plaene + Masse zwischen Lieferanten</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="inlineStr">
+        <is>
+          <t>3-5 Std</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Verteilt ueber Wochen</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>KOORDINATIONS-TOTAL</t>
+        </is>
+      </c>
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>15-26 Std</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>ueber mehrere Wochen verteilt</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="8" customHeight="1"/>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>BLOCK 7: OPTIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>AC4 Boden verlegen falls genommen</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>4-6 Std</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Schwimmend, Klicksystem</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Innen-Ausbau Moebel</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>variabel</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Nicht in Eigenarbeit gerechnet</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1"/>
+    <row r="51" ht="21" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>GESAMT-TOTAL OHNE BLOCK 7</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>86-127 Std</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Realistisch 100-130 Std fuer normalen DIY-Hintergrund</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Mit Erfahrung Holzarbeiten</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>80-100 Std</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Anfaenger DIY</t>
+        </is>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
+        <is>
+          <t>130-160 Std</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr"/>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>AUSLAGERUNGS-OPTIONEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Plattform fertig bauen lokaler PT-Zimmermann</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>spart 30 Std</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>+1.500-2.500 EUR extra</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Frame-Aufbau-Hilfe 4 Helfer 2 Tage</t>
+        </is>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>spart 10 Std</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>+800 EUR (Sebastian noch dabei)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Plane bei Atilla naehen lassen vor Versand</t>
+        </is>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>spart 5 Std</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>+500-800 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Termiten-Behandlung PT-Profi</t>
+        </is>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
+        <is>
+          <t>spart 6 Std</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>+300-500 EUR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Mit allen Auslagerungen</t>
+        </is>
+      </c>
+      <c r="B60" s="20" t="inlineStr">
+        <is>
+          <t>40-50 Std</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Aber +3.000-4.500 EUR = ca. 22.500 EUR all-in (kein Vorteil mehr vs Dani)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="8" customHeight="1"/>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>VERGLEICH EIGENARBEIT ALLER OPTIONEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="21" customHeight="1">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Atilla DIY-Modify</t>
+        </is>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>100-130 Std</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Bei 30 EUR/h Hobby-Wert = 3.000-3.900 EUR Eigenleistung</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Mikael Pacific Yurts</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>40-50 Std</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Plattform+Schrauben+Termiten+Aufbau-Hilfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Dani Standard (sie baut Jurte auf)</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="inlineStr">
+        <is>
+          <t>25-35 Std</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Nur Plattform-DIY</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>FAZIT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Atilla 100 Std = real (verteilt 7 Bloecke)</t>
+        </is>
+      </c>
+      <c r="B68" s="20" t="inlineStr"/>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Vor allem Koordination 15-26 Std + Plattform 26-37 Std + Aufbau 15-21 Std macht Hauptteil</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Wert der Eigenarbeit</t>
+        </is>
+      </c>
+      <c r="B69" s="20" t="inlineStr"/>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>2.000 EUR gespart vs Dani, dafuer 70-100 Std mehr Arbeit. Lohnt sich wenn DIY-Hobby + Zeit. Nicht lohnt wenn knapp Zeit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A26:C26"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8049,7 +8049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>Mikael (Bento)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -10595,71 +10595,71 @@
       </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Mikael</t>
+          <t>Dani -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
+          <t>Locker mit Humor ('aha 😜'): bestaetigt sie hat NUR ueber ESVO Holland bestellt+genaeht. ESVO liefert KOSTENLOS nach PT bei Menge. Bei neuem Material wuerde sie evtl. laenger zum Naehen brauchen, was Aufbau verschieben koennte - aber 'relativ schnell absehbar' wenn sie damit beginnt. Sebastian darf entscheiden was er will, sie unterstuetzt das.</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Sehr kooperativ + ESVO-Hinweis</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
+          <t>GAME-CHANGER: ESVO hat Sauleda im Sortiment! Recherche bestaetigt: 'ESVO Holland is Europe's market leader outdoor fabrics, carries Sauleda as best acrylic fabric brand for boat marine'. Damit haben wir Sauleda bei DANI's BESTEHENDEM LIEFERANTEN + kostenloser PT-Lieferung.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>25.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Dani</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>Begeistert: 'ESVO hat ja Sauleda und andere Marine-Acryl im Programm!' Sebastian schaut bei ESVO konkret. Vorschlag: Premium-Variante ueber Dani's gewohnten ESVO-Weg gehen (sie kennt Bestell-Prozedur, ESVO liefert kostenlos PT). Bittet Dani um EMPFEHLUNG welche ESVO-Marine-Variante fuer Algarve-Wohnjurte. Demuetig: 'falls ihr Sauleda nie genaeht habt, kein Druck - dann ESVO-Standard mit Wartung alle paar Jahre'.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Smart strategisch: Material-Wahl Dani uebergeben (sie kennt ESVO besser), Verantwortung Verarbeitung bei Dani. ESVO-Sauleda-Links als Verifikation.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -10669,12 +10669,12 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
         </is>
       </c>
     </row>
@@ -10696,67 +10696,141 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E73" s="3" t="inlineStr">
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F73" s="19" t="inlineStr">
+      <c r="F75" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G75" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -10637,7 +10637,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Begeistert: 'ESVO hat ja Sauleda und andere Marine-Acryl im Programm!' Sebastian schaut bei ESVO konkret. Vorschlag: Premium-Variante ueber Dani's gewohnten ESVO-Weg gehen (sie kennt Bestell-Prozedur, ESVO liefert kostenlos PT). Bittet Dani um EMPFEHLUNG welche ESVO-Marine-Variante fuer Algarve-Wohnjurte. Demuetig: 'falls ihr Sauleda nie genaeht habt, kein Druck - dann ESVO-Standard mit Wartung alle paar Jahre'.</t>
+          <t>Begeistert: 'ESVO hat ja Sauleda und andere Marine-Acryl im Programm!' Mit konkreten ESVO-Links (Sauleda + Boat-Canvas + Acrylic). Vorschlag: Premium-Variante ueber Danis gewohnten ESVO-Weg gehen (sie kennt Bestell-Prozedur, ESVO liefert kostenlos PT). Bittet Dani um EMPFEHLUNG welche ESVO-Marine-Variante fuer Algarve-Wohnjurte.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Smart strategisch: Material-Wahl Dani uebergeben (sie kennt ESVO besser), Verantwortung Verarbeitung bei Dani. ESVO-Sauleda-Links als Verifikation.</t>
+          <t>Smart strategisch: Material-Wahl Dani uebergeben (sie kennt ESVO besser), Verantwortung Verarbeitung bei Dani. Direkte ESVO-Links als Verifikation. Demuetiger 'Wartungs-Aufwand'-Teil rausgenommen - klare offensive Botschaft.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -2774,7 +2774,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Dani + Chris (Castelo de Vide Community-Projekt) - 7m Custom</t>
+          <t>Dani + Chris (Castelo de Vide Community-Projekt) - 7m Custom + TenCate Campshield Option</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -8049,7 +8049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10642,24 +10642,24 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Smart strategisch: Material-Wahl Dani uebergeben (sie kennt ESVO besser), Verantwortung Verarbeitung bei Dani. Direkte ESVO-Links als Verifikation. Demuetiger 'Wartungs-Aufwand'-Teil rausgenommen - klare offensive Botschaft.</t>
+          <t>Smart strategisch: Material-Wahl Dani uebergeben (sie kennt ESVO besser), Verantwortung Verarbeitung bei Dani. Direkte ESVO-Links als Verifikation.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Mikael (Bento)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -10669,71 +10669,71 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Mikael</t>
+          <t>Dani -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
+          <t>MARINESTOFF noch nie genaeht. Aber: 'CAMPSHIELD' einmal vernaeht - empfiehlt das anzuschauen bei ESVO.</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Konkrete Material-Empfehlung</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
+          <t>TenCate Campshield = Glamping-Industriestandard, BW/Poly atmungsaktiv, inherent flammhemmend, in 290 g/m² oder 420 g/m² Varianten. PERFEKTE Mittelposition zwischen Standard BW/Poly Canvas und Premium Sauleda Acryl. Dani hat schon Erfahrung damit.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>25.05.2026 (Sebastians Folge)</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Dani</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>Recherche: TenCate Campshield = Glamping-Industriestandard, flammhemmend, 290 oder 420 g/m². 3 Fragen: 1) 290 oder 420 g/m² verwendet, wie hat sie sich gehalten? 2) Preis bei ESVO pro Meter / pro Jurte? 3) Algarve-Sonne: schwerere 420 g/m² empfehlen oder 290 g/m² reichen?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Bei Antwort: konkrete Preise + Empfehlung. Wenn 420 g/m² Variante moeglich: Premium-Setup mit Algarve-tauglichem Material UND atmungsaktivem BW/Poly UND Glamping-Industriestandard. Lebensdauer geschaetzt 10+ Jahre in Algarve.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -10743,12 +10743,12 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
         </is>
       </c>
     </row>
@@ -10770,67 +10770,141 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E75" s="3" t="inlineStr">
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F75" s="19" t="inlineStr">
+      <c r="F77" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G77" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8049,7 +8049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10716,24 +10716,24 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Bei Antwort: konkrete Preise + Empfehlung. Wenn 420 g/m² Variante moeglich: Premium-Setup mit Algarve-tauglichem Material UND atmungsaktivem BW/Poly UND Glamping-Industriestandard. Lebensdauer geschaetzt 10+ Jahre in Algarve.</t>
+          <t>Bei Antwort: konkrete Preise + Empfehlung.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
+          <t>25.05.2026</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Mikael (Bento)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -10743,71 +10743,71 @@
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Mikael</t>
+          <t>Dani -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
+          <t>Kein direkter Vergleich leicht/schwer. Aber: hat damals den SCHWEREN 420 g/m² + UV-Schutz darueber verwendet (doppelter Schutz). Schwerer ist DOPPELTER PREIS gegenueber leichtem. Leichter 290 g/m² gerade im SALE in grau bei ESVO: https://www.esvocampingshop.com/de/outdoorstoffe-zeltstoff/merken-de/campshield-de/</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Erfahrungs-Info + Sale-Link</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
+          <t>STRATEGISCHE OPTION: Da Sebastian SOWIESO Schattennetz fuer Algarve plant (240 EUR), reicht potentiell der LEICHTE 290 g/m² im Sale + Schattennetz = aequivalent zu Dani's damaliger Loesung. Spart ~700-1.000 EUR vs schwerer Variante.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>25.05.2026 (Sebastians smarte Folge)</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Dani</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>Logik-Frage: 'Schattennetz drueber plane ich fuer Algarve sowieso (UV+Sommer-Hitze) - reicht dann der leichte 290er nicht? Bei euch damals wars schwer+UV-Schutz = doppelt abgesichert.' Sale-Preis erwaehnt aber Dani's Erfahrung als Autoritaet anerkannt.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Smart: zeigt Sebastian denkt selber mit. 3 moegliche Reaktionen: a) 'Mit Schattennetz reicht leichter' = spart 700+ EUR, b) 'In Algarve trotzdem schwer' = Erfahrung folgen, c) 'Kommt auf Standort an' = situationsbezogene Empfehlung.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -10817,12 +10817,12 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
         </is>
       </c>
     </row>
@@ -10844,67 +10844,141 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E77" s="3" t="inlineStr">
+      <c r="E79" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F77" s="19" t="inlineStr">
+      <c r="F79" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G77" s="3" t="inlineStr">
+      <c r="G79" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -10802,7 +10802,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>24.05.2026 (Sebastians ehrliche Folge)</t>
+          <t>~26.05.2026</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>EHRLICHE CASHFLOW-NACHRICHT: Sebastian hat 5k sofort, kann Rest 16k ueber 3 Monate aufbringen. Vorschlag: 5k jetzt Anzahlung + 5k 15.06 + 5k 15.07 + 6k 15.08 = 21k total. Pickup erst nach Vollzahlung (Sicherheit fuer Mikael). Respektvoll: 'wenn das nicht geht weil du Geld schneller brauchst, kein Problem, dann warte ich bis ich mehr gespart habe'.</t>
+          <t>Ehrlich-empathische Cashflow-Mail: Entschuldigung fuer Verzoegerung, transparent ueber Cashflow (5k sofort + Rest bis Aug). Vorschlag Etappenzahlung 5/5/5/Rest mit Pickup Ende August. Anerkennt Mikaels Brand+Baby-Situation. Ausweg geben: 'wenn nicht moeglich, verkauf an wen schneller zahlen kann - kein hard feelings'. Erwaehnt parallel andere Optionen + Lob Mikaels Transparenz.</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>DREI MOEGLICHE REAKTIONEN: A) Mikael sagt JA = Deal mit Ratenzahlung. B) Mikael verhandelt = Mittelweg suchen. C) Mikael sagt NEIN = respektvoll Plan B (Dani Custom-Bau)</t>
+          <t>STRATEGISCHE LAGE: Dani gewinnt gerade Boden mit Campshield-Loesung. Mikael ist Plan B. Sebastian haelt ihn nicht hin sondern gibt ehrliche Frage zurueck. 3 moegliche Reaktionen: a) Ja Etappenzahlung = Luxus-Problem zwei Optionen, b) Nein brauche Geld = klare Absage moeglich, c) Schon verkauft = Karten gespielt.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8049,7 +8049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10790,24 +10790,24 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Smart: zeigt Sebastian denkt selber mit. 3 moegliche Reaktionen: a) 'Mit Schattennetz reicht leichter' = spart 700+ EUR, b) 'In Algarve trotzdem schwer' = Erfahrung folgen, c) 'Kommt auf Standort an' = situationsbezogene Empfehlung.</t>
+          <t>Smart: zeigt Sebastian denkt selber mit. Antwort 27.05 erhalten.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>~26.05.2026</t>
+          <t>27.05.2026 16:19</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>Mikael (Bento)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -10817,71 +10817,71 @@
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Mikael</t>
+          <t>Dani -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>Ehrlich-empathische Cashflow-Mail: Entschuldigung fuer Verzoegerung, transparent ueber Cashflow (5k sofort + Rest bis Aug). Vorschlag Etappenzahlung 5/5/5/Rest mit Pickup Ende August. Anerkennt Mikaels Brand+Baby-Situation. Ausweg geben: 'wenn nicht moeglich, verkauf an wen schneller zahlen kann - kein hard feelings'. Erwaehnt parallel andere Optionen + Lob Mikaels Transparenz.</t>
+          <t>PREIS-KONKRETISIERUNG: Leichter Campshield 290 g/m² = ~1.400 EUR bei 7m-Jurte. (Standard BW/Poly Canvas via ESVO war auch ~1.400 EUR im 16k-Preis). Schwerer = doppelter Preis ~2.800 EUR. Sebastian fragt jetzt Klarstellung: Aufpreis fuer Campshield wegen Markenstoff oder gleichwertig im 16k?</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Konkrete Preis-Info</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>STRATEGISCHE LAGE: Dani gewinnt gerade Boden mit Campshield-Loesung. Mikael ist Plan B. Sebastian haelt ihn nicht hin sondern gibt ehrliche Frage zurueck. 3 moegliche Reaktionen: a) Ja Etappenzahlung = Luxus-Problem zwei Optionen, b) Nein brauche Geld = klare Absage moeglich, c) Schon verkauft = Karten gespielt.</t>
+          <t>GAME-CHANGER: Leichter Campshield = vermutlich KEIN AUFPREIS! Gleicher Preis wie Standard-Canvas. Damit upgrade Sebastian ohne Mehrkosten von BW/Poly Standard auf TenCate Glamping-Marken-Stoff. Mit Schattennetz drueber Top-Setup. Klarstellungs-Mail an Dani sofort raus.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>~28.05.2026 (Sebastians Klarstellung)</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Dani (Castelo de Vide)</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Sebastian -&gt; Dani</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>Klarstellungs-Frage: 'Verstehe ich das richtig - leichter Campshield 290 g/m² ersetzt einfach Standard-Canvas, also OHNE AUFPREIS im 16k? Wenn ja nehmen wir den.' Plus Bestaetigung dass Sebastian mit Schattennetz fuer Algarve gut aufgestellt ist + flammhemmende Markenqualitaet als Bonus.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Wenn Dani bestaetigt 'kein Aufpreis': finale Kalkulation Dani 20.620 EUR all-in (TOP-LOESUNG). Mikael verliert dann fast jeden Vorteil ausser 12m² Mehrflaeche.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>~26.05.2026</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -10891,94 +10891,242 @@
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>Ehrlich-empathische Cashflow-Mail: Entschuldigung fuer Verzoegerung, transparent ueber Cashflow (5k sofort + Rest bis Aug). Vorschlag Etappenzahlung 5/5/5/Rest mit Pickup Ende August. Anerkennt Mikaels Brand+Baby-Situation. Ausweg geben: 'wenn nicht moeglich, verkauf an wen schneller zahlen kann - kein hard feelings'. Erwaehnt parallel andere Optionen + Lob Mikaels Transparenz.</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>Antwort 28.05 erhalten</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>28.05.2026 12:16</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>POSITIVE ANTWORT: 'no problem with that at all'. Schlaegt vor 5+5+5 = 15k (statt Sebastians 5+5+5+6 = 21k) - vermutlich nur Jurte-Basis, AC4+Vinyl+Versand extra. Drei Monate: jetzt + Juni + Juli. Pickup vermutlich Ende Juli nach Vollzahlung.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Etappenzahlung akzeptiert</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>ABER STRATEGISCH: Sebastian noch nicht entschieden Mikael vs Dani. 5k blind anzuzahlen vor Juni-Besuch+Rost-Verifikation+Dani-Vergleich ist Risiko. Sollte um Verschiebung der ersten Rate auf Ende Juni (nach Besuch) bitten.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
+          <t>~29.05.2026 (Sebastians Folge)</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>Mikael (Bento)</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Mikael</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Bedankt sich + akzeptiert 5/5/5-Schema. Bittet um Verschiebung der ersten 5k-Anzahlung auf NACH dem Juni-Besuch (Ende Juni statt jetzt). Begruendung: 'fuehlt sich nicht ganz richtig an, blind anzuzahlen vor Treffen'. Konkretes Schema: Ende Juni 5k + Mitte Juli 5k + Anfang August 5k + Pickup Mitte August. Ausweg geben: 'wenn Geld frueher gebraucht, sag Bescheid'. Konkrete Termin-Frage: Sa 14 oder 21 Juni?</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>Drei mögliche Reaktionen: a) Ok nach Besuch = ideal, Sebastian hat 3 Wochen Bedenkzeit. b) Kompromiss 2k jetzt + Rest spaeter = 10% Reservierung. c) Ultimatum 'jetzt oder weg' = Sebastian muss blind entscheiden oder Mikael loslassen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Dror (Telegram-Gruppe)</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Telegram-Post</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Dror -&gt; Gruppe</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>✓ Wertvoller Kontakt</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G81" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E79" s="3" t="inlineStr">
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F79" s="19" t="inlineStr">
+      <c r="F83" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G79" s="3" t="inlineStr">
+      <c r="G83" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -8049,7 +8049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10975,61 +10975,61 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>✓ Gesendet</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>Drei mögliche Reaktionen: a) Ok nach Besuch = ideal, Sebastian hat 3 Wochen Bedenkzeit. b) Kompromiss 2k jetzt + Rest spaeter = 10% Reservierung. c) Ultimatum 'jetzt oder weg' = Sebastian muss blind entscheiden oder Mikael loslassen.</t>
+          <t>Antwort 28.05 16:41 erhalten</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>28.05.2026 16:41</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Dror (Telegram-Gruppe)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Telegram-Post</t>
+          <t>Telegram DM</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Dror -&gt; Gruppe</t>
+          <t>Mikael -&gt; Sebastian</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
+          <t>VERKAUFSDRUCK: 'I need you to give me a guarantee that you want this; I have many people asking for information about this yurt.' Klassischer Drucker-Move - kann wahr oder Bluff sein. Mikael will Sicherheit ueber Geld/Commitment.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>✓ Wertvoller Kontakt</t>
+          <t>✓ Druck-Move</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
+          <t>Sebastian 3 Optionen: A) 2k Reservierung (Kompromiss, begrenzt Risiko), B) Klare Absage 'kein Geld vor Besuch', C) Volle 5k blind anzahlen (riskant). Empfehlung: Option A wenn Mikael interessant, Option B wenn Dani jetzt klare 1. Wahl.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>23.05.2026</t>
+          <t>~29.05.2026 (Sebastian-Entscheidung)</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>Dror (Telegram)</t>
+          <t>Mikael (Bento)</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -11039,22 +11039,22 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Dror</t>
+          <t>Sebastian -&gt; Mikael</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+          <t>OPTION A (empfohlen): 2.000 EUR Reservierungs-Anzahlung sofort. Kompromiss: Mikael bekommt Liquiditaet + Commitment. Sebastian's Risiko 2k begrenzt. Bei Vertragsabschluss nach Besuch: 2k zaehlt zu 15k Total. Bei Rueckzug nach Besuch: Mikael behaelt 2k als Reservierungsgebuehr. Dann 5+5+3 = 15k bis Mitte August. Falls Mikael 2k nicht reicht: respektvoller Rueckzug mit 'no hard feelings'.</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden</t>
+          <t>⏳ Zu entscheiden</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+          <t>ALTERNATIVE B: Kein Geld vor Besuch + Mikael akzeptiert wenn er an anderen verkauft. Sebastian's persoenliche Risiko-Bereitschaft entscheidet.</t>
         </is>
       </c>
     </row>
@@ -11066,67 +11066,141 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Sebastian -&gt; Selbst-Klaerung</t>
+          <t>Dror (Telegram-Gruppe)</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Analyse</t>
+          <t>Telegram-Post</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Dror -&gt; Gruppe</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+          <t>Stellt sich vor: viel Erfahrung im Jurten-BAU UND REPARATUR, baut selbst (noch) keine. Bietet sich als Kontakt fuer Jurten-Fragen an.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Analyse fertig</t>
+          <t>✓ Wertvoller Kontakt</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+          <t>Sebastian -&gt; Dror DM: warm danken, Projekt kurz erklaeren, signalisieren dass spaeter Sanity-Check kommen wird. Frage: Standort PT?</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>Dror (Telegram)</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Telegram DM</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Dror</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>Warmer Erstkontakt: Vorstellung, Projekt-Beschreibung, signalisieren dass spaeter Sanity-Check kommt. Frage Standort PT.</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr">
+        <is>
+          <t>⏳ Zu senden</t>
+        </is>
+      </c>
+      <c r="G83" s="3" t="inlineStr">
+        <is>
+          <t>DROR ALS WERTVOLLE RESSOURCE: Sanity-Check auf Dani/Benedikt/Mikael Angebote, Material-Beurteilung, Plattform-Engineering, Reparatur-Wissen fuer Zukunft. Konkrete Anfragen erst bei Auslosern (vor Anzahlung, vor Plattform-Bau, etc.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>23.05.2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Sebastian -&gt; Selbst-Klaerung</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Analyse</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Intern</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Frage 4cm Schafwolle Daemmung fuer Algarve-Winter ausreichend? Antwort: KNAPP. Dani's 4cm (R~1.05) ist halb so gut wie Bēt 8cm PET (R~2.1) und 1/3 vom DE-Niedrig-Bau-Standard. Aljezur-Atlantikkueste hat mildere Temperaturen als Castelo de Vide, aber starker Wind+Feuchtigkeit verstaerken Waermeverlust. MIT aktivem Holzofen+Top-Plattform-Daemmung (60-80mm Kork) = wohnen ja, mit Komfort-Limits. OHNE Heizen = nachts 8-12°C. DRINGEND: 8cm Upgrade bei Dani anfragen.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Analyse fertig</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Bei Dani 8cm Upgrade anfragen ODER Plattform-Daemmung als Kompensation auslegen (60-80mm Kork)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>Brett, Quinta Glamping (Algarve)</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>Online-Buchung</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>Sebastian (geplant)</t>
         </is>
       </c>
-      <c r="E83" s="3" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Uebernachtung im Lake View Yurt (Casa dos Sonhos)</t>
         </is>
       </c>
-      <c r="F83" s="19" t="inlineStr">
+      <c r="F85" s="19" t="inlineStr">
         <is>
           <t>⏳ noch nicht gebucht</t>
         </is>
       </c>
-      <c r="G83" s="3" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t>Booking direkt: https://www.quintaglamping.com/rooms/lake-view-yurt.html - vor Anzahlung an Casa wertvoll</t>
         </is>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -11024,7 +11024,7 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>~29.05.2026 (Sebastian-Entscheidung)</t>
+          <t>29.05.2026 (Sebastians Entscheidung)</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
@@ -11044,17 +11044,17 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>OPTION A (empfohlen): 2.000 EUR Reservierungs-Anzahlung sofort. Kompromiss: Mikael bekommt Liquiditaet + Commitment. Sebastian's Risiko 2k begrenzt. Bei Vertragsabschluss nach Besuch: 2k zaehlt zu 15k Total. Bei Rueckzug nach Besuch: Mikael behaelt 2k als Reservierungsgebuehr. Dann 5+5+3 = 15k bis Mitte August. Falls Mikael 2k nicht reicht: respektvoller Rueckzug mit 'no hard feelings'.</t>
+          <t>OPTION B GEWAEHLT: Klare Linie - kein Geld vor Besuch. Ehrlich: 'cannot give full guarantee or any deposit before visit'. Akzeptiert wenn Mikael an anderen verkauft. Falls warten: Besuch 14/21 Juni, 5k sofort danach wenn alles wie beschrieben. Demuetig: 'whatever works for you - let me know honestly'.</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu entscheiden</t>
+          <t>⏳ Zu senden (Option B)</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>ALTERNATIVE B: Kein Geld vor Besuch + Mikael akzeptiert wenn er an anderen verkauft. Sebastian's persoenliche Risiko-Bereitschaft entscheidet.</t>
+          <t>STRATEGISCHE BEDEUTUNG: Dani ist Sebastian's erste Wahl. Mikael ist akzeptables Verlustrisiko. Maximum Schutz. 3 mögliche Reaktionen: a) Ok ich warte bis Juni = Sebastian besucht beide. b) Doch 1-2k? = Nachverhandeln moeglich. c) Sorry muss verkaufen = Fokus voll auf Dani.</t>
         </is>
       </c>
     </row>

--- a/Jurten_Recherche_Algarve.xlsx
+++ b/Jurten_Recherche_Algarve.xlsx
@@ -11044,17 +11044,17 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>OPTION B GEWAEHLT: Klare Linie - kein Geld vor Besuch. Ehrlich: 'cannot give full guarantee or any deposit before visit'. Akzeptiert wenn Mikael an anderen verkauft. Falls warten: Besuch 14/21 Juni, 5k sofort danach wenn alles wie beschrieben. Demuetig: 'whatever works for you - let me know honestly'.</t>
+          <t>OPTION B FINAL: 'I need a bit more time to make this decision. Big step for our family.' Verstaendnis fuer Mikaels Lage. Klare Ausweg-Option: 'if you can't wait, go ahead with another buyer - no hard feelings'. Falls warten: Besuch 14/21 Juni, 5k sofort danach. Demuetig + ehrlich: 'let me know honestly what works for you'.</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>⏳ Zu senden (Option B)</t>
+          <t>⏳ Zu senden</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>STRATEGISCHE BEDEUTUNG: Dani ist Sebastian's erste Wahl. Mikael ist akzeptables Verlustrisiko. Maximum Schutz. 3 mögliche Reaktionen: a) Ok ich warte bis Juni = Sebastian besucht beide. b) Doch 1-2k? = Nachverhandeln moeglich. c) Sorry muss verkaufen = Fokus voll auf Dani.</t>
+          <t>STRATEGIE: Sebastian will Zeit fuer Vergleich Dani vs Mikael. Maximum Ehrlichkeit + Akzeptanz Mikael verkauft. 3 mögliche Reaktionen: a) Mikael wartet = Sebastian besucht beide. b) Reservierungs-Verhandlung = Sebastian kann dann entscheiden. c) Mikael verkauft = Dani-Track fokussieren.</t>
         </is>
       </c>
     </row>
